--- a/dataland-framework-toolbox/inputs/eutaxonomy-financials-2026-73/eutaxonomy-financials-2026-73.xlsx
+++ b/dataland-framework-toolbox/inputs/eutaxonomy-financials-2026-73/eutaxonomy-financials-2026-73.xlsx
@@ -517,7 +517,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P212"/>
+  <dimension ref="A1:P213"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelRow="0"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
@@ -906,17 +906,17 @@
       </c>
       <c r="D7" s="4" t="inlineStr">
         <is>
-          <t>Is NFRD mandatory?</t>
+          <t>Is EU Taxonomy data reported on a mandatory basis?</t>
         </is>
       </c>
       <c r="E7" s="4" t="inlineStr">
         <is>
-          <t>NFRD_MANDATORY</t>
+          <t>EU_TAXONOMY_MANDATORY</t>
         </is>
       </c>
       <c r="F7" s="4" t="inlineStr">
         <is>
-          <t>Is the NFRD mandatory for your company?</t>
+          <t>Does Article 1(2) of Regulation (EU) 2020/852 apply to the undertaking and, therefore, is EU Taxonomy data reported on a mandatory basis?</t>
         </is>
       </c>
       <c r="G7" s="4" t="inlineStr">
@@ -996,59 +996,47 @@
       </c>
       <c r="B9" s="3" t="inlineStr">
         <is>
-          <t>Credit Institution</t>
+          <t>General</t>
         </is>
       </c>
       <c r="C9" s="3" t="inlineStr">
         <is>
-          <t>Assets for Calculation of Green Asset Ratio</t>
+          <t>General</t>
         </is>
       </c>
       <c r="D9" s="4" t="inlineStr">
         <is>
-          <t>Total (gross) Carrying Amount</t>
+          <t>Reports in accordance with Article 7(9) of Regulation (EU) 2026/73</t>
         </is>
       </c>
       <c r="E9" s="4" t="inlineStr">
         <is>
-          <t>CI_GAR_ASSETS_TOTAL_GROSS_CARRYING_AMOUNT</t>
+          <t>REPORTS_NO_TAXONOMY_ELIGIBLE_ACTIVITIES</t>
         </is>
       </c>
       <c r="F9" s="4" t="inlineStr">
         <is>
-          <t>Total overall covered assets which are included in the numerator. Do not include assets which not covered for GAR calculation.</t>
+          <t>Does the financial undertaking report in accordance with Article 7(9) of Regulation (EU) 2026/73 by including in their management report the following statement: "No activities are claimed as being associated with economic activities that qualify as environmentally sustainable under Articles 3 and 9 of Regulation (EU) 2020/852 (Taxonomy Regulation)</t>
         </is>
       </c>
       <c r="G9" s="4" t="inlineStr">
         <is>
-          <t>Currency</t>
-        </is>
-      </c>
-      <c r="H9" s="4" t="inlineStr">
-        <is>
-          <t>Allowed Range: [0, INF]</t>
-        </is>
-      </c>
-      <c r="I9" s="4" t="inlineStr"/>
+          <t>Yes/No</t>
+        </is>
+      </c>
+      <c r="H9" s="4" t="n"/>
+      <c r="I9" s="4" t="n"/>
       <c r="J9" s="4" t="inlineStr">
         <is>
           <t>Extended</t>
         </is>
       </c>
-      <c r="K9" s="4" t="inlineStr"/>
-      <c r="L9" s="4" t="inlineStr"/>
-      <c r="M9" s="4" t="inlineStr"/>
-      <c r="N9" s="4" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="O9" s="4" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
-      <c r="P9" s="4" t="inlineStr"/>
+      <c r="K9" s="4" t="n"/>
+      <c r="L9" s="4" t="n"/>
+      <c r="M9" s="4" t="n"/>
+      <c r="N9" s="4" t="n"/>
+      <c r="O9" s="4" t="n"/>
+      <c r="P9" s="4" t="n"/>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
@@ -1068,17 +1056,17 @@
       </c>
       <c r="D10" s="4" t="inlineStr">
         <is>
-          <t>Total Amount of Non-Assessed Exposures</t>
+          <t>Total (gross) Carrying Amount</t>
         </is>
       </c>
       <c r="E10" s="4" t="inlineStr">
         <is>
-          <t>CI_GAR_ASSETS_NON_ASSESSED</t>
+          <t>CI_GAR_ASSETS_TOTAL_GROSS_CARRYING_AMOUNT</t>
         </is>
       </c>
       <c r="F10" s="4" t="inlineStr">
         <is>
-          <t>Total amount of assets of which Non-Assessed Exposures</t>
+          <t>Total overall covered assets which are included in the numerator. Do not include assets which not covered for GAR calculation.</t>
         </is>
       </c>
       <c r="G10" s="4" t="inlineStr">
@@ -1130,17 +1118,17 @@
       </c>
       <c r="D11" s="4" t="inlineStr">
         <is>
-          <t>Total Amount Of Non-Assessed Exposures - Of which Financing Non-Material Activities of Counterparties</t>
+          <t>Total Amount of Non-Assessed Exposures</t>
         </is>
       </c>
       <c r="E11" s="4" t="inlineStr">
         <is>
-          <t>CI_GAR_ASSETS_NON_ASSESSED_NON_MATERIAL_CP</t>
+          <t>CI_GAR_ASSETS_NON_ASSESSED</t>
         </is>
       </c>
       <c r="F11" s="4" t="inlineStr">
         <is>
-          <t>Total amount of assets of which Financing Non-Material Activities of Counterparties</t>
+          <t>Total amount of assets of which Non-Assessed Exposures</t>
         </is>
       </c>
       <c r="G11" s="4" t="inlineStr">
@@ -1192,17 +1180,17 @@
       </c>
       <c r="D12" s="4" t="inlineStr">
         <is>
-          <t>Total Amount Of Non-Assessed Exposures - Of which Exposures Financing Counterparties Reporting no Taxonomy-eligible Activities</t>
+          <t>Total Amount Of Non-Assessed Exposures - Of which Financing Non-Material Activities of Counterparties</t>
         </is>
       </c>
       <c r="E12" s="4" t="inlineStr">
         <is>
-          <t>CI_GAR_ASSETS_NON_ASSESSED_NO_ELIGIBLE_CP</t>
+          <t>CI_GAR_ASSETS_NON_ASSESSED_NON_MATERIAL_CP</t>
         </is>
       </c>
       <c r="F12" s="4" t="inlineStr">
         <is>
-          <t>Total amount of assets Of which exposures financing counterparties reporting in accordance with Article 7(9) of Regulation (EU) 2026/73</t>
+          <t>Total amount of assets of which Financing Non-Material Activities of Counterparties</t>
         </is>
       </c>
       <c r="G12" s="4" t="inlineStr">
@@ -1254,17 +1242,17 @@
       </c>
       <c r="D13" s="4" t="inlineStr">
         <is>
-          <t>Total Amount Of Non-Assessed Exposures - Of which Not Assessed Considered Non-Material by the Credit Institution</t>
+          <t>Total Amount Of Non-Assessed Exposures - Of which Exposures Financing Counterparties Reporting no Taxonomy-eligible Activities</t>
         </is>
       </c>
       <c r="E13" s="4" t="inlineStr">
         <is>
-          <t>CI_GAR_ASSETS_NON_ASSESSED_NON_MATERIAL_CI</t>
+          <t>CI_GAR_ASSETS_NON_ASSESSED_NO_ELIGIBLE_CP</t>
         </is>
       </c>
       <c r="F13" s="4" t="inlineStr">
         <is>
-          <t>Total amount of assets of which Not Assessed Considered Non-Material by the Credit Institution</t>
+          <t>Total amount of assets Of which exposures financing counterparties reporting in accordance with Article 7(9) of Regulation (EU) 2026/73</t>
         </is>
       </c>
       <c r="G13" s="4" t="inlineStr">
@@ -1311,22 +1299,22 @@
       </c>
       <c r="C14" s="3" t="inlineStr">
         <is>
-          <t>Turnover-based Green Asset Ratio Sector Information</t>
+          <t>Assets for Calculation of Green Asset Ratio</t>
         </is>
       </c>
       <c r="D14" s="4" t="inlineStr">
         <is>
-          <t>Turnover-based Total Amount of Assets Exposed towards Nuclear Activities</t>
+          <t>Total Amount Of Non-Assessed Exposures - Of which Not Assessed Considered Non-Material by the Credit Institution</t>
         </is>
       </c>
       <c r="E14" s="4" t="inlineStr">
         <is>
-          <t>CI_TURNOVER_BASED_GAR_SECTOR_NUCLEAR_TOTAL_GROSS_CARRYING_AMOUNT</t>
+          <t>CI_GAR_ASSETS_NON_ASSESSED_NON_MATERIAL_CI</t>
         </is>
       </c>
       <c r="F14" s="4" t="inlineStr">
         <is>
-          <t>Turnover-based total amount of assets exposed towards Nuclear Activities</t>
+          <t>Total amount of assets of which Not Assessed Considered Non-Material by the Credit Institution</t>
         </is>
       </c>
       <c r="G14" s="4" t="inlineStr">
@@ -1378,17 +1366,17 @@
       </c>
       <c r="D15" s="4" t="inlineStr">
         <is>
-          <t>Turnover-based Total Amount of Assets Exposed towards Nuclear Activities (Taxonomy-eligible)</t>
+          <t>Turnover-based Total Amount of Assets Exposed towards Nuclear Activities</t>
         </is>
       </c>
       <c r="E15" s="4" t="inlineStr">
         <is>
-          <t>CI_TURNOVER_BASED_GAR_SECTOR_NUCLEAR_ELIGIBLE</t>
+          <t>CI_TURNOVER_BASED_GAR_SECTOR_NUCLEAR_TOTAL_GROSS_CARRYING_AMOUNT</t>
         </is>
       </c>
       <c r="F15" s="4" t="inlineStr">
         <is>
-          <t>Turnover-based total amount of assets exposed towards Nuclear Activities which are Taxonomy-eligible</t>
+          <t>Turnover-based total amount of assets exposed towards Nuclear Activities</t>
         </is>
       </c>
       <c r="G15" s="4" t="inlineStr">
@@ -1440,17 +1428,17 @@
       </c>
       <c r="D16" s="4" t="inlineStr">
         <is>
-          <t>Turnover-based Total Amount of Assets Exposed towards Nuclear Activities (Taxonomy-aligned)</t>
+          <t>Turnover-based Total Amount of Assets Exposed towards Nuclear Activities (Taxonomy-eligible)</t>
         </is>
       </c>
       <c r="E16" s="4" t="inlineStr">
         <is>
-          <t>CI_TURNOVER_BASED_GAR_SECTOR_NUCLEAR_ALIGNED</t>
+          <t>CI_TURNOVER_BASED_GAR_SECTOR_NUCLEAR_ELIGIBLE</t>
         </is>
       </c>
       <c r="F16" s="4" t="inlineStr">
         <is>
-          <t>Turnover-based total amount of assets exposed towards Nuclear Activities which are Taxonomy-aligned</t>
+          <t>Turnover-based total amount of assets exposed towards Nuclear Activities which are Taxonomy-eligible</t>
         </is>
       </c>
       <c r="G16" s="4" t="inlineStr">
@@ -1502,17 +1490,17 @@
       </c>
       <c r="D17" s="4" t="inlineStr">
         <is>
-          <t>Turnover-based Total Amount of Assets Exposed towards Fossil Gas Activities</t>
+          <t>Turnover-based Total Amount of Assets Exposed towards Nuclear Activities (Taxonomy-aligned)</t>
         </is>
       </c>
       <c r="E17" s="4" t="inlineStr">
         <is>
-          <t>CI_TURNOVER_BASED_GAR_SECTOR_GAS_TOTAL_GROSS_CARRYING_AMOUNT</t>
+          <t>CI_TURNOVER_BASED_GAR_SECTOR_NUCLEAR_ALIGNED</t>
         </is>
       </c>
       <c r="F17" s="4" t="inlineStr">
         <is>
-          <t>Turnover-based total amount of assets exposed towards Fossil Gas Activities</t>
+          <t>Turnover-based total amount of assets exposed towards Nuclear Activities which are Taxonomy-aligned</t>
         </is>
       </c>
       <c r="G17" s="4" t="inlineStr">
@@ -1564,17 +1552,17 @@
       </c>
       <c r="D18" s="4" t="inlineStr">
         <is>
-          <t>Turnover-based Total Amount of Assets Exposed towards Fossil Gas Activities (Taxonomy-eligible)</t>
+          <t>Turnover-based Total Amount of Assets Exposed towards Fossil Gas Activities</t>
         </is>
       </c>
       <c r="E18" s="4" t="inlineStr">
         <is>
-          <t>CI_TURNOVER_BASED_GAR_SECTOR_GAS_ELIGIBLE</t>
+          <t>CI_TURNOVER_BASED_GAR_SECTOR_GAS_TOTAL_GROSS_CARRYING_AMOUNT</t>
         </is>
       </c>
       <c r="F18" s="4" t="inlineStr">
         <is>
-          <t>Turnover-based total amount of assets exposed towards Fossil Gas Activities which are Taxonomy-eligible</t>
+          <t>Turnover-based total amount of assets exposed towards Fossil Gas Activities</t>
         </is>
       </c>
       <c r="G18" s="4" t="inlineStr">
@@ -1626,17 +1614,17 @@
       </c>
       <c r="D19" s="4" t="inlineStr">
         <is>
-          <t>Turnover-based Total Amount of Assets Exposed towards Fossil Gas Activities (Taxonomy-aligned)</t>
+          <t>Turnover-based Total Amount of Assets Exposed towards Fossil Gas Activities (Taxonomy-eligible)</t>
         </is>
       </c>
       <c r="E19" s="4" t="inlineStr">
         <is>
-          <t>CI_TURNOVER_BASED_GAR_SECTOR_GAS_ALIGNED</t>
+          <t>CI_TURNOVER_BASED_GAR_SECTOR_GAS_ELIGIBLE</t>
         </is>
       </c>
       <c r="F19" s="4" t="inlineStr">
         <is>
-          <t>Turnover-based total amount of assets exposed towards Fossil Gas Activities which are Taxonomy-aligned</t>
+          <t>Turnover-based total amount of assets exposed towards Fossil Gas Activities which are Taxonomy-eligible</t>
         </is>
       </c>
       <c r="G19" s="4" t="inlineStr">
@@ -1683,22 +1671,22 @@
       </c>
       <c r="C20" s="3" t="inlineStr">
         <is>
-          <t>CapEx-based Green Asset Ratio Sector Information</t>
+          <t>Turnover-based Green Asset Ratio Sector Information</t>
         </is>
       </c>
       <c r="D20" s="4" t="inlineStr">
         <is>
-          <t>CapEx-based Total Amount of Assets Exposed towards Nuclear Activities</t>
+          <t>Turnover-based Total Amount of Assets Exposed towards Fossil Gas Activities (Taxonomy-aligned)</t>
         </is>
       </c>
       <c r="E20" s="4" t="inlineStr">
         <is>
-          <t>CI_CAPEX_BASED_GAR_SECTOR_NUCLEAR_TOTAL_GROSS_CARRYING_AMOUNT</t>
+          <t>CI_TURNOVER_BASED_GAR_SECTOR_GAS_ALIGNED</t>
         </is>
       </c>
       <c r="F20" s="4" t="inlineStr">
         <is>
-          <t>CapEx-based total amount of assets exposed towards Nuclear Activities</t>
+          <t>Turnover-based total amount of assets exposed towards Fossil Gas Activities which are Taxonomy-aligned</t>
         </is>
       </c>
       <c r="G20" s="4" t="inlineStr">
@@ -1750,17 +1738,17 @@
       </c>
       <c r="D21" s="4" t="inlineStr">
         <is>
-          <t>CapEx-based Total Amount of Assets Exposed towards Nuclear Activities (Taxonomy-eligible)</t>
+          <t>CapEx-based Total Amount of Assets Exposed towards Nuclear Activities</t>
         </is>
       </c>
       <c r="E21" s="4" t="inlineStr">
         <is>
-          <t>CI_CAPEX_BASED_GAR_SECTOR_NUCLEAR_ELIGIBLE</t>
+          <t>CI_CAPEX_BASED_GAR_SECTOR_NUCLEAR_TOTAL_GROSS_CARRYING_AMOUNT</t>
         </is>
       </c>
       <c r="F21" s="4" t="inlineStr">
         <is>
-          <t>CapEx-based total amount of assets exposed towards Nuclear Activities which are Taxonomy-eligible</t>
+          <t>CapEx-based total amount of assets exposed towards Nuclear Activities</t>
         </is>
       </c>
       <c r="G21" s="4" t="inlineStr">
@@ -1812,17 +1800,17 @@
       </c>
       <c r="D22" s="4" t="inlineStr">
         <is>
-          <t>CapEx-based Total Amount of Assets Exposed towards Nuclear Activities (Taxonomy-aligned)</t>
+          <t>CapEx-based Total Amount of Assets Exposed towards Nuclear Activities (Taxonomy-eligible)</t>
         </is>
       </c>
       <c r="E22" s="4" t="inlineStr">
         <is>
-          <t>CI_CAPEX_BASED_GAR_SECTOR_NUCLEAR_ALIGNED</t>
+          <t>CI_CAPEX_BASED_GAR_SECTOR_NUCLEAR_ELIGIBLE</t>
         </is>
       </c>
       <c r="F22" s="4" t="inlineStr">
         <is>
-          <t>CapEx-based total amount of assets exposed towards Nuclear Activities which are Taxonomy-aligned</t>
+          <t>CapEx-based total amount of assets exposed towards Nuclear Activities which are Taxonomy-eligible</t>
         </is>
       </c>
       <c r="G22" s="4" t="inlineStr">
@@ -1874,17 +1862,17 @@
       </c>
       <c r="D23" s="4" t="inlineStr">
         <is>
-          <t>CapEx-based Total Amount of Assets Exposed towards Fossil Gas Activities</t>
+          <t>CapEx-based Total Amount of Assets Exposed towards Nuclear Activities (Taxonomy-aligned)</t>
         </is>
       </c>
       <c r="E23" s="4" t="inlineStr">
         <is>
-          <t>CI_CAPEX_BASED_GAR_SECTOR_GAS_TOTAL_GROSS_CARRYING_AMOUNT</t>
+          <t>CI_CAPEX_BASED_GAR_SECTOR_NUCLEAR_ALIGNED</t>
         </is>
       </c>
       <c r="F23" s="4" t="inlineStr">
         <is>
-          <t>CapEx-based total amount of assets exposed towards Fossil Gas Activities</t>
+          <t>CapEx-based total amount of assets exposed towards Nuclear Activities which are Taxonomy-aligned</t>
         </is>
       </c>
       <c r="G23" s="4" t="inlineStr">
@@ -1936,17 +1924,17 @@
       </c>
       <c r="D24" s="4" t="inlineStr">
         <is>
-          <t>CapEx-based Total Amount of Assets Exposed towards Fossil Gas Activities (Taxonomy-eligible)</t>
+          <t>CapEx-based Total Amount of Assets Exposed towards Fossil Gas Activities</t>
         </is>
       </c>
       <c r="E24" s="4" t="inlineStr">
         <is>
-          <t>CI_CAPEX_BASED_GAR_SECTOR_GAS_ELIGIBLE</t>
+          <t>CI_CAPEX_BASED_GAR_SECTOR_GAS_TOTAL_GROSS_CARRYING_AMOUNT</t>
         </is>
       </c>
       <c r="F24" s="4" t="inlineStr">
         <is>
-          <t>CapEx-based total amount of assets exposed towards Fossil Gas Activities which are Taxonomy-eligible</t>
+          <t>CapEx-based total amount of assets exposed towards Fossil Gas Activities</t>
         </is>
       </c>
       <c r="G24" s="4" t="inlineStr">
@@ -1998,17 +1986,17 @@
       </c>
       <c r="D25" s="4" t="inlineStr">
         <is>
-          <t>CapEx-based Total Amount of Assets Exposed towards Fossil Gas Activities (Taxonomy-aligned)</t>
+          <t>CapEx-based Total Amount of Assets Exposed towards Fossil Gas Activities (Taxonomy-eligible)</t>
         </is>
       </c>
       <c r="E25" s="4" t="inlineStr">
         <is>
-          <t>CI_CAPEX_BASED_GAR_SECTOR_GAS_ALIGNED</t>
+          <t>CI_CAPEX_BASED_GAR_SECTOR_GAS_ELIGIBLE</t>
         </is>
       </c>
       <c r="F25" s="4" t="inlineStr">
         <is>
-          <t>CapEx-based total amount of assets exposed towards Fossil Gas Activities which are Taxonomy-aligned</t>
+          <t>CapEx-based total amount of assets exposed towards Fossil Gas Activities which are Taxonomy-eligible</t>
         </is>
       </c>
       <c r="G25" s="4" t="inlineStr">
@@ -2055,30 +2043,34 @@
       </c>
       <c r="C26" s="3" t="inlineStr">
         <is>
-          <t>Turnover-based Green Asset Ratio (stock)</t>
+          <t>CapEx-based Green Asset Ratio Sector Information</t>
         </is>
       </c>
       <c r="D26" s="4" t="inlineStr">
         <is>
-          <t>Substantial Contribution to Climate Change Mitigation in Percent - Aligned</t>
+          <t>CapEx-based Total Amount of Assets Exposed towards Fossil Gas Activities (Taxonomy-aligned)</t>
         </is>
       </c>
       <c r="E26" s="4" t="inlineStr">
         <is>
-          <t>CI_TURNOVER_BASED_GAR_STOCK_SC_TO_CCM_PCT_ALIGNED</t>
+          <t>CI_CAPEX_BASED_GAR_SECTOR_GAS_ALIGNED</t>
         </is>
       </c>
       <c r="F26" s="4" t="inlineStr">
         <is>
-          <t>Taxonomy-aligned Proportion of Revenue-based Green Asset Ratio substantially contributing to Climate Change Mitigation</t>
+          <t>CapEx-based total amount of assets exposed towards Fossil Gas Activities which are Taxonomy-aligned</t>
         </is>
       </c>
       <c r="G26" s="4" t="inlineStr">
         <is>
-          <t>Percentage</t>
-        </is>
-      </c>
-      <c r="H26" s="4" t="inlineStr"/>
+          <t>Currency</t>
+        </is>
+      </c>
+      <c r="H26" s="4" t="inlineStr">
+        <is>
+          <t>Allowed Range: [0, INF]</t>
+        </is>
+      </c>
       <c r="I26" s="4" t="inlineStr"/>
       <c r="J26" s="4" t="inlineStr">
         <is>
@@ -2118,17 +2110,17 @@
       </c>
       <c r="D27" s="4" t="inlineStr">
         <is>
-          <t>Substantial Contribution to Climate Change Adaptation in Percent - Aligned</t>
+          <t>Substantial Contribution to Climate Change Mitigation in Percent - Aligned</t>
         </is>
       </c>
       <c r="E27" s="4" t="inlineStr">
         <is>
-          <t>CI_TURNOVER_BASED_GAR_STOCK_SC_TO_CCA_PCT_ALIGNED</t>
+          <t>CI_TURNOVER_BASED_GAR_STOCK_SC_TO_CCM_PCT_ALIGNED</t>
         </is>
       </c>
       <c r="F27" s="4" t="inlineStr">
         <is>
-          <t>Taxonomy-aligned Proportion of Revenue-based Green Asset Ratio substantially contributing to Climate Change Adaptation</t>
+          <t>Taxonomy-aligned Proportion of Revenue-based Green Asset Ratio substantially contributing to Climate Change Mitigation</t>
         </is>
       </c>
       <c r="G27" s="4" t="inlineStr">
@@ -2176,17 +2168,17 @@
       </c>
       <c r="D28" s="4" t="inlineStr">
         <is>
-          <t>Substantial Contribution to Sustainable Use and Protection of Water and Marine Resources in Percent - Aligned</t>
+          <t>Substantial Contribution to Climate Change Adaptation in Percent - Aligned</t>
         </is>
       </c>
       <c r="E28" s="4" t="inlineStr">
         <is>
-          <t>CI_TURNOVER_BASED_GAR_STOCK_SC_TO_WTR_PCT_ALIGNED</t>
+          <t>CI_TURNOVER_BASED_GAR_STOCK_SC_TO_CCA_PCT_ALIGNED</t>
         </is>
       </c>
       <c r="F28" s="4" t="inlineStr">
         <is>
-          <t>Taxonomy-aligned Proportion of Revenue-based Green Asset Ratio substantially contributing to Sustainable Use and Protection of Water and Marine Resources</t>
+          <t>Taxonomy-aligned Proportion of Revenue-based Green Asset Ratio substantially contributing to Climate Change Adaptation</t>
         </is>
       </c>
       <c r="G28" s="4" t="inlineStr">
@@ -2234,17 +2226,17 @@
       </c>
       <c r="D29" s="4" t="inlineStr">
         <is>
-          <t>Substantial Contribution to Transition to a Circular Economy in Percent - Aligned</t>
+          <t>Substantial Contribution to Sustainable Use and Protection of Water and Marine Resources in Percent - Aligned</t>
         </is>
       </c>
       <c r="E29" s="4" t="inlineStr">
         <is>
-          <t>CI_TURNOVER_BASED_GAR_STOCK_SC_TO_CE_PCT_ALIGNED</t>
+          <t>CI_TURNOVER_BASED_GAR_STOCK_SC_TO_WTR_PCT_ALIGNED</t>
         </is>
       </c>
       <c r="F29" s="4" t="inlineStr">
         <is>
-          <t>Taxonomy-aligned Proportion of Revenue-based Green Asset Ratio substantially contributing to Circular Economy</t>
+          <t>Taxonomy-aligned Proportion of Revenue-based Green Asset Ratio substantially contributing to Sustainable Use and Protection of Water and Marine Resources</t>
         </is>
       </c>
       <c r="G29" s="4" t="inlineStr">
@@ -2292,17 +2284,17 @@
       </c>
       <c r="D30" s="4" t="inlineStr">
         <is>
-          <t>Substantial Contribution to Pollution Prevention and Control in Percent - Aligned</t>
+          <t>Substantial Contribution to Transition to a Circular Economy in Percent - Aligned</t>
         </is>
       </c>
       <c r="E30" s="4" t="inlineStr">
         <is>
-          <t>CI_TURNOVER_BASED_GAR_STOCK_SC_TO_PPC_PCT_ALIGNED</t>
+          <t>CI_TURNOVER_BASED_GAR_STOCK_SC_TO_CE_PCT_ALIGNED</t>
         </is>
       </c>
       <c r="F30" s="4" t="inlineStr">
         <is>
-          <t>Taxonomy-aligned Proportion of Revenue-based Green Asset Ratio substantially contributing to Pollution Prevention and Control</t>
+          <t>Taxonomy-aligned Proportion of Revenue-based Green Asset Ratio substantially contributing to Circular Economy</t>
         </is>
       </c>
       <c r="G30" s="4" t="inlineStr">
@@ -2350,17 +2342,17 @@
       </c>
       <c r="D31" s="4" t="inlineStr">
         <is>
-          <t>Substantial Contribution to Protection and Restoration of Biodiversity and Ecosystems in Percent - Aligned</t>
+          <t>Substantial Contribution to Pollution Prevention and Control in Percent - Aligned</t>
         </is>
       </c>
       <c r="E31" s="4" t="inlineStr">
         <is>
-          <t>CI_TURNOVER_BASED_GAR_STOCK_SC_TO_BIO_PCT_ALIGNED</t>
+          <t>CI_TURNOVER_BASED_GAR_STOCK_SC_TO_PPC_PCT_ALIGNED</t>
         </is>
       </c>
       <c r="F31" s="4" t="inlineStr">
         <is>
-          <t>Taxonomy-aligned Proportion of Revenue-based Green Asset Ratio substantially contributing to Protection and Restoration of Biodiversity and Ecosystems</t>
+          <t>Taxonomy-aligned Proportion of Revenue-based Green Asset Ratio substantially contributing to Pollution Prevention and Control</t>
         </is>
       </c>
       <c r="G31" s="4" t="inlineStr">
@@ -2408,17 +2400,17 @@
       </c>
       <c r="D32" s="4" t="inlineStr">
         <is>
-          <t>Substantial Contribution to any of the six Environmental Objectives in Percent - Eligible</t>
+          <t>Substantial Contribution to Protection and Restoration of Biodiversity and Ecosystems in Percent - Aligned</t>
         </is>
       </c>
       <c r="E32" s="4" t="inlineStr">
         <is>
-          <t>CI_TURNOVER_BASED_GAR_STOCK_SC_TO_ANY_PCT_ELIGIBLE</t>
+          <t>CI_TURNOVER_BASED_GAR_STOCK_SC_TO_BIO_PCT_ALIGNED</t>
         </is>
       </c>
       <c r="F32" s="4" t="inlineStr">
         <is>
-          <t>Taxonomy-eligible Proportion of Revenue-based Green Asset Ratio substantially contributing to any of the six Environmental Objectives</t>
+          <t>Taxonomy-aligned Proportion of Revenue-based Green Asset Ratio substantially contributing to Protection and Restoration of Biodiversity and Ecosystems</t>
         </is>
       </c>
       <c r="G32" s="4" t="inlineStr">
@@ -2466,17 +2458,17 @@
       </c>
       <c r="D33" s="4" t="inlineStr">
         <is>
-          <t>Substantial Contribution to any of the six Environmental Objectives in Percent - Aligned</t>
+          <t>Substantial Contribution to any of the six Environmental Objectives in Percent - Eligible</t>
         </is>
       </c>
       <c r="E33" s="4" t="inlineStr">
         <is>
-          <t>CI_TURNOVER_BASED_GAR_STOCK_SC_TO_ANY_PCT_ALIGNED</t>
+          <t>CI_TURNOVER_BASED_GAR_STOCK_SC_TO_ANY_PCT_ELIGIBLE</t>
         </is>
       </c>
       <c r="F33" s="4" t="inlineStr">
         <is>
-          <t>Taxonomy-aligned Proportion of Revenue-based Green Asset Ratio substantially contributing to any of the six Environmental Objectives</t>
+          <t>Taxonomy-eligible Proportion of Revenue-based Green Asset Ratio substantially contributing to any of the six Environmental Objectives</t>
         </is>
       </c>
       <c r="G33" s="4" t="inlineStr">
@@ -2524,17 +2516,17 @@
       </c>
       <c r="D34" s="4" t="inlineStr">
         <is>
-          <t>Substantial Contribution to any of the six Environmental Objectives in Percent - Of which Use of Proceeds</t>
+          <t>Substantial Contribution to any of the six Environmental Objectives in Percent - Aligned</t>
         </is>
       </c>
       <c r="E34" s="4" t="inlineStr">
         <is>
-          <t>CI_TURNOVER_BASED_GAR_STOCK_SC_TO_ANY_PCT_USE_OF_PROCEEDS</t>
+          <t>CI_TURNOVER_BASED_GAR_STOCK_SC_TO_ANY_PCT_ALIGNED</t>
         </is>
       </c>
       <c r="F34" s="4" t="inlineStr">
         <is>
-          <t>Taxonomy-aligned Use of Proceeds Share substantially contributing to any of the six Environmental Objectives</t>
+          <t>Taxonomy-aligned Proportion of Revenue-based Green Asset Ratio substantially contributing to any of the six Environmental Objectives</t>
         </is>
       </c>
       <c r="G34" s="4" t="inlineStr">
@@ -2582,17 +2574,17 @@
       </c>
       <c r="D35" s="4" t="inlineStr">
         <is>
-          <t>Substantial Contribution to any of the six Environmental Objectives in Percent - Of which Enabling</t>
+          <t>Substantial Contribution to any of the six Environmental Objectives in Percent - Of which Use of Proceeds</t>
         </is>
       </c>
       <c r="E35" s="4" t="inlineStr">
         <is>
-          <t>CI_TURNOVER_BASED_GAR_STOCK_SC_TO_ANY_PCT_ENABLING</t>
+          <t>CI_TURNOVER_BASED_GAR_STOCK_SC_TO_ANY_PCT_USE_OF_PROCEEDS</t>
         </is>
       </c>
       <c r="F35" s="4" t="inlineStr">
         <is>
-          <t>Taxonomy-aligned and enabling Proportion of Revenue-based Green Asset Ratio substantially contributing to any of the six Environmental Objectives</t>
+          <t>Taxonomy-aligned Use of Proceeds Share substantially contributing to any of the six Environmental Objectives</t>
         </is>
       </c>
       <c r="G35" s="4" t="inlineStr">
@@ -2640,17 +2632,17 @@
       </c>
       <c r="D36" s="4" t="inlineStr">
         <is>
-          <t>Substantial Contribution to any of the six Environmental Objectives in Percent - Of which Transitional</t>
+          <t>Substantial Contribution to any of the six Environmental Objectives in Percent - Of which Enabling</t>
         </is>
       </c>
       <c r="E36" s="4" t="inlineStr">
         <is>
-          <t>CI_TURNOVER_BASED_GAR_STOCK_SC_TO_ANY_PCT_TRANSITIONAL</t>
+          <t>CI_TURNOVER_BASED_GAR_STOCK_SC_TO_ANY_PCT_ENABLING</t>
         </is>
       </c>
       <c r="F36" s="4" t="inlineStr">
         <is>
-          <t>Taxonomy-aligned and transitional Proportion of Revenue-based Green Asset Ratio substantially contributing to any of the six Environmental Objectives</t>
+          <t>Taxonomy-aligned and enabling Proportion of Revenue-based Green Asset Ratio substantially contributing to any of the six Environmental Objectives</t>
         </is>
       </c>
       <c r="G36" s="4" t="inlineStr">
@@ -2698,17 +2690,17 @@
       </c>
       <c r="D37" s="4" t="inlineStr">
         <is>
-          <t>Turnover-based Non-Assessed Exposures</t>
+          <t>Substantial Contribution to any of the six Environmental Objectives in Percent - Of which Transitional</t>
         </is>
       </c>
       <c r="E37" s="4" t="inlineStr">
         <is>
-          <t>CI_TURNOVER_BASED_GAR_STOCK_NON_ASSESSED</t>
+          <t>CI_TURNOVER_BASED_GAR_STOCK_SC_TO_ANY_PCT_TRANSITIONAL</t>
         </is>
       </c>
       <c r="F37" s="4" t="inlineStr">
         <is>
-          <t>Proportion of Revenue-based Green Asset Ratio of which non-assessed exposures</t>
+          <t>Taxonomy-aligned and transitional Proportion of Revenue-based Green Asset Ratio substantially contributing to any of the six Environmental Objectives</t>
         </is>
       </c>
       <c r="G37" s="4" t="inlineStr">
@@ -2751,22 +2743,22 @@
       </c>
       <c r="C38" s="3" t="inlineStr">
         <is>
-          <t>CapEx-based Green Asset Ratio (stock)</t>
+          <t>Turnover-based Green Asset Ratio (stock)</t>
         </is>
       </c>
       <c r="D38" s="4" t="inlineStr">
         <is>
-          <t>Substantial Contribution to Climate Change Mitigation in Percent - Aligned</t>
+          <t>Turnover-based Non-Assessed Exposures</t>
         </is>
       </c>
       <c r="E38" s="4" t="inlineStr">
         <is>
-          <t>CI_CAPEX_BASED_GAR_STOCK_SC_TO_CCM_PCT_ALIGNED</t>
+          <t>CI_TURNOVER_BASED_GAR_STOCK_NON_ASSESSED</t>
         </is>
       </c>
       <c r="F38" s="4" t="inlineStr">
         <is>
-          <t>Taxonomy-aligned Proportion of CapEx-based Green Asset Ratio substantially contributing to Climate Change Mitigation</t>
+          <t>Proportion of Revenue-based Green Asset Ratio of which non-assessed exposures</t>
         </is>
       </c>
       <c r="G38" s="4" t="inlineStr">
@@ -2814,17 +2806,17 @@
       </c>
       <c r="D39" s="4" t="inlineStr">
         <is>
-          <t>Substantial Contribution to Climate Change Adaptation in Percent - Aligned</t>
+          <t>Substantial Contribution to Climate Change Mitigation in Percent - Aligned</t>
         </is>
       </c>
       <c r="E39" s="4" t="inlineStr">
         <is>
-          <t>CI_CAPEX_BASED_GAR_STOCK_SC_TO_CCA_PCT_ALIGNED</t>
+          <t>CI_CAPEX_BASED_GAR_STOCK_SC_TO_CCM_PCT_ALIGNED</t>
         </is>
       </c>
       <c r="F39" s="4" t="inlineStr">
         <is>
-          <t>Taxonomy-aligned Proportion of CapEx-based Green Asset Ratio substantially contributing to Climate Change Adaptation</t>
+          <t>Taxonomy-aligned Proportion of CapEx-based Green Asset Ratio substantially contributing to Climate Change Mitigation</t>
         </is>
       </c>
       <c r="G39" s="4" t="inlineStr">
@@ -2872,17 +2864,17 @@
       </c>
       <c r="D40" s="4" t="inlineStr">
         <is>
-          <t>Substantial Contribution to Sustainable Use and Protection of Water and Marine Resources in Percent - Aligned</t>
+          <t>Substantial Contribution to Climate Change Adaptation in Percent - Aligned</t>
         </is>
       </c>
       <c r="E40" s="4" t="inlineStr">
         <is>
-          <t>CI_CAPEX_BASED_GAR_STOCK_SC_TO_WTR_PCT_ALIGNED</t>
+          <t>CI_CAPEX_BASED_GAR_STOCK_SC_TO_CCA_PCT_ALIGNED</t>
         </is>
       </c>
       <c r="F40" s="4" t="inlineStr">
         <is>
-          <t>Taxonomy-aligned Proportion of CapEx-based Green Asset Ratio substantially contributing to Sustainable Use and Protection of Water and Marine Resources</t>
+          <t>Taxonomy-aligned Proportion of CapEx-based Green Asset Ratio substantially contributing to Climate Change Adaptation</t>
         </is>
       </c>
       <c r="G40" s="4" t="inlineStr">
@@ -2930,17 +2922,17 @@
       </c>
       <c r="D41" s="4" t="inlineStr">
         <is>
-          <t>Substantial Contribution to Transition to a Circular Economy in Percent - Aligned</t>
+          <t>Substantial Contribution to Sustainable Use and Protection of Water and Marine Resources in Percent - Aligned</t>
         </is>
       </c>
       <c r="E41" s="4" t="inlineStr">
         <is>
-          <t>CI_CAPEX_BASED_GAR_STOCK_SC_TO_CE_PCT_ALIGNED</t>
+          <t>CI_CAPEX_BASED_GAR_STOCK_SC_TO_WTR_PCT_ALIGNED</t>
         </is>
       </c>
       <c r="F41" s="4" t="inlineStr">
         <is>
-          <t>Taxonomy-aligned Proportion of CapEx-based Green Asset Ratio substantially contributing to Circular Economy</t>
+          <t>Taxonomy-aligned Proportion of CapEx-based Green Asset Ratio substantially contributing to Sustainable Use and Protection of Water and Marine Resources</t>
         </is>
       </c>
       <c r="G41" s="4" t="inlineStr">
@@ -2988,17 +2980,17 @@
       </c>
       <c r="D42" s="4" t="inlineStr">
         <is>
-          <t>Substantial Contribution to Pollution Prevention and Control in Percent - Aligned</t>
+          <t>Substantial Contribution to Transition to a Circular Economy in Percent - Aligned</t>
         </is>
       </c>
       <c r="E42" s="4" t="inlineStr">
         <is>
-          <t>CI_CAPEX_BASED_GAR_STOCK_SC_TO_PPC_PCT_ALIGNED</t>
+          <t>CI_CAPEX_BASED_GAR_STOCK_SC_TO_CE_PCT_ALIGNED</t>
         </is>
       </c>
       <c r="F42" s="4" t="inlineStr">
         <is>
-          <t>Taxonomy-aligned Proportion of CapEx-based Green Asset Ratio substantially contributing to Pollution Prevention and Control</t>
+          <t>Taxonomy-aligned Proportion of CapEx-based Green Asset Ratio substantially contributing to Circular Economy</t>
         </is>
       </c>
       <c r="G42" s="4" t="inlineStr">
@@ -3046,17 +3038,17 @@
       </c>
       <c r="D43" s="4" t="inlineStr">
         <is>
-          <t>Substantial Contribution to Protection and Restoration of Biodiversity and Ecosystems in Percent - Aligned</t>
+          <t>Substantial Contribution to Pollution Prevention and Control in Percent - Aligned</t>
         </is>
       </c>
       <c r="E43" s="4" t="inlineStr">
         <is>
-          <t>CI_CAPEX_BASED_GAR_STOCK_SC_TO_BIO_PCT_ALIGNED</t>
+          <t>CI_CAPEX_BASED_GAR_STOCK_SC_TO_PPC_PCT_ALIGNED</t>
         </is>
       </c>
       <c r="F43" s="4" t="inlineStr">
         <is>
-          <t>Taxonomy-aligned Proportion of CapEx-based Green Asset Ratio substantially contributing to Protection and Restoration of Biodiversity and Ecosystems</t>
+          <t>Taxonomy-aligned Proportion of CapEx-based Green Asset Ratio substantially contributing to Pollution Prevention and Control</t>
         </is>
       </c>
       <c r="G43" s="4" t="inlineStr">
@@ -3104,17 +3096,17 @@
       </c>
       <c r="D44" s="4" t="inlineStr">
         <is>
-          <t>Substantial Contribution to any of the six Environmental Objectives in Percent - Eligible</t>
+          <t>Substantial Contribution to Protection and Restoration of Biodiversity and Ecosystems in Percent - Aligned</t>
         </is>
       </c>
       <c r="E44" s="4" t="inlineStr">
         <is>
-          <t>CI_CAPEX_BASED_GAR_STOCK_SC_TO_ANY_PCT_ELIGIBLE</t>
+          <t>CI_CAPEX_BASED_GAR_STOCK_SC_TO_BIO_PCT_ALIGNED</t>
         </is>
       </c>
       <c r="F44" s="4" t="inlineStr">
         <is>
-          <t>Taxonomy-eligible Proportion of CapEx-based Green Asset Ratio substantially contributing to any of the six Environmental Objectives</t>
+          <t>Taxonomy-aligned Proportion of CapEx-based Green Asset Ratio substantially contributing to Protection and Restoration of Biodiversity and Ecosystems</t>
         </is>
       </c>
       <c r="G44" s="4" t="inlineStr">
@@ -3162,17 +3154,17 @@
       </c>
       <c r="D45" s="4" t="inlineStr">
         <is>
-          <t>Substantial Contribution to any of the six Environmental Objectives in Percent - Aligned</t>
+          <t>Substantial Contribution to any of the six Environmental Objectives in Percent - Eligible</t>
         </is>
       </c>
       <c r="E45" s="4" t="inlineStr">
         <is>
-          <t>CI_CAPEX_BASED_GAR_STOCK_SC_TO_ANY_PCT_ALIGNED</t>
+          <t>CI_CAPEX_BASED_GAR_STOCK_SC_TO_ANY_PCT_ELIGIBLE</t>
         </is>
       </c>
       <c r="F45" s="4" t="inlineStr">
         <is>
-          <t>Taxonomy-aligned Proportion of CapEx-based Green Asset Ratio substantially contributing to any of the six Environmental Objectives</t>
+          <t>Taxonomy-eligible Proportion of CapEx-based Green Asset Ratio substantially contributing to any of the six Environmental Objectives</t>
         </is>
       </c>
       <c r="G45" s="4" t="inlineStr">
@@ -3220,17 +3212,17 @@
       </c>
       <c r="D46" s="4" t="inlineStr">
         <is>
-          <t>Substantial Contribution to any of the six Environmental Objectives in Percent - Of which Use of Proceeds</t>
+          <t>Substantial Contribution to any of the six Environmental Objectives in Percent - Aligned</t>
         </is>
       </c>
       <c r="E46" s="4" t="inlineStr">
         <is>
-          <t>CI_CAPEX_BASED_GAR_STOCK_SC_TO_ANY_PCT_USE_OF_PROCEEDS</t>
+          <t>CI_CAPEX_BASED_GAR_STOCK_SC_TO_ANY_PCT_ALIGNED</t>
         </is>
       </c>
       <c r="F46" s="4" t="inlineStr">
         <is>
-          <t>Taxonomy-aligned Use of Proceeds Share substantially contributing to any of the six Environmental Objectives</t>
+          <t>Taxonomy-aligned Proportion of CapEx-based Green Asset Ratio substantially contributing to any of the six Environmental Objectives</t>
         </is>
       </c>
       <c r="G46" s="4" t="inlineStr">
@@ -3278,17 +3270,17 @@
       </c>
       <c r="D47" s="4" t="inlineStr">
         <is>
-          <t>Substantial Contribution to any of the six Environmental Objectives in Percent - Of which Enabling</t>
+          <t>Substantial Contribution to any of the six Environmental Objectives in Percent - Of which Use of Proceeds</t>
         </is>
       </c>
       <c r="E47" s="4" t="inlineStr">
         <is>
-          <t>CI_CAPEX_BASED_GAR_STOCK_SC_TO_ANY_PCT_ENABLING</t>
+          <t>CI_CAPEX_BASED_GAR_STOCK_SC_TO_ANY_PCT_USE_OF_PROCEEDS</t>
         </is>
       </c>
       <c r="F47" s="4" t="inlineStr">
         <is>
-          <t>Taxonomy-aligned and enabling Proportion of CapEx-based Green Asset Ratio substantially contributing to any of the six Environmental Objectives</t>
+          <t>Taxonomy-aligned Use of Proceeds Share substantially contributing to any of the six Environmental Objectives</t>
         </is>
       </c>
       <c r="G47" s="4" t="inlineStr">
@@ -3336,17 +3328,17 @@
       </c>
       <c r="D48" s="4" t="inlineStr">
         <is>
-          <t>Substantial Contribution to any of the six Environmental Objectives in Percent - Of which Transitional</t>
+          <t>Substantial Contribution to any of the six Environmental Objectives in Percent - Of which Enabling</t>
         </is>
       </c>
       <c r="E48" s="4" t="inlineStr">
         <is>
-          <t>CI_CAPEX_BASED_GAR_STOCK_SC_TO_ANY_PCT_TRANSITIONAL</t>
+          <t>CI_CAPEX_BASED_GAR_STOCK_SC_TO_ANY_PCT_ENABLING</t>
         </is>
       </c>
       <c r="F48" s="4" t="inlineStr">
         <is>
-          <t>Taxonomy-aligned and transitional Proportion of CapEx-based Green Asset Ratio substantially contributing to any of the six Environmental Objectives</t>
+          <t>Taxonomy-aligned and enabling Proportion of CapEx-based Green Asset Ratio substantially contributing to any of the six Environmental Objectives</t>
         </is>
       </c>
       <c r="G48" s="4" t="inlineStr">
@@ -3394,17 +3386,17 @@
       </c>
       <c r="D49" s="4" t="inlineStr">
         <is>
-          <t>CapEx-based Non-Assessed Exposures</t>
+          <t>Substantial Contribution to any of the six Environmental Objectives in Percent - Of which Transitional</t>
         </is>
       </c>
       <c r="E49" s="4" t="inlineStr">
         <is>
-          <t>CI_CAPEX_BASED_GAR_STOCK_NON_ASSESSED</t>
+          <t>CI_CAPEX_BASED_GAR_STOCK_SC_TO_ANY_PCT_TRANSITIONAL</t>
         </is>
       </c>
       <c r="F49" s="4" t="inlineStr">
         <is>
-          <t>Proportion of CapEx-based Green Asset Ratio of which non-assessed exposures</t>
+          <t>Taxonomy-aligned and transitional Proportion of CapEx-based Green Asset Ratio substantially contributing to any of the six Environmental Objectives</t>
         </is>
       </c>
       <c r="G49" s="4" t="inlineStr">
@@ -3442,32 +3434,32 @@
       </c>
       <c r="B50" s="3" t="inlineStr">
         <is>
-          <t>Asset Management</t>
+          <t>Credit Institution</t>
         </is>
       </c>
       <c r="C50" s="3" t="inlineStr">
         <is>
-          <t>Asset under Management</t>
+          <t>CapEx-based Green Asset Ratio (stock)</t>
         </is>
       </c>
       <c r="D50" s="4" t="inlineStr">
         <is>
-          <t>Total Asset under Management - monetary amount</t>
+          <t>CapEx-based Non-Assessed Exposures</t>
         </is>
       </c>
       <c r="E50" s="4" t="inlineStr">
         <is>
-          <t>AM_AUM_TOTAL_AMOUNT</t>
+          <t>CI_CAPEX_BASED_GAR_STOCK_NON_ASSESSED</t>
         </is>
       </c>
       <c r="F50" s="4" t="inlineStr">
         <is>
-          <t>The value of all Asset under Management (AuM) - monetary amount.</t>
+          <t>Proportion of CapEx-based Green Asset Ratio of which non-assessed exposures</t>
         </is>
       </c>
       <c r="G50" s="4" t="inlineStr">
         <is>
-          <t>Currency</t>
+          <t>Percentage</t>
         </is>
       </c>
       <c r="H50" s="4" t="inlineStr"/>
@@ -3510,22 +3502,22 @@
       </c>
       <c r="D51" s="4" t="inlineStr">
         <is>
-          <t>Assets covered by the KPI - in Percent</t>
+          <t>Total Asset under Management - monetary amount</t>
         </is>
       </c>
       <c r="E51" s="4" t="inlineStr">
         <is>
-          <t>AM_AUM_COVERED_BY_KPI_PCT</t>
+          <t>AM_AUM_TOTAL_AMOUNT</t>
         </is>
       </c>
       <c r="F51" s="4" t="inlineStr">
         <is>
-          <t>The value of all Asset under Management (AuM) covered under Article 7(6) of Regulation (EU) 2026/73 resulting from both collective and individual portfolio management activities of asset managers relative to the value of total asset under management - in Percent.</t>
+          <t>The value of all Asset under Management (AuM) - monetary amount.</t>
         </is>
       </c>
       <c r="G51" s="4" t="inlineStr">
         <is>
-          <t>Percentage</t>
+          <t>Currency</t>
         </is>
       </c>
       <c r="H51" s="4" t="inlineStr"/>
@@ -3568,29 +3560,25 @@
       </c>
       <c r="D52" s="4" t="inlineStr">
         <is>
-          <t>Assets covered by the KPI - monetary amount</t>
+          <t>Assets covered by the KPI - in Percent</t>
         </is>
       </c>
       <c r="E52" s="4" t="inlineStr">
         <is>
-          <t>AM_AUM_COVERED_BY_KPI_AMOUNT</t>
+          <t>AM_AUM_COVERED_BY_KPI_PCT</t>
         </is>
       </c>
       <c r="F52" s="4" t="inlineStr">
         <is>
-          <t>The value of all Asset under Management (AuM) covered under Article 7(6) of Regulation (EU) 2026/73 resulting from both collective and individual portfolio management activities of asset managers - monetary amount.</t>
+          <t>The value of all Asset under Management (AuM) covered under Article 7(6) of Regulation (EU) 2026/73 resulting from both collective and individual portfolio management activities of asset managers relative to the value of total asset under management - in Percent.</t>
         </is>
       </c>
       <c r="G52" s="4" t="inlineStr">
         <is>
-          <t>Currency</t>
-        </is>
-      </c>
-      <c r="H52" s="4" t="inlineStr">
-        <is>
-          <t>Allowed Range: [0, INF]</t>
-        </is>
-      </c>
+          <t>Percentage</t>
+        </is>
+      </c>
+      <c r="H52" s="4" t="inlineStr"/>
       <c r="I52" s="4" t="inlineStr"/>
       <c r="J52" s="4" t="inlineStr">
         <is>
@@ -3625,30 +3613,34 @@
       </c>
       <c r="C53" s="3" t="inlineStr">
         <is>
-          <t>Breakdown of the Numerator of the KPI - Turnover-based</t>
+          <t>Asset under Management</t>
         </is>
       </c>
       <c r="D53" s="4" t="inlineStr">
         <is>
-          <t>Share of Turnover-based KPI in Percent - Eligible</t>
+          <t>Assets covered by the KPI - monetary amount</t>
         </is>
       </c>
       <c r="E53" s="4" t="inlineStr">
         <is>
-          <t>AM_TURNOVER_BASED_PCT_ELIGIBLE</t>
+          <t>AM_AUM_COVERED_BY_KPI_AMOUNT</t>
         </is>
       </c>
       <c r="F53" s="4" t="inlineStr">
         <is>
-          <t>Taxonomy-eligible Proportion of Turnover-based KPI</t>
+          <t>The value of all Asset under Management (AuM) covered under Article 7(6) of Regulation (EU) 2026/73 resulting from both collective and individual portfolio management activities of asset managers - monetary amount.</t>
         </is>
       </c>
       <c r="G53" s="4" t="inlineStr">
         <is>
-          <t>Percentage</t>
-        </is>
-      </c>
-      <c r="H53" s="4" t="inlineStr"/>
+          <t>Currency</t>
+        </is>
+      </c>
+      <c r="H53" s="4" t="inlineStr">
+        <is>
+          <t>Allowed Range: [0, INF]</t>
+        </is>
+      </c>
       <c r="I53" s="4" t="inlineStr"/>
       <c r="J53" s="4" t="inlineStr">
         <is>
@@ -3688,17 +3680,17 @@
       </c>
       <c r="D54" s="4" t="inlineStr">
         <is>
-          <t>Share of Turnover-based KPI Exposed towards Nuclear Activities in Percent - Eligible</t>
+          <t>Share of Turnover-based KPI in Percent - Eligible</t>
         </is>
       </c>
       <c r="E54" s="4" t="inlineStr">
         <is>
-          <t>AM_TURNOVER_BASED_NUCLEAR_PCT_ELIGIBLE</t>
+          <t>AM_TURNOVER_BASED_PCT_ELIGIBLE</t>
         </is>
       </c>
       <c r="F54" s="4" t="inlineStr">
         <is>
-          <t>Taxonomy-eligible Proportion of Turnover-based KPI exposed towards Nuclear Activities</t>
+          <t>Taxonomy-eligible Proportion of Turnover-based KPI</t>
         </is>
       </c>
       <c r="G54" s="4" t="inlineStr">
@@ -3746,17 +3738,17 @@
       </c>
       <c r="D55" s="4" t="inlineStr">
         <is>
-          <t>Share of Turnover-based KPI Exposed towards Fossil Gas Activities in Percent - Eligible</t>
+          <t>Share of Turnover-based KPI Exposed towards Nuclear Activities in Percent - Eligible</t>
         </is>
       </c>
       <c r="E55" s="4" t="inlineStr">
         <is>
-          <t>AM_TURNOVER_BASED_GAS_PCT_ELIGIBLE</t>
+          <t>AM_TURNOVER_BASED_NUCLEAR_PCT_ELIGIBLE</t>
         </is>
       </c>
       <c r="F55" s="4" t="inlineStr">
         <is>
-          <t>Taxonomy-eligible Proportion of Turnover-based KPI exposed towards Fossil Gas Activities</t>
+          <t>Taxonomy-eligible Proportion of Turnover-based KPI exposed towards Nuclear Activities</t>
         </is>
       </c>
       <c r="G55" s="4" t="inlineStr">
@@ -3804,17 +3796,17 @@
       </c>
       <c r="D56" s="4" t="inlineStr">
         <is>
-          <t>Share of Turnover-based KPI in Percent - Aligned</t>
+          <t>Share of Turnover-based KPI Exposed towards Fossil Gas Activities in Percent - Eligible</t>
         </is>
       </c>
       <c r="E56" s="4" t="inlineStr">
         <is>
-          <t>AM_TURNOVER_BASED_PCT_ALIGNED</t>
+          <t>AM_TURNOVER_BASED_GAS_PCT_ELIGIBLE</t>
         </is>
       </c>
       <c r="F56" s="4" t="inlineStr">
         <is>
-          <t>Taxonomy-aligned Proportion of Turnover-based KPI</t>
+          <t>Taxonomy-eligible Proportion of Turnover-based KPI exposed towards Fossil Gas Activities</t>
         </is>
       </c>
       <c r="G56" s="4" t="inlineStr">
@@ -3842,7 +3834,7 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="P56" s="4" t="n"/>
+      <c r="P56" s="4" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" s="2" t="inlineStr">
@@ -3862,17 +3854,17 @@
       </c>
       <c r="D57" s="4" t="inlineStr">
         <is>
-          <t>Share of Turnover-based KPI Exposed towards Nuclear Activities in Percent - Aligned</t>
+          <t>Share of Turnover-based KPI in Percent - Aligned</t>
         </is>
       </c>
       <c r="E57" s="4" t="inlineStr">
         <is>
-          <t>AM_TURNOVER_BASED_NUCLEAR_PCT_ALIGNED</t>
+          <t>AM_TURNOVER_BASED_PCT_ALIGNED</t>
         </is>
       </c>
       <c r="F57" s="4" t="inlineStr">
         <is>
-          <t>Taxonomy-aligned Proportion of Turnover-based KPI exposed towards Nuclear Activities</t>
+          <t>Taxonomy-aligned Proportion of Turnover-based KPI</t>
         </is>
       </c>
       <c r="G57" s="4" t="inlineStr">
@@ -3900,7 +3892,7 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="P57" s="4" t="inlineStr"/>
+      <c r="P57" s="4" t="n"/>
     </row>
     <row r="58">
       <c r="A58" s="2" t="inlineStr">
@@ -3920,17 +3912,17 @@
       </c>
       <c r="D58" s="4" t="inlineStr">
         <is>
-          <t>Share of Turnover-based KPI Exposed towards Fossil Gas Activities in Percent - Aligned</t>
+          <t>Share of Turnover-based KPI Exposed towards Nuclear Activities in Percent - Aligned</t>
         </is>
       </c>
       <c r="E58" s="4" t="inlineStr">
         <is>
-          <t>AM_TURNOVER_BASED_GAS_PCT_ALIGNED</t>
+          <t>AM_TURNOVER_BASED_NUCLEAR_PCT_ALIGNED</t>
         </is>
       </c>
       <c r="F58" s="4" t="inlineStr">
         <is>
-          <t>Taxonomy-aligned Proportion of Turnover-based KPI exposed towards Fossil Gas Activities</t>
+          <t>Taxonomy-aligned Proportion of Turnover-based KPI exposed towards Nuclear Activities</t>
         </is>
       </c>
       <c r="G58" s="4" t="inlineStr">
@@ -3978,17 +3970,17 @@
       </c>
       <c r="D59" s="4" t="inlineStr">
         <is>
-          <t>Share of Turnover-based KPI in Percent - Of which Transitional</t>
+          <t>Share of Turnover-based KPI Exposed towards Fossil Gas Activities in Percent - Aligned</t>
         </is>
       </c>
       <c r="E59" s="4" t="inlineStr">
         <is>
-          <t>AM_TURNOVER_BASED_PCT_TRANSITIONAL</t>
+          <t>AM_TURNOVER_BASED_GAS_PCT_ALIGNED</t>
         </is>
       </c>
       <c r="F59" s="4" t="inlineStr">
         <is>
-          <t>Taxonomy-aligned and Transitional Proportion of Turnover-based KPI</t>
+          <t>Taxonomy-aligned Proportion of Turnover-based KPI exposed towards Fossil Gas Activities</t>
         </is>
       </c>
       <c r="G59" s="4" t="inlineStr">
@@ -4016,7 +4008,7 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="P59" s="4" t="n"/>
+      <c r="P59" s="4" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" s="2" t="inlineStr">
@@ -4036,17 +4028,17 @@
       </c>
       <c r="D60" s="4" t="inlineStr">
         <is>
-          <t>Share of Turnover-based KPI in Percent - Of which Enabling</t>
+          <t>Share of Turnover-based KPI in Percent - Of which Transitional</t>
         </is>
       </c>
       <c r="E60" s="4" t="inlineStr">
         <is>
-          <t>AM_TURNOVER_BASED_PCT_ENABLING</t>
+          <t>AM_TURNOVER_BASED_PCT_TRANSITIONAL</t>
         </is>
       </c>
       <c r="F60" s="4" t="inlineStr">
         <is>
-          <t>Taxonomy-aligned and Enabling Proportion of Turnover-based KPI</t>
+          <t>Taxonomy-aligned and Transitional Proportion of Turnover-based KPI</t>
         </is>
       </c>
       <c r="G60" s="4" t="inlineStr">
@@ -4074,7 +4066,7 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="P60" s="4" t="inlineStr"/>
+      <c r="P60" s="4" t="n"/>
     </row>
     <row r="61">
       <c r="A61" s="2" t="inlineStr">
@@ -4094,17 +4086,17 @@
       </c>
       <c r="D61" s="4" t="inlineStr">
         <is>
-          <t>Turnover-based Non-Assessed Exposures</t>
+          <t>Share of Turnover-based KPI in Percent - Of which Enabling</t>
         </is>
       </c>
       <c r="E61" s="4" t="inlineStr">
         <is>
-          <t>AM_TURNOVER_BASED_PCT_NON_ASSESSED</t>
+          <t>AM_TURNOVER_BASED_PCT_ENABLING</t>
         </is>
       </c>
       <c r="F61" s="4" t="inlineStr">
         <is>
-          <t>Proportion of Turnover-based KPI of which non-assessed exposures</t>
+          <t>Taxonomy-aligned and Enabling Proportion of Turnover-based KPI</t>
         </is>
       </c>
       <c r="G61" s="4" t="inlineStr">
@@ -4152,17 +4144,17 @@
       </c>
       <c r="D62" s="4" t="inlineStr">
         <is>
-          <t>Turnover-based Non-Assessed Exposures - Of which Exposures Financing Non-Assessed Non-Material Activities of Counterparties</t>
+          <t>Turnover-based Non-Assessed Exposures</t>
         </is>
       </c>
       <c r="E62" s="4" t="inlineStr">
         <is>
-          <t>AM_TURNOVER_BASED_PCT_NON_ASSESSED_NON_MATERIAL_CP</t>
+          <t>AM_TURNOVER_BASED_PCT_NON_ASSESSED</t>
         </is>
       </c>
       <c r="F62" s="4" t="inlineStr">
         <is>
-          <t>Proportion of Turnover-based KPI of which exposures financing non-assessed non-material activities of counterparties</t>
+          <t>Proportion of Turnover-based KPI of which non-assessed exposures</t>
         </is>
       </c>
       <c r="G62" s="4" t="inlineStr">
@@ -4210,17 +4202,17 @@
       </c>
       <c r="D63" s="4" t="inlineStr">
         <is>
-          <t>Turnover-based Non-Assessed Exposures - Of which Non-Assessed Exposures Considered Non-Material by the Reporting Entity</t>
+          <t>Turnover-based Non-Assessed Exposures - Of which Exposures Financing Non-Assessed Non-Material Activities of Counterparties</t>
         </is>
       </c>
       <c r="E63" s="4" t="inlineStr">
         <is>
-          <t>AM_TURNOVER_BASED_PCT_NON_ASSESSED_NON_MATERIAL_RE</t>
+          <t>AM_TURNOVER_BASED_PCT_NON_ASSESSED_NON_MATERIAL_CP</t>
         </is>
       </c>
       <c r="F63" s="4" t="inlineStr">
         <is>
-          <t>Proportion of Turnover-based KPI of which non-assessed exposures considered non-material by the reporting entity</t>
+          <t>Proportion of Turnover-based KPI of which exposures financing non-assessed non-material activities of counterparties</t>
         </is>
       </c>
       <c r="G63" s="4" t="inlineStr">
@@ -4268,17 +4260,17 @@
       </c>
       <c r="D64" s="4" t="inlineStr">
         <is>
-          <t>Turnover-based Non-Assessed Exposures - Of which Exposures to Counterparties Reporting no Taxonomy-eligible Activities</t>
+          <t>Turnover-based Non-Assessed Exposures - Of which Non-Assessed Exposures Considered Non-Material by the Reporting Entity</t>
         </is>
       </c>
       <c r="E64" s="4" t="inlineStr">
         <is>
-          <t>AM_TURNOVER_BASED_PCT_NON_ASSESSED_NO_ELIGIBLE_CP</t>
+          <t>AM_TURNOVER_BASED_PCT_NON_ASSESSED_NON_MATERIAL_RE</t>
         </is>
       </c>
       <c r="F64" s="4" t="inlineStr">
         <is>
-          <t>Proportion of Turnover-based KPI of which exposures to counterparties reporting in accordance with Article 7(9) of Regulation (EU) 2026/73</t>
+          <t>Proportion of Turnover-based KPI of which non-assessed exposures considered non-material by the reporting entity</t>
         </is>
       </c>
       <c r="G64" s="4" t="inlineStr">
@@ -4321,22 +4313,22 @@
       </c>
       <c r="C65" s="3" t="inlineStr">
         <is>
-          <t>Breakdown of the Numerator of the KPI per Environmental Objective - Turnover-based</t>
+          <t>Breakdown of the Numerator of the KPI - Turnover-based</t>
         </is>
       </c>
       <c r="D65" s="4" t="inlineStr">
         <is>
-          <t>Share of Turnover-based KPI substantially contributing to Climate Change Mitigation in Percent - Aligned</t>
+          <t>Turnover-based Non-Assessed Exposures - Of which Exposures to Counterparties Reporting no Taxonomy-eligible Activities</t>
         </is>
       </c>
       <c r="E65" s="4" t="inlineStr">
         <is>
-          <t>AM_TURNOVER_BASED_SC_TO_CCM_PCT_ALIGNED</t>
+          <t>AM_TURNOVER_BASED_PCT_NON_ASSESSED_NO_ELIGIBLE_CP</t>
         </is>
       </c>
       <c r="F65" s="4" t="inlineStr">
         <is>
-          <t>Taxonomy-aligned Proportion of Turnover-based KPI substantially contributing to Climate Change Mitigation</t>
+          <t>Proportion of Turnover-based KPI of which exposures to counterparties reporting in accordance with Article 7(9) of Regulation (EU) 2026/73</t>
         </is>
       </c>
       <c r="G65" s="4" t="inlineStr">
@@ -4384,17 +4376,17 @@
       </c>
       <c r="D66" s="4" t="inlineStr">
         <is>
-          <t>Share of Turnover-based KPI substantially contributing to Climate Change Adaptation in Percent - Aligned</t>
+          <t>Share of Turnover-based KPI substantially contributing to Climate Change Mitigation in Percent - Aligned</t>
         </is>
       </c>
       <c r="E66" s="4" t="inlineStr">
         <is>
-          <t>AM_TURNOVER_BASED_SC_TO_CCA_PCT_ALIGNED</t>
+          <t>AM_TURNOVER_BASED_SC_TO_CCM_PCT_ALIGNED</t>
         </is>
       </c>
       <c r="F66" s="4" t="inlineStr">
         <is>
-          <t>Taxonomy-aligned Proportion of Turnover-based KPI substantially contributing to Climate Change Adaptation</t>
+          <t>Taxonomy-aligned Proportion of Turnover-based KPI substantially contributing to Climate Change Mitigation</t>
         </is>
       </c>
       <c r="G66" s="4" t="inlineStr">
@@ -4442,17 +4434,17 @@
       </c>
       <c r="D67" s="4" t="inlineStr">
         <is>
-          <t>Share of Turnover-based KPI substantially contributing to Sustainable Use and Protection of Water and Marine Resources in Percent - Aligned</t>
+          <t>Share of Turnover-based KPI substantially contributing to Climate Change Adaptation in Percent - Aligned</t>
         </is>
       </c>
       <c r="E67" s="4" t="inlineStr">
         <is>
-          <t>AM_TURNOVER_BASED_SC_TO_WTR_PCT_ALIGNED</t>
+          <t>AM_TURNOVER_BASED_SC_TO_CCA_PCT_ALIGNED</t>
         </is>
       </c>
       <c r="F67" s="4" t="inlineStr">
         <is>
-          <t>Taxonomy-aligned Proportion of Turnover-based KPI substantially contributing to Sustainable Use and Protection of Water and Marine Resources</t>
+          <t>Taxonomy-aligned Proportion of Turnover-based KPI substantially contributing to Climate Change Adaptation</t>
         </is>
       </c>
       <c r="G67" s="4" t="inlineStr">
@@ -4500,17 +4492,17 @@
       </c>
       <c r="D68" s="4" t="inlineStr">
         <is>
-          <t>Share of Turnover-based KPI substantially contributing to Transition to a Circular Economy in Percent - Aligned</t>
+          <t>Share of Turnover-based KPI substantially contributing to Sustainable Use and Protection of Water and Marine Resources in Percent - Aligned</t>
         </is>
       </c>
       <c r="E68" s="4" t="inlineStr">
         <is>
-          <t>AM_TURNOVER_BASED_SC_TO_CE_PCT_ALIGNED</t>
+          <t>AM_TURNOVER_BASED_SC_TO_WTR_PCT_ALIGNED</t>
         </is>
       </c>
       <c r="F68" s="4" t="inlineStr">
         <is>
-          <t>Taxonomy-aligned Proportion of Turnover-based KPI substantially contributing to Circular Economy</t>
+          <t>Taxonomy-aligned Proportion of Turnover-based KPI substantially contributing to Sustainable Use and Protection of Water and Marine Resources</t>
         </is>
       </c>
       <c r="G68" s="4" t="inlineStr">
@@ -4558,17 +4550,17 @@
       </c>
       <c r="D69" s="4" t="inlineStr">
         <is>
-          <t>Share of Turnover-based KPI substantially contributing to Pollution Prevention and Control in Percent - Aligned</t>
+          <t>Share of Turnover-based KPI substantially contributing to Transition to a Circular Economy in Percent - Aligned</t>
         </is>
       </c>
       <c r="E69" s="4" t="inlineStr">
         <is>
-          <t>AM_TURNOVER_BASED_SC_TO_PPC_PCT_ALIGNED</t>
+          <t>AM_TURNOVER_BASED_SC_TO_CE_PCT_ALIGNED</t>
         </is>
       </c>
       <c r="F69" s="4" t="inlineStr">
         <is>
-          <t>Taxonomy-aligned Proportion of Turnover-based KPI substantially contributing to Pollution Prevention and Control</t>
+          <t>Taxonomy-aligned Proportion of Turnover-based KPI substantially contributing to Circular Economy</t>
         </is>
       </c>
       <c r="G69" s="4" t="inlineStr">
@@ -4616,17 +4608,17 @@
       </c>
       <c r="D70" s="4" t="inlineStr">
         <is>
-          <t>Share of Turnover-based KPI substantially contributing to Protection and Restoration of Biodiversity and Ecosystems in Percent - Aligned</t>
+          <t>Share of Turnover-based KPI substantially contributing to Pollution Prevention and Control in Percent - Aligned</t>
         </is>
       </c>
       <c r="E70" s="4" t="inlineStr">
         <is>
-          <t>AM_TURNOVER_BASED_SC_TO_BIO_PCT_ALIGNED</t>
+          <t>AM_TURNOVER_BASED_SC_TO_PPC_PCT_ALIGNED</t>
         </is>
       </c>
       <c r="F70" s="4" t="inlineStr">
         <is>
-          <t>Taxonomy-aligned Proportion of Turnover-based KPI substantially contributing to Protection and Restoration of Biodiversity and Ecosystems</t>
+          <t>Taxonomy-aligned Proportion of Turnover-based KPI substantially contributing to Pollution Prevention and Control</t>
         </is>
       </c>
       <c r="G70" s="4" t="inlineStr">
@@ -4669,22 +4661,22 @@
       </c>
       <c r="C71" s="3" t="inlineStr">
         <is>
-          <t>Breakdown of the Numerator of the KPI - CapEx-based</t>
+          <t>Breakdown of the Numerator of the KPI per Environmental Objective - Turnover-based</t>
         </is>
       </c>
       <c r="D71" s="4" t="inlineStr">
         <is>
-          <t>Share of CapEx-based KPI in Percent - Eligible</t>
+          <t>Share of Turnover-based KPI substantially contributing to Protection and Restoration of Biodiversity and Ecosystems in Percent - Aligned</t>
         </is>
       </c>
       <c r="E71" s="4" t="inlineStr">
         <is>
-          <t>AM_CAPEX_BASED_PCT_ELIGIBLE</t>
+          <t>AM_TURNOVER_BASED_SC_TO_BIO_PCT_ALIGNED</t>
         </is>
       </c>
       <c r="F71" s="4" t="inlineStr">
         <is>
-          <t>Taxonomy-eligible Proportion of CapEx-based KPI</t>
+          <t>Taxonomy-aligned Proportion of Turnover-based KPI substantially contributing to Protection and Restoration of Biodiversity and Ecosystems</t>
         </is>
       </c>
       <c r="G71" s="4" t="inlineStr">
@@ -4732,17 +4724,17 @@
       </c>
       <c r="D72" s="4" t="inlineStr">
         <is>
-          <t>Share of CapEx-based KPI Exposed towards Nuclear Activities in Percent - Eligible</t>
+          <t>Share of CapEx-based KPI in Percent - Eligible</t>
         </is>
       </c>
       <c r="E72" s="4" t="inlineStr">
         <is>
-          <t>AM_CAPEX_BASED_NUCLEAR_PCT_ELIGIBLE</t>
+          <t>AM_CAPEX_BASED_PCT_ELIGIBLE</t>
         </is>
       </c>
       <c r="F72" s="4" t="inlineStr">
         <is>
-          <t>Taxonomy-eligible Proportion of CapEx-based KPI exposed towards Nuclear Activities</t>
+          <t>Taxonomy-eligible Proportion of CapEx-based KPI</t>
         </is>
       </c>
       <c r="G72" s="4" t="inlineStr">
@@ -4790,17 +4782,17 @@
       </c>
       <c r="D73" s="4" t="inlineStr">
         <is>
-          <t>Share of CapEx-based KPI Exposed towards Fossil Gas Activities in Percent - Eligible</t>
+          <t>Share of CapEx-based KPI Exposed towards Nuclear Activities in Percent - Eligible</t>
         </is>
       </c>
       <c r="E73" s="4" t="inlineStr">
         <is>
-          <t>AM_CAPEX_BASED_GAS_PCT_ELIGIBLE</t>
+          <t>AM_CAPEX_BASED_NUCLEAR_PCT_ELIGIBLE</t>
         </is>
       </c>
       <c r="F73" s="4" t="inlineStr">
         <is>
-          <t>Taxonomy-eligible Proportion of CapEx-based KPI exposed towards Fossil Gas Activities</t>
+          <t>Taxonomy-eligible Proportion of CapEx-based KPI exposed towards Nuclear Activities</t>
         </is>
       </c>
       <c r="G73" s="4" t="inlineStr">
@@ -4848,17 +4840,17 @@
       </c>
       <c r="D74" s="4" t="inlineStr">
         <is>
-          <t>Share of CapEx-based KPI in Percent - Aligned</t>
+          <t>Share of CapEx-based KPI Exposed towards Fossil Gas Activities in Percent - Eligible</t>
         </is>
       </c>
       <c r="E74" s="4" t="inlineStr">
         <is>
-          <t>AM_CAPEX_BASED_PCT_ALIGNED</t>
+          <t>AM_CAPEX_BASED_GAS_PCT_ELIGIBLE</t>
         </is>
       </c>
       <c r="F74" s="4" t="inlineStr">
         <is>
-          <t>Taxonomy-aligned Proportion of CapEx-based KPI</t>
+          <t>Taxonomy-eligible Proportion of CapEx-based KPI exposed towards Fossil Gas Activities</t>
         </is>
       </c>
       <c r="G74" s="4" t="inlineStr">
@@ -4886,7 +4878,7 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="P74" s="4" t="n"/>
+      <c r="P74" s="4" t="inlineStr"/>
     </row>
     <row r="75">
       <c r="A75" s="2" t="inlineStr">
@@ -4906,17 +4898,17 @@
       </c>
       <c r="D75" s="4" t="inlineStr">
         <is>
-          <t>Share of CapEx-based KPI Exposed towards Nuclear Activities in Percent - Aligned</t>
+          <t>Share of CapEx-based KPI in Percent - Aligned</t>
         </is>
       </c>
       <c r="E75" s="4" t="inlineStr">
         <is>
-          <t>AM_CAPEX_BASED_NUCLEAR_PCT_ALIGNED</t>
+          <t>AM_CAPEX_BASED_PCT_ALIGNED</t>
         </is>
       </c>
       <c r="F75" s="4" t="inlineStr">
         <is>
-          <t>Taxonomy-aligned Proportion of CapEx-based KPI exposed towards Nuclear Activities</t>
+          <t>Taxonomy-aligned Proportion of CapEx-based KPI</t>
         </is>
       </c>
       <c r="G75" s="4" t="inlineStr">
@@ -4944,7 +4936,7 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="P75" s="4" t="inlineStr"/>
+      <c r="P75" s="4" t="n"/>
     </row>
     <row r="76">
       <c r="A76" s="2" t="inlineStr">
@@ -4964,17 +4956,17 @@
       </c>
       <c r="D76" s="4" t="inlineStr">
         <is>
-          <t>Share of CapEx-based KPI Exposed towards Fossil Gas Activities in Percent - Aligned</t>
+          <t>Share of CapEx-based KPI Exposed towards Nuclear Activities in Percent - Aligned</t>
         </is>
       </c>
       <c r="E76" s="4" t="inlineStr">
         <is>
-          <t>AM_CAPEX_BASED_GAS_PCT_ALIGNED</t>
+          <t>AM_CAPEX_BASED_NUCLEAR_PCT_ALIGNED</t>
         </is>
       </c>
       <c r="F76" s="4" t="inlineStr">
         <is>
-          <t>Taxonomy-aligned Proportion of CapEx-based KPI exposed towards Fossil Gas Activities</t>
+          <t>Taxonomy-aligned Proportion of CapEx-based KPI exposed towards Nuclear Activities</t>
         </is>
       </c>
       <c r="G76" s="4" t="inlineStr">
@@ -5022,17 +5014,17 @@
       </c>
       <c r="D77" s="4" t="inlineStr">
         <is>
-          <t>Share of CapEx-based KPI in Percent - Of which Transitional</t>
+          <t>Share of CapEx-based KPI Exposed towards Fossil Gas Activities in Percent - Aligned</t>
         </is>
       </c>
       <c r="E77" s="4" t="inlineStr">
         <is>
-          <t>AM_CAPEX_BASED_PCT_TRANSITIONAL</t>
+          <t>AM_CAPEX_BASED_GAS_PCT_ALIGNED</t>
         </is>
       </c>
       <c r="F77" s="4" t="inlineStr">
         <is>
-          <t>Taxonomy-aligned and Transitional Proportion of CapEx-based KPI</t>
+          <t>Taxonomy-aligned Proportion of CapEx-based KPI exposed towards Fossil Gas Activities</t>
         </is>
       </c>
       <c r="G77" s="4" t="inlineStr">
@@ -5060,7 +5052,7 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="P77" s="4" t="n"/>
+      <c r="P77" s="4" t="inlineStr"/>
     </row>
     <row r="78">
       <c r="A78" s="2" t="inlineStr">
@@ -5080,17 +5072,17 @@
       </c>
       <c r="D78" s="4" t="inlineStr">
         <is>
-          <t>Share of CapEx-based KPI in Percent - Of which Enabling</t>
+          <t>Share of CapEx-based KPI in Percent - Of which Transitional</t>
         </is>
       </c>
       <c r="E78" s="4" t="inlineStr">
         <is>
-          <t>AM_CAPEX_BASED_PCT_ENABLING</t>
+          <t>AM_CAPEX_BASED_PCT_TRANSITIONAL</t>
         </is>
       </c>
       <c r="F78" s="4" t="inlineStr">
         <is>
-          <t>Taxonomy-aligned and Enabling Proportion of CapEx-based KPI</t>
+          <t>Taxonomy-aligned and Transitional Proportion of CapEx-based KPI</t>
         </is>
       </c>
       <c r="G78" s="4" t="inlineStr">
@@ -5118,7 +5110,7 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="P78" s="4" t="inlineStr"/>
+      <c r="P78" s="4" t="n"/>
     </row>
     <row r="79">
       <c r="A79" s="2" t="inlineStr">
@@ -5138,17 +5130,17 @@
       </c>
       <c r="D79" s="4" t="inlineStr">
         <is>
-          <t>CapEx-based Non-Assessed Exposures</t>
+          <t>Share of CapEx-based KPI in Percent - Of which Enabling</t>
         </is>
       </c>
       <c r="E79" s="4" t="inlineStr">
         <is>
-          <t>AM_CAPEX_BASED_PCT_NON_ASSESSED</t>
+          <t>AM_CAPEX_BASED_PCT_ENABLING</t>
         </is>
       </c>
       <c r="F79" s="4" t="inlineStr">
         <is>
-          <t>Proportion of CapEx-based KPI of which non-assessed exposures</t>
+          <t>Taxonomy-aligned and Enabling Proportion of CapEx-based KPI</t>
         </is>
       </c>
       <c r="G79" s="4" t="inlineStr">
@@ -5196,17 +5188,17 @@
       </c>
       <c r="D80" s="4" t="inlineStr">
         <is>
-          <t>CapEx-based Non-Assessed Exposures - Of which Exposures Financing Non-Assessed Non-Material Activities of Counterparties</t>
+          <t>CapEx-based Non-Assessed Exposures</t>
         </is>
       </c>
       <c r="E80" s="4" t="inlineStr">
         <is>
-          <t>AM_CAPEX_BASED_PCT_NON_ASSESSED_NON_MATERIAL_CP</t>
+          <t>AM_CAPEX_BASED_PCT_NON_ASSESSED</t>
         </is>
       </c>
       <c r="F80" s="4" t="inlineStr">
         <is>
-          <t>Proportion of CapEx-based KPI of which exposures financing non-assessed non-material activities of counterparties</t>
+          <t>Proportion of CapEx-based KPI of which non-assessed exposures</t>
         </is>
       </c>
       <c r="G80" s="4" t="inlineStr">
@@ -5254,17 +5246,17 @@
       </c>
       <c r="D81" s="4" t="inlineStr">
         <is>
-          <t>CapEx-based Non-Assessed Exposures - Of which Non-Assessed Exposures Considered Non-Material by the Reporting Entity</t>
+          <t>CapEx-based Non-Assessed Exposures - Of which Exposures Financing Non-Assessed Non-Material Activities of Counterparties</t>
         </is>
       </c>
       <c r="E81" s="4" t="inlineStr">
         <is>
-          <t>AM_CAPEX_BASED_PCT_NON_ASSESSED_NON_MATERIAL_RE</t>
+          <t>AM_CAPEX_BASED_PCT_NON_ASSESSED_NON_MATERIAL_CP</t>
         </is>
       </c>
       <c r="F81" s="4" t="inlineStr">
         <is>
-          <t>Proportion of CapEx-based KPI of which non-assessed exposures considered non-material by the reporting entity</t>
+          <t>Proportion of CapEx-based KPI of which exposures financing non-assessed non-material activities of counterparties</t>
         </is>
       </c>
       <c r="G81" s="4" t="inlineStr">
@@ -5312,17 +5304,17 @@
       </c>
       <c r="D82" s="4" t="inlineStr">
         <is>
-          <t>CapEx-based Non-Assessed Exposures - Of which Exposures to Counterparties Reporting no Taxonomy-eligible Activities</t>
+          <t>CapEx-based Non-Assessed Exposures - Of which Non-Assessed Exposures Considered Non-Material by the Reporting Entity</t>
         </is>
       </c>
       <c r="E82" s="4" t="inlineStr">
         <is>
-          <t>AM_CAPEX_BASED_PCT_NON_ASSESSED_NO_ELIGIBLE_CP</t>
+          <t>AM_CAPEX_BASED_PCT_NON_ASSESSED_NON_MATERIAL_RE</t>
         </is>
       </c>
       <c r="F82" s="4" t="inlineStr">
         <is>
-          <t>Proportion of CapEx-based KPI of which exposures to counterparties reporting in accordance with Article 7(9) of Regulation (EU) 2026/73</t>
+          <t>Proportion of CapEx-based KPI of which non-assessed exposures considered non-material by the reporting entity</t>
         </is>
       </c>
       <c r="G82" s="4" t="inlineStr">
@@ -5365,22 +5357,22 @@
       </c>
       <c r="C83" s="3" t="inlineStr">
         <is>
-          <t>Breakdown of the Numerator of the KPI per Environmental Objective - CapEx-based</t>
+          <t>Breakdown of the Numerator of the KPI - CapEx-based</t>
         </is>
       </c>
       <c r="D83" s="4" t="inlineStr">
         <is>
-          <t>Share of CapEx-based KPI substantially contributing to Climate Change Mitigation in Percent - Aligned</t>
+          <t>CapEx-based Non-Assessed Exposures - Of which Exposures to Counterparties Reporting no Taxonomy-eligible Activities</t>
         </is>
       </c>
       <c r="E83" s="4" t="inlineStr">
         <is>
-          <t>AM_CAPEX_BASED_SC_TO_CCM_PCT_ALIGNED</t>
+          <t>AM_CAPEX_BASED_PCT_NON_ASSESSED_NO_ELIGIBLE_CP</t>
         </is>
       </c>
       <c r="F83" s="4" t="inlineStr">
         <is>
-          <t>Taxonomy-aligned Proportion of CapEx-based KPI substantially contributing to Climate Change Mitigation</t>
+          <t>Proportion of CapEx-based KPI of which exposures to counterparties reporting in accordance with Article 7(9) of Regulation (EU) 2026/73</t>
         </is>
       </c>
       <c r="G83" s="4" t="inlineStr">
@@ -5428,17 +5420,17 @@
       </c>
       <c r="D84" s="4" t="inlineStr">
         <is>
-          <t>Share of CapEx-based KPI substantially contributing to Climate Change Adaptation in Percent - Aligned</t>
+          <t>Share of CapEx-based KPI substantially contributing to Climate Change Mitigation in Percent - Aligned</t>
         </is>
       </c>
       <c r="E84" s="4" t="inlineStr">
         <is>
-          <t>AM_CAPEX_BASED_SC_TO_CCA_PCT_ALIGNED</t>
+          <t>AM_CAPEX_BASED_SC_TO_CCM_PCT_ALIGNED</t>
         </is>
       </c>
       <c r="F84" s="4" t="inlineStr">
         <is>
-          <t>Taxonomy-aligned Proportion of CapEx-based KPI substantially contributing to Climate Change Adaptation</t>
+          <t>Taxonomy-aligned Proportion of CapEx-based KPI substantially contributing to Climate Change Mitigation</t>
         </is>
       </c>
       <c r="G84" s="4" t="inlineStr">
@@ -5486,17 +5478,17 @@
       </c>
       <c r="D85" s="4" t="inlineStr">
         <is>
-          <t>Share of CapEx-based KPI substantially contributing to Sustainable Use and Protection of Water and Marine Resources in Percent - Aligned</t>
+          <t>Share of CapEx-based KPI substantially contributing to Climate Change Adaptation in Percent - Aligned</t>
         </is>
       </c>
       <c r="E85" s="4" t="inlineStr">
         <is>
-          <t>AM_CAPEX_BASED_SC_TO_WTR_PCT_ALIGNED</t>
+          <t>AM_CAPEX_BASED_SC_TO_CCA_PCT_ALIGNED</t>
         </is>
       </c>
       <c r="F85" s="4" t="inlineStr">
         <is>
-          <t>Taxonomy-aligned Proportion of CapEx-based KPI substantially contributing to Sustainable Use and Protection of Water and Marine Resources</t>
+          <t>Taxonomy-aligned Proportion of CapEx-based KPI substantially contributing to Climate Change Adaptation</t>
         </is>
       </c>
       <c r="G85" s="4" t="inlineStr">
@@ -5544,17 +5536,17 @@
       </c>
       <c r="D86" s="4" t="inlineStr">
         <is>
-          <t>Share of CapEx-based KPI substantially contributing to Transition to a Circular Economy in Percent - Aligned</t>
+          <t>Share of CapEx-based KPI substantially contributing to Sustainable Use and Protection of Water and Marine Resources in Percent - Aligned</t>
         </is>
       </c>
       <c r="E86" s="4" t="inlineStr">
         <is>
-          <t>AM_CAPEX_BASED_SC_TO_CE_PCT_ALIGNED</t>
+          <t>AM_CAPEX_BASED_SC_TO_WTR_PCT_ALIGNED</t>
         </is>
       </c>
       <c r="F86" s="4" t="inlineStr">
         <is>
-          <t>Taxonomy-aligned Proportion of CapEx-based KPI substantially contributing to Circular Economy</t>
+          <t>Taxonomy-aligned Proportion of CapEx-based KPI substantially contributing to Sustainable Use and Protection of Water and Marine Resources</t>
         </is>
       </c>
       <c r="G86" s="4" t="inlineStr">
@@ -5602,17 +5594,17 @@
       </c>
       <c r="D87" s="4" t="inlineStr">
         <is>
-          <t>Share of CapEx-based KPI substantially contributing to Pollution Prevention and Control in Percent - Aligned</t>
+          <t>Share of CapEx-based KPI substantially contributing to Transition to a Circular Economy in Percent - Aligned</t>
         </is>
       </c>
       <c r="E87" s="4" t="inlineStr">
         <is>
-          <t>AM_CAPEX_BASED_SC_TO_PPC_PCT_ALIGNED</t>
+          <t>AM_CAPEX_BASED_SC_TO_CE_PCT_ALIGNED</t>
         </is>
       </c>
       <c r="F87" s="4" t="inlineStr">
         <is>
-          <t>Taxonomy-aligned Proportion of CapEx-based KPI substantially contributing to Pollution Prevention and Control</t>
+          <t>Taxonomy-aligned Proportion of CapEx-based KPI substantially contributing to Circular Economy</t>
         </is>
       </c>
       <c r="G87" s="4" t="inlineStr">
@@ -5660,17 +5652,17 @@
       </c>
       <c r="D88" s="4" t="inlineStr">
         <is>
-          <t>Share of CapEx-based KPI substantially contributing to Protection and Restoration of Biodiversity and Ecosystems in Percent - Aligned</t>
+          <t>Share of CapEx-based KPI substantially contributing to Pollution Prevention and Control in Percent - Aligned</t>
         </is>
       </c>
       <c r="E88" s="4" t="inlineStr">
         <is>
-          <t>AM_CAPEX_BASED_SC_TO_BIO_PCT_ALIGNED</t>
+          <t>AM_CAPEX_BASED_SC_TO_PPC_PCT_ALIGNED</t>
         </is>
       </c>
       <c r="F88" s="4" t="inlineStr">
         <is>
-          <t>Taxonomy-aligned Proportion of CapEx-based KPI substantially contributing to Protection and Restoration of Biodiversity and Ecosystems</t>
+          <t>Taxonomy-aligned Proportion of CapEx-based KPI substantially contributing to Pollution Prevention and Control</t>
         </is>
       </c>
       <c r="G88" s="4" t="inlineStr">
@@ -5708,39 +5700,35 @@
       </c>
       <c r="B89" s="3" t="inlineStr">
         <is>
-          <t>Insurance/Reinsurance</t>
+          <t>Asset Management</t>
         </is>
       </c>
       <c r="C89" s="3" t="inlineStr">
         <is>
-          <t>Underwriting KPI</t>
+          <t>Breakdown of the Numerator of the KPI per Environmental Objective - CapEx-based</t>
         </is>
       </c>
       <c r="D89" s="4" t="inlineStr">
         <is>
-          <t>Total of Absolute Premiums of Taxonomy-aligned Activities</t>
+          <t>Share of CapEx-based KPI substantially contributing to Protection and Restoration of Biodiversity and Ecosystems in Percent - Aligned</t>
         </is>
       </c>
       <c r="E89" s="4" t="inlineStr">
         <is>
-          <t>IR_UNDERWRITING_TOTAL_OF_ABS_PREMIUMS_ALIGNED</t>
+          <t>AM_CAPEX_BASED_SC_TO_BIO_PCT_ALIGNED</t>
         </is>
       </c>
       <c r="F89" s="4" t="inlineStr">
         <is>
-          <t>Non-life Insurance and Reinsurance Undertakings underwriting Taxonomy-aligned Activities. Shall be reported as ‘gross premiums written’ or, as applicable, turnover relating to non-life insurance and reinsurance activity.</t>
+          <t>Taxonomy-aligned Proportion of CapEx-based KPI substantially contributing to Protection and Restoration of Biodiversity and Ecosystems</t>
         </is>
       </c>
       <c r="G89" s="4" t="inlineStr">
         <is>
-          <t>Currency</t>
-        </is>
-      </c>
-      <c r="H89" s="4" t="inlineStr">
-        <is>
-          <t>Allowed Range: [0, INF]</t>
-        </is>
-      </c>
+          <t>Percentage</t>
+        </is>
+      </c>
+      <c r="H89" s="4" t="inlineStr"/>
       <c r="I89" s="4" t="inlineStr"/>
       <c r="J89" s="4" t="inlineStr">
         <is>
@@ -5755,7 +5743,11 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="O89" s="4" t="inlineStr"/>
+      <c r="O89" s="4" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
       <c r="P89" s="4" t="inlineStr"/>
     </row>
     <row r="90">
@@ -5776,25 +5768,29 @@
       </c>
       <c r="D90" s="4" t="inlineStr">
         <is>
-          <t>Proportion of Absolute Premiums of Taxonomy-aligned Activities</t>
+          <t>Total of Absolute Premiums of Taxonomy-aligned Activities</t>
         </is>
       </c>
       <c r="E90" s="4" t="inlineStr">
         <is>
-          <t>IR_UNDERWRITING_PROP_OF_ABS_PREMIUMS_ALIGNED</t>
+          <t>IR_UNDERWRITING_TOTAL_OF_ABS_PREMIUMS_ALIGNED</t>
         </is>
       </c>
       <c r="F90" s="4" t="inlineStr">
         <is>
-          <t>Proportion of Non-life Insurance and Reinsurance Undertakings underwriting Taxonomy-aligned Activities. Shall be reported as ‘gross premiums written’ or, as applicable, turnover relating to non-life insurance and reinsurance activity.</t>
+          <t>Non-life Insurance and Reinsurance Undertakings underwriting Taxonomy-aligned Activities. Shall be reported as ‘gross premiums written’ or, as applicable, turnover relating to non-life insurance and reinsurance activity.</t>
         </is>
       </c>
       <c r="G90" s="4" t="inlineStr">
         <is>
-          <t>Percentage</t>
-        </is>
-      </c>
-      <c r="H90" s="4" t="inlineStr"/>
+          <t>Currency</t>
+        </is>
+      </c>
+      <c r="H90" s="4" t="inlineStr">
+        <is>
+          <t>Allowed Range: [0, INF]</t>
+        </is>
+      </c>
       <c r="I90" s="4" t="inlineStr"/>
       <c r="J90" s="4" t="inlineStr">
         <is>
@@ -5830,17 +5826,17 @@
       </c>
       <c r="D91" s="4" t="inlineStr">
         <is>
-          <t>Proportion of Absolute Premiums of Taxonomy-aligned Nuclear Activities</t>
+          <t>Proportion of Absolute Premiums of Taxonomy-aligned Activities</t>
         </is>
       </c>
       <c r="E91" s="4" t="inlineStr">
         <is>
-          <t>IR_UNDERWRITING_PROP_OF_ABS_PREMIUMS_NUCLEAR_ALIGNED</t>
+          <t>IR_UNDERWRITING_PROP_OF_ABS_PREMIUMS_ALIGNED</t>
         </is>
       </c>
       <c r="F91" s="4" t="inlineStr">
         <is>
-          <t>Proportion of Non-life Insurance and Reinsurance Undertakings underwriting Taxonomy-aligned Nuclear Activities. Shall be reported as ‘gross premiums written’ or, as applicable, turnover relating to non-life insurance and reinsurance activity.</t>
+          <t>Proportion of Non-life Insurance and Reinsurance Undertakings underwriting Taxonomy-aligned Activities. Shall be reported as ‘gross premiums written’ or, as applicable, turnover relating to non-life insurance and reinsurance activity.</t>
         </is>
       </c>
       <c r="G91" s="4" t="inlineStr">
@@ -5884,17 +5880,17 @@
       </c>
       <c r="D92" s="4" t="inlineStr">
         <is>
-          <t>Proportion of Absolute Premiums of Taxonomy-aligned Fossil Gas Activities</t>
+          <t>Proportion of Absolute Premiums of Taxonomy-aligned Nuclear Activities</t>
         </is>
       </c>
       <c r="E92" s="4" t="inlineStr">
         <is>
-          <t>IR_UNDERWRITING_PROP_OF_ABS_PREMIUMS_GAS_ALIGNED</t>
+          <t>IR_UNDERWRITING_PROP_OF_ABS_PREMIUMS_NUCLEAR_ALIGNED</t>
         </is>
       </c>
       <c r="F92" s="4" t="inlineStr">
         <is>
-          <t>Proportion of Non-life Insurance and Reinsurance Undertakings underwriting Taxonomy-aligned Fossil Gas Activities. Shall be reported as ‘gross premiums written’ or, as applicable, turnover relating to non-life insurance and reinsurance activity.</t>
+          <t>Proportion of Non-life Insurance and Reinsurance Undertakings underwriting Taxonomy-aligned Nuclear Activities. Shall be reported as ‘gross premiums written’ or, as applicable, turnover relating to non-life insurance and reinsurance activity.</t>
         </is>
       </c>
       <c r="G92" s="4" t="inlineStr">
@@ -5938,29 +5934,25 @@
       </c>
       <c r="D93" s="4" t="inlineStr">
         <is>
-          <t>Total of Absolute Premiums of Taxonomy-eligible Activities</t>
+          <t>Proportion of Absolute Premiums of Taxonomy-aligned Fossil Gas Activities</t>
         </is>
       </c>
       <c r="E93" s="4" t="inlineStr">
         <is>
-          <t>IR_UNDERWRITING_TOTAL_OF_ABS_PREMIUMS_ELIGIBLE</t>
+          <t>IR_UNDERWRITING_PROP_OF_ABS_PREMIUMS_GAS_ALIGNED</t>
         </is>
       </c>
       <c r="F93" s="4" t="inlineStr">
         <is>
-          <t>Non-life Insurance and Reinsurance Undertakings underwriting Taxonomy-eligible Activities. Shall be reported as ‘gross premiums written’ or, as applicable, turnover relating to non-life insurance and reinsurance activity.</t>
+          <t>Proportion of Non-life Insurance and Reinsurance Undertakings underwriting Taxonomy-aligned Fossil Gas Activities. Shall be reported as ‘gross premiums written’ or, as applicable, turnover relating to non-life insurance and reinsurance activity.</t>
         </is>
       </c>
       <c r="G93" s="4" t="inlineStr">
         <is>
-          <t>Currency</t>
-        </is>
-      </c>
-      <c r="H93" s="4" t="inlineStr">
-        <is>
-          <t>Allowed Range: [0, INF]</t>
-        </is>
-      </c>
+          <t>Percentage</t>
+        </is>
+      </c>
+      <c r="H93" s="4" t="inlineStr"/>
       <c r="I93" s="4" t="inlineStr"/>
       <c r="J93" s="4" t="inlineStr">
         <is>
@@ -5996,25 +5988,29 @@
       </c>
       <c r="D94" s="4" t="inlineStr">
         <is>
-          <t>Proportion of Absolute Premiums of Taxonomy-eligible Activities</t>
+          <t>Total of Absolute Premiums of Taxonomy-eligible Activities</t>
         </is>
       </c>
       <c r="E94" s="4" t="inlineStr">
         <is>
-          <t>IR_UNDERWRITING_PROP_OF_ABS_PREMIUMS_ELIGIBLE</t>
+          <t>IR_UNDERWRITING_TOTAL_OF_ABS_PREMIUMS_ELIGIBLE</t>
         </is>
       </c>
       <c r="F94" s="4" t="inlineStr">
         <is>
-          <t>Proportion of Non-life Insurance and Reinsurance Undertakings underwriting Taxonomy-eligible Activities. Shall be reported as ‘gross premiums written’ or, as applicable, turnover relating to non-life insurance and reinsurance activity.</t>
+          <t>Non-life Insurance and Reinsurance Undertakings underwriting Taxonomy-eligible Activities. Shall be reported as ‘gross premiums written’ or, as applicable, turnover relating to non-life insurance and reinsurance activity.</t>
         </is>
       </c>
       <c r="G94" s="4" t="inlineStr">
         <is>
-          <t>Percentage</t>
-        </is>
-      </c>
-      <c r="H94" s="4" t="inlineStr"/>
+          <t>Currency</t>
+        </is>
+      </c>
+      <c r="H94" s="4" t="inlineStr">
+        <is>
+          <t>Allowed Range: [0, INF]</t>
+        </is>
+      </c>
       <c r="I94" s="4" t="inlineStr"/>
       <c r="J94" s="4" t="inlineStr">
         <is>
@@ -6050,17 +6046,17 @@
       </c>
       <c r="D95" s="4" t="inlineStr">
         <is>
-          <t>Proportion of Absolute Premiums of Taxonomy-eligible Nuclear Activities</t>
+          <t>Proportion of Absolute Premiums of Taxonomy-eligible Activities</t>
         </is>
       </c>
       <c r="E95" s="4" t="inlineStr">
         <is>
-          <t>IR_UNDERWRITING_PROP_OF_ABS_PREMIUMS_NUCLEAR_ELIGIBLE</t>
+          <t>IR_UNDERWRITING_PROP_OF_ABS_PREMIUMS_ELIGIBLE</t>
         </is>
       </c>
       <c r="F95" s="4" t="inlineStr">
         <is>
-          <t>Proportion of Non-life Insurance and Reinsurance Undertakings underwriting Taxonomy-eligible Nuclear Activities. Shall be reported as ‘gross premiums written’ or, as applicable, turnover relating to non-life insurance and reinsurance activity.</t>
+          <t>Proportion of Non-life Insurance and Reinsurance Undertakings underwriting Taxonomy-eligible Activities. Shall be reported as ‘gross premiums written’ or, as applicable, turnover relating to non-life insurance and reinsurance activity.</t>
         </is>
       </c>
       <c r="G95" s="4" t="inlineStr">
@@ -6104,17 +6100,17 @@
       </c>
       <c r="D96" s="4" t="inlineStr">
         <is>
-          <t>Proportion of Absolute Premiums of Taxonomy-eligible Fossil Gas Activities</t>
+          <t>Proportion of Absolute Premiums of Taxonomy-eligible Nuclear Activities</t>
         </is>
       </c>
       <c r="E96" s="4" t="inlineStr">
         <is>
-          <t>IR_UNDERWRITING_PROP_OF_ABS_PREMIUMS_GAS_ELIGIBLE</t>
+          <t>IR_UNDERWRITING_PROP_OF_ABS_PREMIUMS_NUCLEAR_ELIGIBLE</t>
         </is>
       </c>
       <c r="F96" s="4" t="inlineStr">
         <is>
-          <t>Proportion of Non-life Insurance and Reinsurance Undertakings underwriting Taxonomy-eligible Fossil Gas Activities. Shall be reported as ‘gross premiums written’ or, as applicable, turnover relating to non-life insurance and reinsurance activity.</t>
+          <t>Proportion of Non-life Insurance and Reinsurance Undertakings underwriting Taxonomy-eligible Nuclear Activities. Shall be reported as ‘gross premiums written’ or, as applicable, turnover relating to non-life insurance and reinsurance activity.</t>
         </is>
       </c>
       <c r="G96" s="4" t="inlineStr">
@@ -6158,29 +6154,25 @@
       </c>
       <c r="D97" s="4" t="inlineStr">
         <is>
-          <t>Total Of Absolute Premiums Of Non-Assessed Activities Considered Non-Material</t>
+          <t>Proportion of Absolute Premiums of Taxonomy-eligible Fossil Gas Activities</t>
         </is>
       </c>
       <c r="E97" s="4" t="inlineStr">
         <is>
-          <t>IR_UNDERWRITING_TOTAL_OF_ABS_PREMIUMS_NON_ASSESSED</t>
+          <t>IR_UNDERWRITING_PROP_OF_ABS_PREMIUMS_GAS_ELIGIBLE</t>
         </is>
       </c>
       <c r="F97" s="4" t="inlineStr">
         <is>
-          <t>Non-life Insurance and Reinsurance Undertakings underwriting non-assessed activities considered non-material, reported as gross premiums written or, as applicable, revenue relating to non-life insurance or reinsurance activity</t>
+          <t>Proportion of Non-life Insurance and Reinsurance Undertakings underwriting Taxonomy-eligible Fossil Gas Activities. Shall be reported as ‘gross premiums written’ or, as applicable, turnover relating to non-life insurance and reinsurance activity.</t>
         </is>
       </c>
       <c r="G97" s="4" t="inlineStr">
         <is>
-          <t>Currency</t>
-        </is>
-      </c>
-      <c r="H97" s="4" t="inlineStr">
-        <is>
-          <t>Allowed Range: [0, INF]</t>
-        </is>
-      </c>
+          <t>Percentage</t>
+        </is>
+      </c>
+      <c r="H97" s="4" t="inlineStr"/>
       <c r="I97" s="4" t="inlineStr"/>
       <c r="J97" s="4" t="inlineStr">
         <is>
@@ -6216,25 +6208,29 @@
       </c>
       <c r="D98" s="4" t="inlineStr">
         <is>
-          <t>Proportion Of Absolute Premiums Of  Non-Assed Activities Considered Non-Material</t>
+          <t>Total Of Absolute Premiums Of Non-Assessed Activities Considered Non-Material</t>
         </is>
       </c>
       <c r="E98" s="4" t="inlineStr">
         <is>
-          <t>IR_UNDERWRITING_PROP_OF_ABS_PREMIUMS_NON_ASSESSED</t>
+          <t>IR_UNDERWRITING_TOTAL_OF_ABS_PREMIUMS_NON_ASSESSED</t>
         </is>
       </c>
       <c r="F98" s="4" t="inlineStr">
         <is>
-          <t>Proportion of Non-life Insurance and Reinsurance Undertakings underwriting non-assessed activities considered non-material, reported as gross premiums written or, as applicable, revenue relating to non-life insurance or reinsurance activity</t>
+          <t>Non-life Insurance and Reinsurance Undertakings underwriting non-assessed activities considered non-material, reported as gross premiums written or, as applicable, revenue relating to non-life insurance or reinsurance activity</t>
         </is>
       </c>
       <c r="G98" s="4" t="inlineStr">
         <is>
-          <t>Percentage</t>
-        </is>
-      </c>
-      <c r="H98" s="4" t="inlineStr"/>
+          <t>Currency</t>
+        </is>
+      </c>
+      <c r="H98" s="4" t="inlineStr">
+        <is>
+          <t>Allowed Range: [0, INF]</t>
+        </is>
+      </c>
       <c r="I98" s="4" t="inlineStr"/>
       <c r="J98" s="4" t="inlineStr">
         <is>
@@ -6270,29 +6266,25 @@
       </c>
       <c r="D99" s="4" t="inlineStr">
         <is>
-          <t>Total of Absolute Premiums</t>
+          <t>Proportion Of Absolute Premiums Of  Non-Assessed Activities Considered Non-Material</t>
         </is>
       </c>
       <c r="E99" s="4" t="inlineStr">
         <is>
-          <t>IR_UNDERWRITING_TOTAL_OF_ABS_PREMIUMS</t>
+          <t>IR_UNDERWRITING_PROP_OF_ABS_PREMIUMS_NON_ASSESSED</t>
         </is>
       </c>
       <c r="F99" s="4" t="inlineStr">
         <is>
-          <t>Non-life Insurance and Reinsurance Undertakings. Shall be reported as ‘gross premiums written’ or, as applicable, turnover relating to non-life insurance and reinsurance activity.</t>
+          <t>Proportion of Non-life Insurance and Reinsurance Undertakings underwriting non-assessed activities considered non-material, reported as gross premiums written or, as applicable, revenue relating to non-life insurance or reinsurance activity</t>
         </is>
       </c>
       <c r="G99" s="4" t="inlineStr">
         <is>
-          <t>Currency</t>
-        </is>
-      </c>
-      <c r="H99" s="4" t="inlineStr">
-        <is>
-          <t>Allowed Range: [0, INF]</t>
-        </is>
-      </c>
+          <t>Percentage</t>
+        </is>
+      </c>
+      <c r="H99" s="4" t="inlineStr"/>
       <c r="I99" s="4" t="inlineStr"/>
       <c r="J99" s="4" t="inlineStr">
         <is>
@@ -6323,22 +6315,22 @@
       </c>
       <c r="C100" s="3" t="inlineStr">
         <is>
-          <t>Asset under Management</t>
+          <t>Underwriting KPI</t>
         </is>
       </c>
       <c r="D100" s="4" t="inlineStr">
         <is>
-          <t>Total Asset under Management - monetary amount</t>
+          <t>Total of Absolute Premiums</t>
         </is>
       </c>
       <c r="E100" s="4" t="inlineStr">
         <is>
-          <t>IR_AUM_TOTAL_AMOUNT</t>
+          <t>IR_UNDERWRITING_TOTAL_OF_ABS_PREMIUMS</t>
         </is>
       </c>
       <c r="F100" s="4" t="inlineStr">
         <is>
-          <t>The value of total investments of insurance or reinsurance undertakings (total AuM) - monetary amount.</t>
+          <t>Non-life Insurance and Reinsurance Undertakings. Shall be reported as ‘gross premiums written’ or, as applicable, turnover relating to non-life insurance and reinsurance activity.</t>
         </is>
       </c>
       <c r="G100" s="4" t="inlineStr">
@@ -6365,11 +6357,7 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="O100" s="4" t="inlineStr">
-        <is>
-          <t>Yes</t>
-        </is>
-      </c>
+      <c r="O100" s="4" t="inlineStr"/>
       <c r="P100" s="4" t="inlineStr"/>
     </row>
     <row r="101">
@@ -6390,25 +6378,29 @@
       </c>
       <c r="D101" s="4" t="inlineStr">
         <is>
-          <t>Assets covered by the KPI - in Percent</t>
+          <t>Total Asset under Management - monetary amount</t>
         </is>
       </c>
       <c r="E101" s="4" t="inlineStr">
         <is>
-          <t>IR_AUM_COVERED_BY_KPI_PCT</t>
+          <t>IR_AUM_TOTAL_AMOUNT</t>
         </is>
       </c>
       <c r="F101" s="4" t="inlineStr">
         <is>
-          <t>The value of all direct and indirect investments and exposures, covered under Article 7(6) of Regulation (EU) 2026/73, including investments in collective investment undertakings and participations, loans and mortgages relative to total investments of insurance or reinsurance undertakings (total AuM) - in Percent.</t>
+          <t>The value of total investments of insurance or reinsurance undertakings (total AuM) - monetary amount.</t>
         </is>
       </c>
       <c r="G101" s="4" t="inlineStr">
         <is>
-          <t>Percentage</t>
-        </is>
-      </c>
-      <c r="H101" s="4" t="inlineStr"/>
+          <t>Currency</t>
+        </is>
+      </c>
+      <c r="H101" s="4" t="inlineStr">
+        <is>
+          <t>Allowed Range: [0, INF]</t>
+        </is>
+      </c>
       <c r="I101" s="4" t="inlineStr"/>
       <c r="J101" s="4" t="inlineStr">
         <is>
@@ -6448,29 +6440,25 @@
       </c>
       <c r="D102" s="4" t="inlineStr">
         <is>
-          <t>Assets covered by the KPI - monetary amount</t>
+          <t>Assets covered by the KPI - in Percent</t>
         </is>
       </c>
       <c r="E102" s="4" t="inlineStr">
         <is>
-          <t>IR_AUM_COVERED_BY_KPI_AMOUNT</t>
+          <t>IR_AUM_COVERED_BY_KPI_PCT</t>
         </is>
       </c>
       <c r="F102" s="4" t="inlineStr">
         <is>
-          <t>The value of all direct and indirect investments and exposures, covered under Article 7(6) of Regulation (EU) 2026/73, including investments in collective investment undertakings and participations, loans and mortgages - monetary amount.</t>
+          <t>The value of all direct and indirect investments and exposures, covered under Article 7(6) of Regulation (EU) 2026/73, including investments in collective investment undertakings and participations, loans and mortgages relative to total investments of insurance or reinsurance undertakings (total AuM) - in Percent.</t>
         </is>
       </c>
       <c r="G102" s="4" t="inlineStr">
         <is>
-          <t>Currency</t>
-        </is>
-      </c>
-      <c r="H102" s="4" t="inlineStr">
-        <is>
-          <t>Allowed Range: [0, INF]</t>
-        </is>
-      </c>
+          <t>Percentage</t>
+        </is>
+      </c>
+      <c r="H102" s="4" t="inlineStr"/>
       <c r="I102" s="4" t="inlineStr"/>
       <c r="J102" s="4" t="inlineStr">
         <is>
@@ -6505,30 +6493,34 @@
       </c>
       <c r="C103" s="3" t="inlineStr">
         <is>
-          <t>Breakdown of the Numerator of the KPI - Turnover-based</t>
+          <t>Asset under Management</t>
         </is>
       </c>
       <c r="D103" s="4" t="inlineStr">
         <is>
-          <t>Share of Turnover-based KPI in Percent - Eligible</t>
+          <t>Assets covered by the KPI - monetary amount</t>
         </is>
       </c>
       <c r="E103" s="4" t="inlineStr">
         <is>
-          <t>IR_TURNOVER_BASED_PCT_ELIGIBLE</t>
+          <t>IR_AUM_COVERED_BY_KPI_AMOUNT</t>
         </is>
       </c>
       <c r="F103" s="4" t="inlineStr">
         <is>
-          <t>Taxonomy-eligible Proportion of Turnover-based KPI</t>
+          <t>The value of all direct and indirect investments and exposures, covered under Article 7(6) of Regulation (EU) 2026/73, including investments in collective investment undertakings and participations, loans and mortgages - monetary amount.</t>
         </is>
       </c>
       <c r="G103" s="4" t="inlineStr">
         <is>
-          <t>Percentage</t>
-        </is>
-      </c>
-      <c r="H103" s="4" t="inlineStr"/>
+          <t>Currency</t>
+        </is>
+      </c>
+      <c r="H103" s="4" t="inlineStr">
+        <is>
+          <t>Allowed Range: [0, INF]</t>
+        </is>
+      </c>
       <c r="I103" s="4" t="inlineStr"/>
       <c r="J103" s="4" t="inlineStr">
         <is>
@@ -6568,17 +6560,17 @@
       </c>
       <c r="D104" s="4" t="inlineStr">
         <is>
-          <t>Share of Turnover-based KPI Exposed towards Nuclear Activities in Percent - Eligible</t>
+          <t>Share of Turnover-based KPI in Percent - Eligible</t>
         </is>
       </c>
       <c r="E104" s="4" t="inlineStr">
         <is>
-          <t>IR_TURNOVER_BASED_NUCLEAR_PCT_ELIGIBLE</t>
+          <t>IR_TURNOVER_BASED_PCT_ELIGIBLE</t>
         </is>
       </c>
       <c r="F104" s="4" t="inlineStr">
         <is>
-          <t>Taxonomy-eligible Proportion of Turnover-based KPI exposed towards Nuclear Activities</t>
+          <t>Taxonomy-eligible Proportion of Turnover-based KPI</t>
         </is>
       </c>
       <c r="G104" s="4" t="inlineStr">
@@ -6626,17 +6618,17 @@
       </c>
       <c r="D105" s="4" t="inlineStr">
         <is>
-          <t>Share of Turnover-based KPI Exposed towards Fossil Gas Activities in Percent - Eligible</t>
+          <t>Share of Turnover-based KPI Exposed towards Nuclear Activities in Percent - Eligible</t>
         </is>
       </c>
       <c r="E105" s="4" t="inlineStr">
         <is>
-          <t>IR_TURNOVER_BASED_GAS_PCT_ELIGIBLE</t>
+          <t>IR_TURNOVER_BASED_NUCLEAR_PCT_ELIGIBLE</t>
         </is>
       </c>
       <c r="F105" s="4" t="inlineStr">
         <is>
-          <t>Taxonomy-eligible Proportion of Turnover-based KPI exposed towards Fossil Gas Activities</t>
+          <t>Taxonomy-eligible Proportion of Turnover-based KPI exposed towards Nuclear Activities</t>
         </is>
       </c>
       <c r="G105" s="4" t="inlineStr">
@@ -6684,17 +6676,17 @@
       </c>
       <c r="D106" s="4" t="inlineStr">
         <is>
-          <t>Share of Turnover-based KPI in Percent - Aligned</t>
+          <t>Share of Turnover-based KPI Exposed towards Fossil Gas Activities in Percent - Eligible</t>
         </is>
       </c>
       <c r="E106" s="4" t="inlineStr">
         <is>
-          <t>IR_TURNOVER_BASED_PCT_ALIGNED</t>
+          <t>IR_TURNOVER_BASED_GAS_PCT_ELIGIBLE</t>
         </is>
       </c>
       <c r="F106" s="4" t="inlineStr">
         <is>
-          <t>Taxonomy-aligned Proportion of Turnover-based KPI</t>
+          <t>Taxonomy-eligible Proportion of Turnover-based KPI exposed towards Fossil Gas Activities</t>
         </is>
       </c>
       <c r="G106" s="4" t="inlineStr">
@@ -6722,7 +6714,7 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="P106" s="4" t="n"/>
+      <c r="P106" s="4" t="inlineStr"/>
     </row>
     <row r="107">
       <c r="A107" s="2" t="inlineStr">
@@ -6742,17 +6734,17 @@
       </c>
       <c r="D107" s="4" t="inlineStr">
         <is>
-          <t>Share of Turnover-based KPI Exposed towards Nuclear Activities in Percent - Aligned</t>
+          <t>Share of Turnover-based KPI in Percent - Aligned</t>
         </is>
       </c>
       <c r="E107" s="4" t="inlineStr">
         <is>
-          <t>IR_TURNOVER_BASED_NUCLEAR_PCT_ALIGNED</t>
+          <t>IR_TURNOVER_BASED_PCT_ALIGNED</t>
         </is>
       </c>
       <c r="F107" s="4" t="inlineStr">
         <is>
-          <t>Taxonomy-aligned Proportion of Turnover-based KPI exposed towards Nuclear Activities</t>
+          <t>Taxonomy-aligned Proportion of Turnover-based KPI</t>
         </is>
       </c>
       <c r="G107" s="4" t="inlineStr">
@@ -6780,7 +6772,7 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="P107" s="4" t="inlineStr"/>
+      <c r="P107" s="4" t="n"/>
     </row>
     <row r="108">
       <c r="A108" s="2" t="inlineStr">
@@ -6800,17 +6792,17 @@
       </c>
       <c r="D108" s="4" t="inlineStr">
         <is>
-          <t>Share of Turnover-based KPI Exposed towards Fossil Gas Activities in Percent - Aligned</t>
+          <t>Share of Turnover-based KPI Exposed towards Nuclear Activities in Percent - Aligned</t>
         </is>
       </c>
       <c r="E108" s="4" t="inlineStr">
         <is>
-          <t>IR_TURNOVER_BASED_GAS_PCT_ALIGNED</t>
+          <t>IR_TURNOVER_BASED_NUCLEAR_PCT_ALIGNED</t>
         </is>
       </c>
       <c r="F108" s="4" t="inlineStr">
         <is>
-          <t>Taxonomy-aligned Proportion of Turnover-based KPI exposed towards Fossil Gas Activities</t>
+          <t>Taxonomy-aligned Proportion of Turnover-based KPI exposed towards Nuclear Activities</t>
         </is>
       </c>
       <c r="G108" s="4" t="inlineStr">
@@ -6858,17 +6850,17 @@
       </c>
       <c r="D109" s="4" t="inlineStr">
         <is>
-          <t>Share of Turnover-based KPI in Percent - Of which Transitional</t>
+          <t>Share of Turnover-based KPI Exposed towards Fossil Gas Activities in Percent - Aligned</t>
         </is>
       </c>
       <c r="E109" s="4" t="inlineStr">
         <is>
-          <t>IR_TURNOVER_BASED_PCT_TRANSITIONAL</t>
+          <t>IR_TURNOVER_BASED_GAS_PCT_ALIGNED</t>
         </is>
       </c>
       <c r="F109" s="4" t="inlineStr">
         <is>
-          <t>Taxonomy-aligned and Transitional Proportion of Turnover-based KPI</t>
+          <t>Taxonomy-aligned Proportion of Turnover-based KPI exposed towards Fossil Gas Activities</t>
         </is>
       </c>
       <c r="G109" s="4" t="inlineStr">
@@ -6896,7 +6888,7 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="P109" s="4" t="n"/>
+      <c r="P109" s="4" t="inlineStr"/>
     </row>
     <row r="110">
       <c r="A110" s="2" t="inlineStr">
@@ -6916,17 +6908,17 @@
       </c>
       <c r="D110" s="4" t="inlineStr">
         <is>
-          <t>Share of Turnover-based KPI in Percent - Of which Enabling</t>
+          <t>Share of Turnover-based KPI in Percent - Of which Transitional</t>
         </is>
       </c>
       <c r="E110" s="4" t="inlineStr">
         <is>
-          <t>IR_TURNOVER_BASED_PCT_ENABLING</t>
+          <t>IR_TURNOVER_BASED_PCT_TRANSITIONAL</t>
         </is>
       </c>
       <c r="F110" s="4" t="inlineStr">
         <is>
-          <t>Taxonomy-aligned and Enabling Proportion of Turnover-based KPI</t>
+          <t>Taxonomy-aligned and Transitional Proportion of Turnover-based KPI</t>
         </is>
       </c>
       <c r="G110" s="4" t="inlineStr">
@@ -6954,7 +6946,7 @@
           <t>Yes</t>
         </is>
       </c>
-      <c r="P110" s="4" t="inlineStr"/>
+      <c r="P110" s="4" t="n"/>
     </row>
     <row r="111">
       <c r="A111" s="2" t="inlineStr">
@@ -6974,17 +6966,17 @@
       </c>
       <c r="D111" s="4" t="inlineStr">
         <is>
-          <t>Turnover-based Non-Assessed Exposures</t>
+          <t>Share of Turnover-based KPI in Percent - Of which Enabling</t>
         </is>
       </c>
       <c r="E111" s="4" t="inlineStr">
         <is>
-          <t>IR_TURNOVER_BASED_PCT_NON_ASSESSED</t>
+          <t>IR_TURNOVER_BASED_PCT_ENABLING</t>
         </is>
       </c>
       <c r="F111" s="4" t="inlineStr">
         <is>
-          <t>Proportion of Turnover-based KPI of which non-assessed exposures</t>
+          <t>Taxonomy-aligned and Enabling Proportion of Turnover-based KPI</t>
         </is>
       </c>
       <c r="G111" s="4" t="inlineStr">
@@ -7032,17 +7024,17 @@
       </c>
       <c r="D112" s="4" t="inlineStr">
         <is>
-          <t>Turnover-based Non-Assessed Exposures - Of which Exposures Financing Non-Assessed Non-Material Activities of Counterparties</t>
+          <t>Turnover-based Non-Assessed Exposures</t>
         </is>
       </c>
       <c r="E112" s="4" t="inlineStr">
         <is>
-          <t>IR_TURNOVER_BASED_PCT_NON_ASSESSED_NON_MATERIAL_CP</t>
+          <t>IR_TURNOVER_BASED_PCT_NON_ASSESSED</t>
         </is>
       </c>
       <c r="F112" s="4" t="inlineStr">
         <is>
-          <t>Proportion of Turnover-based KPI of which exposures financing non-assessed non-material activities of counterparties</t>
+          <t>Proportion of Turnover-based KPI of which non-assessed exposures</t>
         </is>
       </c>
       <c r="G112" s="4" t="inlineStr">
@@ -7090,17 +7082,17 @@
       </c>
       <c r="D113" s="4" t="inlineStr">
         <is>
-          <t>Turnover-based Non-Assessed Exposures - Of which Non-Assessed Exposures Considered Non-Material by the Reporting Entity</t>
+          <t>Turnover-based Non-Assessed Exposures - Of which Exposures Financing Non-Assessed Non-Material Activities of Counterparties</t>
         </is>
       </c>
       <c r="E113" s="4" t="inlineStr">
         <is>
-          <t>IR_TURNOVER_BASED_PCT_NON_ASSESSED_NON_MATERIAL_RE</t>
+          <t>IR_TURNOVER_BASED_PCT_NON_ASSESSED_NON_MATERIAL_CP</t>
         </is>
       </c>
       <c r="F113" s="4" t="inlineStr">
         <is>
-          <t>Proportion of Turnover-based KPI of which non-assessed exposures considered non-material by the reporting entity</t>
+          <t>Proportion of Turnover-based KPI of which exposures financing non-assessed non-material activities of counterparties</t>
         </is>
       </c>
       <c r="G113" s="4" t="inlineStr">
@@ -7148,17 +7140,17 @@
       </c>
       <c r="D114" s="4" t="inlineStr">
         <is>
-          <t>Turnover-based Non-Assessed Exposures - Of which Exposures Financing Counterparties Reporting no Taxonomy-eligible Activities</t>
+          <t>Turnover-based Non-Assessed Exposures - Of which Non-Assessed Exposures Considered Non-Material by the Reporting Entity</t>
         </is>
       </c>
       <c r="E114" s="4" t="inlineStr">
         <is>
-          <t>IR_TURNOVER_BASED_PCT_NON_ASSESSED_NO_ELIGIBLE_CP</t>
+          <t>IR_TURNOVER_BASED_PCT_NON_ASSESSED_NON_MATERIAL_RE</t>
         </is>
       </c>
       <c r="F114" s="4" t="inlineStr">
         <is>
-          <t>Proportion of Turnover-based KPI of which exposures financing counterparties reporting in accordance with Article 7(9) of Regulation (EU) 2026/73</t>
+          <t>Proportion of Turnover-based KPI of which non-assessed exposures considered non-material by the reporting entity</t>
         </is>
       </c>
       <c r="G114" s="4" t="inlineStr">
@@ -7201,22 +7193,22 @@
       </c>
       <c r="C115" s="3" t="inlineStr">
         <is>
-          <t>Breakdown of the Numerator of the KPI per Environmental Objective - Turnover-based</t>
+          <t>Breakdown of the Numerator of the KPI - Turnover-based</t>
         </is>
       </c>
       <c r="D115" s="4" t="inlineStr">
         <is>
-          <t>Share of Turnover-based KPI substantially contributing to Climate Change Mitigation in Percent - Aligned</t>
+          <t>Turnover-based Non-Assessed Exposures - Of which Exposures Financing Counterparties Reporting no Taxonomy-eligible Activities</t>
         </is>
       </c>
       <c r="E115" s="4" t="inlineStr">
         <is>
-          <t>IR_TURNOVER_BASED_SC_TO_CCM_PCT_ALIGNED</t>
+          <t>IR_TURNOVER_BASED_PCT_NON_ASSESSED_NO_ELIGIBLE_CP</t>
         </is>
       </c>
       <c r="F115" s="4" t="inlineStr">
         <is>
-          <t>Taxonomy-aligned Proportion of Turnover-based KPI substantially contributing to Climate Change Mitigation - provided 'do-not-significant harm' (DNSH) and social safeguards positive assessment</t>
+          <t>Proportion of Turnover-based KPI of which exposures financing counterparties reporting in accordance with Article 7(9) of Regulation (EU) 2026/73</t>
         </is>
       </c>
       <c r="G115" s="4" t="inlineStr">
@@ -7264,17 +7256,17 @@
       </c>
       <c r="D116" s="4" t="inlineStr">
         <is>
-          <t>Share of Turnover-based KPI substantially contributing to Climate Change Adaptation in Percent - Aligned</t>
+          <t>Share of Turnover-based KPI substantially contributing to Climate Change Mitigation in Percent - Aligned</t>
         </is>
       </c>
       <c r="E116" s="4" t="inlineStr">
         <is>
-          <t>IR_TURNOVER_BASED_SC_TO_CCA_PCT_ALIGNED</t>
+          <t>IR_TURNOVER_BASED_SC_TO_CCM_PCT_ALIGNED</t>
         </is>
       </c>
       <c r="F116" s="4" t="inlineStr">
         <is>
-          <t>Taxonomy-aligned Proportion of Turnover-based KPI substantially contributing to Climate Change Adaptation - provided 'do-not-significant harm' (DNSH) and social safeguards positive assessment</t>
+          <t>Taxonomy-aligned Proportion of Turnover-based KPI substantially contributing to Climate Change Mitigation - provided 'do-not-significant harm' (DNSH) and social safeguards positive assessment</t>
         </is>
       </c>
       <c r="G116" s="4" t="inlineStr">
@@ -7322,17 +7314,17 @@
       </c>
       <c r="D117" s="4" t="inlineStr">
         <is>
-          <t>Share of Turnover-based KPI substantially contributing to Sustainable Use and Protection of Water and Marine Resources in Percent - Aligned</t>
+          <t>Share of Turnover-based KPI substantially contributing to Climate Change Adaptation in Percent - Aligned</t>
         </is>
       </c>
       <c r="E117" s="4" t="inlineStr">
         <is>
-          <t>IR_TURNOVER_BASED_SC_TO_WTR_PCT_ALIGNED</t>
+          <t>IR_TURNOVER_BASED_SC_TO_CCA_PCT_ALIGNED</t>
         </is>
       </c>
       <c r="F117" s="4" t="inlineStr">
         <is>
-          <t>Taxonomy-aligned Proportion of Turnover-based KPI substantially contributing to Sustainable Use and Protection of Water and Marine Resources - provided 'do-not-significant harm' (DNSH) and social safeguards positive assessment</t>
+          <t>Taxonomy-aligned Proportion of Turnover-based KPI substantially contributing to Climate Change Adaptation - provided 'do-not-significant harm' (DNSH) and social safeguards positive assessment</t>
         </is>
       </c>
       <c r="G117" s="4" t="inlineStr">
@@ -7380,17 +7372,17 @@
       </c>
       <c r="D118" s="4" t="inlineStr">
         <is>
-          <t>Share of Turnover-based KPI substantially contributing to Transition to a Circular Economy in Percent - Aligned</t>
+          <t>Share of Turnover-based KPI substantially contributing to Sustainable Use and Protection of Water and Marine Resources in Percent - Aligned</t>
         </is>
       </c>
       <c r="E118" s="4" t="inlineStr">
         <is>
-          <t>IR_TURNOVER_BASED_SC_TO_CE_PCT_ALIGNED</t>
+          <t>IR_TURNOVER_BASED_SC_TO_WTR_PCT_ALIGNED</t>
         </is>
       </c>
       <c r="F118" s="4" t="inlineStr">
         <is>
-          <t>Taxonomy-aligned Proportion of Turnover-based KPI substantially contributing to Circular Economy - provided 'do-not-significant harm' (DNSH) and social safeguards positive assessment</t>
+          <t>Taxonomy-aligned Proportion of Turnover-based KPI substantially contributing to Sustainable Use and Protection of Water and Marine Resources - provided 'do-not-significant harm' (DNSH) and social safeguards positive assessment</t>
         </is>
       </c>
       <c r="G118" s="4" t="inlineStr">
@@ -7438,17 +7430,17 @@
       </c>
       <c r="D119" s="4" t="inlineStr">
         <is>
-          <t>Share of Turnover-based KPI substantially contributing to Pollution Prevention and Control in Percent - Aligned</t>
+          <t>Share of Turnover-based KPI substantially contributing to Transition to a Circular Economy in Percent - Aligned</t>
         </is>
       </c>
       <c r="E119" s="4" t="inlineStr">
         <is>
-          <t>IR_TURNOVER_BASED_SC_TO_PPC_PCT_ALIGNED</t>
+          <t>IR_TURNOVER_BASED_SC_TO_CE_PCT_ALIGNED</t>
         </is>
       </c>
       <c r="F119" s="4" t="inlineStr">
         <is>
-          <t>Taxonomy-aligned Proportion of Turnover-based KPI substantially contributing to Pollution Prevention and Control - provided 'do-not-significant harm' (DNSH) and social safeguards positive assessment</t>
+          <t>Taxonomy-aligned Proportion of Turnover-based KPI substantially contributing to Circular Economy - provided 'do-not-significant harm' (DNSH) and social safeguards positive assessment</t>
         </is>
       </c>
       <c r="G119" s="4" t="inlineStr">
@@ -7496,17 +7488,17 @@
       </c>
       <c r="D120" s="4" t="inlineStr">
         <is>
-          <t>Share of Turnover-based KPI substantially contributing to Protection and Restoration of Biodiversity and Ecosystems in Percent - Aligned</t>
+          <t>Share of Turnover-based KPI substantially contributing to Pollution Prevention and Control in Percent - Aligned</t>
         </is>
       </c>
       <c r="E120" s="4" t="inlineStr">
         <is>
-          <t>IR_TURNOVER_BASED_SC_TO_BIO_PCT_ALIGNED</t>
+          <t>IR_TURNOVER_BASED_SC_TO_PPC_PCT_ALIGNED</t>
         </is>
       </c>
       <c r="F120" s="4" t="inlineStr">
         <is>
-          <t>Taxonomy-aligned Proportion of Turnover-based KPI substantially contributing to Protection and Restoration of Biodiversity and Ecosystems - provided 'do-not-significant harm' (DNSH) and social safeguards positive assessment</t>
+          <t>Taxonomy-aligned Proportion of Turnover-based KPI substantially contributing to Pollution Prevention and Control - provided 'do-not-significant harm' (DNSH) and social safeguards positive assessment</t>
         </is>
       </c>
       <c r="G120" s="4" t="inlineStr">
@@ -7549,22 +7541,22 @@
       </c>
       <c r="C121" s="3" t="inlineStr">
         <is>
-          <t>Breakdown of the Numerator of the KPI - CapEx-based</t>
+          <t>Breakdown of the Numerator of the KPI per Environmental Objective - Turnover-based</t>
         </is>
       </c>
       <c r="D121" s="4" t="inlineStr">
         <is>
-          <t>Share of CapEx-based KPI in Percent - Eligible</t>
+          <t>Share of Turnover-based KPI substantially contributing to Protection and Restoration of Biodiversity and Ecosystems in Percent - Aligned</t>
         </is>
       </c>
       <c r="E121" s="4" t="inlineStr">
         <is>
-          <t>IR_CAPEX_BASED_PCT_ELIGIBLE</t>
+          <t>IR_TURNOVER_BASED_SC_TO_BIO_PCT_ALIGNED</t>
         </is>
       </c>
       <c r="F121" s="4" t="inlineStr">
         <is>
-          <t>Taxonomy-eligible Proportion of CapEx-based KPI</t>
+          <t>Taxonomy-aligned Proportion of Turnover-based KPI substantially contributing to Protection and Restoration of Biodiversity and Ecosystems - provided 'do-not-significant harm' (DNSH) and social safeguards positive assessment</t>
         </is>
       </c>
       <c r="G121" s="4" t="inlineStr">
@@ -7612,17 +7604,17 @@
       </c>
       <c r="D122" s="4" t="inlineStr">
         <is>
-          <t>Share of CapEx-based KPI Exposed towards Nuclear Activities in Percent - Eligible</t>
+          <t>Share of CapEx-based KPI in Percent - Eligible</t>
         </is>
       </c>
       <c r="E122" s="4" t="inlineStr">
         <is>
-          <t>IR_CAPEX_BASED_NUCLEAR_PCT_ELIGIBLE</t>
+          <t>IR_CAPEX_BASED_PCT_ELIGIBLE</t>
         </is>
       </c>
       <c r="F122" s="4" t="inlineStr">
         <is>
-          <t>Taxonomy-eligible Proportion of CapEx-based KPI exposed towards Nuclear Activities</t>
+          <t>Taxonomy-eligible Proportion of CapEx-based KPI</t>
         </is>
       </c>
       <c r="G122" s="4" t="inlineStr">
@@ -7670,17 +7662,17 @@
       </c>
       <c r="D123" s="4" t="inlineStr">
         <is>
-          <t>Share of CapEx-based KPI Exposed towards Fossil Gas Activities in Percent - Eligible</t>
+          <t>Share of CapEx-based KPI Exposed towards Nuclear Activities in Percent - Eligible</t>
         </is>
       </c>
       <c r="E123" s="4" t="inlineStr">
         <is>
-          <t>IR_CAPEX_BASED_GAS_PCT_ELIGIBLE</t>
+          <t>IR_CAPEX_BASED_NUCLEAR_PCT_ELIGIBLE</t>
         </is>
       </c>
       <c r="F123" s="4" t="inlineStr">
         <is>
-          <t>Taxonomy-eligible Proportion of CapEx-based KPI exposed towards Fossil Gas Activities</t>
+          <t>Taxonomy-eligible Proportion of CapEx-based KPI exposed towards Nuclear Activities</t>
         </is>
       </c>
       <c r="G123" s="4" t="inlineStr">
@@ -7728,17 +7720,17 @@
       </c>
       <c r="D124" s="4" t="inlineStr">
         <is>
-          <t>Share of CapEx-based KPI in Percent - Aligned</t>
+          <t>Share of CapEx-based KPI Exposed towards Fossil Gas Activities in Percent - Eligible</t>
         </is>
       </c>
       <c r="E124" s="4" t="inlineStr">
         <is>
-          <t>IR_CAPEX_BASED_PCT_ALIGNED</t>
+          <t>IR_CAPEX_BASED_GAS_PCT_ELIGIBLE</t>
         </is>
       </c>
       <c r="F124" s="4" t="inlineStr">
         <is>
-          <t>Taxonomy-aligned Proportion of CapEx-based KPI</t>
+          <t>Taxonomy-eligible Proportion of CapEx-based KPI exposed towards Fossil Gas Activities</t>
         </is>
       </c>
       <c r="G124" s="4" t="inlineStr">
@@ -7786,17 +7778,17 @@
       </c>
       <c r="D125" s="4" t="inlineStr">
         <is>
-          <t>Share of CapEx-based KPI Exposed towards Nuclear Activities in Percent - Aligned</t>
+          <t>Share of CapEx-based KPI in Percent - Aligned</t>
         </is>
       </c>
       <c r="E125" s="4" t="inlineStr">
         <is>
-          <t>IR_CAPEX_BASED_NUCLEAR_PCT_ALIGNED</t>
+          <t>IR_CAPEX_BASED_PCT_ALIGNED</t>
         </is>
       </c>
       <c r="F125" s="4" t="inlineStr">
         <is>
-          <t>Taxonomy-aligned Proportion of CapEx-based KPI exposed towards Nuclear Activities</t>
+          <t>Taxonomy-aligned Proportion of CapEx-based KPI</t>
         </is>
       </c>
       <c r="G125" s="4" t="inlineStr">
@@ -7844,17 +7836,17 @@
       </c>
       <c r="D126" s="4" t="inlineStr">
         <is>
-          <t>Share of CapEx-based KPI Exposed towards Fossil Gas Activities in Percent - Aligned</t>
+          <t>Share of CapEx-based KPI Exposed towards Nuclear Activities in Percent - Aligned</t>
         </is>
       </c>
       <c r="E126" s="4" t="inlineStr">
         <is>
-          <t>IR_CAPEX_BASED_GAS_PCT_ALIGNED</t>
+          <t>IR_CAPEX_BASED_NUCLEAR_PCT_ALIGNED</t>
         </is>
       </c>
       <c r="F126" s="4" t="inlineStr">
         <is>
-          <t>Taxonomy-aligned Proportion of CapEx-based KPI exposed towards Fossil Gas Activities</t>
+          <t>Taxonomy-aligned Proportion of CapEx-based KPI exposed towards Nuclear Activities</t>
         </is>
       </c>
       <c r="G126" s="4" t="inlineStr">
@@ -7902,17 +7894,17 @@
       </c>
       <c r="D127" s="4" t="inlineStr">
         <is>
-          <t>Share of CapEx-based KPI in Percent - Of which Transitional</t>
+          <t>Share of CapEx-based KPI Exposed towards Fossil Gas Activities in Percent - Aligned</t>
         </is>
       </c>
       <c r="E127" s="4" t="inlineStr">
         <is>
-          <t>IR_CAPEX_BASED_PCT_TRANSITIONAL</t>
+          <t>IR_CAPEX_BASED_GAS_PCT_ALIGNED</t>
         </is>
       </c>
       <c r="F127" s="4" t="inlineStr">
         <is>
-          <t>Taxonomy-aligned and Transitional Proportion of CapEx-based KPI</t>
+          <t>Taxonomy-aligned Proportion of CapEx-based KPI exposed towards Fossil Gas Activities</t>
         </is>
       </c>
       <c r="G127" s="4" t="inlineStr">
@@ -7960,17 +7952,17 @@
       </c>
       <c r="D128" s="4" t="inlineStr">
         <is>
-          <t>Share of CapEx-based KPI in Percent - Of which Enabling</t>
+          <t>Share of CapEx-based KPI in Percent - Of which Transitional</t>
         </is>
       </c>
       <c r="E128" s="4" t="inlineStr">
         <is>
-          <t>IR_CAPEX_BASED_PCT_ENABLING</t>
+          <t>IR_CAPEX_BASED_PCT_TRANSITIONAL</t>
         </is>
       </c>
       <c r="F128" s="4" t="inlineStr">
         <is>
-          <t>Taxonomy-aligned and Enabling Proportion of CapEx-based KPI</t>
+          <t>Taxonomy-aligned and Transitional Proportion of CapEx-based KPI</t>
         </is>
       </c>
       <c r="G128" s="4" t="inlineStr">
@@ -8018,17 +8010,17 @@
       </c>
       <c r="D129" s="4" t="inlineStr">
         <is>
-          <t>CapEx-based Non-Assessed Exposures</t>
+          <t>Share of CapEx-based KPI in Percent - Of which Enabling</t>
         </is>
       </c>
       <c r="E129" s="4" t="inlineStr">
         <is>
-          <t>IR_CAPEX_BASED_PCT_NON_ASSESSED</t>
+          <t>IR_CAPEX_BASED_PCT_ENABLING</t>
         </is>
       </c>
       <c r="F129" s="4" t="inlineStr">
         <is>
-          <t>Proportion of CapEx-based KPI of which non-assessed exposures</t>
+          <t>Taxonomy-aligned and Enabling Proportion of CapEx-based KPI</t>
         </is>
       </c>
       <c r="G129" s="4" t="inlineStr">
@@ -8076,17 +8068,17 @@
       </c>
       <c r="D130" s="4" t="inlineStr">
         <is>
-          <t>CapEx-based Non-Assessed Exposures - Of which Exposures Financing Non-Assessed Non-Material Activities of Counterparties</t>
+          <t>CapEx-based Non-Assessed Exposures</t>
         </is>
       </c>
       <c r="E130" s="4" t="inlineStr">
         <is>
-          <t>IR_CAPEX_BASED_PCT_NON_ASSESSED_NON_MATERIAL_CP</t>
+          <t>IR_CAPEX_BASED_PCT_NON_ASSESSED</t>
         </is>
       </c>
       <c r="F130" s="4" t="inlineStr">
         <is>
-          <t>Proportion of CapEx-based KPI of which exposures financing non-assessed non-material activities of counterparties</t>
+          <t>Proportion of CapEx-based KPI of which non-assessed exposures</t>
         </is>
       </c>
       <c r="G130" s="4" t="inlineStr">
@@ -8134,17 +8126,17 @@
       </c>
       <c r="D131" s="4" t="inlineStr">
         <is>
-          <t>CapEx-based Non-Assessed Exposures - Of which Non-Assessed Exposures Considered Non-Material by the Reporting Entity</t>
+          <t>CapEx-based Non-Assessed Exposures - Of which Exposures Financing Non-Assessed Non-Material Activities of Counterparties</t>
         </is>
       </c>
       <c r="E131" s="4" t="inlineStr">
         <is>
-          <t>IR_CAPEX_BASED_PCT_NON_ASSESSED_NON_MATERIAL_RE</t>
+          <t>IR_CAPEX_BASED_PCT_NON_ASSESSED_NON_MATERIAL_CP</t>
         </is>
       </c>
       <c r="F131" s="4" t="inlineStr">
         <is>
-          <t>Proportion of CapEx-based KPI of which non-assessed exposures considered non-material by the reporting entity</t>
+          <t>Proportion of CapEx-based KPI of which exposures financing non-assessed non-material activities of counterparties</t>
         </is>
       </c>
       <c r="G131" s="4" t="inlineStr">
@@ -8192,17 +8184,17 @@
       </c>
       <c r="D132" s="4" t="inlineStr">
         <is>
-          <t>CapEx-based Non-Assessed Exposures - Of which Exposures to Counterparties Reporting no Taxonomy-eligible Activities</t>
+          <t>CapEx-based Non-Assessed Exposures - Of which Non-Assessed Exposures Considered Non-Material by the Reporting Entity</t>
         </is>
       </c>
       <c r="E132" s="4" t="inlineStr">
         <is>
-          <t>IR_CAPEX_BASED_PCT_NON_ASSESSED_NO_ELIGIBLE_CP</t>
+          <t>IR_CAPEX_BASED_PCT_NON_ASSESSED_NON_MATERIAL_RE</t>
         </is>
       </c>
       <c r="F132" s="4" t="inlineStr">
         <is>
-          <t>Proportion of CapEx-based KPI of which exposures to counterparties reporting in accordance with Article 7(9) of Regulation (EU) 2026/73</t>
+          <t>Proportion of CapEx-based KPI of which non-assessed exposures considered non-material by the reporting entity</t>
         </is>
       </c>
       <c r="G132" s="4" t="inlineStr">
@@ -8245,22 +8237,22 @@
       </c>
       <c r="C133" s="3" t="inlineStr">
         <is>
-          <t>Breakdown of the Numerator of the KPI per Environmental Objective - CapEx-based</t>
+          <t>Breakdown of the Numerator of the KPI - CapEx-based</t>
         </is>
       </c>
       <c r="D133" s="4" t="inlineStr">
         <is>
-          <t>Share of CapEx-based KPI substantially contributing to Climate Change Mitigation in Percent - Aligned</t>
+          <t>CapEx-based Non-Assessed Exposures - Of which Exposures to Counterparties Reporting no Taxonomy-eligible Activities</t>
         </is>
       </c>
       <c r="E133" s="4" t="inlineStr">
         <is>
-          <t>IR_CAPEX_BASED_SC_TO_CCM_PCT_ALIGNED</t>
+          <t>IR_CAPEX_BASED_PCT_NON_ASSESSED_NO_ELIGIBLE_CP</t>
         </is>
       </c>
       <c r="F133" s="4" t="inlineStr">
         <is>
-          <t>Taxonomy-aligned Proportion of CapEx-based KPI substantially contributing to Climate Change Mitigation - provided 'do-not-significant harm' (DNSH) and social safeguards positive assessment</t>
+          <t>Proportion of CapEx-based KPI of which exposures to counterparties reporting in accordance with Article 7(9) of Regulation (EU) 2026/73</t>
         </is>
       </c>
       <c r="G133" s="4" t="inlineStr">
@@ -8308,17 +8300,17 @@
       </c>
       <c r="D134" s="4" t="inlineStr">
         <is>
-          <t>Share of CapEx-based KPI substantially contributing to Climate Change Adaptation in Percent - Aligned</t>
+          <t>Share of CapEx-based KPI substantially contributing to Climate Change Mitigation in Percent - Aligned</t>
         </is>
       </c>
       <c r="E134" s="4" t="inlineStr">
         <is>
-          <t>IR_CAPEX_BASED_SC_TO_CCA_PCT_ALIGNED</t>
+          <t>IR_CAPEX_BASED_SC_TO_CCM_PCT_ALIGNED</t>
         </is>
       </c>
       <c r="F134" s="4" t="inlineStr">
         <is>
-          <t>Taxonomy-aligned Proportion of CapEx-based KPI substantially contributing to Climate Change Adaptation - provided 'do-not-significant harm' (DNSH) and social safeguards positive assessment</t>
+          <t>Taxonomy-aligned Proportion of CapEx-based KPI substantially contributing to Climate Change Mitigation - provided 'do-not-significant harm' (DNSH) and social safeguards positive assessment</t>
         </is>
       </c>
       <c r="G134" s="4" t="inlineStr">
@@ -8366,17 +8358,17 @@
       </c>
       <c r="D135" s="4" t="inlineStr">
         <is>
-          <t>Share of CapEx-based KPI substantially contributing to Sustainable Use and Protection of Water and Marine Resources in Percent - Aligned</t>
+          <t>Share of CapEx-based KPI substantially contributing to Climate Change Adaptation in Percent - Aligned</t>
         </is>
       </c>
       <c r="E135" s="4" t="inlineStr">
         <is>
-          <t>IR_CAPEX_BASED_SC_TO_WTR_PCT_ALIGNED</t>
+          <t>IR_CAPEX_BASED_SC_TO_CCA_PCT_ALIGNED</t>
         </is>
       </c>
       <c r="F135" s="4" t="inlineStr">
         <is>
-          <t>Taxonomy-aligned Proportion of CapEx-based KPI substantially contributing to Sustainable Use and Protection of Water and Marine Resources - provided 'do-not-significant harm' (DNSH) and social safeguards positive assessment</t>
+          <t>Taxonomy-aligned Proportion of CapEx-based KPI substantially contributing to Climate Change Adaptation - provided 'do-not-significant harm' (DNSH) and social safeguards positive assessment</t>
         </is>
       </c>
       <c r="G135" s="4" t="inlineStr">
@@ -8424,17 +8416,17 @@
       </c>
       <c r="D136" s="4" t="inlineStr">
         <is>
-          <t>Share of CapEx-based KPI substantially contributing to Transition to a Circular Economy in Percent - Aligned</t>
+          <t>Share of CapEx-based KPI substantially contributing to Sustainable Use and Protection of Water and Marine Resources in Percent - Aligned</t>
         </is>
       </c>
       <c r="E136" s="4" t="inlineStr">
         <is>
-          <t>IR_CAPEX_BASED_SC_TO_CE_PCT_ALIGNED</t>
+          <t>IR_CAPEX_BASED_SC_TO_WTR_PCT_ALIGNED</t>
         </is>
       </c>
       <c r="F136" s="4" t="inlineStr">
         <is>
-          <t>Taxonomy-aligned Proportion of CapEx-based KPI substantially contributing to Circular Economy - provided 'do-not-significant harm' (DNSH) and social safeguards positive assessment</t>
+          <t>Taxonomy-aligned Proportion of CapEx-based KPI substantially contributing to Sustainable Use and Protection of Water and Marine Resources - provided 'do-not-significant harm' (DNSH) and social safeguards positive assessment</t>
         </is>
       </c>
       <c r="G136" s="4" t="inlineStr">
@@ -8482,17 +8474,17 @@
       </c>
       <c r="D137" s="4" t="inlineStr">
         <is>
-          <t>Share of CapEx-based KPI substantially contributing to Pollution Prevention and Control in Percent - Aligned</t>
+          <t>Share of CapEx-based KPI substantially contributing to Transition to a Circular Economy in Percent - Aligned</t>
         </is>
       </c>
       <c r="E137" s="4" t="inlineStr">
         <is>
-          <t>IR_CAPEX_BASED_SC_TO_PPC_PCT_ALIGNED</t>
+          <t>IR_CAPEX_BASED_SC_TO_CE_PCT_ALIGNED</t>
         </is>
       </c>
       <c r="F137" s="4" t="inlineStr">
         <is>
-          <t>Taxonomy-aligned Proportion of CapEx-based KPI substantially contributing to Pollution Prevention and Control - provided 'do-not-significant harm' (DNSH) and social safeguards positive assessment</t>
+          <t>Taxonomy-aligned Proportion of CapEx-based KPI substantially contributing to Circular Economy - provided 'do-not-significant harm' (DNSH) and social safeguards positive assessment</t>
         </is>
       </c>
       <c r="G137" s="4" t="inlineStr">
@@ -8540,17 +8532,17 @@
       </c>
       <c r="D138" s="4" t="inlineStr">
         <is>
-          <t>Share of CapEx-based KPI substantially contributing to Protection and Restoration of Biodiversity and Ecosystems in Percent - Aligned</t>
+          <t>Share of CapEx-based KPI substantially contributing to Pollution Prevention and Control in Percent - Aligned</t>
         </is>
       </c>
       <c r="E138" s="4" t="inlineStr">
         <is>
-          <t>IR_CAPEX_BASED_SC_TO_BIO_PCT_ALIGNED</t>
+          <t>IR_CAPEX_BASED_SC_TO_PPC_PCT_ALIGNED</t>
         </is>
       </c>
       <c r="F138" s="4" t="inlineStr">
         <is>
-          <t>Taxonomy-aligned Proportion of CapEx-based KPI substantially contributing to Protection and Restoration of Biodiversity and Ecosystems - provided 'do-not-significant harm' (DNSH) and social safeguards positive assessment</t>
+          <t>Taxonomy-aligned Proportion of CapEx-based KPI substantially contributing to Pollution Prevention and Control - provided 'do-not-significant harm' (DNSH) and social safeguards positive assessment</t>
         </is>
       </c>
       <c r="G138" s="4" t="inlineStr">
@@ -8588,39 +8580,35 @@
       </c>
       <c r="B139" s="3" t="inlineStr">
         <is>
-          <t>Investment firms</t>
+          <t>Insurance/Reinsurance</t>
         </is>
       </c>
       <c r="C139" s="3" t="inlineStr">
         <is>
-          <t>Dealing on own Account Services - Turnover-based</t>
+          <t>Breakdown of the Numerator of the KPI per Environmental Objective - CapEx-based</t>
         </is>
       </c>
       <c r="D139" s="4" t="inlineStr">
         <is>
-          <t>Turnover-based Total Assets invested under Investment Firm's Activities dealing on own Account</t>
+          <t>Share of CapEx-based KPI substantially contributing to Protection and Restoration of Biodiversity and Ecosystems in Percent - Aligned</t>
         </is>
       </c>
       <c r="E139" s="4" t="inlineStr">
         <is>
-          <t>IF_OWN_ACCOUNT_TURNOVER_BASED_TOTAL_ASSETS</t>
+          <t>IR_CAPEX_BASED_SC_TO_BIO_PCT_ALIGNED</t>
         </is>
       </c>
       <c r="F139" s="4" t="inlineStr">
         <is>
-          <t>Total assets invested under investment firms' activities dealing on own account (as per Section A of Annex I to Directive 2014/65/EU)</t>
+          <t>Taxonomy-aligned Proportion of CapEx-based KPI substantially contributing to Protection and Restoration of Biodiversity and Ecosystems - provided 'do-not-significant harm' (DNSH) and social safeguards positive assessment</t>
         </is>
       </c>
       <c r="G139" s="4" t="inlineStr">
         <is>
-          <t>Currency</t>
-        </is>
-      </c>
-      <c r="H139" s="4" t="inlineStr">
-        <is>
-          <t>Allowed Range: [0, INF]</t>
-        </is>
-      </c>
+          <t>Percentage</t>
+        </is>
+      </c>
+      <c r="H139" s="4" t="inlineStr"/>
       <c r="I139" s="4" t="inlineStr"/>
       <c r="J139" s="4" t="inlineStr">
         <is>
@@ -8660,17 +8648,17 @@
       </c>
       <c r="D140" s="4" t="inlineStr">
         <is>
-          <t>Turnover-based Total Assets invested under Investment Firm's Activities dealing on own Account of which covered by the Turnover</t>
+          <t>Turnover-based Total Assets invested under Investment Firm's Activities dealing on own Account</t>
         </is>
       </c>
       <c r="E140" s="4" t="inlineStr">
         <is>
-          <t>IF_OWN_ACCOUNT_TURNOVER_BASED_COVERED_ASSETS</t>
+          <t>IF_OWN_ACCOUNT_TURNOVER_BASED_TOTAL_ASSETS</t>
         </is>
       </c>
       <c r="F140" s="4" t="inlineStr">
         <is>
-          <t>Total assets invested under investment firms' activities dealing on own account (as per Section A of Annex I to Directive 2014/65/EU) of which covered by the Turnover</t>
+          <t>Total assets invested under investment firms' activities dealing on own account (as per Section A of Annex I to Directive 2014/65/EU)</t>
         </is>
       </c>
       <c r="G140" s="4" t="inlineStr">
@@ -8722,25 +8710,29 @@
       </c>
       <c r="D141" s="4" t="inlineStr">
         <is>
-          <t>Turnover-based Proportion of Assets substantially contributing to Climate Change Mitigation - Aligned</t>
+          <t>Turnover-based Total Assets invested under Investment Firm's Activities dealing on own Account of which covered by the Turnover</t>
         </is>
       </c>
       <c r="E141" s="4" t="inlineStr">
         <is>
-          <t>IF_OWN_ACCOUNT_TURNOVER_BASED_SC_TO_CCM_ALIGNED</t>
+          <t>IF_OWN_ACCOUNT_TURNOVER_BASED_COVERED_ASSETS</t>
         </is>
       </c>
       <c r="F141" s="4" t="inlineStr">
         <is>
-          <t>Taxonomy-aligned Turnover-based Proportion of Total Assets invested under Investment Firms' Activities dealing on own Account (as per Section A of Annex I to Directive 2014/65/EU) substantially contributing to Climate Change Mitigation</t>
+          <t>Total assets invested under investment firms' activities dealing on own account (as per Section A of Annex I to Directive 2014/65/EU) of which covered by the Turnover</t>
         </is>
       </c>
       <c r="G141" s="4" t="inlineStr">
         <is>
-          <t>Percentage</t>
-        </is>
-      </c>
-      <c r="H141" s="4" t="inlineStr"/>
+          <t>Currency</t>
+        </is>
+      </c>
+      <c r="H141" s="4" t="inlineStr">
+        <is>
+          <t>Allowed Range: [0, INF]</t>
+        </is>
+      </c>
       <c r="I141" s="4" t="inlineStr"/>
       <c r="J141" s="4" t="inlineStr">
         <is>
@@ -8780,17 +8772,17 @@
       </c>
       <c r="D142" s="4" t="inlineStr">
         <is>
-          <t>Turnover-based Proportion of Assets substantially contributing to Climate Change Adaptation - Aligned</t>
+          <t>Turnover-based Proportion of Assets substantially contributing to Climate Change Mitigation - Aligned</t>
         </is>
       </c>
       <c r="E142" s="4" t="inlineStr">
         <is>
-          <t>IF_OWN_ACCOUNT_TURNOVER_BASED_SC_TO_CCA_ALIGNED</t>
+          <t>IF_OWN_ACCOUNT_TURNOVER_BASED_SC_TO_CCM_ALIGNED</t>
         </is>
       </c>
       <c r="F142" s="4" t="inlineStr">
         <is>
-          <t>Taxonomy-aligned Turnover-based Proportion of Total Assets invested under Investment Firms' Activities dealing on own Account (as per Section A of Annex I to Directive 2014/65/EU) substantially contributing to Climate Change Adaptation</t>
+          <t>Taxonomy-aligned Turnover-based Proportion of Total Assets invested under Investment Firms' Activities dealing on own Account (as per Section A of Annex I to Directive 2014/65/EU) substantially contributing to Climate Change Mitigation</t>
         </is>
       </c>
       <c r="G142" s="4" t="inlineStr">
@@ -8838,17 +8830,17 @@
       </c>
       <c r="D143" s="4" t="inlineStr">
         <is>
-          <t>Turnover-based Proportion of Assets substantially contributing to Sustainable Use and Protection of Water and Marine Resources - Aligned</t>
+          <t>Turnover-based Proportion of Assets substantially contributing to Climate Change Adaptation - Aligned</t>
         </is>
       </c>
       <c r="E143" s="4" t="inlineStr">
         <is>
-          <t>IF_OWN_ACCOUNT_TURNOVER_BASED_SC_TO_WTR_ALIGNED</t>
+          <t>IF_OWN_ACCOUNT_TURNOVER_BASED_SC_TO_CCA_ALIGNED</t>
         </is>
       </c>
       <c r="F143" s="4" t="inlineStr">
         <is>
-          <t>Taxonomy-aligned Turnover-based Proportion of Total Assets invested under Investment Firms' Activities dealing on own Account (as per Section A of Annex I to Directive 2014/65/EU) substantially contributing to Sustainable Use and Protection of Water and Marine Resources</t>
+          <t>Taxonomy-aligned Turnover-based Proportion of Total Assets invested under Investment Firms' Activities dealing on own Account (as per Section A of Annex I to Directive 2014/65/EU) substantially contributing to Climate Change Adaptation</t>
         </is>
       </c>
       <c r="G143" s="4" t="inlineStr">
@@ -8896,17 +8888,17 @@
       </c>
       <c r="D144" s="4" t="inlineStr">
         <is>
-          <t>Turnover-based Proportion of Assets substantially contributing to Circular Economy - Aligned</t>
+          <t>Turnover-based Proportion of Assets substantially contributing to Sustainable Use and Protection of Water and Marine Resources - Aligned</t>
         </is>
       </c>
       <c r="E144" s="4" t="inlineStr">
         <is>
-          <t>IF_OWN_ACCOUNT_TURNOVER_BASED_SC_TO_CE_ALIGNED</t>
+          <t>IF_OWN_ACCOUNT_TURNOVER_BASED_SC_TO_WTR_ALIGNED</t>
         </is>
       </c>
       <c r="F144" s="4" t="inlineStr">
         <is>
-          <t>Taxonomy-aligned Turnover-based Proportion of Total Assets invested under Investment Firms' Activities dealing on own Account (as per Section A of Annex I to Directive 2014/65/EU) substantially contributing to Circular Economy</t>
+          <t>Taxonomy-aligned Turnover-based Proportion of Total Assets invested under Investment Firms' Activities dealing on own Account (as per Section A of Annex I to Directive 2014/65/EU) substantially contributing to Sustainable Use and Protection of Water and Marine Resources</t>
         </is>
       </c>
       <c r="G144" s="4" t="inlineStr">
@@ -8954,17 +8946,17 @@
       </c>
       <c r="D145" s="4" t="inlineStr">
         <is>
-          <t>Turnover-based Proportion of Assets substantially contributing to Pollution Prevention and Control - Aligned</t>
+          <t>Turnover-based Proportion of Assets substantially contributing to Circular Economy - Aligned</t>
         </is>
       </c>
       <c r="E145" s="4" t="inlineStr">
         <is>
-          <t>IF_OWN_ACCOUNT_TURNOVER_BASED_SC_TO_PPC_ALIGNED</t>
+          <t>IF_OWN_ACCOUNT_TURNOVER_BASED_SC_TO_CE_ALIGNED</t>
         </is>
       </c>
       <c r="F145" s="4" t="inlineStr">
         <is>
-          <t>Taxonomy-aligned Turnover-based Proportion of Total Assets invested under Investment Firms' Activities dealing on own Account (as per Section A of Annex I to Directive 2014/65/EU) substantially contributing to Pollution Prevention and Control</t>
+          <t>Taxonomy-aligned Turnover-based Proportion of Total Assets invested under Investment Firms' Activities dealing on own Account (as per Section A of Annex I to Directive 2014/65/EU) substantially contributing to Circular Economy</t>
         </is>
       </c>
       <c r="G145" s="4" t="inlineStr">
@@ -9012,17 +9004,17 @@
       </c>
       <c r="D146" s="4" t="inlineStr">
         <is>
-          <t>Turnover-based Proportion of Assets substantially contributing to Protection and Restoration of Biodiversity and Ecosystems - Aligned</t>
+          <t>Turnover-based Proportion of Assets substantially contributing to Pollution Prevention and Control - Aligned</t>
         </is>
       </c>
       <c r="E146" s="4" t="inlineStr">
         <is>
-          <t>IF_OWN_ACCOUNT_TURNOVER_BASED_SC_TO_BIO_ALIGNED</t>
+          <t>IF_OWN_ACCOUNT_TURNOVER_BASED_SC_TO_PPC_ALIGNED</t>
         </is>
       </c>
       <c r="F146" s="4" t="inlineStr">
         <is>
-          <t>Taxonomy-aligned Turnover-based Proportion of Total Assets invested under Investment Firms' Activities dealing on own Account (as per Section A of Annex I to Directive 2014/65/EU) substantially contributing to Protection and Restoration of Biodiversity and Ecosystems</t>
+          <t>Taxonomy-aligned Turnover-based Proportion of Total Assets invested under Investment Firms' Activities dealing on own Account (as per Section A of Annex I to Directive 2014/65/EU) substantially contributing to Pollution Prevention and Control</t>
         </is>
       </c>
       <c r="G146" s="4" t="inlineStr">
@@ -9070,17 +9062,17 @@
       </c>
       <c r="D147" s="4" t="inlineStr">
         <is>
-          <t>Turnover-based Proportion of Assets substantially contributing to any of the six Environmental Objectives - Eligible</t>
+          <t>Turnover-based Proportion of Assets substantially contributing to Protection and Restoration of Biodiversity and Ecosystems - Aligned</t>
         </is>
       </c>
       <c r="E147" s="4" t="inlineStr">
         <is>
-          <t>IF_OWN_ACCOUNT_TURNOVER_BASED_SC_TO_ANY_ELIGIBLE</t>
+          <t>IF_OWN_ACCOUNT_TURNOVER_BASED_SC_TO_BIO_ALIGNED</t>
         </is>
       </c>
       <c r="F147" s="4" t="inlineStr">
         <is>
-          <t>Taxonomy-aligned Turnover-based Proportion of Total Assets invested under Investment Firms' Activities dealing on own Account (as per Section A of Annex I to Directive 2014/65/EU) substantially contributing to any of the six Environmental Objectives</t>
+          <t>Taxonomy-aligned Turnover-based Proportion of Total Assets invested under Investment Firms' Activities dealing on own Account (as per Section A of Annex I to Directive 2014/65/EU) substantially contributing to Protection and Restoration of Biodiversity and Ecosystems</t>
         </is>
       </c>
       <c r="G147" s="4" t="inlineStr">
@@ -9128,12 +9120,12 @@
       </c>
       <c r="D148" s="4" t="inlineStr">
         <is>
-          <t>Turnover-based Proportion of Assets substantially contributing to any of the six Environmental Objectives - Aligned</t>
+          <t>Turnover-based Proportion of Assets substantially contributing to any of the six Environmental Objectives - Eligible</t>
         </is>
       </c>
       <c r="E148" s="4" t="inlineStr">
         <is>
-          <t>IF_OWN_ACCOUNT_TURNOVER_BASED_SC_TO_ANY_ALIGNED</t>
+          <t>IF_OWN_ACCOUNT_TURNOVER_BASED_SC_TO_ANY_ELIGIBLE</t>
         </is>
       </c>
       <c r="F148" s="4" t="inlineStr">
@@ -9186,17 +9178,17 @@
       </c>
       <c r="D149" s="4" t="inlineStr">
         <is>
-          <t>Turnover-based Proportion of Assets substantially contributing to any of the six Environmental Objectives - Of which Transitional</t>
+          <t>Turnover-based Proportion of Assets substantially contributing to any of the six Environmental Objectives - Aligned</t>
         </is>
       </c>
       <c r="E149" s="4" t="inlineStr">
         <is>
-          <t>IF_OWN_ACCOUNT_TURNOVER_BASED_SC_TO_ANY_TRANSITIONAL</t>
+          <t>IF_OWN_ACCOUNT_TURNOVER_BASED_SC_TO_ANY_ALIGNED</t>
         </is>
       </c>
       <c r="F149" s="4" t="inlineStr">
         <is>
-          <t>Taxonomy-aligned and transitional Turnover-based Proportion of Total Assets invested under Investment Firms' Activities dealing on own Account (as per Section A of Annex I to Directive 2014/65/EU) substantially contributing to any of the six Environmental Objectives</t>
+          <t>Taxonomy-aligned Turnover-based Proportion of Total Assets invested under Investment Firms' Activities dealing on own Account (as per Section A of Annex I to Directive 2014/65/EU) substantially contributing to any of the six Environmental Objectives</t>
         </is>
       </c>
       <c r="G149" s="4" t="inlineStr">
@@ -9244,17 +9236,17 @@
       </c>
       <c r="D150" s="4" t="inlineStr">
         <is>
-          <t>Turnover-based Proportion of Assets substantially contributing to any of the six Environmental Objectives - Of which Enabling</t>
+          <t>Turnover-based Proportion of Assets substantially contributing to any of the six Environmental Objectives - Of which Transitional</t>
         </is>
       </c>
       <c r="E150" s="4" t="inlineStr">
         <is>
-          <t>IF_OWN_ACCOUNT_TURNOVER_BASED_SC_TO_ANY_ENABLING</t>
+          <t>IF_OWN_ACCOUNT_TURNOVER_BASED_SC_TO_ANY_TRANSITIONAL</t>
         </is>
       </c>
       <c r="F150" s="4" t="inlineStr">
         <is>
-          <t>Taxonomy-aligned and enabling Turnover-based Proportion of Total Assets invested under Investment Firms' Activities dealing on own Account (as per Section A of Annex I to Directive 2014/65/EU) substantially contributing to any of the six Environmental Objectives</t>
+          <t>Taxonomy-aligned and transitional Turnover-based Proportion of Total Assets invested under Investment Firms' Activities dealing on own Account (as per Section A of Annex I to Directive 2014/65/EU) substantially contributing to any of the six Environmental Objectives</t>
         </is>
       </c>
       <c r="G150" s="4" t="inlineStr">
@@ -9302,17 +9294,17 @@
       </c>
       <c r="D151" s="4" t="inlineStr">
         <is>
-          <t>Turnover-based Non-Assessed Exposures</t>
+          <t>Turnover-based Proportion of Assets substantially contributing to any of the six Environmental Objectives - Of which Enabling</t>
         </is>
       </c>
       <c r="E151" s="4" t="inlineStr">
         <is>
-          <t>IF_OWN_ACCOUNT_TURNOVER_BASED_PCT_NON_ASSESSED</t>
+          <t>IF_OWN_ACCOUNT_TURNOVER_BASED_SC_TO_ANY_ENABLING</t>
         </is>
       </c>
       <c r="F151" s="4" t="inlineStr">
         <is>
-          <t>Turnover-based Proportion of Total Assets invested under Investment Firms' Activities dealing on own Account (as per Section A of Annex I to Directive 2014/65/EU) of which Non-Assessed Exposures</t>
+          <t>Taxonomy-aligned and enabling Turnover-based Proportion of Total Assets invested under Investment Firms' Activities dealing on own Account (as per Section A of Annex I to Directive 2014/65/EU) substantially contributing to any of the six Environmental Objectives</t>
         </is>
       </c>
       <c r="G151" s="4" t="inlineStr">
@@ -9360,17 +9352,17 @@
       </c>
       <c r="D152" s="4" t="inlineStr">
         <is>
-          <t>Turnover-based Non-Assessed Exposures - Of which Exposures Financing Non-Assessed Non-Material Activities of Counterparties</t>
+          <t>Turnover-based Non-Assessed Exposures</t>
         </is>
       </c>
       <c r="E152" s="4" t="inlineStr">
         <is>
-          <t>IF_OWN_ACCOUNT_TURNOVER_BASED_PCT_NON_ASSESSED_NON_MATERIAL_CP</t>
+          <t>IF_OWN_ACCOUNT_TURNOVER_BASED_PCT_NON_ASSESSED</t>
         </is>
       </c>
       <c r="F152" s="4" t="inlineStr">
         <is>
-          <t>Turnover-based Proportion of Total Assets invested under Investment Firms' Activities dealing on own Account (as per Section A of Annex I to Directive 2014/65/EU) of which Exposures Financing Non-Assessed Non-Material Activities of Counterparties</t>
+          <t>Turnover-based Proportion of Total Assets invested under Investment Firms' Activities dealing on own Account (as per Section A of Annex I to Directive 2014/65/EU) of which Non-Assessed Exposures</t>
         </is>
       </c>
       <c r="G152" s="4" t="inlineStr">
@@ -9418,17 +9410,17 @@
       </c>
       <c r="D153" s="4" t="inlineStr">
         <is>
-          <t>Turnover-based Non-Assessed Exposures - Of which Exposures Financing Counterparties Reporting no Taxonomy-eligible Activities</t>
+          <t>Turnover-based Non-Assessed Exposures - Of which Exposures Financing Non-Assessed Non-Material Activities of Counterparties</t>
         </is>
       </c>
       <c r="E153" s="4" t="inlineStr">
         <is>
-          <t>IF_OWN_ACCOUNT_TURNOVER_BASED_PCT_NON_ASSESSED_NO_ELIGIBLE_CP</t>
+          <t>IF_OWN_ACCOUNT_TURNOVER_BASED_PCT_NON_ASSESSED_NON_MATERIAL_CP</t>
         </is>
       </c>
       <c r="F153" s="4" t="inlineStr">
         <is>
-          <t>Turnover-based Proportion of Total Assets invested under Investment Firms' Activities dealing on own Account (as per Section A of Annex I to Directive 2014/65/EU) of which exposures financing counterparties reporting in accordance with Article 7(9) of Regulation (EU) 2026/73</t>
+          <t>Turnover-based Proportion of Total Assets invested under Investment Firms' Activities dealing on own Account (as per Section A of Annex I to Directive 2014/65/EU) of which Exposures Financing Non-Assessed Non-Material Activities of Counterparties</t>
         </is>
       </c>
       <c r="G153" s="4" t="inlineStr">
@@ -9476,17 +9468,17 @@
       </c>
       <c r="D154" s="4" t="inlineStr">
         <is>
-          <t>Turnover-based Non-Assessed Exposures - Of which Non-Assessed Exposures Considered Non-Material by the Reporting Entity</t>
+          <t>Turnover-based Non-Assessed Exposures - Of which Exposures Financing Counterparties Reporting no Taxonomy-eligible Activities</t>
         </is>
       </c>
       <c r="E154" s="4" t="inlineStr">
         <is>
-          <t>IF_OWN_ACCOUNT_TURNOVER_BASED_PCT_NON_ASSESSED_NON_MATERIAL_RE</t>
+          <t>IF_OWN_ACCOUNT_TURNOVER_BASED_PCT_NON_ASSESSED_NO_ELIGIBLE_CP</t>
         </is>
       </c>
       <c r="F154" s="4" t="inlineStr">
         <is>
-          <t>Turnover-based Proportion of Total Assets invested under Investment Firms' Activities dealing on own Account (as per Section A of Annex I to Directive 2014/65/EU) of which Non-Assessed Exposures Considered Non-Material by the Reporting Entity</t>
+          <t>Turnover-based Proportion of Total Assets invested under Investment Firms' Activities dealing on own Account (as per Section A of Annex I to Directive 2014/65/EU) of which exposures financing counterparties reporting in accordance with Article 7(9) of Regulation (EU) 2026/73</t>
         </is>
       </c>
       <c r="G154" s="4" t="inlineStr">
@@ -9534,17 +9526,17 @@
       </c>
       <c r="D155" s="4" t="inlineStr">
         <is>
-          <t>Turnover-based Proportion of Assets Exposed towards Nuclear Activities - Eligible</t>
+          <t>Turnover-based Non-Assessed Exposures - Of which Non-Assessed Exposures Considered Non-Material by the Reporting Entity</t>
         </is>
       </c>
       <c r="E155" s="4" t="inlineStr">
         <is>
-          <t>IF_OWN_ACCOUNT_TURNOVER_BASED_NUCLEAR_PCT_ELIGIBLE</t>
+          <t>IF_OWN_ACCOUNT_TURNOVER_BASED_PCT_NON_ASSESSED_NON_MATERIAL_RE</t>
         </is>
       </c>
       <c r="F155" s="4" t="inlineStr">
         <is>
-          <t>Taxonomy-eligible Turnover-based Proportion of Total Assets invested under Investment Firms' Activities dealing on own Account (as per Section A of Annex I to Directive 2014/65/EU) which are exposed towards Nuclear Activities</t>
+          <t>Turnover-based Proportion of Total Assets invested under Investment Firms' Activities dealing on own Account (as per Section A of Annex I to Directive 2014/65/EU) of which Non-Assessed Exposures Considered Non-Material by the Reporting Entity</t>
         </is>
       </c>
       <c r="G155" s="4" t="inlineStr">
@@ -9592,17 +9584,17 @@
       </c>
       <c r="D156" s="4" t="inlineStr">
         <is>
-          <t>Turnover-based Proportion of Assets Exposed towards Fossil Gas Activities - Eligible</t>
+          <t>Turnover-based Proportion of Assets Exposed towards Nuclear Activities - Eligible</t>
         </is>
       </c>
       <c r="E156" s="4" t="inlineStr">
         <is>
-          <t>IF_OWN_ACCOUNT_TURNOVER_BASED_GAS_PCT_ELIGIBLE</t>
+          <t>IF_OWN_ACCOUNT_TURNOVER_BASED_NUCLEAR_PCT_ELIGIBLE</t>
         </is>
       </c>
       <c r="F156" s="4" t="inlineStr">
         <is>
-          <t>Taxonomy-eligible Turnover-based Proportion of Total Assets invested under Investment Firms' Activities dealing on own Account (as per Section A of Annex I to Directive 2014/65/EU) which are exposed towards Fossil Gas Activities</t>
+          <t>Taxonomy-eligible Turnover-based Proportion of Total Assets invested under Investment Firms' Activities dealing on own Account (as per Section A of Annex I to Directive 2014/65/EU) which are exposed towards Nuclear Activities</t>
         </is>
       </c>
       <c r="G156" s="4" t="inlineStr">
@@ -9650,17 +9642,17 @@
       </c>
       <c r="D157" s="4" t="inlineStr">
         <is>
-          <t>Turnover-based Proportion of Assets Exposed towards Nuclear Activities - Aligned</t>
+          <t>Turnover-based Proportion of Assets Exposed towards Fossil Gas Activities - Eligible</t>
         </is>
       </c>
       <c r="E157" s="4" t="inlineStr">
         <is>
-          <t>IF_OWN_ACCOUNT_TURNOVER_BASED_NUCLEAR_PCT_ALIGNED</t>
+          <t>IF_OWN_ACCOUNT_TURNOVER_BASED_GAS_PCT_ELIGIBLE</t>
         </is>
       </c>
       <c r="F157" s="4" t="inlineStr">
         <is>
-          <t>Taxonomy-aligned Turnover-based Proportion of Total Assets invested under Investment Firms' Activities dealing on own Account (as per Section A of Annex I to Directive 2014/65/EU) which are exposed towards Nuclear Activities</t>
+          <t>Taxonomy-eligible Turnover-based Proportion of Total Assets invested under Investment Firms' Activities dealing on own Account (as per Section A of Annex I to Directive 2014/65/EU) which are exposed towards Fossil Gas Activities</t>
         </is>
       </c>
       <c r="G157" s="4" t="inlineStr">
@@ -9708,17 +9700,17 @@
       </c>
       <c r="D158" s="4" t="inlineStr">
         <is>
-          <t>Turnover-based Proportion of Assets Exposed towards Fossil Gas Activities - Aligned</t>
+          <t>Turnover-based Proportion of Assets Exposed towards Nuclear Activities - Aligned</t>
         </is>
       </c>
       <c r="E158" s="4" t="inlineStr">
         <is>
-          <t>IF_OWN_ACCOUNT_TURNOVER_BASED_GAS_PCT_ALIGNED</t>
+          <t>IF_OWN_ACCOUNT_TURNOVER_BASED_NUCLEAR_PCT_ALIGNED</t>
         </is>
       </c>
       <c r="F158" s="4" t="inlineStr">
         <is>
-          <t>Taxonomy-aligned Turnover-based Proportion of Total Assets invested under Investment Firms' Activities dealing on own Account (as per Section A of Annex I to Directive 2014/65/EU) which are exposed towards Fossil Gas Activities</t>
+          <t>Taxonomy-aligned Turnover-based Proportion of Total Assets invested under Investment Firms' Activities dealing on own Account (as per Section A of Annex I to Directive 2014/65/EU) which are exposed towards Nuclear Activities</t>
         </is>
       </c>
       <c r="G158" s="4" t="inlineStr">
@@ -9761,34 +9753,30 @@
       </c>
       <c r="C159" s="3" t="inlineStr">
         <is>
-          <t>Dealing on own Account Services - CapEx-based</t>
+          <t>Dealing on own Account Services - Turnover-based</t>
         </is>
       </c>
       <c r="D159" s="4" t="inlineStr">
         <is>
-          <t>CapEx-based Total Assets invested under Investment Firm's Activities dealing on own Account</t>
+          <t>Turnover-based Proportion of Assets Exposed towards Fossil Gas Activities - Aligned</t>
         </is>
       </c>
       <c r="E159" s="4" t="inlineStr">
         <is>
-          <t>IF_OWN_ACCOUNT_CAPEX_BASED_TOTAL_ASSETS</t>
+          <t>IF_OWN_ACCOUNT_TURNOVER_BASED_GAS_PCT_ALIGNED</t>
         </is>
       </c>
       <c r="F159" s="4" t="inlineStr">
         <is>
-          <t>Total assets invested under investment firms' activities dealing on own account (as per Section A of Annex I to Directive 2014/65/EU)</t>
+          <t>Taxonomy-aligned Turnover-based Proportion of Total Assets invested under Investment Firms' Activities dealing on own Account (as per Section A of Annex I to Directive 2014/65/EU) which are exposed towards Fossil Gas Activities</t>
         </is>
       </c>
       <c r="G159" s="4" t="inlineStr">
         <is>
-          <t>Currency</t>
-        </is>
-      </c>
-      <c r="H159" s="4" t="inlineStr">
-        <is>
-          <t>Allowed Range: [0, INF]</t>
-        </is>
-      </c>
+          <t>Percentage</t>
+        </is>
+      </c>
+      <c r="H159" s="4" t="inlineStr"/>
       <c r="I159" s="4" t="inlineStr"/>
       <c r="J159" s="4" t="inlineStr">
         <is>
@@ -9828,17 +9816,17 @@
       </c>
       <c r="D160" s="4" t="inlineStr">
         <is>
-          <t>CapEx-based Total Assets invested under Investment Firm's Activities dealing on own Account of which covered by the CapEx</t>
+          <t>CapEx-based Total Assets invested under Investment Firm's Activities dealing on own Account</t>
         </is>
       </c>
       <c r="E160" s="4" t="inlineStr">
         <is>
-          <t>IF_OWN_ACCOUNT_CAPEX_BASED_COVERED_ASSETS</t>
+          <t>IF_OWN_ACCOUNT_CAPEX_BASED_TOTAL_ASSETS</t>
         </is>
       </c>
       <c r="F160" s="4" t="inlineStr">
         <is>
-          <t>Total assets invested under investment firms' activities dealing on own account (as per Section A of Annex I to Directive 2014/65/EU) of which covered by the CapEx</t>
+          <t>Total assets invested under investment firms' activities dealing on own account (as per Section A of Annex I to Directive 2014/65/EU)</t>
         </is>
       </c>
       <c r="G160" s="4" t="inlineStr">
@@ -9890,25 +9878,29 @@
       </c>
       <c r="D161" s="4" t="inlineStr">
         <is>
-          <t>CapEx-based Proportion of Assets substantially contributing to Climate Change Mitigation - Aligned</t>
+          <t>CapEx-based Total Assets invested under Investment Firm's Activities dealing on own Account of which covered by the CapEx</t>
         </is>
       </c>
       <c r="E161" s="4" t="inlineStr">
         <is>
-          <t>IF_OWN_ACCOUNT_CAPEX_BASED_SC_TO_CCM_ALIGNED</t>
+          <t>IF_OWN_ACCOUNT_CAPEX_BASED_COVERED_ASSETS</t>
         </is>
       </c>
       <c r="F161" s="4" t="inlineStr">
         <is>
-          <t>Taxonomy-aligned CapEx-based Proportion of Total Assets invested under Investment Firms' Activities dealing on own Account (as per Section A of Annex I to Directive 2014/65/EU) substantially contributing to Climate Change Mitigation</t>
+          <t>Total assets invested under investment firms' activities dealing on own account (as per Section A of Annex I to Directive 2014/65/EU) of which covered by the CapEx</t>
         </is>
       </c>
       <c r="G161" s="4" t="inlineStr">
         <is>
-          <t>Percentage</t>
-        </is>
-      </c>
-      <c r="H161" s="4" t="inlineStr"/>
+          <t>Currency</t>
+        </is>
+      </c>
+      <c r="H161" s="4" t="inlineStr">
+        <is>
+          <t>Allowed Range: [0, INF]</t>
+        </is>
+      </c>
       <c r="I161" s="4" t="inlineStr"/>
       <c r="J161" s="4" t="inlineStr">
         <is>
@@ -9948,17 +9940,17 @@
       </c>
       <c r="D162" s="4" t="inlineStr">
         <is>
-          <t>CapEx-based Proportion of Assets substantially contributing to Climate Change Adaptation - Aligned</t>
+          <t>CapEx-based Proportion of Assets substantially contributing to Climate Change Mitigation - Aligned</t>
         </is>
       </c>
       <c r="E162" s="4" t="inlineStr">
         <is>
-          <t>IF_OWN_ACCOUNT_CAPEX_BASED_SC_TO_CCA_ALIGNED</t>
+          <t>IF_OWN_ACCOUNT_CAPEX_BASED_SC_TO_CCM_ALIGNED</t>
         </is>
       </c>
       <c r="F162" s="4" t="inlineStr">
         <is>
-          <t>Taxonomy-aligned CapEx-based Proportion of Total Assets invested under Investment Firms' Activities dealing on own Account (as per Section A of Annex I to Directive 2014/65/EU) substantially contributing to Climate Change Adaptation</t>
+          <t>Taxonomy-aligned CapEx-based Proportion of Total Assets invested under Investment Firms' Activities dealing on own Account (as per Section A of Annex I to Directive 2014/65/EU) substantially contributing to Climate Change Mitigation</t>
         </is>
       </c>
       <c r="G162" s="4" t="inlineStr">
@@ -10006,17 +9998,17 @@
       </c>
       <c r="D163" s="4" t="inlineStr">
         <is>
-          <t>CapEx-based Proportion of Assets substantially contributing to Sustainable Use and Protection of Water and Marine Resources - Aligned</t>
+          <t>CapEx-based Proportion of Assets substantially contributing to Climate Change Adaptation - Aligned</t>
         </is>
       </c>
       <c r="E163" s="4" t="inlineStr">
         <is>
-          <t>IF_OWN_ACCOUNT_CAPEX_BASED_SC_TO_WTR_ALIGNED</t>
+          <t>IF_OWN_ACCOUNT_CAPEX_BASED_SC_TO_CCA_ALIGNED</t>
         </is>
       </c>
       <c r="F163" s="4" t="inlineStr">
         <is>
-          <t>Taxonomy-aligned CapEx-based Proportion of Total Assets invested under Investment Firms' Activities dealing on own Account (as per Section A of Annex I to Directive 2014/65/EU) substantially contributing to Sustainable Use and Protection of Water and Marine Resources</t>
+          <t>Taxonomy-aligned CapEx-based Proportion of Total Assets invested under Investment Firms' Activities dealing on own Account (as per Section A of Annex I to Directive 2014/65/EU) substantially contributing to Climate Change Adaptation</t>
         </is>
       </c>
       <c r="G163" s="4" t="inlineStr">
@@ -10064,17 +10056,17 @@
       </c>
       <c r="D164" s="4" t="inlineStr">
         <is>
-          <t>CapEx-based Proportion of Assets substantially contributing to Circular Economy - Aligned</t>
+          <t>CapEx-based Proportion of Assets substantially contributing to Sustainable Use and Protection of Water and Marine Resources - Aligned</t>
         </is>
       </c>
       <c r="E164" s="4" t="inlineStr">
         <is>
-          <t>IF_OWN_ACCOUNT_CAPEX_BASED_SC_TO_CE_ALIGNED</t>
+          <t>IF_OWN_ACCOUNT_CAPEX_BASED_SC_TO_WTR_ALIGNED</t>
         </is>
       </c>
       <c r="F164" s="4" t="inlineStr">
         <is>
-          <t>Taxonomy-aligned CapEx-based Proportion of Total Assets invested under Investment Firms' Activities dealing on own Account (as per Section A of Annex I to Directive 2014/65/EU) substantially contributing to Circular Economy</t>
+          <t>Taxonomy-aligned CapEx-based Proportion of Total Assets invested under Investment Firms' Activities dealing on own Account (as per Section A of Annex I to Directive 2014/65/EU) substantially contributing to Sustainable Use and Protection of Water and Marine Resources</t>
         </is>
       </c>
       <c r="G164" s="4" t="inlineStr">
@@ -10122,17 +10114,17 @@
       </c>
       <c r="D165" s="4" t="inlineStr">
         <is>
-          <t>CapEx-based Proportion of Assets substantially contributing to Pollution Prevention and Control - Aligned</t>
+          <t>CapEx-based Proportion of Assets substantially contributing to Circular Economy - Aligned</t>
         </is>
       </c>
       <c r="E165" s="4" t="inlineStr">
         <is>
-          <t>IF_OWN_ACCOUNT_CAPEX_BASED_SC_TO_PPC_ALIGNED</t>
+          <t>IF_OWN_ACCOUNT_CAPEX_BASED_SC_TO_CE_ALIGNED</t>
         </is>
       </c>
       <c r="F165" s="4" t="inlineStr">
         <is>
-          <t>Taxonomy-aligned CapEx-based Proportion of Total Assets invested under Investment Firms' Activities dealing on own Account (as per Section A of Annex I to Directive 2014/65/EU) substantially contributing to Pollution Prevention and Control</t>
+          <t>Taxonomy-aligned CapEx-based Proportion of Total Assets invested under Investment Firms' Activities dealing on own Account (as per Section A of Annex I to Directive 2014/65/EU) substantially contributing to Circular Economy</t>
         </is>
       </c>
       <c r="G165" s="4" t="inlineStr">
@@ -10180,17 +10172,17 @@
       </c>
       <c r="D166" s="4" t="inlineStr">
         <is>
-          <t>CapEx-based Proportion of Assets substantially contributing to Protection and Restoration of Biodiversity and Ecosystems - Aligned</t>
+          <t>CapEx-based Proportion of Assets substantially contributing to Pollution Prevention and Control - Aligned</t>
         </is>
       </c>
       <c r="E166" s="4" t="inlineStr">
         <is>
-          <t>IF_OWN_ACCOUNT_CAPEX_BASED_SC_TO_BIO_ALIGNED</t>
+          <t>IF_OWN_ACCOUNT_CAPEX_BASED_SC_TO_PPC_ALIGNED</t>
         </is>
       </c>
       <c r="F166" s="4" t="inlineStr">
         <is>
-          <t>Taxonomy-aligned CapEx-based Proportion of Total Assets invested under Investment Firms' Activities dealing on own Account (as per Section A of Annex I to Directive 2014/65/EU) substantially contributing to Protection and Restoration of Biodiversity and Ecosystems</t>
+          <t>Taxonomy-aligned CapEx-based Proportion of Total Assets invested under Investment Firms' Activities dealing on own Account (as per Section A of Annex I to Directive 2014/65/EU) substantially contributing to Pollution Prevention and Control</t>
         </is>
       </c>
       <c r="G166" s="4" t="inlineStr">
@@ -10238,17 +10230,17 @@
       </c>
       <c r="D167" s="4" t="inlineStr">
         <is>
-          <t>CapEx-based Proportion of Assets substantially contributing to any of the six Environmental Objectives - Eligible</t>
+          <t>CapEx-based Proportion of Assets substantially contributing to Protection and Restoration of Biodiversity and Ecosystems - Aligned</t>
         </is>
       </c>
       <c r="E167" s="4" t="inlineStr">
         <is>
-          <t>IF_OWN_ACCOUNT_CAPEX_BASED_SC_TO_ANY_ELIGIBLE</t>
+          <t>IF_OWN_ACCOUNT_CAPEX_BASED_SC_TO_BIO_ALIGNED</t>
         </is>
       </c>
       <c r="F167" s="4" t="inlineStr">
         <is>
-          <t>Taxonomy-aligned CapEx-based Proportion of Total Assets invested under Investment Firms' Activities dealing on own Account (as per Section A of Annex I to Directive 2014/65/EU) substantially contributing to any of the six Environmental Objectives</t>
+          <t>Taxonomy-aligned CapEx-based Proportion of Total Assets invested under Investment Firms' Activities dealing on own Account (as per Section A of Annex I to Directive 2014/65/EU) substantially contributing to Protection and Restoration of Biodiversity and Ecosystems</t>
         </is>
       </c>
       <c r="G167" s="4" t="inlineStr">
@@ -10296,12 +10288,12 @@
       </c>
       <c r="D168" s="4" t="inlineStr">
         <is>
-          <t>CapEx-based Proportion of Assets substantially contributing to any of the six Environmental Objectives - Aligned</t>
+          <t>CapEx-based Proportion of Assets substantially contributing to any of the six Environmental Objectives - Eligible</t>
         </is>
       </c>
       <c r="E168" s="4" t="inlineStr">
         <is>
-          <t>IF_OWN_ACCOUNT_CAPEX_BASED_SC_TO_ANY_ALIGNED</t>
+          <t>IF_OWN_ACCOUNT_CAPEX_BASED_SC_TO_ANY_ELIGIBLE</t>
         </is>
       </c>
       <c r="F168" s="4" t="inlineStr">
@@ -10354,17 +10346,17 @@
       </c>
       <c r="D169" s="4" t="inlineStr">
         <is>
-          <t>CapEx-based Proportion of Assets substantially contributing to any of the six Environmental Objectives - Of which Transitional</t>
+          <t>CapEx-based Proportion of Assets substantially contributing to any of the six Environmental Objectives - Aligned</t>
         </is>
       </c>
       <c r="E169" s="4" t="inlineStr">
         <is>
-          <t>IF_OWN_ACCOUNT_CAPEX_BASED_SC_TO_ANY_TRANSITIONAL</t>
+          <t>IF_OWN_ACCOUNT_CAPEX_BASED_SC_TO_ANY_ALIGNED</t>
         </is>
       </c>
       <c r="F169" s="4" t="inlineStr">
         <is>
-          <t>Taxonomy-aligned and transitional CapEx-based Proportion of Total Assets invested under Investment Firms' Activities dealing on own Account (as per Section A of Annex I to Directive 2014/65/EU) substantially contributing to any of the six Environmental Objectives</t>
+          <t>Taxonomy-aligned CapEx-based Proportion of Total Assets invested under Investment Firms' Activities dealing on own Account (as per Section A of Annex I to Directive 2014/65/EU) substantially contributing to any of the six Environmental Objectives</t>
         </is>
       </c>
       <c r="G169" s="4" t="inlineStr">
@@ -10412,17 +10404,17 @@
       </c>
       <c r="D170" s="4" t="inlineStr">
         <is>
-          <t>CapEx-based Proportion of Assets substantially contributing to any of the six Environmental Objectives - Of which Enabling</t>
+          <t>CapEx-based Proportion of Assets substantially contributing to any of the six Environmental Objectives - Of which Transitional</t>
         </is>
       </c>
       <c r="E170" s="4" t="inlineStr">
         <is>
-          <t>IF_OWN_ACCOUNT_CAPEX_BASED_SC_TO_ANY_ENABLING</t>
+          <t>IF_OWN_ACCOUNT_CAPEX_BASED_SC_TO_ANY_TRANSITIONAL</t>
         </is>
       </c>
       <c r="F170" s="4" t="inlineStr">
         <is>
-          <t>Taxonomy-aligned and enabling CapEx-based Proportion of Total Assets invested under Investment Firms' Activities dealing on own Account (as per Section A of Annex I to Directive 2014/65/EU) substantially contributing to any of the six Environmental Objectives</t>
+          <t>Taxonomy-aligned and transitional CapEx-based Proportion of Total Assets invested under Investment Firms' Activities dealing on own Account (as per Section A of Annex I to Directive 2014/65/EU) substantially contributing to any of the six Environmental Objectives</t>
         </is>
       </c>
       <c r="G170" s="4" t="inlineStr">
@@ -10470,17 +10462,17 @@
       </c>
       <c r="D171" s="4" t="inlineStr">
         <is>
-          <t>CapEx-based Non-Assessed Exposures</t>
+          <t>CapEx-based Proportion of Assets substantially contributing to any of the six Environmental Objectives - Of which Enabling</t>
         </is>
       </c>
       <c r="E171" s="4" t="inlineStr">
         <is>
-          <t>IF_OWN_ACCOUNT_CAPEX_BASED_PCT_NON_ASSESSED</t>
+          <t>IF_OWN_ACCOUNT_CAPEX_BASED_SC_TO_ANY_ENABLING</t>
         </is>
       </c>
       <c r="F171" s="4" t="inlineStr">
         <is>
-          <t>CapEx-based Proportion of Total Assets invested under Investment Firms' Activities dealing on own Account (as per Section A of Annex I to Directive 2014/65/EU) of which Non-Assessed Exposures</t>
+          <t>Taxonomy-aligned and enabling CapEx-based Proportion of Total Assets invested under Investment Firms' Activities dealing on own Account (as per Section A of Annex I to Directive 2014/65/EU) substantially contributing to any of the six Environmental Objectives</t>
         </is>
       </c>
       <c r="G171" s="4" t="inlineStr">
@@ -10528,17 +10520,17 @@
       </c>
       <c r="D172" s="4" t="inlineStr">
         <is>
-          <t>CapEx-based Non-Assessed Exposures - Of which Exposures Financing Non-Assessed Non-Material Activities of Counterparties</t>
+          <t>CapEx-based Non-Assessed Exposures</t>
         </is>
       </c>
       <c r="E172" s="4" t="inlineStr">
         <is>
-          <t>IF_OWN_ACCOUNT_CAPEX_BASED_PCT_NON_ASSESSED_NON_MATERIAL_CP</t>
+          <t>IF_OWN_ACCOUNT_CAPEX_BASED_PCT_NON_ASSESSED</t>
         </is>
       </c>
       <c r="F172" s="4" t="inlineStr">
         <is>
-          <t>CapEx-based Proportion of Total Assets invested under Investment Firms' Activities dealing on own Account (as per Section A of Annex I to Directive 2014/65/EU) of which Exposures Financing Non-Assessed Non-Material Activities of Counterparties</t>
+          <t>CapEx-based Proportion of Total Assets invested under Investment Firms' Activities dealing on own Account (as per Section A of Annex I to Directive 2014/65/EU) of which Non-Assessed Exposures</t>
         </is>
       </c>
       <c r="G172" s="4" t="inlineStr">
@@ -10586,17 +10578,17 @@
       </c>
       <c r="D173" s="4" t="inlineStr">
         <is>
-          <t>CapEx-based Non-Assessed Exposures - Of which Exposures Financing Counterparties Reporting no Taxonomy-eligible Activities</t>
+          <t>CapEx-based Non-Assessed Exposures - Of which Exposures Financing Non-Assessed Non-Material Activities of Counterparties</t>
         </is>
       </c>
       <c r="E173" s="4" t="inlineStr">
         <is>
-          <t>IF_OWN_ACCOUNT_CAPEX_BASED_PCT_NON_ASSESSED_NO_ELIGIBLE_CP</t>
+          <t>IF_OWN_ACCOUNT_CAPEX_BASED_PCT_NON_ASSESSED_NON_MATERIAL_CP</t>
         </is>
       </c>
       <c r="F173" s="4" t="inlineStr">
         <is>
-          <t>CapEx-based Proportion of Total Assets invested under Investment Firms' Activities dealing on own Account (as per Section A of Annex I to Directive 2014/65/EU) of which exposures financing counterparties reporting in accordance with Article 7(9) of Regulation (EU) 2026/73</t>
+          <t>CapEx-based Proportion of Total Assets invested under Investment Firms' Activities dealing on own Account (as per Section A of Annex I to Directive 2014/65/EU) of which Exposures Financing Non-Assessed Non-Material Activities of Counterparties</t>
         </is>
       </c>
       <c r="G173" s="4" t="inlineStr">
@@ -10644,17 +10636,17 @@
       </c>
       <c r="D174" s="4" t="inlineStr">
         <is>
-          <t>CapEx-based Non-Assessed Exposures - Of which Non-Assessed Exposures Considered Non-Material by the Reporting Entity</t>
+          <t>CapEx-based Non-Assessed Exposures - Of which Exposures Financing Counterparties Reporting no Taxonomy-eligible Activities</t>
         </is>
       </c>
       <c r="E174" s="4" t="inlineStr">
         <is>
-          <t>IF_OWN_ACCOUNT_CAPEX_BASED_PCT_NON_ASSESSED_NON_MATERIAL_RE</t>
+          <t>IF_OWN_ACCOUNT_CAPEX_BASED_PCT_NON_ASSESSED_NO_ELIGIBLE_CP</t>
         </is>
       </c>
       <c r="F174" s="4" t="inlineStr">
         <is>
-          <t>CapEx-based Proportion of Total Assets invested under Investment Firms' Activities dealing on own Account (as per Section A of Annex I to Directive 2014/65/EU) of which Non-Assessed Exposures Considered Non-Material by the Reporting Entity</t>
+          <t>CapEx-based Proportion of Total Assets invested under Investment Firms' Activities dealing on own Account (as per Section A of Annex I to Directive 2014/65/EU) of which exposures financing counterparties reporting in accordance with Article 7(9) of Regulation (EU) 2026/73</t>
         </is>
       </c>
       <c r="G174" s="4" t="inlineStr">
@@ -10702,17 +10694,17 @@
       </c>
       <c r="D175" s="4" t="inlineStr">
         <is>
-          <t>CapEx-based Proportion of Assets Exposed towards Nuclear Activities - Eligible</t>
+          <t>CapEx-based Non-Assessed Exposures - Of which Non-Assessed Exposures Considered Non-Material by the Reporting Entity</t>
         </is>
       </c>
       <c r="E175" s="4" t="inlineStr">
         <is>
-          <t>IF_OWN_ACCOUNT_CAPEX_BASED_NUCLEAR_PCT_ELIGIBLE</t>
+          <t>IF_OWN_ACCOUNT_CAPEX_BASED_PCT_NON_ASSESSED_NON_MATERIAL_RE</t>
         </is>
       </c>
       <c r="F175" s="4" t="inlineStr">
         <is>
-          <t>Taxonomy-eligible CapEx-based Proportion of Total Assets invested under Investment Firms' Activities dealing on own Account (as per Section A of Annex I to Directive 2014/65/EU) which are exposed towards Nuclear Activities</t>
+          <t>CapEx-based Proportion of Total Assets invested under Investment Firms' Activities dealing on own Account (as per Section A of Annex I to Directive 2014/65/EU) of which Non-Assessed Exposures Considered Non-Material by the Reporting Entity</t>
         </is>
       </c>
       <c r="G175" s="4" t="inlineStr">
@@ -10760,17 +10752,17 @@
       </c>
       <c r="D176" s="4" t="inlineStr">
         <is>
-          <t>CapEx-based Proportion of Assets Exposed towards Fossil Gas Activities - Eligible</t>
+          <t>CapEx-based Proportion of Assets Exposed towards Nuclear Activities - Eligible</t>
         </is>
       </c>
       <c r="E176" s="4" t="inlineStr">
         <is>
-          <t>IF_OWN_ACCOUNT_CAPEX_BASED_GAS_PCT_ELIGIBLE</t>
+          <t>IF_OWN_ACCOUNT_CAPEX_BASED_NUCLEAR_PCT_ELIGIBLE</t>
         </is>
       </c>
       <c r="F176" s="4" t="inlineStr">
         <is>
-          <t>Taxonomy-eligible CapEx-based Proportion of Total Assets invested under Investment Firms' Activities dealing on own Account (as per Section A of Annex I to Directive 2014/65/EU) which are exposed towards Fossil Gas Activities</t>
+          <t>Taxonomy-eligible CapEx-based Proportion of Total Assets invested under Investment Firms' Activities dealing on own Account (as per Section A of Annex I to Directive 2014/65/EU) which are exposed towards Nuclear Activities</t>
         </is>
       </c>
       <c r="G176" s="4" t="inlineStr">
@@ -10818,17 +10810,17 @@
       </c>
       <c r="D177" s="4" t="inlineStr">
         <is>
-          <t>CapEx-based Proportion of Assets Exposed towards Nuclear Activities - Aligned</t>
+          <t>CapEx-based Proportion of Assets Exposed towards Fossil Gas Activities - Eligible</t>
         </is>
       </c>
       <c r="E177" s="4" t="inlineStr">
         <is>
-          <t>IF_OWN_ACCOUNT_CAPEX_BASED_NUCLEAR_PCT_ALIGNED</t>
+          <t>IF_OWN_ACCOUNT_CAPEX_BASED_GAS_PCT_ELIGIBLE</t>
         </is>
       </c>
       <c r="F177" s="4" t="inlineStr">
         <is>
-          <t>Taxonomy-aligned CapEx-based Proportion of Total Assets invested under Investment Firms' Activities dealing on own Account (as per Section A of Annex I to Directive 2014/65/EU) which are exposed towards Nuclear Activities</t>
+          <t>Taxonomy-eligible CapEx-based Proportion of Total Assets invested under Investment Firms' Activities dealing on own Account (as per Section A of Annex I to Directive 2014/65/EU) which are exposed towards Fossil Gas Activities</t>
         </is>
       </c>
       <c r="G177" s="4" t="inlineStr">
@@ -10876,17 +10868,17 @@
       </c>
       <c r="D178" s="4" t="inlineStr">
         <is>
-          <t>CapEx-based Proportion of Assets Exposed towards Fossil Gas Activities - Aligned</t>
+          <t>CapEx-based Proportion of Assets Exposed towards Nuclear Activities - Aligned</t>
         </is>
       </c>
       <c r="E178" s="4" t="inlineStr">
         <is>
-          <t>IF_OWN_ACCOUNT_CAPEX_BASED_GAS_PCT_ALIGNED</t>
+          <t>IF_OWN_ACCOUNT_CAPEX_BASED_NUCLEAR_PCT_ALIGNED</t>
         </is>
       </c>
       <c r="F178" s="4" t="inlineStr">
         <is>
-          <t>Taxonomy-aligned CapEx-based Proportion of Total Assets invested under Investment Firms' Activities dealing on own Account (as per Section A of Annex I to Directive 2014/65/EU) which are exposed towards Fossil Gas Activities</t>
+          <t>Taxonomy-aligned CapEx-based Proportion of Total Assets invested under Investment Firms' Activities dealing on own Account (as per Section A of Annex I to Directive 2014/65/EU) which are exposed towards Nuclear Activities</t>
         </is>
       </c>
       <c r="G178" s="4" t="inlineStr">
@@ -10929,34 +10921,30 @@
       </c>
       <c r="C179" s="3" t="inlineStr">
         <is>
-          <t>Other Services - Turnover-based</t>
+          <t>Dealing on own Account Services - CapEx-based</t>
         </is>
       </c>
       <c r="D179" s="4" t="inlineStr">
         <is>
-          <t>Turnover-based Total Revenue from Investments and Services and Activities other than Dealing on own Account</t>
+          <t>CapEx-based Proportion of Assets Exposed towards Fossil Gas Activities - Aligned</t>
         </is>
       </c>
       <c r="E179" s="4" t="inlineStr">
         <is>
-          <t>IF_OTHER_TURNOVER_BASED_TOTAL_REVENUE</t>
+          <t>IF_OWN_ACCOUNT_CAPEX_BASED_GAS_PCT_ALIGNED</t>
         </is>
       </c>
       <c r="F179" s="4" t="inlineStr">
         <is>
-          <t>Total Revenue (i.e. fees, commissions and other monetary benefits) from investment and services and activities other than dealing on own account (as per Section A of Annex I to Directive 2014/65/EU)</t>
+          <t>Taxonomy-aligned CapEx-based Proportion of Total Assets invested under Investment Firms' Activities dealing on own Account (as per Section A of Annex I to Directive 2014/65/EU) which are exposed towards Fossil Gas Activities</t>
         </is>
       </c>
       <c r="G179" s="4" t="inlineStr">
         <is>
-          <t>Currency</t>
-        </is>
-      </c>
-      <c r="H179" s="4" t="inlineStr">
-        <is>
-          <t>Allowed Range: [0, INF]</t>
-        </is>
-      </c>
+          <t>Percentage</t>
+        </is>
+      </c>
+      <c r="H179" s="4" t="inlineStr"/>
       <c r="I179" s="4" t="inlineStr"/>
       <c r="J179" s="4" t="inlineStr">
         <is>
@@ -10996,17 +10984,17 @@
       </c>
       <c r="D180" s="4" t="inlineStr">
         <is>
-          <t>Turnover-based Total Revenue from Investments and Services and Activities other than Dealing on own Account of which covered by the Turnover</t>
+          <t>Turnover-based Total Revenue from Investments and Services and Activities other than Dealing on own Account</t>
         </is>
       </c>
       <c r="E180" s="4" t="inlineStr">
         <is>
-          <t>IF_OTHER_TURNOVER_BASED_COVERED_REVENUE</t>
+          <t>IF_OTHER_TURNOVER_BASED_TOTAL_REVENUE</t>
         </is>
       </c>
       <c r="F180" s="4" t="inlineStr">
         <is>
-          <t>Total Revenue (i.e. fees, commissions and other monetary benefits) from investment and services and activities other than dealing on own account (as per Section A of Annex I to Directive 2014/65/EU) of which covered by the Turnover</t>
+          <t>Total Revenue (i.e. fees, commissions and other monetary benefits) from investment and services and activities other than dealing on own account (as per Section A of Annex I to Directive 2014/65/EU)</t>
         </is>
       </c>
       <c r="G180" s="4" t="inlineStr">
@@ -11058,25 +11046,29 @@
       </c>
       <c r="D181" s="4" t="inlineStr">
         <is>
-          <t>Turnover-based Proportion of Revenue substantially contributing to Climate Change Mitigation - Aligned</t>
+          <t>Turnover-based Total Revenue from Investments and Services and Activities other than Dealing on own Account of which covered by the Turnover</t>
         </is>
       </c>
       <c r="E181" s="4" t="inlineStr">
         <is>
-          <t>IF_OTHER_TURNOVER_BASED_SC_TO_CCM_ALIGNED</t>
+          <t>IF_OTHER_TURNOVER_BASED_COVERED_REVENUE</t>
         </is>
       </c>
       <c r="F181" s="4" t="inlineStr">
         <is>
-          <t>Taxonomy-aligned Turnover-based Proportion of Revenue (Fees, Commissions and other Monetary Services) from Investments and Services and Activities substantially contributing to Climate Change Mitigation</t>
+          <t>Total Revenue (i.e. fees, commissions and other monetary benefits) from investment and services and activities other than dealing on own account (as per Section A of Annex I to Directive 2014/65/EU) of which covered by the Turnover</t>
         </is>
       </c>
       <c r="G181" s="4" t="inlineStr">
         <is>
-          <t>Percentage</t>
-        </is>
-      </c>
-      <c r="H181" s="4" t="inlineStr"/>
+          <t>Currency</t>
+        </is>
+      </c>
+      <c r="H181" s="4" t="inlineStr">
+        <is>
+          <t>Allowed Range: [0, INF]</t>
+        </is>
+      </c>
       <c r="I181" s="4" t="inlineStr"/>
       <c r="J181" s="4" t="inlineStr">
         <is>
@@ -11116,17 +11108,17 @@
       </c>
       <c r="D182" s="4" t="inlineStr">
         <is>
-          <t>Turnover-based Proportion of Revenue substantially contributing to Climate Change Adaptation - Aligned</t>
+          <t>Turnover-based Proportion of Revenue substantially contributing to Climate Change Mitigation - Aligned</t>
         </is>
       </c>
       <c r="E182" s="4" t="inlineStr">
         <is>
-          <t>IF_OTHER_TURNOVER_BASED_SC_TO_CCA_ALIGNED</t>
+          <t>IF_OTHER_TURNOVER_BASED_SC_TO_CCM_ALIGNED</t>
         </is>
       </c>
       <c r="F182" s="4" t="inlineStr">
         <is>
-          <t>Taxonomy-aligned Turnover-based Proportion of Revenue (Fees, Commissions and other Monetary Services) from Investments and Services and Activities substantially contributing to Climate Change Adaptation</t>
+          <t>Taxonomy-aligned Turnover-based Proportion of Revenue (Fees, Commissions and other Monetary Services) from Investments and Services and Activities substantially contributing to Climate Change Mitigation</t>
         </is>
       </c>
       <c r="G182" s="4" t="inlineStr">
@@ -11174,17 +11166,17 @@
       </c>
       <c r="D183" s="4" t="inlineStr">
         <is>
-          <t>Turnover-based Proportion of Revenue substantially contributing to Sustainable Use and Protection of Water and Marine Resources - Aligned</t>
+          <t>Turnover-based Proportion of Revenue substantially contributing to Climate Change Adaptation - Aligned</t>
         </is>
       </c>
       <c r="E183" s="4" t="inlineStr">
         <is>
-          <t>IF_OTHER_TURNOVER_BASED_SC_TO_WTR_ALIGNED</t>
+          <t>IF_OTHER_TURNOVER_BASED_SC_TO_CCA_ALIGNED</t>
         </is>
       </c>
       <c r="F183" s="4" t="inlineStr">
         <is>
-          <t>Taxonomy-aligned Turnover-based Proportion of Revenue (Fees, Commissions and other Monetary Services) from Investments and Services and Activities substantially contributing to Sustainable Use and Protection of Water and Marine Resources</t>
+          <t>Taxonomy-aligned Turnover-based Proportion of Revenue (Fees, Commissions and other Monetary Services) from Investments and Services and Activities substantially contributing to Climate Change Adaptation</t>
         </is>
       </c>
       <c r="G183" s="4" t="inlineStr">
@@ -11232,17 +11224,17 @@
       </c>
       <c r="D184" s="4" t="inlineStr">
         <is>
-          <t>Turnover-based Proportion of Revenue substantially contributing to Circular Economy - Aligned</t>
+          <t>Turnover-based Proportion of Revenue substantially contributing to Sustainable Use and Protection of Water and Marine Resources - Aligned</t>
         </is>
       </c>
       <c r="E184" s="4" t="inlineStr">
         <is>
-          <t>IF_OTHER_TURNOVER_BASED_SC_TO_CE_ALIGNED</t>
+          <t>IF_OTHER_TURNOVER_BASED_SC_TO_WTR_ALIGNED</t>
         </is>
       </c>
       <c r="F184" s="4" t="inlineStr">
         <is>
-          <t>Taxonomy-aligned Turnover-based Proportion of Revenue (Fees, Commissions and other Monetary Services) from Investments and Services and Activities substantially contributing to Circular Economy</t>
+          <t>Taxonomy-aligned Turnover-based Proportion of Revenue (Fees, Commissions and other Monetary Services) from Investments and Services and Activities substantially contributing to Sustainable Use and Protection of Water and Marine Resources</t>
         </is>
       </c>
       <c r="G184" s="4" t="inlineStr">
@@ -11290,17 +11282,17 @@
       </c>
       <c r="D185" s="4" t="inlineStr">
         <is>
-          <t>Turnover-based Proportion of Revenue substantially contributing to Pollution Prevention and Control - Aligned</t>
+          <t>Turnover-based Proportion of Revenue substantially contributing to Circular Economy - Aligned</t>
         </is>
       </c>
       <c r="E185" s="4" t="inlineStr">
         <is>
-          <t>IF_OTHER_TURNOVER_BASED_SC_TO_PPC_ALIGNED</t>
+          <t>IF_OTHER_TURNOVER_BASED_SC_TO_CE_ALIGNED</t>
         </is>
       </c>
       <c r="F185" s="4" t="inlineStr">
         <is>
-          <t>Taxonomy-aligned Turnover-based Proportion of Revenue (Fees, Commissions and other Monetary Services) from Investments and Services and Activities substantially contributing to Pollution Prevention and Control</t>
+          <t>Taxonomy-aligned Turnover-based Proportion of Revenue (Fees, Commissions and other Monetary Services) from Investments and Services and Activities substantially contributing to Circular Economy</t>
         </is>
       </c>
       <c r="G185" s="4" t="inlineStr">
@@ -11348,17 +11340,17 @@
       </c>
       <c r="D186" s="4" t="inlineStr">
         <is>
-          <t>Turnover-based Proportion of Revenue substantially contributing to Protection and Restoration of Biodiversity and Ecosystems - Aligned</t>
+          <t>Turnover-based Proportion of Revenue substantially contributing to Pollution Prevention and Control - Aligned</t>
         </is>
       </c>
       <c r="E186" s="4" t="inlineStr">
         <is>
-          <t>IF_OTHER_TURNOVER_BASED_SC_TO_BIO_ALIGNED</t>
+          <t>IF_OTHER_TURNOVER_BASED_SC_TO_PPC_ALIGNED</t>
         </is>
       </c>
       <c r="F186" s="4" t="inlineStr">
         <is>
-          <t>Taxonomy-aligned Turnover-based Proportion of Revenue (Fees, Commissions and other Monetary Services) from Investments and Services and Activities substantially contributing to Protection and Restoration of Biodiversity and Ecosystems</t>
+          <t>Taxonomy-aligned Turnover-based Proportion of Revenue (Fees, Commissions and other Monetary Services) from Investments and Services and Activities substantially contributing to Pollution Prevention and Control</t>
         </is>
       </c>
       <c r="G186" s="4" t="inlineStr">
@@ -11406,17 +11398,17 @@
       </c>
       <c r="D187" s="4" t="inlineStr">
         <is>
-          <t>Turnover-based Proportion of Revenue substantially contributing to any of the six Environmental Objectives - Eligible</t>
+          <t>Turnover-based Proportion of Revenue substantially contributing to Protection and Restoration of Biodiversity and Ecosystems - Aligned</t>
         </is>
       </c>
       <c r="E187" s="4" t="inlineStr">
         <is>
-          <t>IF_OTHER_TURNOVER_BASED_SC_TO_ANY_ELIGIBLE</t>
+          <t>IF_OTHER_TURNOVER_BASED_SC_TO_BIO_ALIGNED</t>
         </is>
       </c>
       <c r="F187" s="4" t="inlineStr">
         <is>
-          <t>Taxonomy-aligned Turnover-based Proportion of Revenue (Fees, Commissions and other Monetary Services) from Investments and Services and Activities substantially contributing to any of the six Environmental Objectives</t>
+          <t>Taxonomy-aligned Turnover-based Proportion of Revenue (Fees, Commissions and other Monetary Services) from Investments and Services and Activities substantially contributing to Protection and Restoration of Biodiversity and Ecosystems</t>
         </is>
       </c>
       <c r="G187" s="4" t="inlineStr">
@@ -11464,12 +11456,12 @@
       </c>
       <c r="D188" s="4" t="inlineStr">
         <is>
-          <t>Turnover-based Proportion of Revenue substantially contributing to any of the six Environmental Objectives - Aligned</t>
+          <t>Turnover-based Proportion of Revenue substantially contributing to any of the six Environmental Objectives - Eligible</t>
         </is>
       </c>
       <c r="E188" s="4" t="inlineStr">
         <is>
-          <t>IF_OTHER_TURNOVER_BASED_SC_TO_ANY_ALIGNED</t>
+          <t>IF_OTHER_TURNOVER_BASED_SC_TO_ANY_ELIGIBLE</t>
         </is>
       </c>
       <c r="F188" s="4" t="inlineStr">
@@ -11522,17 +11514,17 @@
       </c>
       <c r="D189" s="4" t="inlineStr">
         <is>
-          <t>Turnover-based Proportion of Revenue substantially contributing to any of the six Environmental Objectives - Of which Transitional</t>
+          <t>Turnover-based Proportion of Revenue substantially contributing to any of the six Environmental Objectives - Aligned</t>
         </is>
       </c>
       <c r="E189" s="4" t="inlineStr">
         <is>
-          <t>IF_OTHER_TURNOVER_BASED_SC_TO_ANY_TRANSITIONAL</t>
+          <t>IF_OTHER_TURNOVER_BASED_SC_TO_ANY_ALIGNED</t>
         </is>
       </c>
       <c r="F189" s="4" t="inlineStr">
         <is>
-          <t>Taxonomy-aligned and transitional Turnover-based Proportion of Revenue (Fees, Commissions and other Monetary Services) from Investments and Services and Activities substantially contributing to any of the six Environmental Objectives</t>
+          <t>Taxonomy-aligned Turnover-based Proportion of Revenue (Fees, Commissions and other Monetary Services) from Investments and Services and Activities substantially contributing to any of the six Environmental Objectives</t>
         </is>
       </c>
       <c r="G189" s="4" t="inlineStr">
@@ -11580,17 +11572,17 @@
       </c>
       <c r="D190" s="4" t="inlineStr">
         <is>
-          <t>Turnover-based Proportion of Revenue substantially contributing to any of the six Environmental Objectives - Of which Enabling</t>
+          <t>Turnover-based Proportion of Revenue substantially contributing to any of the six Environmental Objectives - Of which Transitional</t>
         </is>
       </c>
       <c r="E190" s="4" t="inlineStr">
         <is>
-          <t>IF_OTHER_TURNOVER_BASED_SC_TO_ANY_ENABLING</t>
+          <t>IF_OTHER_TURNOVER_BASED_SC_TO_ANY_TRANSITIONAL</t>
         </is>
       </c>
       <c r="F190" s="4" t="inlineStr">
         <is>
-          <t>Taxonomy-aligned and enabling Turnover-based Proportion of Revenue (Fees, Commissions and other Monetary Services) from Investments and Services and Activities substantially contributing to any of the six Environmental Objectives</t>
+          <t>Taxonomy-aligned and transitional Turnover-based Proportion of Revenue (Fees, Commissions and other Monetary Services) from Investments and Services and Activities substantially contributing to any of the six Environmental Objectives</t>
         </is>
       </c>
       <c r="G190" s="4" t="inlineStr">
@@ -11638,17 +11630,17 @@
       </c>
       <c r="D191" s="4" t="inlineStr">
         <is>
-          <t>Turnover-based Non-Assessed Exposures</t>
+          <t>Turnover-based Proportion of Revenue substantially contributing to any of the six Environmental Objectives - Of which Enabling</t>
         </is>
       </c>
       <c r="E191" s="4" t="inlineStr">
         <is>
-          <t>IF_OTHER_TURNOVER_BASED_PCT_NON_ASSESSED</t>
+          <t>IF_OTHER_TURNOVER_BASED_SC_TO_ANY_ENABLING</t>
         </is>
       </c>
       <c r="F191" s="4" t="inlineStr">
         <is>
-          <t>Turnover-based Proportion of Revenue (Fees, Commissions and other Monetary Services) from Investments and Services and Activities of which Non-Assessed Exposures</t>
+          <t>Taxonomy-aligned and enabling Turnover-based Proportion of Revenue (Fees, Commissions and other Monetary Services) from Investments and Services and Activities substantially contributing to any of the six Environmental Objectives</t>
         </is>
       </c>
       <c r="G191" s="4" t="inlineStr">
@@ -11696,17 +11688,17 @@
       </c>
       <c r="D192" s="4" t="inlineStr">
         <is>
-          <t>Turnover-based Proportion of Revenue from Operation of an OTF of which Nuclear Activities - Eligible</t>
+          <t>Turnover-based Non-Assessed Exposures</t>
         </is>
       </c>
       <c r="E192" s="4" t="inlineStr">
         <is>
-          <t>IF_OTHER_TURNOVER_BASED_NUCLEAR_PCT_ELIGIBLE</t>
+          <t>IF_OTHER_TURNOVER_BASED_PCT_NON_ASSESSED</t>
         </is>
       </c>
       <c r="F192" s="4" t="inlineStr">
         <is>
-          <t>Taxonomy-eligible Turnover-based Proportion of Revenue from Operation of an OTF which are exposed towards Nuclear Activities</t>
+          <t>Turnover-based Proportion of Revenue (Fees, Commissions and other Monetary Services) from Investments and Services and Activities of which Non-Assessed Exposures</t>
         </is>
       </c>
       <c r="G192" s="4" t="inlineStr">
@@ -11754,17 +11746,17 @@
       </c>
       <c r="D193" s="4" t="inlineStr">
         <is>
-          <t>Turnover-based Proportion of Revenue from Operation of an OTF of which Fossil Gas Activities - Eligible</t>
+          <t>Turnover-based Proportion of Revenue from Operation of an OTF of which Nuclear Activities - Eligible</t>
         </is>
       </c>
       <c r="E193" s="4" t="inlineStr">
         <is>
-          <t>IF_OTHER_TURNOVER_BASED_GAS_PCT_ELIGIBLE</t>
+          <t>IF_OTHER_TURNOVER_BASED_NUCLEAR_PCT_ELIGIBLE</t>
         </is>
       </c>
       <c r="F193" s="4" t="inlineStr">
         <is>
-          <t>Taxonomy-eligible Turnover-based Proportion of Revenue from Operation of an OTF which are exposed towards Fossil Gas Activities</t>
+          <t>Taxonomy-eligible Turnover-based Proportion of Revenue from Operation of an OTF which are exposed towards Nuclear Activities</t>
         </is>
       </c>
       <c r="G193" s="4" t="inlineStr">
@@ -11812,17 +11804,17 @@
       </c>
       <c r="D194" s="4" t="inlineStr">
         <is>
-          <t>Turnover-based Proportion of Revenue from Operation of an OTF of which Nuclear Activities - Aligned</t>
+          <t>Turnover-based Proportion of Revenue from Operation of an OTF of which Fossil Gas Activities - Eligible</t>
         </is>
       </c>
       <c r="E194" s="4" t="inlineStr">
         <is>
-          <t>IF_OTHER_TURNOVER_BASED_NUCLEAR_PCT_ALIGNED</t>
+          <t>IF_OTHER_TURNOVER_BASED_GAS_PCT_ELIGIBLE</t>
         </is>
       </c>
       <c r="F194" s="4" t="inlineStr">
         <is>
-          <t>Taxonomy-aligned Turnover-based Proportion of Revenue from Operation of an OTF which are exposed towards Nuclear Activities</t>
+          <t>Taxonomy-eligible Turnover-based Proportion of Revenue from Operation of an OTF which are exposed towards Fossil Gas Activities</t>
         </is>
       </c>
       <c r="G194" s="4" t="inlineStr">
@@ -11870,17 +11862,17 @@
       </c>
       <c r="D195" s="4" t="inlineStr">
         <is>
-          <t>Turnover-based Proportion of Revenue from Operation of an OTF of which Fossil Gas Activities - Aligned</t>
+          <t>Turnover-based Proportion of Revenue from Operation of an OTF of which Nuclear Activities - Aligned</t>
         </is>
       </c>
       <c r="E195" s="4" t="inlineStr">
         <is>
-          <t>IF_OTHER_TURNOVER_BASED_GAS_PCT_ALIGNED</t>
+          <t>IF_OTHER_TURNOVER_BASED_NUCLEAR_PCT_ALIGNED</t>
         </is>
       </c>
       <c r="F195" s="4" t="inlineStr">
         <is>
-          <t>Taxonomy-aligned Turnover-based Proportion of Revenue from Operation of an OTF which are exposed towards Fossil Gas Activities</t>
+          <t>Taxonomy-aligned Turnover-based Proportion of Revenue from Operation of an OTF which are exposed towards Nuclear Activities</t>
         </is>
       </c>
       <c r="G195" s="4" t="inlineStr">
@@ -11923,34 +11915,30 @@
       </c>
       <c r="C196" s="3" t="inlineStr">
         <is>
-          <t>Other Services - CapEx-based</t>
+          <t>Other Services - Turnover-based</t>
         </is>
       </c>
       <c r="D196" s="4" t="inlineStr">
         <is>
-          <t>CapEx-based Total Revenue from Investments and Services and Activities other than Dealing on own Account</t>
+          <t>Turnover-based Proportion of Revenue from Operation of an OTF of which Fossil Gas Activities - Aligned</t>
         </is>
       </c>
       <c r="E196" s="4" t="inlineStr">
         <is>
-          <t>IF_OTHER_CAPEX_BASED_TOTAL_REVENUE</t>
+          <t>IF_OTHER_TURNOVER_BASED_GAS_PCT_ALIGNED</t>
         </is>
       </c>
       <c r="F196" s="4" t="inlineStr">
         <is>
-          <t>Total assets invested under investment firms' activities Other Services (as per Section A of Annex I to Directive 2014/65/EU)</t>
+          <t>Taxonomy-aligned Turnover-based Proportion of Revenue from Operation of an OTF which are exposed towards Fossil Gas Activities</t>
         </is>
       </c>
       <c r="G196" s="4" t="inlineStr">
         <is>
-          <t>Currency</t>
-        </is>
-      </c>
-      <c r="H196" s="4" t="inlineStr">
-        <is>
-          <t>Allowed Range: [0, INF]</t>
-        </is>
-      </c>
+          <t>Percentage</t>
+        </is>
+      </c>
+      <c r="H196" s="4" t="inlineStr"/>
       <c r="I196" s="4" t="inlineStr"/>
       <c r="J196" s="4" t="inlineStr">
         <is>
@@ -11990,17 +11978,17 @@
       </c>
       <c r="D197" s="4" t="inlineStr">
         <is>
-          <t>CapEx-based Total Revenue from Investments and Services and Activities other than Dealing on own Account of which covered by the CapEx</t>
+          <t>CapEx-based Total Revenue from Investments and Services and Activities other than Dealing on own Account</t>
         </is>
       </c>
       <c r="E197" s="4" t="inlineStr">
         <is>
-          <t>IF_OTHER_CAPEX_BASED_COVERED_REVENUE</t>
+          <t>IF_OTHER_CAPEX_BASED_TOTAL_REVENUE</t>
         </is>
       </c>
       <c r="F197" s="4" t="inlineStr">
         <is>
-          <t>Total Revenue (i.e. fees, commissions and other monetary benefits) from investment and services and activities other than dealing on own account (as per Section A of Annex I to Directive 2014/65/EU) of which covered by the CapEx</t>
+          <t>Total assets invested under investment firms' activities Other Services (as per Section A of Annex I to Directive 2014/65/EU)</t>
         </is>
       </c>
       <c r="G197" s="4" t="inlineStr">
@@ -12052,25 +12040,29 @@
       </c>
       <c r="D198" s="4" t="inlineStr">
         <is>
-          <t>CapEx-based Proportion of Revenue substantially contributing to Climate Change Mitigation - Aligned</t>
+          <t>CapEx-based Total Revenue from Investments and Services and Activities other than Dealing on own Account of which covered by the CapEx</t>
         </is>
       </c>
       <c r="E198" s="4" t="inlineStr">
         <is>
-          <t>IF_OTHER_CAPEX_BASED_SC_TO_CCM_ALIGNED</t>
+          <t>IF_OTHER_CAPEX_BASED_COVERED_REVENUE</t>
         </is>
       </c>
       <c r="F198" s="4" t="inlineStr">
         <is>
-          <t>Taxonomy-aligned CapEx-based Proportion of Revenue (Fees, Commissions and other Monetary Services) from Investments and Services and Activities substantially contributing to Climate Change Mitigation</t>
+          <t>Total Revenue (i.e. fees, commissions and other monetary benefits) from investment and services and activities other than dealing on own account (as per Section A of Annex I to Directive 2014/65/EU) of which covered by the CapEx</t>
         </is>
       </c>
       <c r="G198" s="4" t="inlineStr">
         <is>
-          <t>Percentage</t>
-        </is>
-      </c>
-      <c r="H198" s="4" t="inlineStr"/>
+          <t>Currency</t>
+        </is>
+      </c>
+      <c r="H198" s="4" t="inlineStr">
+        <is>
+          <t>Allowed Range: [0, INF]</t>
+        </is>
+      </c>
       <c r="I198" s="4" t="inlineStr"/>
       <c r="J198" s="4" t="inlineStr">
         <is>
@@ -12110,17 +12102,17 @@
       </c>
       <c r="D199" s="4" t="inlineStr">
         <is>
-          <t>CapEx-based Proportion of Revenue substantially contributing to Climate Change Adaptation - Aligned</t>
+          <t>CapEx-based Proportion of Revenue substantially contributing to Climate Change Mitigation - Aligned</t>
         </is>
       </c>
       <c r="E199" s="4" t="inlineStr">
         <is>
-          <t>IF_OTHER_CAPEX_BASED_SC_TO_CCA_ALIGNED</t>
+          <t>IF_OTHER_CAPEX_BASED_SC_TO_CCM_ALIGNED</t>
         </is>
       </c>
       <c r="F199" s="4" t="inlineStr">
         <is>
-          <t>Taxonomy-aligned CapEx-based Proportion of Revenue (Fees, Commissions and other Monetary Services) from Investments and Services and Activities substantially contributing to Climate Change Adaptation</t>
+          <t>Taxonomy-aligned CapEx-based Proportion of Revenue (Fees, Commissions and other Monetary Services) from Investments and Services and Activities substantially contributing to Climate Change Mitigation</t>
         </is>
       </c>
       <c r="G199" s="4" t="inlineStr">
@@ -12168,17 +12160,17 @@
       </c>
       <c r="D200" s="4" t="inlineStr">
         <is>
-          <t>CapEx-based Proportion of Revenue substantially contributing to Sustainable Use and Protection of Water and Marine Resources - Aligned</t>
+          <t>CapEx-based Proportion of Revenue substantially contributing to Climate Change Adaptation - Aligned</t>
         </is>
       </c>
       <c r="E200" s="4" t="inlineStr">
         <is>
-          <t>IF_OTHER_CAPEX_BASED_SC_TO_WTR_ALIGNED</t>
+          <t>IF_OTHER_CAPEX_BASED_SC_TO_CCA_ALIGNED</t>
         </is>
       </c>
       <c r="F200" s="4" t="inlineStr">
         <is>
-          <t>Taxonomy-aligned CapEx-based Proportion of Revenue (Fees, Commissions and other Monetary Services) from Investments and Services and Activities substantially contributing to Sustainable Use and Protection of Water and Marine Resources</t>
+          <t>Taxonomy-aligned CapEx-based Proportion of Revenue (Fees, Commissions and other Monetary Services) from Investments and Services and Activities substantially contributing to Climate Change Adaptation</t>
         </is>
       </c>
       <c r="G200" s="4" t="inlineStr">
@@ -12226,17 +12218,17 @@
       </c>
       <c r="D201" s="4" t="inlineStr">
         <is>
-          <t>CapEx-based Proportion of Revenue substantially contributing to Circular Economy - Aligned</t>
+          <t>CapEx-based Proportion of Revenue substantially contributing to Sustainable Use and Protection of Water and Marine Resources - Aligned</t>
         </is>
       </c>
       <c r="E201" s="4" t="inlineStr">
         <is>
-          <t>IF_OTHER_CAPEX_BASED_SC_TO_CE_ALIGNED</t>
+          <t>IF_OTHER_CAPEX_BASED_SC_TO_WTR_ALIGNED</t>
         </is>
       </c>
       <c r="F201" s="4" t="inlineStr">
         <is>
-          <t>Taxonomy-aligned CapEx-based Proportion of Revenue (Fees, Commissions and other Monetary Services) from Investments and Services and Activities substantially contributing to Circular Economy</t>
+          <t>Taxonomy-aligned CapEx-based Proportion of Revenue (Fees, Commissions and other Monetary Services) from Investments and Services and Activities substantially contributing to Sustainable Use and Protection of Water and Marine Resources</t>
         </is>
       </c>
       <c r="G201" s="4" t="inlineStr">
@@ -12284,17 +12276,17 @@
       </c>
       <c r="D202" s="4" t="inlineStr">
         <is>
-          <t>CapEx-based Proportion of Revenue substantially contributing to Pollution Prevention and Control - Aligned</t>
+          <t>CapEx-based Proportion of Revenue substantially contributing to Circular Economy - Aligned</t>
         </is>
       </c>
       <c r="E202" s="4" t="inlineStr">
         <is>
-          <t>IF_OTHER_CAPEX_BASED_SC_TO_PPC_ALIGNED</t>
+          <t>IF_OTHER_CAPEX_BASED_SC_TO_CE_ALIGNED</t>
         </is>
       </c>
       <c r="F202" s="4" t="inlineStr">
         <is>
-          <t>Taxonomy-aligned CapEx-based Proportion of Revenue (Fees, Commissions and other Monetary Services) from Investments and Services and Activities substantially contributing to Pollution Prevention and Control</t>
+          <t>Taxonomy-aligned CapEx-based Proportion of Revenue (Fees, Commissions and other Monetary Services) from Investments and Services and Activities substantially contributing to Circular Economy</t>
         </is>
       </c>
       <c r="G202" s="4" t="inlineStr">
@@ -12342,17 +12334,17 @@
       </c>
       <c r="D203" s="4" t="inlineStr">
         <is>
-          <t>CapEx-based Proportion of Revenue substantially contributing to Protection and Restoration of Biodiversity and Ecosystems - Aligned</t>
+          <t>CapEx-based Proportion of Revenue substantially contributing to Pollution Prevention and Control - Aligned</t>
         </is>
       </c>
       <c r="E203" s="4" t="inlineStr">
         <is>
-          <t>IF_OTHER_CAPEX_BASED_SC_TO_BIO_ALIGNED</t>
+          <t>IF_OTHER_CAPEX_BASED_SC_TO_PPC_ALIGNED</t>
         </is>
       </c>
       <c r="F203" s="4" t="inlineStr">
         <is>
-          <t>Taxonomy-aligned CapEx-based Proportion of Revenue (Fees, Commissions and other Monetary Services) from Investments and Services and Activities substantially contributing to Protection and Restoration of Biodiversity and Ecosystems</t>
+          <t>Taxonomy-aligned CapEx-based Proportion of Revenue (Fees, Commissions and other Monetary Services) from Investments and Services and Activities substantially contributing to Pollution Prevention and Control</t>
         </is>
       </c>
       <c r="G203" s="4" t="inlineStr">
@@ -12400,17 +12392,17 @@
       </c>
       <c r="D204" s="4" t="inlineStr">
         <is>
-          <t>CapEx-based Proportion of Revenue substantially contributing to any of the six Environmental Objectives - Eligible</t>
+          <t>CapEx-based Proportion of Revenue substantially contributing to Protection and Restoration of Biodiversity and Ecosystems - Aligned</t>
         </is>
       </c>
       <c r="E204" s="4" t="inlineStr">
         <is>
-          <t>IF_OTHER_CAPEX_BASED_SC_TO_ANY_ELIGIBLE</t>
+          <t>IF_OTHER_CAPEX_BASED_SC_TO_BIO_ALIGNED</t>
         </is>
       </c>
       <c r="F204" s="4" t="inlineStr">
         <is>
-          <t>Taxonomy-aligned CapEx-based Proportion of Revenue (Fees, Commissions and other Monetary Services) from Investments and Services and Activities substantially contributing to any of the six Environmental Objectives</t>
+          <t>Taxonomy-aligned CapEx-based Proportion of Revenue (Fees, Commissions and other Monetary Services) from Investments and Services and Activities substantially contributing to Protection and Restoration of Biodiversity and Ecosystems</t>
         </is>
       </c>
       <c r="G204" s="4" t="inlineStr">
@@ -12458,12 +12450,12 @@
       </c>
       <c r="D205" s="4" t="inlineStr">
         <is>
-          <t>CapEx-based Proportion of Revenue substantially contributing to any of the six Environmental Objectives - Aligned</t>
+          <t>CapEx-based Proportion of Revenue substantially contributing to any of the six Environmental Objectives - Eligible</t>
         </is>
       </c>
       <c r="E205" s="4" t="inlineStr">
         <is>
-          <t>IF_OTHER_CAPEX_BASED_SC_TO_ANY_ALIGNED</t>
+          <t>IF_OTHER_CAPEX_BASED_SC_TO_ANY_ELIGIBLE</t>
         </is>
       </c>
       <c r="F205" s="4" t="inlineStr">
@@ -12516,17 +12508,17 @@
       </c>
       <c r="D206" s="4" t="inlineStr">
         <is>
-          <t>CapEx-based Proportion of Revenue substantially contributing to any of the six Environmental Objectives - Of which Transitional</t>
+          <t>CapEx-based Proportion of Revenue substantially contributing to any of the six Environmental Objectives - Aligned</t>
         </is>
       </c>
       <c r="E206" s="4" t="inlineStr">
         <is>
-          <t>IF_OTHER_CAPEX_BASED_SC_TO_ANY_TRANSITIONAL</t>
+          <t>IF_OTHER_CAPEX_BASED_SC_TO_ANY_ALIGNED</t>
         </is>
       </c>
       <c r="F206" s="4" t="inlineStr">
         <is>
-          <t>Taxonomy-aligned and transitional CapEx-based Proportion of Revenue (Fees, Commissions and other Monetary Services) from Investments and Services and Activities substantially contributing to any of the six Environmental Objectives</t>
+          <t>Taxonomy-aligned CapEx-based Proportion of Revenue (Fees, Commissions and other Monetary Services) from Investments and Services and Activities substantially contributing to any of the six Environmental Objectives</t>
         </is>
       </c>
       <c r="G206" s="4" t="inlineStr">
@@ -12574,17 +12566,17 @@
       </c>
       <c r="D207" s="4" t="inlineStr">
         <is>
-          <t>CapEx-based Proportion of Revenue substantially contributing to any of the six Environmental Objectives - Of which Enabling</t>
+          <t>CapEx-based Proportion of Revenue substantially contributing to any of the six Environmental Objectives - Of which Transitional</t>
         </is>
       </c>
       <c r="E207" s="4" t="inlineStr">
         <is>
-          <t>IF_OTHER_CAPEX_BASED_SC_TO_ANY_ENABLING</t>
+          <t>IF_OTHER_CAPEX_BASED_SC_TO_ANY_TRANSITIONAL</t>
         </is>
       </c>
       <c r="F207" s="4" t="inlineStr">
         <is>
-          <t>Taxonomy-aligned and enabling CapEx-based Proportion of Revenue (Fees, Commissions and other Monetary Services) from Investments and Services and Activities substantially contributing to any of the six Environmental Objectives</t>
+          <t>Taxonomy-aligned and transitional CapEx-based Proportion of Revenue (Fees, Commissions and other Monetary Services) from Investments and Services and Activities substantially contributing to any of the six Environmental Objectives</t>
         </is>
       </c>
       <c r="G207" s="4" t="inlineStr">
@@ -12632,17 +12624,17 @@
       </c>
       <c r="D208" s="4" t="inlineStr">
         <is>
-          <t>CapEx-based Non-Assessed Exposures</t>
+          <t>CapEx-based Proportion of Revenue substantially contributing to any of the six Environmental Objectives - Of which Enabling</t>
         </is>
       </c>
       <c r="E208" s="4" t="inlineStr">
         <is>
-          <t>IF_OTHER_CAPEX_BASED_PCT_NON_ASSESSED</t>
+          <t>IF_OTHER_CAPEX_BASED_SC_TO_ANY_ENABLING</t>
         </is>
       </c>
       <c r="F208" s="4" t="inlineStr">
         <is>
-          <t>CapEx-based Proportion of Revenue (Fees, Commissions and other Monetary Services) from Investments and Services and Activities of which Non-Assessed Exposures</t>
+          <t>Taxonomy-aligned and enabling CapEx-based Proportion of Revenue (Fees, Commissions and other Monetary Services) from Investments and Services and Activities substantially contributing to any of the six Environmental Objectives</t>
         </is>
       </c>
       <c r="G208" s="4" t="inlineStr">
@@ -12690,17 +12682,17 @@
       </c>
       <c r="D209" s="4" t="inlineStr">
         <is>
-          <t>CapEx-based Proportion of Revenue from Operation of an OTF of which Nuclear Activities - Eligible</t>
+          <t>CapEx-based Non-Assessed Exposures</t>
         </is>
       </c>
       <c r="E209" s="4" t="inlineStr">
         <is>
-          <t>IF_OTHER_CAPEX_BASED_BASED_NUCLEAR_PCT_ELIGIBLE</t>
+          <t>IF_OTHER_CAPEX_BASED_PCT_NON_ASSESSED</t>
         </is>
       </c>
       <c r="F209" s="4" t="inlineStr">
         <is>
-          <t>Taxonomy-eligible CapEx-based Proportion of Revenue from Operation of an OTF which are exposed towards Nuclear Activities</t>
+          <t>CapEx-based Proportion of Revenue (Fees, Commissions and other Monetary Services) from Investments and Services and Activities of which Non-Assessed Exposures</t>
         </is>
       </c>
       <c r="G209" s="4" t="inlineStr">
@@ -12748,17 +12740,17 @@
       </c>
       <c r="D210" s="4" t="inlineStr">
         <is>
-          <t>CapEx-based Proportion of Revenue from Operation of an OTF of which Fossil Gas Activities - Eligible</t>
+          <t>CapEx-based Proportion of Revenue from Operation of an OTF of which Nuclear Activities - Eligible</t>
         </is>
       </c>
       <c r="E210" s="4" t="inlineStr">
         <is>
-          <t>IF_OTHER_CAPEX_BASED_BASED_GAS_PCT_ELIGIBLE</t>
+          <t>IF_OTHER_CAPEX_BASED_NUCLEAR_PCT_ELIGIBLE</t>
         </is>
       </c>
       <c r="F210" s="4" t="inlineStr">
         <is>
-          <t>Taxonomy-eligible CapEx-based Proportion of Revenue from Operation of an OTF which are exposed towards Fossil Gas Activities</t>
+          <t>Taxonomy-eligible CapEx-based Proportion of Revenue from Operation of an OTF which are exposed towards Nuclear Activities</t>
         </is>
       </c>
       <c r="G210" s="4" t="inlineStr">
@@ -12806,17 +12798,17 @@
       </c>
       <c r="D211" s="4" t="inlineStr">
         <is>
-          <t>CapEx-based Proportion of Revenue from Operation of an OTF of which Nuclear Activities - Aligned</t>
+          <t>CapEx-based Proportion of Revenue from Operation of an OTF of which Fossil Gas Activities - Eligible</t>
         </is>
       </c>
       <c r="E211" s="4" t="inlineStr">
         <is>
-          <t>IF_OTHER_CAPEX_BASED_BASED_NUCLEAR_PCT_ALIGNED</t>
+          <t>IF_OTHER_CAPEX_BASED_GAS_PCT_ELIGIBLE</t>
         </is>
       </c>
       <c r="F211" s="4" t="inlineStr">
         <is>
-          <t>Taxonomy-aligned CapEx-based Proportion of Revenue from Operation of an OTF which are exposed towards Nuclear Activities</t>
+          <t>Taxonomy-eligible CapEx-based Proportion of Revenue from Operation of an OTF which are exposed towards Fossil Gas Activities</t>
         </is>
       </c>
       <c r="G211" s="4" t="inlineStr">
@@ -12864,17 +12856,17 @@
       </c>
       <c r="D212" s="4" t="inlineStr">
         <is>
-          <t>CapEx-based Proportion of Revenue from Operation of an OTF of which Fossil Gas Activities - Aligned</t>
+          <t>CapEx-based Proportion of Revenue from Operation of an OTF of which Nuclear Activities - Aligned</t>
         </is>
       </c>
       <c r="E212" s="4" t="inlineStr">
         <is>
-          <t>IF_OTHER_CAPEX_BASED_BASED_GAS_PCT_ALIGNED</t>
+          <t>IF_OTHER_CAPEX_BASED_NUCLEAR_PCT_ALIGNED</t>
         </is>
       </c>
       <c r="F212" s="4" t="inlineStr">
         <is>
-          <t>Taxonomy-aligned CapEx-based Proportion of Revenue from Operation of an OTF which are exposed towards Fossil Gas Activities</t>
+          <t>Taxonomy-aligned CapEx-based Proportion of Revenue from Operation of an OTF which are exposed towards Nuclear Activities</t>
         </is>
       </c>
       <c r="G212" s="4" t="inlineStr">
@@ -12903,6 +12895,64 @@
         </is>
       </c>
       <c r="P212" s="4" t="inlineStr"/>
+    </row>
+    <row r="213">
+      <c r="A213" s="2" t="inlineStr">
+        <is>
+          <t>212</t>
+        </is>
+      </c>
+      <c r="B213" s="3" t="inlineStr">
+        <is>
+          <t>Investment firms</t>
+        </is>
+      </c>
+      <c r="C213" s="3" t="inlineStr">
+        <is>
+          <t>Other Services - CapEx-based</t>
+        </is>
+      </c>
+      <c r="D213" s="4" t="inlineStr">
+        <is>
+          <t>CapEx-based Proportion of Revenue from Operation of an OTF of which Fossil Gas Activities - Aligned</t>
+        </is>
+      </c>
+      <c r="E213" s="4" t="inlineStr">
+        <is>
+          <t>IF_OTHER_CAPEX_BASED_GAS_PCT_ALIGNED</t>
+        </is>
+      </c>
+      <c r="F213" s="4" t="inlineStr">
+        <is>
+          <t>Taxonomy-aligned CapEx-based Proportion of Revenue from Operation of an OTF which are exposed towards Fossil Gas Activities</t>
+        </is>
+      </c>
+      <c r="G213" s="4" t="inlineStr">
+        <is>
+          <t>Percentage</t>
+        </is>
+      </c>
+      <c r="H213" s="4" t="inlineStr"/>
+      <c r="I213" s="4" t="inlineStr"/>
+      <c r="J213" s="4" t="inlineStr">
+        <is>
+          <t>Extended</t>
+        </is>
+      </c>
+      <c r="K213" s="4" t="inlineStr"/>
+      <c r="L213" s="4" t="inlineStr"/>
+      <c r="M213" s="4" t="inlineStr"/>
+      <c r="N213" s="4" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="O213" s="4" t="inlineStr">
+        <is>
+          <t>Yes</t>
+        </is>
+      </c>
+      <c r="P213" s="4" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/dataland-framework-toolbox/inputs/eutaxonomy-financials-2026-73/eutaxonomy-financials-2026-73.xlsx
+++ b/dataland-framework-toolbox/inputs/eutaxonomy-financials-2026-73/eutaxonomy-financials-2026-73.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\d93814\IdeaProjects\Dataland\dataland-framework-toolbox\inputs\eutaxonomy-financials-2026-73\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\d92477\IdeaProjects\Dataland\dataland-framework-toolbox\inputs\eutaxonomy-financials-2026-73\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C24CF918-BFCC-4301-B5AB-39400A767F44}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A461C037-8824-48B8-9BAB-53AB5FCB7BC3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="67080" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Framework Data Model" sheetId="1" r:id="rId1"/>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2147" uniqueCount="811">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2202" uniqueCount="832">
   <si>
     <t>Field Identifier</t>
   </si>
@@ -221,18 +221,6 @@
     <t>Credit Institution</t>
   </si>
   <si>
-    <t>Assets for Calculation of Green Asset Ratio</t>
-  </si>
-  <si>
-    <t>Total (gross) Carrying Amount</t>
-  </si>
-  <si>
-    <t>CI_GAR_ASSETS_TOTAL_GROSS_CARRYING_AMOUNT</t>
-  </si>
-  <si>
-    <t>Total overall covered assets which are included in the numerator. Do not include assets which not covered for GAR calculation.</t>
-  </si>
-  <si>
     <t>Currency</t>
   </si>
   <si>
@@ -242,51 +230,15 @@
     <t>10</t>
   </si>
   <si>
-    <t>Total Amount of Non-Assessed Exposures</t>
-  </si>
-  <si>
-    <t>CI_GAR_ASSETS_NON_ASSESSED</t>
-  </si>
-  <si>
-    <t>Total amount of assets of which Non-Assessed Exposures</t>
-  </si>
-  <si>
     <t>11</t>
   </si>
   <si>
-    <t>Total Amount Of Non-Assessed Exposures - Of which Financing Non-Material Activities of Counterparties</t>
-  </si>
-  <si>
-    <t>CI_GAR_ASSETS_NON_ASSESSED_NON_MATERIAL_CP</t>
-  </si>
-  <si>
-    <t>Total amount of assets of which Financing Non-Material Activities of Counterparties</t>
-  </si>
-  <si>
     <t>12</t>
   </si>
   <si>
-    <t>Total Amount Of Non-Assessed Exposures - Of which Exposures Financing Counterparties Reporting no Taxonomy-eligible Activities</t>
-  </si>
-  <si>
-    <t>CI_GAR_ASSETS_NON_ASSESSED_NO_ELIGIBLE_CP</t>
-  </si>
-  <si>
-    <t>Total amount of assets Of which exposures financing counterparties reporting in accordance with Article 7(9) of Regulation (EU) 2026/73</t>
-  </si>
-  <si>
     <t>13</t>
   </si>
   <si>
-    <t>Total Amount Of Non-Assessed Exposures - Of which Not Assessed Considered Non-Material by the Credit Institution</t>
-  </si>
-  <si>
-    <t>CI_GAR_ASSETS_NON_ASSESSED_NON_MATERIAL_CI</t>
-  </si>
-  <si>
-    <t>Total amount of assets of which Not Assessed Considered Non-Material by the Credit Institution</t>
-  </si>
-  <si>
     <t>14</t>
   </si>
   <si>
@@ -2466,6 +2418,117 @@
   </si>
   <si>
     <t>Breakdown of the Numerator of the KPI for Non-Assessed Exposures - CapEx-based</t>
+  </si>
+  <si>
+    <t>Turnover-based Assets for Calculation of Green Asset Ratio</t>
+  </si>
+  <si>
+    <t>Turnover-based Total (gross) Carrying Amount</t>
+  </si>
+  <si>
+    <t>Turnover-based Total Amount of Non-Assessed Exposures</t>
+  </si>
+  <si>
+    <t>Turnover-based Total Amount Of Non-Assessed Exposures - Of which Financing Non-Material Activities of Counterparties</t>
+  </si>
+  <si>
+    <t>Turnover-based Total Amount Of Non-Assessed Exposures - Of which Exposures Financing Counterparties Reporting no Taxonomy-eligible Activities</t>
+  </si>
+  <si>
+    <t>Turnover-based Total Amount Of Non-Assessed Exposures - Of which Not Assessed Considered Non-Material by the Credit Institution</t>
+  </si>
+  <si>
+    <t>CapEx-based Assets for Calculation of Green Asset Ratio</t>
+  </si>
+  <si>
+    <t>CapEx-based Total (gross) Carrying Amount</t>
+  </si>
+  <si>
+    <t>CI_CAPEX_BASED_GAR_ASSETS_TOTAL_GROSS_CARRYING_AMOUNT</t>
+  </si>
+  <si>
+    <t>CapEx-based total overall covered assets which are included in the numerator. Do not include assets which not covered for GAR calculation.</t>
+  </si>
+  <si>
+    <t>CapEx-based Total Amount of Non-Assessed Exposures</t>
+  </si>
+  <si>
+    <t>CI_CAPEX_BASED_GAR_ASSETS_NON_ASSESSED</t>
+  </si>
+  <si>
+    <t>CapEx-based total amount of assets of which Non-Assessed Exposures</t>
+  </si>
+  <si>
+    <t>CapEx-based Total Amount Of Non-Assessed Exposures - Of which Financing Non-Material Activities of Counterparties</t>
+  </si>
+  <si>
+    <t>CI_CAPEX_BASED_GAR_ASSETS_NON_ASSESSED_NON_MATERIAL_CP</t>
+  </si>
+  <si>
+    <t>CapEx-based total amount of assets of which Financing Non-Material Activities of Counterparties</t>
+  </si>
+  <si>
+    <t>CapEx-based Total Amount Of Non-Assessed Exposures - Of which Exposures Financing Counterparties Reporting no Taxonomy-eligible Activities</t>
+  </si>
+  <si>
+    <t>CI_CAPEX_BASED_GAR_ASSETS_NON_ASSESSED_NO_ELIGIBLE_CP</t>
+  </si>
+  <si>
+    <t>CapEx-based total amount of assets Of which exposures financing counterparties reporting in accordance with Article 7(9) of Regulation (EU) 2026/73</t>
+  </si>
+  <si>
+    <t>CapEx-based Total Amount Of Non-Assessed Exposures - Of which Not Assessed Considered Non-Material by the Credit Institution</t>
+  </si>
+  <si>
+    <t>CI_CAPEX_BASED_GAR_ASSETS_NON_ASSESSED_NON_MATERIAL_CI</t>
+  </si>
+  <si>
+    <t>CapEx-based total amount of assets of which Not Assessed Considered Non-Material by the Credit Institution</t>
+  </si>
+  <si>
+    <t>213</t>
+  </si>
+  <si>
+    <t>214</t>
+  </si>
+  <si>
+    <t>215</t>
+  </si>
+  <si>
+    <t>216</t>
+  </si>
+  <si>
+    <t>217</t>
+  </si>
+  <si>
+    <t>CI_TURNOVER_BASED_GAR_ASSETS_TOTAL_GROSS_CARRYING_AMOUNT</t>
+  </si>
+  <si>
+    <t>CI_TURNOVER_BASED_GAR_ASSETS_NON_ASSESSED</t>
+  </si>
+  <si>
+    <t>CI_TURNOVER_BASED_GAR_ASSETS_NON_ASSESSED_NON_MATERIAL_CP</t>
+  </si>
+  <si>
+    <t>CI_TURNOVER_BASED_GAR_ASSETS_NON_ASSESSED_NO_ELIGIBLE_CP</t>
+  </si>
+  <si>
+    <t>CI_TURNOVER_BASED_GAR_ASSETS_NON_ASSESSED_NON_MATERIAL_CI</t>
+  </si>
+  <si>
+    <t>Turnover-based total overall covered assets which are included in the numerator. Do not include assets which not covered for GAR calculation.</t>
+  </si>
+  <si>
+    <t>Turnover-based total amount of assets of which Non-Assessed Exposures</t>
+  </si>
+  <si>
+    <t>Turnover-based total amount of assets of which Financing Non-Material Activities of Counterparties</t>
+  </si>
+  <si>
+    <t>Turnover-based total amount of assets Of which exposures financing counterparties reporting in accordance with Article 7(9) of Regulation (EU) 2026/73</t>
+  </si>
+  <si>
+    <t>Turnover-based total amount of assets of which Not Assessed Considered Non-Material by the Credit Institution</t>
   </si>
 </sst>
 </file>
@@ -2606,6 +2669,10 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -2930,26 +2997,26 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:P213"/>
-  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
+  <dimension ref="A1:P218"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="15" customWidth="1"/>
-    <col min="2" max="2" width="18.46484375" customWidth="1"/>
-    <col min="3" max="3" width="70.19921875" customWidth="1"/>
-    <col min="4" max="5" width="117.796875" customWidth="1"/>
+    <col min="2" max="2" width="18.42578125" customWidth="1"/>
+    <col min="3" max="3" width="70.140625" customWidth="1"/>
+    <col min="4" max="5" width="117.85546875" customWidth="1"/>
     <col min="6" max="6" width="92" customWidth="1"/>
-    <col min="7" max="7" width="36.46484375" customWidth="1"/>
-    <col min="8" max="8" width="19.796875" customWidth="1"/>
-    <col min="9" max="9" width="6.46484375" customWidth="1"/>
-    <col min="10" max="10" width="18.73046875" customWidth="1"/>
-    <col min="11" max="11" width="13.265625" customWidth="1"/>
-    <col min="12" max="12" width="19.53125" customWidth="1"/>
-    <col min="13" max="13" width="16.19921875" customWidth="1"/>
-    <col min="14" max="14" width="26.46484375" customWidth="1"/>
-    <col min="15" max="16" width="30.265625" customWidth="1"/>
+    <col min="7" max="7" width="36.42578125" customWidth="1"/>
+    <col min="8" max="8" width="19.85546875" customWidth="1"/>
+    <col min="9" max="9" width="6.42578125" customWidth="1"/>
+    <col min="10" max="10" width="18.7109375" customWidth="1"/>
+    <col min="11" max="11" width="13.28515625" customWidth="1"/>
+    <col min="12" max="12" width="19.5703125" customWidth="1"/>
+    <col min="13" max="13" width="16.140625" customWidth="1"/>
+    <col min="14" max="14" width="26.42578125" customWidth="1"/>
+    <col min="15" max="16" width="30.28515625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:16" ht="14.55" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="1" spans="1:16" ht="14.65" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -2999,7 +3066,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="2" spans="1:16" x14ac:dyDescent="0.45">
+    <row r="2" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
         <v>16</v>
       </c>
@@ -3035,7 +3102,7 @@
       <c r="O2" s="4"/>
       <c r="P2" s="4"/>
     </row>
-    <row r="3" spans="1:16" x14ac:dyDescent="0.45">
+    <row r="3" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A3" s="2" t="s">
         <v>24</v>
       </c>
@@ -3071,7 +3138,7 @@
       <c r="O3" s="4"/>
       <c r="P3" s="4"/>
     </row>
-    <row r="4" spans="1:16" x14ac:dyDescent="0.45">
+    <row r="4" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A4" s="2" t="s">
         <v>30</v>
       </c>
@@ -3105,7 +3172,7 @@
       <c r="O4" s="4"/>
       <c r="P4" s="4"/>
     </row>
-    <row r="5" spans="1:16" x14ac:dyDescent="0.45">
+    <row r="5" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A5" s="2" t="s">
         <v>35</v>
       </c>
@@ -3143,7 +3210,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="6" spans="1:16" x14ac:dyDescent="0.45">
+    <row r="6" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A6" s="2" t="s">
         <v>41</v>
       </c>
@@ -3179,7 +3246,7 @@
       <c r="O6" s="4"/>
       <c r="P6" s="4"/>
     </row>
-    <row r="7" spans="1:16" x14ac:dyDescent="0.45">
+    <row r="7" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A7" s="2" t="s">
         <v>47</v>
       </c>
@@ -3213,7 +3280,7 @@
       <c r="O7" s="4"/>
       <c r="P7" s="4"/>
     </row>
-    <row r="8" spans="1:16" x14ac:dyDescent="0.45">
+    <row r="8" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A8" s="2" t="s">
         <v>51</v>
       </c>
@@ -3247,7 +3314,7 @@
       <c r="O8" s="4"/>
       <c r="P8" s="4"/>
     </row>
-    <row r="9" spans="1:16" x14ac:dyDescent="0.45">
+    <row r="9" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A9" s="2" t="s">
         <v>56</v>
       </c>
@@ -3281,7 +3348,7 @@
       <c r="O9" s="4"/>
       <c r="P9" s="4"/>
     </row>
-    <row r="10" spans="1:16" x14ac:dyDescent="0.45">
+    <row r="10" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A10" s="2" t="s">
         <v>60</v>
       </c>
@@ -3289,19 +3356,19 @@
         <v>61</v>
       </c>
       <c r="C10" s="3" t="s">
+        <v>795</v>
+      </c>
+      <c r="D10" s="4" t="s">
+        <v>796</v>
+      </c>
+      <c r="E10" s="4" t="s">
+        <v>822</v>
+      </c>
+      <c r="F10" s="4" t="s">
+        <v>827</v>
+      </c>
+      <c r="G10" s="4" t="s">
         <v>62</v>
-      </c>
-      <c r="D10" s="4" t="s">
-        <v>63</v>
-      </c>
-      <c r="E10" s="4" t="s">
-        <v>64</v>
-      </c>
-      <c r="F10" s="4" t="s">
-        <v>65</v>
-      </c>
-      <c r="G10" s="4" t="s">
-        <v>66</v>
       </c>
       <c r="H10" s="4" t="s">
         <v>46</v>
@@ -3314,34 +3381,34 @@
       <c r="L10" s="4"/>
       <c r="M10" s="4"/>
       <c r="N10" s="4" t="s">
-        <v>67</v>
+        <v>63</v>
       </c>
       <c r="O10" s="4" t="s">
-        <v>67</v>
+        <v>63</v>
       </c>
       <c r="P10" s="4"/>
     </row>
-    <row r="11" spans="1:16" x14ac:dyDescent="0.45">
+    <row r="11" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A11" s="2" t="s">
-        <v>68</v>
+        <v>64</v>
       </c>
       <c r="B11" s="3" t="s">
         <v>61</v>
       </c>
       <c r="C11" s="3" t="s">
+        <v>795</v>
+      </c>
+      <c r="D11" s="4" t="s">
+        <v>797</v>
+      </c>
+      <c r="E11" s="4" t="s">
+        <v>823</v>
+      </c>
+      <c r="F11" s="4" t="s">
+        <v>828</v>
+      </c>
+      <c r="G11" s="4" t="s">
         <v>62</v>
-      </c>
-      <c r="D11" s="4" t="s">
-        <v>69</v>
-      </c>
-      <c r="E11" s="4" t="s">
-        <v>70</v>
-      </c>
-      <c r="F11" s="4" t="s">
-        <v>71</v>
-      </c>
-      <c r="G11" s="4" t="s">
-        <v>66</v>
       </c>
       <c r="H11" s="4" t="s">
         <v>46</v>
@@ -3354,34 +3421,34 @@
       <c r="L11" s="4"/>
       <c r="M11" s="4"/>
       <c r="N11" s="4" t="s">
-        <v>67</v>
+        <v>63</v>
       </c>
       <c r="O11" s="4" t="s">
-        <v>67</v>
+        <v>63</v>
       </c>
       <c r="P11" s="4"/>
     </row>
-    <row r="12" spans="1:16" x14ac:dyDescent="0.45">
+    <row r="12" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A12" s="2" t="s">
-        <v>72</v>
+        <v>65</v>
       </c>
       <c r="B12" s="3" t="s">
         <v>61</v>
       </c>
       <c r="C12" s="3" t="s">
+        <v>795</v>
+      </c>
+      <c r="D12" s="4" t="s">
+        <v>798</v>
+      </c>
+      <c r="E12" s="4" t="s">
+        <v>824</v>
+      </c>
+      <c r="F12" s="4" t="s">
+        <v>829</v>
+      </c>
+      <c r="G12" s="4" t="s">
         <v>62</v>
-      </c>
-      <c r="D12" s="4" t="s">
-        <v>73</v>
-      </c>
-      <c r="E12" s="4" t="s">
-        <v>74</v>
-      </c>
-      <c r="F12" s="4" t="s">
-        <v>75</v>
-      </c>
-      <c r="G12" s="4" t="s">
-        <v>66</v>
       </c>
       <c r="H12" s="4" t="s">
         <v>46</v>
@@ -3394,34 +3461,34 @@
       <c r="L12" s="4"/>
       <c r="M12" s="4"/>
       <c r="N12" s="4" t="s">
-        <v>67</v>
+        <v>63</v>
       </c>
       <c r="O12" s="4" t="s">
-        <v>67</v>
+        <v>63</v>
       </c>
       <c r="P12" s="4"/>
     </row>
-    <row r="13" spans="1:16" x14ac:dyDescent="0.45">
+    <row r="13" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A13" s="2" t="s">
-        <v>76</v>
+        <v>66</v>
       </c>
       <c r="B13" s="3" t="s">
         <v>61</v>
       </c>
       <c r="C13" s="3" t="s">
+        <v>795</v>
+      </c>
+      <c r="D13" s="4" t="s">
+        <v>799</v>
+      </c>
+      <c r="E13" s="4" t="s">
+        <v>825</v>
+      </c>
+      <c r="F13" s="4" t="s">
+        <v>830</v>
+      </c>
+      <c r="G13" s="4" t="s">
         <v>62</v>
-      </c>
-      <c r="D13" s="4" t="s">
-        <v>77</v>
-      </c>
-      <c r="E13" s="4" t="s">
-        <v>78</v>
-      </c>
-      <c r="F13" s="4" t="s">
-        <v>79</v>
-      </c>
-      <c r="G13" s="4" t="s">
-        <v>66</v>
       </c>
       <c r="H13" s="4" t="s">
         <v>46</v>
@@ -3434,34 +3501,34 @@
       <c r="L13" s="4"/>
       <c r="M13" s="4"/>
       <c r="N13" s="4" t="s">
+        <v>63</v>
+      </c>
+      <c r="O13" s="4" t="s">
+        <v>63</v>
+      </c>
+      <c r="P13" s="4"/>
+    </row>
+    <row r="14" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A14" s="2" t="s">
         <v>67</v>
-      </c>
-      <c r="O13" s="4" t="s">
-        <v>67</v>
-      </c>
-      <c r="P13" s="4"/>
-    </row>
-    <row r="14" spans="1:16" x14ac:dyDescent="0.45">
-      <c r="A14" s="2" t="s">
-        <v>80</v>
       </c>
       <c r="B14" s="3" t="s">
         <v>61</v>
       </c>
       <c r="C14" s="3" t="s">
+        <v>795</v>
+      </c>
+      <c r="D14" s="4" t="s">
+        <v>800</v>
+      </c>
+      <c r="E14" s="4" t="s">
+        <v>826</v>
+      </c>
+      <c r="F14" s="4" t="s">
+        <v>831</v>
+      </c>
+      <c r="G14" s="4" t="s">
         <v>62</v>
-      </c>
-      <c r="D14" s="4" t="s">
-        <v>81</v>
-      </c>
-      <c r="E14" s="4" t="s">
-        <v>82</v>
-      </c>
-      <c r="F14" s="4" t="s">
-        <v>83</v>
-      </c>
-      <c r="G14" s="4" t="s">
-        <v>66</v>
       </c>
       <c r="H14" s="4" t="s">
         <v>46</v>
@@ -3474,34 +3541,34 @@
       <c r="L14" s="4"/>
       <c r="M14" s="4"/>
       <c r="N14" s="4" t="s">
-        <v>67</v>
+        <v>63</v>
       </c>
       <c r="O14" s="4" t="s">
-        <v>67</v>
+        <v>63</v>
       </c>
       <c r="P14" s="4"/>
     </row>
-    <row r="15" spans="1:16" x14ac:dyDescent="0.45">
+    <row r="15" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A15" s="2" t="s">
-        <v>84</v>
+        <v>68</v>
       </c>
       <c r="B15" s="3" t="s">
         <v>61</v>
       </c>
       <c r="C15" s="3" t="s">
-        <v>85</v>
+        <v>801</v>
       </c>
       <c r="D15" s="4" t="s">
-        <v>86</v>
+        <v>802</v>
       </c>
       <c r="E15" s="4" t="s">
-        <v>87</v>
+        <v>803</v>
       </c>
       <c r="F15" s="4" t="s">
-        <v>88</v>
+        <v>804</v>
       </c>
       <c r="G15" s="4" t="s">
-        <v>66</v>
+        <v>62</v>
       </c>
       <c r="H15" s="4" t="s">
         <v>46</v>
@@ -3514,34 +3581,34 @@
       <c r="L15" s="4"/>
       <c r="M15" s="4"/>
       <c r="N15" s="4" t="s">
-        <v>67</v>
+        <v>63</v>
       </c>
       <c r="O15" s="4" t="s">
-        <v>67</v>
+        <v>63</v>
       </c>
       <c r="P15" s="4"/>
     </row>
-    <row r="16" spans="1:16" x14ac:dyDescent="0.45">
+    <row r="16" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A16" s="2" t="s">
-        <v>89</v>
+        <v>73</v>
       </c>
       <c r="B16" s="3" t="s">
         <v>61</v>
       </c>
       <c r="C16" s="3" t="s">
-        <v>85</v>
+        <v>801</v>
       </c>
       <c r="D16" s="4" t="s">
-        <v>90</v>
+        <v>805</v>
       </c>
       <c r="E16" s="4" t="s">
-        <v>91</v>
+        <v>806</v>
       </c>
       <c r="F16" s="4" t="s">
-        <v>92</v>
+        <v>807</v>
       </c>
       <c r="G16" s="4" t="s">
-        <v>66</v>
+        <v>62</v>
       </c>
       <c r="H16" s="4" t="s">
         <v>46</v>
@@ -3554,34 +3621,34 @@
       <c r="L16" s="4"/>
       <c r="M16" s="4"/>
       <c r="N16" s="4" t="s">
-        <v>67</v>
+        <v>63</v>
       </c>
       <c r="O16" s="4" t="s">
-        <v>67</v>
+        <v>63</v>
       </c>
       <c r="P16" s="4"/>
     </row>
-    <row r="17" spans="1:16" x14ac:dyDescent="0.45">
+    <row r="17" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A17" s="2" t="s">
-        <v>93</v>
+        <v>77</v>
       </c>
       <c r="B17" s="3" t="s">
         <v>61</v>
       </c>
       <c r="C17" s="3" t="s">
-        <v>85</v>
+        <v>801</v>
       </c>
       <c r="D17" s="4" t="s">
-        <v>94</v>
+        <v>808</v>
       </c>
       <c r="E17" s="4" t="s">
-        <v>95</v>
+        <v>809</v>
       </c>
       <c r="F17" s="4" t="s">
-        <v>96</v>
+        <v>810</v>
       </c>
       <c r="G17" s="4" t="s">
-        <v>66</v>
+        <v>62</v>
       </c>
       <c r="H17" s="4" t="s">
         <v>46</v>
@@ -3594,34 +3661,34 @@
       <c r="L17" s="4"/>
       <c r="M17" s="4"/>
       <c r="N17" s="4" t="s">
-        <v>67</v>
+        <v>63</v>
       </c>
       <c r="O17" s="4" t="s">
-        <v>67</v>
+        <v>63</v>
       </c>
       <c r="P17" s="4"/>
     </row>
-    <row r="18" spans="1:16" x14ac:dyDescent="0.45">
+    <row r="18" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A18" s="2" t="s">
-        <v>97</v>
+        <v>81</v>
       </c>
       <c r="B18" s="3" t="s">
         <v>61</v>
       </c>
       <c r="C18" s="3" t="s">
-        <v>85</v>
+        <v>801</v>
       </c>
       <c r="D18" s="4" t="s">
-        <v>98</v>
+        <v>811</v>
       </c>
       <c r="E18" s="4" t="s">
-        <v>99</v>
+        <v>812</v>
       </c>
       <c r="F18" s="4" t="s">
-        <v>100</v>
+        <v>813</v>
       </c>
       <c r="G18" s="4" t="s">
-        <v>66</v>
+        <v>62</v>
       </c>
       <c r="H18" s="4" t="s">
         <v>46</v>
@@ -3634,34 +3701,34 @@
       <c r="L18" s="4"/>
       <c r="M18" s="4"/>
       <c r="N18" s="4" t="s">
-        <v>67</v>
+        <v>63</v>
       </c>
       <c r="O18" s="4" t="s">
-        <v>67</v>
+        <v>63</v>
       </c>
       <c r="P18" s="4"/>
     </row>
-    <row r="19" spans="1:16" x14ac:dyDescent="0.45">
+    <row r="19" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A19" s="2" t="s">
-        <v>101</v>
+        <v>85</v>
       </c>
       <c r="B19" s="3" t="s">
         <v>61</v>
       </c>
       <c r="C19" s="3" t="s">
-        <v>85</v>
+        <v>801</v>
       </c>
       <c r="D19" s="4" t="s">
-        <v>102</v>
+        <v>814</v>
       </c>
       <c r="E19" s="4" t="s">
-        <v>103</v>
+        <v>815</v>
       </c>
       <c r="F19" s="4" t="s">
-        <v>104</v>
+        <v>816</v>
       </c>
       <c r="G19" s="4" t="s">
-        <v>66</v>
+        <v>62</v>
       </c>
       <c r="H19" s="4" t="s">
         <v>46</v>
@@ -3674,34 +3741,34 @@
       <c r="L19" s="4"/>
       <c r="M19" s="4"/>
       <c r="N19" s="4" t="s">
-        <v>67</v>
+        <v>63</v>
       </c>
       <c r="O19" s="4" t="s">
-        <v>67</v>
+        <v>63</v>
       </c>
       <c r="P19" s="4"/>
     </row>
-    <row r="20" spans="1:16" x14ac:dyDescent="0.45">
+    <row r="20" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A20" s="2" t="s">
-        <v>105</v>
+        <v>89</v>
       </c>
       <c r="B20" s="3" t="s">
         <v>61</v>
       </c>
       <c r="C20" s="3" t="s">
-        <v>85</v>
+        <v>69</v>
       </c>
       <c r="D20" s="4" t="s">
-        <v>106</v>
+        <v>70</v>
       </c>
       <c r="E20" s="4" t="s">
-        <v>107</v>
+        <v>71</v>
       </c>
       <c r="F20" s="4" t="s">
-        <v>108</v>
+        <v>72</v>
       </c>
       <c r="G20" s="4" t="s">
-        <v>66</v>
+        <v>62</v>
       </c>
       <c r="H20" s="4" t="s">
         <v>46</v>
@@ -3714,34 +3781,34 @@
       <c r="L20" s="4"/>
       <c r="M20" s="4"/>
       <c r="N20" s="4" t="s">
-        <v>67</v>
+        <v>63</v>
       </c>
       <c r="O20" s="4" t="s">
-        <v>67</v>
+        <v>63</v>
       </c>
       <c r="P20" s="4"/>
     </row>
-    <row r="21" spans="1:16" x14ac:dyDescent="0.45">
+    <row r="21" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A21" s="2" t="s">
-        <v>109</v>
+        <v>93</v>
       </c>
       <c r="B21" s="3" t="s">
         <v>61</v>
       </c>
       <c r="C21" s="3" t="s">
-        <v>110</v>
+        <v>69</v>
       </c>
       <c r="D21" s="4" t="s">
-        <v>111</v>
+        <v>74</v>
       </c>
       <c r="E21" s="4" t="s">
-        <v>112</v>
+        <v>75</v>
       </c>
       <c r="F21" s="4" t="s">
-        <v>113</v>
+        <v>76</v>
       </c>
       <c r="G21" s="4" t="s">
-        <v>66</v>
+        <v>62</v>
       </c>
       <c r="H21" s="4" t="s">
         <v>46</v>
@@ -3754,34 +3821,34 @@
       <c r="L21" s="4"/>
       <c r="M21" s="4"/>
       <c r="N21" s="4" t="s">
-        <v>67</v>
+        <v>63</v>
       </c>
       <c r="O21" s="4" t="s">
-        <v>67</v>
+        <v>63</v>
       </c>
       <c r="P21" s="4"/>
     </row>
-    <row r="22" spans="1:16" x14ac:dyDescent="0.45">
+    <row r="22" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A22" s="2" t="s">
-        <v>114</v>
+        <v>98</v>
       </c>
       <c r="B22" s="3" t="s">
         <v>61</v>
       </c>
       <c r="C22" s="3" t="s">
-        <v>110</v>
+        <v>69</v>
       </c>
       <c r="D22" s="4" t="s">
-        <v>115</v>
+        <v>78</v>
       </c>
       <c r="E22" s="4" t="s">
-        <v>116</v>
+        <v>79</v>
       </c>
       <c r="F22" s="4" t="s">
-        <v>117</v>
+        <v>80</v>
       </c>
       <c r="G22" s="4" t="s">
-        <v>66</v>
+        <v>62</v>
       </c>
       <c r="H22" s="4" t="s">
         <v>46</v>
@@ -3794,34 +3861,34 @@
       <c r="L22" s="4"/>
       <c r="M22" s="4"/>
       <c r="N22" s="4" t="s">
-        <v>67</v>
+        <v>63</v>
       </c>
       <c r="O22" s="4" t="s">
-        <v>67</v>
+        <v>63</v>
       </c>
       <c r="P22" s="4"/>
     </row>
-    <row r="23" spans="1:16" x14ac:dyDescent="0.45">
+    <row r="23" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A23" s="2" t="s">
-        <v>118</v>
+        <v>102</v>
       </c>
       <c r="B23" s="3" t="s">
         <v>61</v>
       </c>
       <c r="C23" s="3" t="s">
-        <v>110</v>
+        <v>69</v>
       </c>
       <c r="D23" s="4" t="s">
-        <v>119</v>
+        <v>82</v>
       </c>
       <c r="E23" s="4" t="s">
-        <v>120</v>
+        <v>83</v>
       </c>
       <c r="F23" s="4" t="s">
-        <v>121</v>
+        <v>84</v>
       </c>
       <c r="G23" s="4" t="s">
-        <v>66</v>
+        <v>62</v>
       </c>
       <c r="H23" s="4" t="s">
         <v>46</v>
@@ -3834,34 +3901,34 @@
       <c r="L23" s="4"/>
       <c r="M23" s="4"/>
       <c r="N23" s="4" t="s">
-        <v>67</v>
+        <v>63</v>
       </c>
       <c r="O23" s="4" t="s">
-        <v>67</v>
+        <v>63</v>
       </c>
       <c r="P23" s="4"/>
     </row>
-    <row r="24" spans="1:16" x14ac:dyDescent="0.45">
+    <row r="24" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A24" s="2" t="s">
-        <v>122</v>
+        <v>106</v>
       </c>
       <c r="B24" s="3" t="s">
         <v>61</v>
       </c>
       <c r="C24" s="3" t="s">
-        <v>110</v>
+        <v>69</v>
       </c>
       <c r="D24" s="4" t="s">
-        <v>123</v>
+        <v>86</v>
       </c>
       <c r="E24" s="4" t="s">
-        <v>124</v>
+        <v>87</v>
       </c>
       <c r="F24" s="4" t="s">
-        <v>125</v>
+        <v>88</v>
       </c>
       <c r="G24" s="4" t="s">
-        <v>66</v>
+        <v>62</v>
       </c>
       <c r="H24" s="4" t="s">
         <v>46</v>
@@ -3874,34 +3941,34 @@
       <c r="L24" s="4"/>
       <c r="M24" s="4"/>
       <c r="N24" s="4" t="s">
-        <v>67</v>
+        <v>63</v>
       </c>
       <c r="O24" s="4" t="s">
-        <v>67</v>
+        <v>63</v>
       </c>
       <c r="P24" s="4"/>
     </row>
-    <row r="25" spans="1:16" x14ac:dyDescent="0.45">
+    <row r="25" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A25" s="2" t="s">
-        <v>126</v>
+        <v>110</v>
       </c>
       <c r="B25" s="3" t="s">
         <v>61</v>
       </c>
       <c r="C25" s="3" t="s">
-        <v>110</v>
+        <v>69</v>
       </c>
       <c r="D25" s="4" t="s">
-        <v>127</v>
+        <v>90</v>
       </c>
       <c r="E25" s="4" t="s">
-        <v>128</v>
+        <v>91</v>
       </c>
       <c r="F25" s="4" t="s">
-        <v>129</v>
+        <v>92</v>
       </c>
       <c r="G25" s="4" t="s">
-        <v>66</v>
+        <v>62</v>
       </c>
       <c r="H25" s="4" t="s">
         <v>46</v>
@@ -3914,34 +3981,34 @@
       <c r="L25" s="4"/>
       <c r="M25" s="4"/>
       <c r="N25" s="4" t="s">
-        <v>67</v>
+        <v>63</v>
       </c>
       <c r="O25" s="4" t="s">
-        <v>67</v>
+        <v>63</v>
       </c>
       <c r="P25" s="4"/>
     </row>
-    <row r="26" spans="1:16" x14ac:dyDescent="0.45">
+    <row r="26" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A26" s="2" t="s">
-        <v>130</v>
+        <v>114</v>
       </c>
       <c r="B26" s="3" t="s">
         <v>61</v>
       </c>
       <c r="C26" s="3" t="s">
-        <v>110</v>
+        <v>94</v>
       </c>
       <c r="D26" s="4" t="s">
-        <v>131</v>
+        <v>95</v>
       </c>
       <c r="E26" s="4" t="s">
-        <v>132</v>
+        <v>96</v>
       </c>
       <c r="F26" s="4" t="s">
-        <v>133</v>
+        <v>97</v>
       </c>
       <c r="G26" s="4" t="s">
-        <v>66</v>
+        <v>62</v>
       </c>
       <c r="H26" s="4" t="s">
         <v>46</v>
@@ -3954,36 +4021,38 @@
       <c r="L26" s="4"/>
       <c r="M26" s="4"/>
       <c r="N26" s="4" t="s">
-        <v>67</v>
+        <v>63</v>
       </c>
       <c r="O26" s="4" t="s">
-        <v>67</v>
+        <v>63</v>
       </c>
       <c r="P26" s="4"/>
     </row>
-    <row r="27" spans="1:16" x14ac:dyDescent="0.45">
+    <row r="27" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A27" s="2" t="s">
-        <v>134</v>
+        <v>118</v>
       </c>
       <c r="B27" s="3" t="s">
         <v>61</v>
       </c>
       <c r="C27" s="3" t="s">
-        <v>135</v>
+        <v>94</v>
       </c>
       <c r="D27" s="4" t="s">
-        <v>161</v>
+        <v>99</v>
       </c>
       <c r="E27" s="4" t="s">
-        <v>162</v>
+        <v>100</v>
       </c>
       <c r="F27" s="4" t="s">
-        <v>163</v>
+        <v>101</v>
       </c>
       <c r="G27" s="4" t="s">
-        <v>139</v>
-      </c>
-      <c r="H27" s="4"/>
+        <v>62</v>
+      </c>
+      <c r="H27" s="4" t="s">
+        <v>46</v>
+      </c>
       <c r="I27" s="4"/>
       <c r="J27" s="4" t="s">
         <v>23</v>
@@ -3992,36 +4061,38 @@
       <c r="L27" s="4"/>
       <c r="M27" s="4"/>
       <c r="N27" s="4" t="s">
-        <v>67</v>
+        <v>63</v>
       </c>
       <c r="O27" s="4" t="s">
-        <v>67</v>
+        <v>63</v>
       </c>
       <c r="P27" s="4"/>
     </row>
-    <row r="28" spans="1:16" x14ac:dyDescent="0.45">
+    <row r="28" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A28" s="2" t="s">
-        <v>140</v>
+        <v>124</v>
       </c>
       <c r="B28" s="3" t="s">
         <v>61</v>
       </c>
       <c r="C28" s="3" t="s">
-        <v>135</v>
+        <v>94</v>
       </c>
       <c r="D28" s="4" t="s">
-        <v>165</v>
+        <v>103</v>
       </c>
       <c r="E28" s="4" t="s">
-        <v>166</v>
+        <v>104</v>
       </c>
       <c r="F28" s="4" t="s">
-        <v>167</v>
+        <v>105</v>
       </c>
       <c r="G28" s="4" t="s">
-        <v>139</v>
-      </c>
-      <c r="H28" s="4"/>
+        <v>62</v>
+      </c>
+      <c r="H28" s="4" t="s">
+        <v>46</v>
+      </c>
       <c r="I28" s="4"/>
       <c r="J28" s="4" t="s">
         <v>23</v>
@@ -4030,36 +4101,38 @@
       <c r="L28" s="4"/>
       <c r="M28" s="4"/>
       <c r="N28" s="4" t="s">
-        <v>67</v>
+        <v>63</v>
       </c>
       <c r="O28" s="4" t="s">
-        <v>67</v>
+        <v>63</v>
       </c>
       <c r="P28" s="4"/>
     </row>
-    <row r="29" spans="1:16" x14ac:dyDescent="0.45">
+    <row r="29" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A29" s="2" t="s">
-        <v>144</v>
+        <v>128</v>
       </c>
       <c r="B29" s="3" t="s">
         <v>61</v>
       </c>
       <c r="C29" s="3" t="s">
-        <v>135</v>
+        <v>94</v>
       </c>
       <c r="D29" s="4" t="s">
-        <v>136</v>
+        <v>107</v>
       </c>
       <c r="E29" s="4" t="s">
-        <v>137</v>
+        <v>108</v>
       </c>
       <c r="F29" s="4" t="s">
-        <v>138</v>
+        <v>109</v>
       </c>
       <c r="G29" s="4" t="s">
-        <v>139</v>
-      </c>
-      <c r="H29" s="4"/>
+        <v>62</v>
+      </c>
+      <c r="H29" s="4" t="s">
+        <v>46</v>
+      </c>
       <c r="I29" s="4"/>
       <c r="J29" s="4" t="s">
         <v>23</v>
@@ -4068,36 +4141,38 @@
       <c r="L29" s="4"/>
       <c r="M29" s="4"/>
       <c r="N29" s="4" t="s">
-        <v>67</v>
+        <v>63</v>
       </c>
       <c r="O29" s="4" t="s">
-        <v>67</v>
+        <v>63</v>
       </c>
       <c r="P29" s="4"/>
     </row>
-    <row r="30" spans="1:16" x14ac:dyDescent="0.45">
+    <row r="30" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A30" s="2" t="s">
-        <v>148</v>
+        <v>132</v>
       </c>
       <c r="B30" s="3" t="s">
         <v>61</v>
       </c>
       <c r="C30" s="3" t="s">
-        <v>135</v>
+        <v>94</v>
       </c>
       <c r="D30" s="4" t="s">
-        <v>141</v>
+        <v>111</v>
       </c>
       <c r="E30" s="4" t="s">
-        <v>142</v>
+        <v>112</v>
       </c>
       <c r="F30" s="4" t="s">
-        <v>143</v>
+        <v>113</v>
       </c>
       <c r="G30" s="4" t="s">
-        <v>139</v>
-      </c>
-      <c r="H30" s="4"/>
+        <v>62</v>
+      </c>
+      <c r="H30" s="4" t="s">
+        <v>46</v>
+      </c>
       <c r="I30" s="4"/>
       <c r="J30" s="4" t="s">
         <v>23</v>
@@ -4106,36 +4181,38 @@
       <c r="L30" s="4"/>
       <c r="M30" s="4"/>
       <c r="N30" s="4" t="s">
-        <v>67</v>
+        <v>63</v>
       </c>
       <c r="O30" s="4" t="s">
-        <v>67</v>
+        <v>63</v>
       </c>
       <c r="P30" s="4"/>
     </row>
-    <row r="31" spans="1:16" x14ac:dyDescent="0.45">
+    <row r="31" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A31" s="2" t="s">
-        <v>152</v>
+        <v>136</v>
       </c>
       <c r="B31" s="3" t="s">
         <v>61</v>
       </c>
       <c r="C31" s="3" t="s">
-        <v>135</v>
+        <v>94</v>
       </c>
       <c r="D31" s="4" t="s">
-        <v>145</v>
+        <v>115</v>
       </c>
       <c r="E31" s="4" t="s">
-        <v>146</v>
+        <v>116</v>
       </c>
       <c r="F31" s="4" t="s">
-        <v>147</v>
+        <v>117</v>
       </c>
       <c r="G31" s="4" t="s">
-        <v>139</v>
-      </c>
-      <c r="H31" s="4"/>
+        <v>62</v>
+      </c>
+      <c r="H31" s="4" t="s">
+        <v>46</v>
+      </c>
       <c r="I31" s="4"/>
       <c r="J31" s="4" t="s">
         <v>23</v>
@@ -4144,34 +4221,34 @@
       <c r="L31" s="4"/>
       <c r="M31" s="4"/>
       <c r="N31" s="4" t="s">
-        <v>67</v>
+        <v>63</v>
       </c>
       <c r="O31" s="4" t="s">
-        <v>67</v>
+        <v>63</v>
       </c>
       <c r="P31" s="4"/>
     </row>
-    <row r="32" spans="1:16" x14ac:dyDescent="0.45">
+    <row r="32" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A32" s="2" t="s">
-        <v>156</v>
+        <v>140</v>
       </c>
       <c r="B32" s="3" t="s">
         <v>61</v>
       </c>
       <c r="C32" s="3" t="s">
-        <v>135</v>
+        <v>119</v>
       </c>
       <c r="D32" s="4" t="s">
-        <v>149</v>
+        <v>145</v>
       </c>
       <c r="E32" s="4" t="s">
-        <v>150</v>
+        <v>146</v>
       </c>
       <c r="F32" s="4" t="s">
-        <v>151</v>
+        <v>147</v>
       </c>
       <c r="G32" s="4" t="s">
-        <v>139</v>
+        <v>123</v>
       </c>
       <c r="H32" s="4"/>
       <c r="I32" s="4"/>
@@ -4182,34 +4259,34 @@
       <c r="L32" s="4"/>
       <c r="M32" s="4"/>
       <c r="N32" s="4" t="s">
-        <v>67</v>
+        <v>63</v>
       </c>
       <c r="O32" s="4" t="s">
-        <v>67</v>
+        <v>63</v>
       </c>
       <c r="P32" s="4"/>
     </row>
-    <row r="33" spans="1:16" x14ac:dyDescent="0.45">
+    <row r="33" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A33" s="2" t="s">
-        <v>160</v>
+        <v>144</v>
       </c>
       <c r="B33" s="3" t="s">
         <v>61</v>
       </c>
       <c r="C33" s="3" t="s">
-        <v>135</v>
+        <v>119</v>
       </c>
       <c r="D33" s="4" t="s">
-        <v>153</v>
+        <v>149</v>
       </c>
       <c r="E33" s="4" t="s">
-        <v>154</v>
+        <v>150</v>
       </c>
       <c r="F33" s="4" t="s">
-        <v>155</v>
+        <v>151</v>
       </c>
       <c r="G33" s="4" t="s">
-        <v>139</v>
+        <v>123</v>
       </c>
       <c r="H33" s="4"/>
       <c r="I33" s="4"/>
@@ -4220,34 +4297,34 @@
       <c r="L33" s="4"/>
       <c r="M33" s="4"/>
       <c r="N33" s="4" t="s">
-        <v>67</v>
+        <v>63</v>
       </c>
       <c r="O33" s="4" t="s">
-        <v>67</v>
+        <v>63</v>
       </c>
       <c r="P33" s="4"/>
     </row>
-    <row r="34" spans="1:16" x14ac:dyDescent="0.45">
+    <row r="34" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A34" s="2" t="s">
-        <v>164</v>
+        <v>148</v>
       </c>
       <c r="B34" s="3" t="s">
         <v>61</v>
       </c>
       <c r="C34" s="3" t="s">
-        <v>135</v>
+        <v>119</v>
       </c>
       <c r="D34" s="4" t="s">
-        <v>157</v>
+        <v>120</v>
       </c>
       <c r="E34" s="4" t="s">
-        <v>158</v>
+        <v>121</v>
       </c>
       <c r="F34" s="4" t="s">
-        <v>159</v>
+        <v>122</v>
       </c>
       <c r="G34" s="4" t="s">
-        <v>139</v>
+        <v>123</v>
       </c>
       <c r="H34" s="4"/>
       <c r="I34" s="4"/>
@@ -4258,34 +4335,34 @@
       <c r="L34" s="4"/>
       <c r="M34" s="4"/>
       <c r="N34" s="4" t="s">
-        <v>67</v>
+        <v>63</v>
       </c>
       <c r="O34" s="4" t="s">
-        <v>67</v>
+        <v>63</v>
       </c>
       <c r="P34" s="4"/>
     </row>
-    <row r="35" spans="1:16" x14ac:dyDescent="0.45">
+    <row r="35" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A35" s="2" t="s">
-        <v>168</v>
+        <v>152</v>
       </c>
       <c r="B35" s="3" t="s">
         <v>61</v>
       </c>
       <c r="C35" s="3" t="s">
-        <v>135</v>
+        <v>119</v>
       </c>
       <c r="D35" s="4" t="s">
-        <v>169</v>
+        <v>125</v>
       </c>
       <c r="E35" s="4" t="s">
-        <v>170</v>
+        <v>126</v>
       </c>
       <c r="F35" s="4" t="s">
-        <v>171</v>
+        <v>127</v>
       </c>
       <c r="G35" s="4" t="s">
-        <v>139</v>
+        <v>123</v>
       </c>
       <c r="H35" s="4"/>
       <c r="I35" s="4"/>
@@ -4296,34 +4373,34 @@
       <c r="L35" s="4"/>
       <c r="M35" s="4"/>
       <c r="N35" s="4" t="s">
-        <v>67</v>
+        <v>63</v>
       </c>
       <c r="O35" s="4" t="s">
-        <v>67</v>
+        <v>63</v>
       </c>
       <c r="P35" s="4"/>
     </row>
-    <row r="36" spans="1:16" x14ac:dyDescent="0.45">
+    <row r="36" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A36" s="2" t="s">
-        <v>172</v>
+        <v>156</v>
       </c>
       <c r="B36" s="3" t="s">
         <v>61</v>
       </c>
       <c r="C36" s="3" t="s">
-        <v>135</v>
+        <v>119</v>
       </c>
       <c r="D36" s="4" t="s">
-        <v>177</v>
+        <v>129</v>
       </c>
       <c r="E36" s="4" t="s">
-        <v>178</v>
+        <v>130</v>
       </c>
       <c r="F36" s="4" t="s">
-        <v>179</v>
+        <v>131</v>
       </c>
       <c r="G36" s="4" t="s">
-        <v>139</v>
+        <v>123</v>
       </c>
       <c r="H36" s="4"/>
       <c r="I36" s="4"/>
@@ -4334,34 +4411,34 @@
       <c r="L36" s="4"/>
       <c r="M36" s="4"/>
       <c r="N36" s="4" t="s">
-        <v>67</v>
+        <v>63</v>
       </c>
       <c r="O36" s="4" t="s">
-        <v>67</v>
+        <v>63</v>
       </c>
       <c r="P36" s="4"/>
     </row>
-    <row r="37" spans="1:16" x14ac:dyDescent="0.45">
+    <row r="37" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A37" s="2" t="s">
-        <v>176</v>
+        <v>160</v>
       </c>
       <c r="B37" s="3" t="s">
         <v>61</v>
       </c>
       <c r="C37" s="3" t="s">
+        <v>119</v>
+      </c>
+      <c r="D37" s="4" t="s">
+        <v>133</v>
+      </c>
+      <c r="E37" s="4" t="s">
+        <v>134</v>
+      </c>
+      <c r="F37" s="4" t="s">
         <v>135</v>
       </c>
-      <c r="D37" s="4" t="s">
-        <v>173</v>
-      </c>
-      <c r="E37" s="4" t="s">
-        <v>174</v>
-      </c>
-      <c r="F37" s="4" t="s">
-        <v>175</v>
-      </c>
       <c r="G37" s="4" t="s">
-        <v>139</v>
+        <v>123</v>
       </c>
       <c r="H37" s="4"/>
       <c r="I37" s="4"/>
@@ -4372,34 +4449,34 @@
       <c r="L37" s="4"/>
       <c r="M37" s="4"/>
       <c r="N37" s="4" t="s">
-        <v>67</v>
+        <v>63</v>
       </c>
       <c r="O37" s="4" t="s">
-        <v>67</v>
+        <v>63</v>
       </c>
       <c r="P37" s="4"/>
     </row>
-    <row r="38" spans="1:16" x14ac:dyDescent="0.45">
+    <row r="38" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A38" s="2" t="s">
-        <v>180</v>
+        <v>164</v>
       </c>
       <c r="B38" s="3" t="s">
         <v>61</v>
       </c>
       <c r="C38" s="3" t="s">
-        <v>135</v>
+        <v>119</v>
       </c>
       <c r="D38" s="4" t="s">
-        <v>181</v>
+        <v>137</v>
       </c>
       <c r="E38" s="4" t="s">
-        <v>182</v>
+        <v>138</v>
       </c>
       <c r="F38" s="4" t="s">
-        <v>183</v>
+        <v>139</v>
       </c>
       <c r="G38" s="4" t="s">
-        <v>139</v>
+        <v>123</v>
       </c>
       <c r="H38" s="4"/>
       <c r="I38" s="4"/>
@@ -4410,34 +4487,34 @@
       <c r="L38" s="4"/>
       <c r="M38" s="4"/>
       <c r="N38" s="4" t="s">
-        <v>67</v>
+        <v>63</v>
       </c>
       <c r="O38" s="4" t="s">
-        <v>67</v>
+        <v>63</v>
       </c>
       <c r="P38" s="4"/>
     </row>
-    <row r="39" spans="1:16" x14ac:dyDescent="0.45">
+    <row r="39" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A39" s="2" t="s">
-        <v>184</v>
+        <v>168</v>
       </c>
       <c r="B39" s="3" t="s">
         <v>61</v>
       </c>
       <c r="C39" s="3" t="s">
-        <v>185</v>
+        <v>119</v>
       </c>
       <c r="D39" s="4" t="s">
-        <v>161</v>
+        <v>141</v>
       </c>
       <c r="E39" s="4" t="s">
-        <v>204</v>
+        <v>142</v>
       </c>
       <c r="F39" s="4" t="s">
-        <v>205</v>
+        <v>143</v>
       </c>
       <c r="G39" s="4" t="s">
-        <v>139</v>
+        <v>123</v>
       </c>
       <c r="H39" s="4"/>
       <c r="I39" s="4"/>
@@ -4448,34 +4525,34 @@
       <c r="L39" s="4"/>
       <c r="M39" s="4"/>
       <c r="N39" s="4" t="s">
-        <v>67</v>
+        <v>63</v>
       </c>
       <c r="O39" s="4" t="s">
-        <v>67</v>
+        <v>63</v>
       </c>
       <c r="P39" s="4"/>
     </row>
-    <row r="40" spans="1:16" x14ac:dyDescent="0.45">
+    <row r="40" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A40" s="2" t="s">
-        <v>188</v>
+        <v>172</v>
       </c>
       <c r="B40" s="3" t="s">
         <v>61</v>
       </c>
       <c r="C40" s="3" t="s">
-        <v>185</v>
+        <v>119</v>
       </c>
       <c r="D40" s="4" t="s">
-        <v>165</v>
+        <v>153</v>
       </c>
       <c r="E40" s="4" t="s">
-        <v>207</v>
+        <v>154</v>
       </c>
       <c r="F40" s="4" t="s">
-        <v>208</v>
+        <v>155</v>
       </c>
       <c r="G40" s="4" t="s">
-        <v>139</v>
+        <v>123</v>
       </c>
       <c r="H40" s="4"/>
       <c r="I40" s="4"/>
@@ -4486,34 +4563,34 @@
       <c r="L40" s="4"/>
       <c r="M40" s="4"/>
       <c r="N40" s="4" t="s">
-        <v>67</v>
+        <v>63</v>
       </c>
       <c r="O40" s="4" t="s">
-        <v>67</v>
+        <v>63</v>
       </c>
       <c r="P40" s="4"/>
     </row>
-    <row r="41" spans="1:16" x14ac:dyDescent="0.45">
+    <row r="41" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A41" s="2" t="s">
-        <v>191</v>
+        <v>175</v>
       </c>
       <c r="B41" s="3" t="s">
         <v>61</v>
       </c>
       <c r="C41" s="3" t="s">
-        <v>185</v>
+        <v>119</v>
       </c>
       <c r="D41" s="4" t="s">
-        <v>136</v>
+        <v>161</v>
       </c>
       <c r="E41" s="4" t="s">
-        <v>186</v>
+        <v>162</v>
       </c>
       <c r="F41" s="4" t="s">
-        <v>187</v>
+        <v>163</v>
       </c>
       <c r="G41" s="4" t="s">
-        <v>139</v>
+        <v>123</v>
       </c>
       <c r="H41" s="4"/>
       <c r="I41" s="4"/>
@@ -4524,34 +4601,34 @@
       <c r="L41" s="4"/>
       <c r="M41" s="4"/>
       <c r="N41" s="4" t="s">
-        <v>67</v>
+        <v>63</v>
       </c>
       <c r="O41" s="4" t="s">
-        <v>67</v>
+        <v>63</v>
       </c>
       <c r="P41" s="4"/>
     </row>
-    <row r="42" spans="1:16" x14ac:dyDescent="0.45">
+    <row r="42" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A42" s="2" t="s">
-        <v>194</v>
+        <v>178</v>
       </c>
       <c r="B42" s="3" t="s">
         <v>61</v>
       </c>
       <c r="C42" s="3" t="s">
-        <v>185</v>
+        <v>119</v>
       </c>
       <c r="D42" s="4" t="s">
-        <v>141</v>
+        <v>157</v>
       </c>
       <c r="E42" s="4" t="s">
-        <v>189</v>
+        <v>158</v>
       </c>
       <c r="F42" s="4" t="s">
-        <v>190</v>
+        <v>159</v>
       </c>
       <c r="G42" s="4" t="s">
-        <v>139</v>
+        <v>123</v>
       </c>
       <c r="H42" s="4"/>
       <c r="I42" s="4"/>
@@ -4562,34 +4639,34 @@
       <c r="L42" s="4"/>
       <c r="M42" s="4"/>
       <c r="N42" s="4" t="s">
-        <v>67</v>
+        <v>63</v>
       </c>
       <c r="O42" s="4" t="s">
-        <v>67</v>
+        <v>63</v>
       </c>
       <c r="P42" s="4"/>
     </row>
-    <row r="43" spans="1:16" x14ac:dyDescent="0.45">
+    <row r="43" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A43" s="2" t="s">
-        <v>197</v>
+        <v>181</v>
       </c>
       <c r="B43" s="3" t="s">
         <v>61</v>
       </c>
       <c r="C43" s="3" t="s">
-        <v>185</v>
+        <v>119</v>
       </c>
       <c r="D43" s="4" t="s">
-        <v>145</v>
+        <v>165</v>
       </c>
       <c r="E43" s="4" t="s">
-        <v>192</v>
+        <v>166</v>
       </c>
       <c r="F43" s="4" t="s">
-        <v>193</v>
+        <v>167</v>
       </c>
       <c r="G43" s="4" t="s">
-        <v>139</v>
+        <v>123</v>
       </c>
       <c r="H43" s="4"/>
       <c r="I43" s="4"/>
@@ -4600,34 +4677,34 @@
       <c r="L43" s="4"/>
       <c r="M43" s="4"/>
       <c r="N43" s="4" t="s">
-        <v>67</v>
+        <v>63</v>
       </c>
       <c r="O43" s="4" t="s">
-        <v>67</v>
+        <v>63</v>
       </c>
       <c r="P43" s="4"/>
     </row>
-    <row r="44" spans="1:16" x14ac:dyDescent="0.45">
+    <row r="44" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A44" s="2" t="s">
-        <v>200</v>
+        <v>184</v>
       </c>
       <c r="B44" s="3" t="s">
         <v>61</v>
       </c>
       <c r="C44" s="3" t="s">
-        <v>185</v>
+        <v>169</v>
       </c>
       <c r="D44" s="4" t="s">
-        <v>149</v>
+        <v>145</v>
       </c>
       <c r="E44" s="4" t="s">
-        <v>195</v>
+        <v>188</v>
       </c>
       <c r="F44" s="4" t="s">
-        <v>196</v>
+        <v>189</v>
       </c>
       <c r="G44" s="4" t="s">
-        <v>139</v>
+        <v>123</v>
       </c>
       <c r="H44" s="4"/>
       <c r="I44" s="4"/>
@@ -4638,34 +4715,34 @@
       <c r="L44" s="4"/>
       <c r="M44" s="4"/>
       <c r="N44" s="4" t="s">
-        <v>67</v>
+        <v>63</v>
       </c>
       <c r="O44" s="4" t="s">
-        <v>67</v>
+        <v>63</v>
       </c>
       <c r="P44" s="4"/>
     </row>
-    <row r="45" spans="1:16" x14ac:dyDescent="0.45">
+    <row r="45" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A45" s="2" t="s">
-        <v>203</v>
+        <v>187</v>
       </c>
       <c r="B45" s="3" t="s">
         <v>61</v>
       </c>
       <c r="C45" s="3" t="s">
-        <v>185</v>
+        <v>169</v>
       </c>
       <c r="D45" s="4" t="s">
-        <v>153</v>
+        <v>149</v>
       </c>
       <c r="E45" s="4" t="s">
-        <v>198</v>
+        <v>191</v>
       </c>
       <c r="F45" s="4" t="s">
-        <v>199</v>
+        <v>192</v>
       </c>
       <c r="G45" s="4" t="s">
-        <v>139</v>
+        <v>123</v>
       </c>
       <c r="H45" s="4"/>
       <c r="I45" s="4"/>
@@ -4676,34 +4753,34 @@
       <c r="L45" s="4"/>
       <c r="M45" s="4"/>
       <c r="N45" s="4" t="s">
-        <v>67</v>
+        <v>63</v>
       </c>
       <c r="O45" s="4" t="s">
-        <v>67</v>
+        <v>63</v>
       </c>
       <c r="P45" s="4"/>
     </row>
-    <row r="46" spans="1:16" x14ac:dyDescent="0.45">
+    <row r="46" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A46" s="2" t="s">
-        <v>206</v>
+        <v>190</v>
       </c>
       <c r="B46" s="3" t="s">
         <v>61</v>
       </c>
       <c r="C46" s="3" t="s">
-        <v>185</v>
+        <v>169</v>
       </c>
       <c r="D46" s="4" t="s">
-        <v>157</v>
+        <v>120</v>
       </c>
       <c r="E46" s="4" t="s">
-        <v>201</v>
+        <v>170</v>
       </c>
       <c r="F46" s="4" t="s">
-        <v>202</v>
+        <v>171</v>
       </c>
       <c r="G46" s="4" t="s">
-        <v>139</v>
+        <v>123</v>
       </c>
       <c r="H46" s="4"/>
       <c r="I46" s="4"/>
@@ -4714,34 +4791,34 @@
       <c r="L46" s="4"/>
       <c r="M46" s="4"/>
       <c r="N46" s="4" t="s">
-        <v>67</v>
+        <v>63</v>
       </c>
       <c r="O46" s="4" t="s">
-        <v>67</v>
+        <v>63</v>
       </c>
       <c r="P46" s="4"/>
     </row>
-    <row r="47" spans="1:16" x14ac:dyDescent="0.45">
+    <row r="47" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A47" s="2" t="s">
-        <v>209</v>
+        <v>193</v>
       </c>
       <c r="B47" s="3" t="s">
         <v>61</v>
       </c>
       <c r="C47" s="3" t="s">
-        <v>185</v>
+        <v>169</v>
       </c>
       <c r="D47" s="4" t="s">
-        <v>169</v>
+        <v>125</v>
       </c>
       <c r="E47" s="4" t="s">
-        <v>210</v>
+        <v>173</v>
       </c>
       <c r="F47" s="4" t="s">
-        <v>171</v>
+        <v>174</v>
       </c>
       <c r="G47" s="4" t="s">
-        <v>139</v>
+        <v>123</v>
       </c>
       <c r="H47" s="4"/>
       <c r="I47" s="4"/>
@@ -4752,34 +4829,34 @@
       <c r="L47" s="4"/>
       <c r="M47" s="4"/>
       <c r="N47" s="4" t="s">
-        <v>67</v>
+        <v>63</v>
       </c>
       <c r="O47" s="4" t="s">
-        <v>67</v>
+        <v>63</v>
       </c>
       <c r="P47" s="4"/>
     </row>
-    <row r="48" spans="1:16" x14ac:dyDescent="0.45">
+    <row r="48" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A48" s="2" t="s">
-        <v>211</v>
+        <v>195</v>
       </c>
       <c r="B48" s="3" t="s">
         <v>61</v>
       </c>
       <c r="C48" s="3" t="s">
-        <v>185</v>
+        <v>169</v>
       </c>
       <c r="D48" s="4" t="s">
+        <v>129</v>
+      </c>
+      <c r="E48" s="4" t="s">
+        <v>176</v>
+      </c>
+      <c r="F48" s="4" t="s">
         <v>177</v>
       </c>
-      <c r="E48" s="4" t="s">
-        <v>215</v>
-      </c>
-      <c r="F48" s="4" t="s">
-        <v>216</v>
-      </c>
       <c r="G48" s="4" t="s">
-        <v>139</v>
+        <v>123</v>
       </c>
       <c r="H48" s="4"/>
       <c r="I48" s="4"/>
@@ -4790,34 +4867,34 @@
       <c r="L48" s="4"/>
       <c r="M48" s="4"/>
       <c r="N48" s="4" t="s">
-        <v>67</v>
+        <v>63</v>
       </c>
       <c r="O48" s="4" t="s">
-        <v>67</v>
+        <v>63</v>
       </c>
       <c r="P48" s="4"/>
     </row>
-    <row r="49" spans="1:16" x14ac:dyDescent="0.45">
+    <row r="49" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A49" s="2" t="s">
-        <v>214</v>
+        <v>198</v>
       </c>
       <c r="B49" s="3" t="s">
         <v>61</v>
       </c>
       <c r="C49" s="3" t="s">
-        <v>185</v>
+        <v>169</v>
       </c>
       <c r="D49" s="4" t="s">
-        <v>173</v>
+        <v>133</v>
       </c>
       <c r="E49" s="4" t="s">
-        <v>212</v>
+        <v>179</v>
       </c>
       <c r="F49" s="4" t="s">
-        <v>213</v>
+        <v>180</v>
       </c>
       <c r="G49" s="4" t="s">
-        <v>139</v>
+        <v>123</v>
       </c>
       <c r="H49" s="4"/>
       <c r="I49" s="4"/>
@@ -4828,34 +4905,34 @@
       <c r="L49" s="4"/>
       <c r="M49" s="4"/>
       <c r="N49" s="4" t="s">
-        <v>67</v>
+        <v>63</v>
       </c>
       <c r="O49" s="4" t="s">
-        <v>67</v>
+        <v>63</v>
       </c>
       <c r="P49" s="4"/>
     </row>
-    <row r="50" spans="1:16" x14ac:dyDescent="0.45">
+    <row r="50" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A50" s="2" t="s">
-        <v>217</v>
+        <v>201</v>
       </c>
       <c r="B50" s="3" t="s">
         <v>61</v>
       </c>
       <c r="C50" s="3" t="s">
-        <v>185</v>
+        <v>169</v>
       </c>
       <c r="D50" s="4" t="s">
-        <v>218</v>
+        <v>137</v>
       </c>
       <c r="E50" s="4" t="s">
-        <v>219</v>
+        <v>182</v>
       </c>
       <c r="F50" s="4" t="s">
-        <v>220</v>
+        <v>183</v>
       </c>
       <c r="G50" s="4" t="s">
-        <v>139</v>
+        <v>123</v>
       </c>
       <c r="H50" s="4"/>
       <c r="I50" s="4"/>
@@ -4866,38 +4943,36 @@
       <c r="L50" s="4"/>
       <c r="M50" s="4"/>
       <c r="N50" s="4" t="s">
-        <v>67</v>
+        <v>63</v>
       </c>
       <c r="O50" s="4" t="s">
-        <v>67</v>
+        <v>63</v>
       </c>
       <c r="P50" s="4"/>
     </row>
-    <row r="51" spans="1:16" x14ac:dyDescent="0.45">
+    <row r="51" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A51" s="2" t="s">
-        <v>221</v>
+        <v>205</v>
       </c>
       <c r="B51" s="3" t="s">
-        <v>222</v>
+        <v>61</v>
       </c>
       <c r="C51" s="3" t="s">
-        <v>223</v>
+        <v>169</v>
       </c>
       <c r="D51" s="4" t="s">
-        <v>224</v>
+        <v>141</v>
       </c>
       <c r="E51" s="4" t="s">
-        <v>225</v>
+        <v>185</v>
       </c>
       <c r="F51" s="4" t="s">
-        <v>226</v>
+        <v>186</v>
       </c>
       <c r="G51" s="4" t="s">
-        <v>66</v>
-      </c>
-      <c r="H51" s="4" t="s">
-        <v>46</v>
-      </c>
+        <v>123</v>
+      </c>
+      <c r="H51" s="4"/>
       <c r="I51" s="4"/>
       <c r="J51" s="4" t="s">
         <v>23</v>
@@ -4906,34 +4981,34 @@
       <c r="L51" s="4"/>
       <c r="M51" s="4"/>
       <c r="N51" s="4" t="s">
-        <v>67</v>
+        <v>63</v>
       </c>
       <c r="O51" s="4" t="s">
-        <v>67</v>
+        <v>63</v>
       </c>
       <c r="P51" s="4"/>
     </row>
-    <row r="52" spans="1:16" x14ac:dyDescent="0.45">
+    <row r="52" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A52" s="2" t="s">
-        <v>227</v>
+        <v>211</v>
       </c>
       <c r="B52" s="3" t="s">
-        <v>222</v>
+        <v>61</v>
       </c>
       <c r="C52" s="3" t="s">
-        <v>223</v>
+        <v>169</v>
       </c>
       <c r="D52" s="4" t="s">
-        <v>228</v>
+        <v>153</v>
       </c>
       <c r="E52" s="4" t="s">
-        <v>229</v>
+        <v>194</v>
       </c>
       <c r="F52" s="4" t="s">
-        <v>230</v>
+        <v>155</v>
       </c>
       <c r="G52" s="4" t="s">
-        <v>139</v>
+        <v>123</v>
       </c>
       <c r="H52" s="4"/>
       <c r="I52" s="4"/>
@@ -4944,38 +5019,36 @@
       <c r="L52" s="4"/>
       <c r="M52" s="4"/>
       <c r="N52" s="4" t="s">
-        <v>67</v>
+        <v>63</v>
       </c>
       <c r="O52" s="4" t="s">
-        <v>67</v>
+        <v>63</v>
       </c>
       <c r="P52" s="4"/>
     </row>
-    <row r="53" spans="1:16" x14ac:dyDescent="0.45">
+    <row r="53" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A53" s="2" t="s">
-        <v>231</v>
+        <v>215</v>
       </c>
       <c r="B53" s="3" t="s">
-        <v>222</v>
+        <v>61</v>
       </c>
       <c r="C53" s="3" t="s">
-        <v>223</v>
+        <v>169</v>
       </c>
       <c r="D53" s="4" t="s">
-        <v>232</v>
+        <v>161</v>
       </c>
       <c r="E53" s="4" t="s">
-        <v>233</v>
+        <v>199</v>
       </c>
       <c r="F53" s="4" t="s">
-        <v>234</v>
+        <v>200</v>
       </c>
       <c r="G53" s="4" t="s">
-        <v>66</v>
-      </c>
-      <c r="H53" s="4" t="s">
-        <v>46</v>
-      </c>
+        <v>123</v>
+      </c>
+      <c r="H53" s="4"/>
       <c r="I53" s="4"/>
       <c r="J53" s="4" t="s">
         <v>23</v>
@@ -4984,34 +5057,34 @@
       <c r="L53" s="4"/>
       <c r="M53" s="4"/>
       <c r="N53" s="4" t="s">
-        <v>67</v>
+        <v>63</v>
       </c>
       <c r="O53" s="4" t="s">
-        <v>67</v>
+        <v>63</v>
       </c>
       <c r="P53" s="4"/>
     </row>
-    <row r="54" spans="1:16" x14ac:dyDescent="0.45">
+    <row r="54" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A54" s="2" t="s">
-        <v>235</v>
+        <v>219</v>
       </c>
       <c r="B54" s="3" t="s">
-        <v>222</v>
+        <v>61</v>
       </c>
       <c r="C54" s="3" t="s">
-        <v>236</v>
+        <v>169</v>
       </c>
       <c r="D54" s="4" t="s">
-        <v>237</v>
+        <v>157</v>
       </c>
       <c r="E54" s="4" t="s">
-        <v>238</v>
+        <v>196</v>
       </c>
       <c r="F54" s="4" t="s">
-        <v>239</v>
+        <v>197</v>
       </c>
       <c r="G54" s="4" t="s">
-        <v>139</v>
+        <v>123</v>
       </c>
       <c r="H54" s="4"/>
       <c r="I54" s="4"/>
@@ -5022,34 +5095,34 @@
       <c r="L54" s="4"/>
       <c r="M54" s="4"/>
       <c r="N54" s="4" t="s">
-        <v>67</v>
+        <v>63</v>
       </c>
       <c r="O54" s="4" t="s">
-        <v>67</v>
+        <v>63</v>
       </c>
       <c r="P54" s="4"/>
     </row>
-    <row r="55" spans="1:16" x14ac:dyDescent="0.45">
+    <row r="55" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A55" s="2" t="s">
-        <v>240</v>
+        <v>224</v>
       </c>
       <c r="B55" s="3" t="s">
-        <v>222</v>
+        <v>61</v>
       </c>
       <c r="C55" s="3" t="s">
-        <v>236</v>
+        <v>169</v>
       </c>
       <c r="D55" s="4" t="s">
-        <v>241</v>
+        <v>202</v>
       </c>
       <c r="E55" s="4" t="s">
-        <v>242</v>
+        <v>203</v>
       </c>
       <c r="F55" s="4" t="s">
-        <v>243</v>
+        <v>204</v>
       </c>
       <c r="G55" s="4" t="s">
-        <v>139</v>
+        <v>123</v>
       </c>
       <c r="H55" s="4"/>
       <c r="I55" s="4"/>
@@ -5060,36 +5133,38 @@
       <c r="L55" s="4"/>
       <c r="M55" s="4"/>
       <c r="N55" s="4" t="s">
-        <v>67</v>
+        <v>63</v>
       </c>
       <c r="O55" s="4" t="s">
-        <v>67</v>
+        <v>63</v>
       </c>
       <c r="P55" s="4"/>
     </row>
-    <row r="56" spans="1:16" x14ac:dyDescent="0.45">
+    <row r="56" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A56" s="2" t="s">
-        <v>244</v>
+        <v>228</v>
       </c>
       <c r="B56" s="3" t="s">
-        <v>222</v>
+        <v>206</v>
       </c>
       <c r="C56" s="3" t="s">
-        <v>236</v>
+        <v>207</v>
       </c>
       <c r="D56" s="4" t="s">
-        <v>245</v>
+        <v>208</v>
       </c>
       <c r="E56" s="4" t="s">
-        <v>246</v>
+        <v>209</v>
       </c>
       <c r="F56" s="4" t="s">
-        <v>247</v>
+        <v>210</v>
       </c>
       <c r="G56" s="4" t="s">
-        <v>139</v>
-      </c>
-      <c r="H56" s="4"/>
+        <v>62</v>
+      </c>
+      <c r="H56" s="4" t="s">
+        <v>46</v>
+      </c>
       <c r="I56" s="4"/>
       <c r="J56" s="4" t="s">
         <v>23</v>
@@ -5098,34 +5173,34 @@
       <c r="L56" s="4"/>
       <c r="M56" s="4"/>
       <c r="N56" s="4" t="s">
-        <v>67</v>
+        <v>63</v>
       </c>
       <c r="O56" s="4" t="s">
-        <v>67</v>
+        <v>63</v>
       </c>
       <c r="P56" s="4"/>
     </row>
-    <row r="57" spans="1:16" x14ac:dyDescent="0.45">
+    <row r="57" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A57" s="2" t="s">
-        <v>248</v>
+        <v>232</v>
       </c>
       <c r="B57" s="3" t="s">
-        <v>222</v>
+        <v>206</v>
       </c>
       <c r="C57" s="3" t="s">
-        <v>236</v>
+        <v>207</v>
       </c>
       <c r="D57" s="4" t="s">
-        <v>249</v>
+        <v>212</v>
       </c>
       <c r="E57" s="4" t="s">
-        <v>250</v>
+        <v>213</v>
       </c>
       <c r="F57" s="4" t="s">
-        <v>251</v>
+        <v>214</v>
       </c>
       <c r="G57" s="4" t="s">
-        <v>139</v>
+        <v>123</v>
       </c>
       <c r="H57" s="4"/>
       <c r="I57" s="4"/>
@@ -5136,36 +5211,38 @@
       <c r="L57" s="4"/>
       <c r="M57" s="4"/>
       <c r="N57" s="4" t="s">
-        <v>67</v>
+        <v>63</v>
       </c>
       <c r="O57" s="4" t="s">
-        <v>67</v>
+        <v>63</v>
       </c>
       <c r="P57" s="4"/>
     </row>
-    <row r="58" spans="1:16" x14ac:dyDescent="0.45">
+    <row r="58" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A58" s="2" t="s">
-        <v>252</v>
+        <v>236</v>
       </c>
       <c r="B58" s="3" t="s">
-        <v>222</v>
+        <v>206</v>
       </c>
       <c r="C58" s="3" t="s">
-        <v>236</v>
+        <v>207</v>
       </c>
       <c r="D58" s="4" t="s">
-        <v>261</v>
+        <v>216</v>
       </c>
       <c r="E58" s="4" t="s">
-        <v>262</v>
+        <v>217</v>
       </c>
       <c r="F58" s="4" t="s">
-        <v>263</v>
+        <v>218</v>
       </c>
       <c r="G58" s="4" t="s">
-        <v>139</v>
-      </c>
-      <c r="H58" s="4"/>
+        <v>62</v>
+      </c>
+      <c r="H58" s="4" t="s">
+        <v>46</v>
+      </c>
       <c r="I58" s="4"/>
       <c r="J58" s="4" t="s">
         <v>23</v>
@@ -5174,34 +5251,34 @@
       <c r="L58" s="4"/>
       <c r="M58" s="4"/>
       <c r="N58" s="4" t="s">
-        <v>67</v>
+        <v>63</v>
       </c>
       <c r="O58" s="4" t="s">
-        <v>67</v>
+        <v>63</v>
       </c>
       <c r="P58" s="4"/>
     </row>
-    <row r="59" spans="1:16" x14ac:dyDescent="0.45">
+    <row r="59" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A59" s="2" t="s">
-        <v>256</v>
+        <v>240</v>
       </c>
       <c r="B59" s="3" t="s">
+        <v>206</v>
+      </c>
+      <c r="C59" s="3" t="s">
+        <v>220</v>
+      </c>
+      <c r="D59" s="4" t="s">
+        <v>221</v>
+      </c>
+      <c r="E59" s="4" t="s">
         <v>222</v>
       </c>
-      <c r="C59" s="3" t="s">
-        <v>236</v>
-      </c>
-      <c r="D59" s="4" t="s">
-        <v>265</v>
-      </c>
-      <c r="E59" s="4" t="s">
-        <v>266</v>
-      </c>
       <c r="F59" s="4" t="s">
-        <v>267</v>
+        <v>223</v>
       </c>
       <c r="G59" s="4" t="s">
-        <v>139</v>
+        <v>123</v>
       </c>
       <c r="H59" s="4"/>
       <c r="I59" s="4"/>
@@ -5212,34 +5289,34 @@
       <c r="L59" s="4"/>
       <c r="M59" s="4"/>
       <c r="N59" s="4" t="s">
-        <v>67</v>
+        <v>63</v>
       </c>
       <c r="O59" s="4" t="s">
-        <v>67</v>
+        <v>63</v>
       </c>
       <c r="P59" s="4"/>
     </row>
-    <row r="60" spans="1:16" x14ac:dyDescent="0.45">
+    <row r="60" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A60" s="2" t="s">
-        <v>260</v>
+        <v>244</v>
       </c>
       <c r="B60" s="3" t="s">
-        <v>222</v>
+        <v>206</v>
       </c>
       <c r="C60" s="3" t="s">
-        <v>236</v>
+        <v>220</v>
       </c>
       <c r="D60" s="4" t="s">
-        <v>253</v>
+        <v>225</v>
       </c>
       <c r="E60" s="4" t="s">
-        <v>254</v>
+        <v>226</v>
       </c>
       <c r="F60" s="4" t="s">
-        <v>255</v>
+        <v>227</v>
       </c>
       <c r="G60" s="4" t="s">
-        <v>139</v>
+        <v>123</v>
       </c>
       <c r="H60" s="4"/>
       <c r="I60" s="4"/>
@@ -5250,34 +5327,34 @@
       <c r="L60" s="4"/>
       <c r="M60" s="4"/>
       <c r="N60" s="4" t="s">
-        <v>67</v>
+        <v>63</v>
       </c>
       <c r="O60" s="4" t="s">
-        <v>67</v>
+        <v>63</v>
       </c>
       <c r="P60" s="4"/>
     </row>
-    <row r="61" spans="1:16" x14ac:dyDescent="0.45">
+    <row r="61" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A61" s="2" t="s">
-        <v>264</v>
+        <v>248</v>
       </c>
       <c r="B61" s="3" t="s">
-        <v>222</v>
+        <v>206</v>
       </c>
       <c r="C61" s="3" t="s">
-        <v>236</v>
+        <v>220</v>
       </c>
       <c r="D61" s="4" t="s">
-        <v>257</v>
+        <v>229</v>
       </c>
       <c r="E61" s="4" t="s">
-        <v>258</v>
+        <v>230</v>
       </c>
       <c r="F61" s="4" t="s">
-        <v>259</v>
+        <v>231</v>
       </c>
       <c r="G61" s="4" t="s">
-        <v>139</v>
+        <v>123</v>
       </c>
       <c r="H61" s="4"/>
       <c r="I61" s="4"/>
@@ -5288,34 +5365,34 @@
       <c r="L61" s="4"/>
       <c r="M61" s="4"/>
       <c r="N61" s="4" t="s">
-        <v>67</v>
+        <v>63</v>
       </c>
       <c r="O61" s="4" t="s">
-        <v>67</v>
+        <v>63</v>
       </c>
       <c r="P61" s="4"/>
     </row>
-    <row r="62" spans="1:16" x14ac:dyDescent="0.45">
+    <row r="62" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A62" s="2" t="s">
-        <v>268</v>
+        <v>252</v>
       </c>
       <c r="B62" s="3" t="s">
-        <v>222</v>
+        <v>206</v>
       </c>
       <c r="C62" s="3" t="s">
-        <v>284</v>
+        <v>220</v>
       </c>
       <c r="D62" s="4" t="s">
-        <v>285</v>
+        <v>233</v>
       </c>
       <c r="E62" s="4" t="s">
-        <v>286</v>
+        <v>234</v>
       </c>
       <c r="F62" s="4" t="s">
-        <v>287</v>
+        <v>235</v>
       </c>
       <c r="G62" s="4" t="s">
-        <v>139</v>
+        <v>123</v>
       </c>
       <c r="H62" s="4"/>
       <c r="I62" s="4"/>
@@ -5326,34 +5403,34 @@
       <c r="L62" s="4"/>
       <c r="M62" s="4"/>
       <c r="N62" s="4" t="s">
-        <v>67</v>
+        <v>63</v>
       </c>
       <c r="O62" s="4" t="s">
-        <v>67</v>
+        <v>63</v>
       </c>
       <c r="P62" s="4"/>
     </row>
-    <row r="63" spans="1:16" x14ac:dyDescent="0.45">
+    <row r="63" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A63" s="2" t="s">
-        <v>271</v>
+        <v>255</v>
       </c>
       <c r="B63" s="3" t="s">
-        <v>222</v>
+        <v>206</v>
       </c>
       <c r="C63" s="3" t="s">
-        <v>284</v>
+        <v>220</v>
       </c>
       <c r="D63" s="4" t="s">
-        <v>289</v>
+        <v>245</v>
       </c>
       <c r="E63" s="4" t="s">
-        <v>290</v>
+        <v>246</v>
       </c>
       <c r="F63" s="4" t="s">
-        <v>291</v>
+        <v>247</v>
       </c>
       <c r="G63" s="4" t="s">
-        <v>139</v>
+        <v>123</v>
       </c>
       <c r="H63" s="4"/>
       <c r="I63" s="4"/>
@@ -5364,34 +5441,34 @@
       <c r="L63" s="4"/>
       <c r="M63" s="4"/>
       <c r="N63" s="4" t="s">
-        <v>67</v>
+        <v>63</v>
       </c>
       <c r="O63" s="4" t="s">
-        <v>67</v>
+        <v>63</v>
       </c>
       <c r="P63" s="4"/>
     </row>
-    <row r="64" spans="1:16" x14ac:dyDescent="0.45">
+    <row r="64" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A64" s="2" t="s">
-        <v>275</v>
+        <v>259</v>
       </c>
       <c r="B64" s="3" t="s">
-        <v>222</v>
+        <v>206</v>
       </c>
       <c r="C64" s="3" t="s">
-        <v>284</v>
+        <v>220</v>
       </c>
       <c r="D64" s="4" t="s">
-        <v>293</v>
+        <v>249</v>
       </c>
       <c r="E64" s="4" t="s">
-        <v>294</v>
+        <v>250</v>
       </c>
       <c r="F64" s="4" t="s">
-        <v>295</v>
+        <v>251</v>
       </c>
       <c r="G64" s="4" t="s">
-        <v>139</v>
+        <v>123</v>
       </c>
       <c r="H64" s="4"/>
       <c r="I64" s="4"/>
@@ -5402,34 +5479,34 @@
       <c r="L64" s="4"/>
       <c r="M64" s="4"/>
       <c r="N64" s="4" t="s">
-        <v>67</v>
+        <v>63</v>
       </c>
       <c r="O64" s="4" t="s">
-        <v>67</v>
+        <v>63</v>
       </c>
       <c r="P64" s="4"/>
     </row>
-    <row r="65" spans="1:16" x14ac:dyDescent="0.45">
+    <row r="65" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A65" s="2" t="s">
-        <v>279</v>
+        <v>263</v>
       </c>
       <c r="B65" s="3" t="s">
-        <v>222</v>
+        <v>206</v>
       </c>
       <c r="C65" s="3" t="s">
-        <v>284</v>
+        <v>220</v>
       </c>
       <c r="D65" s="4" t="s">
-        <v>297</v>
+        <v>237</v>
       </c>
       <c r="E65" s="4" t="s">
-        <v>298</v>
+        <v>238</v>
       </c>
       <c r="F65" s="4" t="s">
-        <v>299</v>
+        <v>239</v>
       </c>
       <c r="G65" s="4" t="s">
-        <v>139</v>
+        <v>123</v>
       </c>
       <c r="H65" s="4"/>
       <c r="I65" s="4"/>
@@ -5440,34 +5517,34 @@
       <c r="L65" s="4"/>
       <c r="M65" s="4"/>
       <c r="N65" s="4" t="s">
-        <v>67</v>
+        <v>63</v>
       </c>
       <c r="O65" s="4" t="s">
-        <v>67</v>
+        <v>63</v>
       </c>
       <c r="P65" s="4"/>
     </row>
-    <row r="66" spans="1:16" x14ac:dyDescent="0.45">
+    <row r="66" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A66" s="2" t="s">
-        <v>283</v>
+        <v>267</v>
       </c>
       <c r="B66" s="3" t="s">
-        <v>222</v>
+        <v>206</v>
       </c>
       <c r="C66" s="3" t="s">
-        <v>284</v>
+        <v>220</v>
       </c>
       <c r="D66" s="4" t="s">
-        <v>301</v>
+        <v>241</v>
       </c>
       <c r="E66" s="4" t="s">
-        <v>302</v>
+        <v>242</v>
       </c>
       <c r="F66" s="4" t="s">
-        <v>303</v>
+        <v>243</v>
       </c>
       <c r="G66" s="4" t="s">
-        <v>139</v>
+        <v>123</v>
       </c>
       <c r="H66" s="4"/>
       <c r="I66" s="4"/>
@@ -5478,34 +5555,34 @@
       <c r="L66" s="4"/>
       <c r="M66" s="4"/>
       <c r="N66" s="4" t="s">
-        <v>67</v>
+        <v>63</v>
       </c>
       <c r="O66" s="4" t="s">
-        <v>67</v>
+        <v>63</v>
       </c>
       <c r="P66" s="4"/>
     </row>
-    <row r="67" spans="1:16" x14ac:dyDescent="0.45">
+    <row r="67" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A67" s="2" t="s">
-        <v>288</v>
+        <v>272</v>
       </c>
       <c r="B67" s="3" t="s">
-        <v>222</v>
+        <v>206</v>
       </c>
       <c r="C67" s="3" t="s">
-        <v>284</v>
+        <v>268</v>
       </c>
       <c r="D67" s="4" t="s">
-        <v>305</v>
+        <v>269</v>
       </c>
       <c r="E67" s="4" t="s">
-        <v>306</v>
+        <v>270</v>
       </c>
       <c r="F67" s="4" t="s">
-        <v>307</v>
+        <v>271</v>
       </c>
       <c r="G67" s="4" t="s">
-        <v>139</v>
+        <v>123</v>
       </c>
       <c r="H67" s="4"/>
       <c r="I67" s="4"/>
@@ -5516,34 +5593,34 @@
       <c r="L67" s="4"/>
       <c r="M67" s="4"/>
       <c r="N67" s="4" t="s">
-        <v>67</v>
+        <v>63</v>
       </c>
       <c r="O67" s="4" t="s">
-        <v>67</v>
+        <v>63</v>
       </c>
       <c r="P67" s="4"/>
     </row>
-    <row r="68" spans="1:16" x14ac:dyDescent="0.45">
+    <row r="68" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A68" s="2" t="s">
-        <v>292</v>
+        <v>276</v>
       </c>
       <c r="B68" s="3" t="s">
-        <v>222</v>
+        <v>206</v>
       </c>
       <c r="C68" s="3" t="s">
-        <v>809</v>
+        <v>268</v>
       </c>
       <c r="D68" s="4" t="s">
-        <v>181</v>
+        <v>273</v>
       </c>
       <c r="E68" s="4" t="s">
-        <v>269</v>
+        <v>274</v>
       </c>
       <c r="F68" s="4" t="s">
-        <v>270</v>
+        <v>275</v>
       </c>
       <c r="G68" s="4" t="s">
-        <v>139</v>
+        <v>123</v>
       </c>
       <c r="H68" s="4"/>
       <c r="I68" s="4"/>
@@ -5554,34 +5631,34 @@
       <c r="L68" s="4"/>
       <c r="M68" s="4"/>
       <c r="N68" s="4" t="s">
-        <v>67</v>
+        <v>63</v>
       </c>
       <c r="O68" s="4" t="s">
-        <v>67</v>
+        <v>63</v>
       </c>
       <c r="P68" s="4"/>
     </row>
-    <row r="69" spans="1:16" x14ac:dyDescent="0.45">
+    <row r="69" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A69" s="2" t="s">
-        <v>296</v>
+        <v>280</v>
       </c>
       <c r="B69" s="3" t="s">
-        <v>222</v>
+        <v>206</v>
       </c>
       <c r="C69" s="3" t="s">
-        <v>809</v>
+        <v>268</v>
       </c>
       <c r="D69" s="4" t="s">
-        <v>272</v>
+        <v>277</v>
       </c>
       <c r="E69" s="4" t="s">
-        <v>273</v>
+        <v>278</v>
       </c>
       <c r="F69" s="4" t="s">
-        <v>274</v>
+        <v>279</v>
       </c>
       <c r="G69" s="4" t="s">
-        <v>139</v>
+        <v>123</v>
       </c>
       <c r="H69" s="4"/>
       <c r="I69" s="4"/>
@@ -5592,34 +5669,34 @@
       <c r="L69" s="4"/>
       <c r="M69" s="4"/>
       <c r="N69" s="4" t="s">
-        <v>67</v>
+        <v>63</v>
       </c>
       <c r="O69" s="4" t="s">
-        <v>67</v>
+        <v>63</v>
       </c>
       <c r="P69" s="4"/>
     </row>
-    <row r="70" spans="1:16" x14ac:dyDescent="0.45">
+    <row r="70" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A70" s="2" t="s">
-        <v>300</v>
+        <v>284</v>
       </c>
       <c r="B70" s="3" t="s">
-        <v>222</v>
+        <v>206</v>
       </c>
       <c r="C70" s="3" t="s">
-        <v>809</v>
+        <v>268</v>
       </c>
       <c r="D70" s="4" t="s">
-        <v>276</v>
+        <v>281</v>
       </c>
       <c r="E70" s="4" t="s">
-        <v>277</v>
+        <v>282</v>
       </c>
       <c r="F70" s="4" t="s">
-        <v>278</v>
+        <v>283</v>
       </c>
       <c r="G70" s="4" t="s">
-        <v>139</v>
+        <v>123</v>
       </c>
       <c r="H70" s="4"/>
       <c r="I70" s="4"/>
@@ -5630,34 +5707,34 @@
       <c r="L70" s="4"/>
       <c r="M70" s="4"/>
       <c r="N70" s="4" t="s">
-        <v>67</v>
+        <v>63</v>
       </c>
       <c r="O70" s="4" t="s">
-        <v>67</v>
+        <v>63</v>
       </c>
       <c r="P70" s="4"/>
     </row>
-    <row r="71" spans="1:16" x14ac:dyDescent="0.45">
+    <row r="71" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A71" s="2" t="s">
-        <v>304</v>
+        <v>288</v>
       </c>
       <c r="B71" s="3" t="s">
-        <v>222</v>
+        <v>206</v>
       </c>
       <c r="C71" s="3" t="s">
-        <v>809</v>
+        <v>268</v>
       </c>
       <c r="D71" s="4" t="s">
-        <v>280</v>
+        <v>285</v>
       </c>
       <c r="E71" s="4" t="s">
-        <v>281</v>
+        <v>286</v>
       </c>
       <c r="F71" s="4" t="s">
-        <v>282</v>
+        <v>287</v>
       </c>
       <c r="G71" s="4" t="s">
-        <v>139</v>
+        <v>123</v>
       </c>
       <c r="H71" s="4"/>
       <c r="I71" s="4"/>
@@ -5668,34 +5745,34 @@
       <c r="L71" s="4"/>
       <c r="M71" s="4"/>
       <c r="N71" s="4" t="s">
-        <v>67</v>
+        <v>63</v>
       </c>
       <c r="O71" s="4" t="s">
-        <v>67</v>
+        <v>63</v>
       </c>
       <c r="P71" s="4"/>
     </row>
-    <row r="72" spans="1:16" x14ac:dyDescent="0.45">
+    <row r="72" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A72" s="2" t="s">
-        <v>308</v>
+        <v>292</v>
       </c>
       <c r="B72" s="3" t="s">
-        <v>222</v>
+        <v>206</v>
       </c>
       <c r="C72" s="3" t="s">
-        <v>309</v>
+        <v>268</v>
       </c>
       <c r="D72" s="4" t="s">
-        <v>310</v>
+        <v>289</v>
       </c>
       <c r="E72" s="4" t="s">
-        <v>311</v>
+        <v>290</v>
       </c>
       <c r="F72" s="4" t="s">
-        <v>312</v>
+        <v>291</v>
       </c>
       <c r="G72" s="4" t="s">
-        <v>139</v>
+        <v>123</v>
       </c>
       <c r="H72" s="4"/>
       <c r="I72" s="4"/>
@@ -5706,34 +5783,34 @@
       <c r="L72" s="4"/>
       <c r="M72" s="4"/>
       <c r="N72" s="4" t="s">
-        <v>67</v>
+        <v>63</v>
       </c>
       <c r="O72" s="4" t="s">
-        <v>67</v>
+        <v>63</v>
       </c>
       <c r="P72" s="4"/>
     </row>
-    <row r="73" spans="1:16" x14ac:dyDescent="0.45">
+    <row r="73" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A73" s="2" t="s">
-        <v>313</v>
+        <v>297</v>
       </c>
       <c r="B73" s="3" t="s">
-        <v>222</v>
+        <v>206</v>
       </c>
       <c r="C73" s="3" t="s">
-        <v>309</v>
+        <v>793</v>
       </c>
       <c r="D73" s="4" t="s">
-        <v>314</v>
+        <v>165</v>
       </c>
       <c r="E73" s="4" t="s">
-        <v>315</v>
+        <v>253</v>
       </c>
       <c r="F73" s="4" t="s">
-        <v>316</v>
+        <v>254</v>
       </c>
       <c r="G73" s="4" t="s">
-        <v>139</v>
+        <v>123</v>
       </c>
       <c r="H73" s="4"/>
       <c r="I73" s="4"/>
@@ -5744,34 +5821,34 @@
       <c r="L73" s="4"/>
       <c r="M73" s="4"/>
       <c r="N73" s="4" t="s">
-        <v>67</v>
+        <v>63</v>
       </c>
       <c r="O73" s="4" t="s">
-        <v>67</v>
+        <v>63</v>
       </c>
       <c r="P73" s="4"/>
     </row>
-    <row r="74" spans="1:16" x14ac:dyDescent="0.45">
+    <row r="74" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A74" s="2" t="s">
-        <v>317</v>
+        <v>301</v>
       </c>
       <c r="B74" s="3" t="s">
-        <v>222</v>
+        <v>206</v>
       </c>
       <c r="C74" s="3" t="s">
-        <v>309</v>
+        <v>793</v>
       </c>
       <c r="D74" s="4" t="s">
-        <v>318</v>
+        <v>256</v>
       </c>
       <c r="E74" s="4" t="s">
-        <v>319</v>
+        <v>257</v>
       </c>
       <c r="F74" s="4" t="s">
-        <v>320</v>
+        <v>258</v>
       </c>
       <c r="G74" s="4" t="s">
-        <v>139</v>
+        <v>123</v>
       </c>
       <c r="H74" s="4"/>
       <c r="I74" s="4"/>
@@ -5782,34 +5859,34 @@
       <c r="L74" s="4"/>
       <c r="M74" s="4"/>
       <c r="N74" s="4" t="s">
-        <v>67</v>
+        <v>63</v>
       </c>
       <c r="O74" s="4" t="s">
-        <v>67</v>
+        <v>63</v>
       </c>
       <c r="P74" s="4"/>
     </row>
-    <row r="75" spans="1:16" x14ac:dyDescent="0.45">
+    <row r="75" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A75" s="2" t="s">
-        <v>321</v>
+        <v>305</v>
       </c>
       <c r="B75" s="3" t="s">
-        <v>222</v>
+        <v>206</v>
       </c>
       <c r="C75" s="3" t="s">
-        <v>309</v>
+        <v>793</v>
       </c>
       <c r="D75" s="4" t="s">
-        <v>322</v>
+        <v>260</v>
       </c>
       <c r="E75" s="4" t="s">
-        <v>323</v>
+        <v>261</v>
       </c>
       <c r="F75" s="4" t="s">
-        <v>324</v>
+        <v>262</v>
       </c>
       <c r="G75" s="4" t="s">
-        <v>139</v>
+        <v>123</v>
       </c>
       <c r="H75" s="4"/>
       <c r="I75" s="4"/>
@@ -5820,34 +5897,34 @@
       <c r="L75" s="4"/>
       <c r="M75" s="4"/>
       <c r="N75" s="4" t="s">
-        <v>67</v>
+        <v>63</v>
       </c>
       <c r="O75" s="4" t="s">
-        <v>67</v>
+        <v>63</v>
       </c>
       <c r="P75" s="4"/>
     </row>
-    <row r="76" spans="1:16" x14ac:dyDescent="0.45">
+    <row r="76" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A76" s="2" t="s">
-        <v>325</v>
+        <v>309</v>
       </c>
       <c r="B76" s="3" t="s">
-        <v>222</v>
+        <v>206</v>
       </c>
       <c r="C76" s="3" t="s">
-        <v>309</v>
+        <v>793</v>
       </c>
       <c r="D76" s="4" t="s">
-        <v>334</v>
+        <v>264</v>
       </c>
       <c r="E76" s="4" t="s">
-        <v>335</v>
+        <v>265</v>
       </c>
       <c r="F76" s="4" t="s">
-        <v>336</v>
+        <v>266</v>
       </c>
       <c r="G76" s="4" t="s">
-        <v>139</v>
+        <v>123</v>
       </c>
       <c r="H76" s="4"/>
       <c r="I76" s="4"/>
@@ -5858,34 +5935,34 @@
       <c r="L76" s="4"/>
       <c r="M76" s="4"/>
       <c r="N76" s="4" t="s">
-        <v>67</v>
+        <v>63</v>
       </c>
       <c r="O76" s="4" t="s">
-        <v>67</v>
+        <v>63</v>
       </c>
       <c r="P76" s="4"/>
     </row>
-    <row r="77" spans="1:16" x14ac:dyDescent="0.45">
+    <row r="77" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A77" s="2" t="s">
-        <v>329</v>
+        <v>313</v>
       </c>
       <c r="B77" s="3" t="s">
-        <v>222</v>
+        <v>206</v>
       </c>
       <c r="C77" s="3" t="s">
-        <v>309</v>
+        <v>293</v>
       </c>
       <c r="D77" s="4" t="s">
-        <v>338</v>
+        <v>294</v>
       </c>
       <c r="E77" s="4" t="s">
-        <v>339</v>
+        <v>295</v>
       </c>
       <c r="F77" s="4" t="s">
-        <v>340</v>
+        <v>296</v>
       </c>
       <c r="G77" s="4" t="s">
-        <v>139</v>
+        <v>123</v>
       </c>
       <c r="H77" s="4"/>
       <c r="I77" s="4"/>
@@ -5896,34 +5973,34 @@
       <c r="L77" s="4"/>
       <c r="M77" s="4"/>
       <c r="N77" s="4" t="s">
-        <v>67</v>
+        <v>63</v>
       </c>
       <c r="O77" s="4" t="s">
-        <v>67</v>
+        <v>63</v>
       </c>
       <c r="P77" s="4"/>
     </row>
-    <row r="78" spans="1:16" x14ac:dyDescent="0.45">
+    <row r="78" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A78" s="2" t="s">
-        <v>333</v>
+        <v>317</v>
       </c>
       <c r="B78" s="3" t="s">
-        <v>222</v>
+        <v>206</v>
       </c>
       <c r="C78" s="3" t="s">
-        <v>309</v>
+        <v>293</v>
       </c>
       <c r="D78" s="4" t="s">
-        <v>326</v>
+        <v>298</v>
       </c>
       <c r="E78" s="4" t="s">
-        <v>327</v>
+        <v>299</v>
       </c>
       <c r="F78" s="4" t="s">
-        <v>328</v>
+        <v>300</v>
       </c>
       <c r="G78" s="4" t="s">
-        <v>139</v>
+        <v>123</v>
       </c>
       <c r="H78" s="4"/>
       <c r="I78" s="4"/>
@@ -5934,34 +6011,34 @@
       <c r="L78" s="4"/>
       <c r="M78" s="4"/>
       <c r="N78" s="4" t="s">
-        <v>67</v>
+        <v>63</v>
       </c>
       <c r="O78" s="4" t="s">
-        <v>67</v>
+        <v>63</v>
       </c>
       <c r="P78" s="4"/>
     </row>
-    <row r="79" spans="1:16" x14ac:dyDescent="0.45">
+    <row r="79" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A79" s="2" t="s">
-        <v>337</v>
+        <v>321</v>
       </c>
       <c r="B79" s="3" t="s">
-        <v>222</v>
+        <v>206</v>
       </c>
       <c r="C79" s="3" t="s">
-        <v>309</v>
+        <v>293</v>
       </c>
       <c r="D79" s="4" t="s">
-        <v>330</v>
+        <v>302</v>
       </c>
       <c r="E79" s="4" t="s">
-        <v>331</v>
+        <v>303</v>
       </c>
       <c r="F79" s="4" t="s">
-        <v>332</v>
+        <v>304</v>
       </c>
       <c r="G79" s="4" t="s">
-        <v>139</v>
+        <v>123</v>
       </c>
       <c r="H79" s="4"/>
       <c r="I79" s="4"/>
@@ -5972,34 +6049,34 @@
       <c r="L79" s="4"/>
       <c r="M79" s="4"/>
       <c r="N79" s="4" t="s">
-        <v>67</v>
+        <v>63</v>
       </c>
       <c r="O79" s="4" t="s">
-        <v>67</v>
+        <v>63</v>
       </c>
       <c r="P79" s="4"/>
     </row>
-    <row r="80" spans="1:16" x14ac:dyDescent="0.45">
+    <row r="80" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A80" s="2" t="s">
-        <v>341</v>
+        <v>325</v>
       </c>
       <c r="B80" s="3" t="s">
-        <v>222</v>
+        <v>206</v>
       </c>
       <c r="C80" s="3" t="s">
-        <v>357</v>
+        <v>293</v>
       </c>
       <c r="D80" s="4" t="s">
-        <v>358</v>
+        <v>306</v>
       </c>
       <c r="E80" s="4" t="s">
-        <v>359</v>
+        <v>307</v>
       </c>
       <c r="F80" s="4" t="s">
-        <v>360</v>
+        <v>308</v>
       </c>
       <c r="G80" s="4" t="s">
-        <v>139</v>
+        <v>123</v>
       </c>
       <c r="H80" s="4"/>
       <c r="I80" s="4"/>
@@ -6010,34 +6087,34 @@
       <c r="L80" s="4"/>
       <c r="M80" s="4"/>
       <c r="N80" s="4" t="s">
-        <v>67</v>
+        <v>63</v>
       </c>
       <c r="O80" s="4" t="s">
-        <v>67</v>
+        <v>63</v>
       </c>
       <c r="P80" s="4"/>
     </row>
-    <row r="81" spans="1:16" x14ac:dyDescent="0.45">
+    <row r="81" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A81" s="2" t="s">
-        <v>344</v>
+        <v>328</v>
       </c>
       <c r="B81" s="3" t="s">
-        <v>222</v>
+        <v>206</v>
       </c>
       <c r="C81" s="3" t="s">
-        <v>357</v>
+        <v>293</v>
       </c>
       <c r="D81" s="4" t="s">
-        <v>362</v>
+        <v>318</v>
       </c>
       <c r="E81" s="4" t="s">
-        <v>363</v>
+        <v>319</v>
       </c>
       <c r="F81" s="4" t="s">
-        <v>364</v>
+        <v>320</v>
       </c>
       <c r="G81" s="4" t="s">
-        <v>139</v>
+        <v>123</v>
       </c>
       <c r="H81" s="4"/>
       <c r="I81" s="4"/>
@@ -6048,34 +6125,34 @@
       <c r="L81" s="4"/>
       <c r="M81" s="4"/>
       <c r="N81" s="4" t="s">
-        <v>67</v>
+        <v>63</v>
       </c>
       <c r="O81" s="4" t="s">
-        <v>67</v>
+        <v>63</v>
       </c>
       <c r="P81" s="4"/>
     </row>
-    <row r="82" spans="1:16" x14ac:dyDescent="0.45">
+    <row r="82" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A82" s="2" t="s">
-        <v>348</v>
+        <v>332</v>
       </c>
       <c r="B82" s="3" t="s">
-        <v>222</v>
+        <v>206</v>
       </c>
       <c r="C82" s="3" t="s">
-        <v>357</v>
+        <v>293</v>
       </c>
       <c r="D82" s="4" t="s">
-        <v>366</v>
+        <v>322</v>
       </c>
       <c r="E82" s="4" t="s">
-        <v>367</v>
+        <v>323</v>
       </c>
       <c r="F82" s="4" t="s">
-        <v>368</v>
+        <v>324</v>
       </c>
       <c r="G82" s="4" t="s">
-        <v>139</v>
+        <v>123</v>
       </c>
       <c r="H82" s="4"/>
       <c r="I82" s="4"/>
@@ -6086,34 +6163,34 @@
       <c r="L82" s="4"/>
       <c r="M82" s="4"/>
       <c r="N82" s="4" t="s">
-        <v>67</v>
+        <v>63</v>
       </c>
       <c r="O82" s="4" t="s">
-        <v>67</v>
+        <v>63</v>
       </c>
       <c r="P82" s="4"/>
     </row>
-    <row r="83" spans="1:16" x14ac:dyDescent="0.45">
+    <row r="83" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A83" s="2" t="s">
-        <v>352</v>
+        <v>336</v>
       </c>
       <c r="B83" s="3" t="s">
-        <v>222</v>
+        <v>206</v>
       </c>
       <c r="C83" s="3" t="s">
-        <v>357</v>
+        <v>293</v>
       </c>
       <c r="D83" s="4" t="s">
-        <v>370</v>
+        <v>310</v>
       </c>
       <c r="E83" s="4" t="s">
-        <v>371</v>
+        <v>311</v>
       </c>
       <c r="F83" s="4" t="s">
-        <v>372</v>
+        <v>312</v>
       </c>
       <c r="G83" s="4" t="s">
-        <v>139</v>
+        <v>123</v>
       </c>
       <c r="H83" s="4"/>
       <c r="I83" s="4"/>
@@ -6124,34 +6201,34 @@
       <c r="L83" s="4"/>
       <c r="M83" s="4"/>
       <c r="N83" s="4" t="s">
-        <v>67</v>
+        <v>63</v>
       </c>
       <c r="O83" s="4" t="s">
-        <v>67</v>
+        <v>63</v>
       </c>
       <c r="P83" s="4"/>
     </row>
-    <row r="84" spans="1:16" x14ac:dyDescent="0.45">
+    <row r="84" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A84" s="2" t="s">
-        <v>356</v>
+        <v>340</v>
       </c>
       <c r="B84" s="3" t="s">
-        <v>222</v>
+        <v>206</v>
       </c>
       <c r="C84" s="3" t="s">
-        <v>357</v>
+        <v>293</v>
       </c>
       <c r="D84" s="4" t="s">
-        <v>374</v>
+        <v>314</v>
       </c>
       <c r="E84" s="4" t="s">
-        <v>375</v>
+        <v>315</v>
       </c>
       <c r="F84" s="4" t="s">
-        <v>376</v>
+        <v>316</v>
       </c>
       <c r="G84" s="4" t="s">
-        <v>139</v>
+        <v>123</v>
       </c>
       <c r="H84" s="4"/>
       <c r="I84" s="4"/>
@@ -6162,34 +6239,34 @@
       <c r="L84" s="4"/>
       <c r="M84" s="4"/>
       <c r="N84" s="4" t="s">
-        <v>67</v>
+        <v>63</v>
       </c>
       <c r="O84" s="4" t="s">
-        <v>67</v>
+        <v>63</v>
       </c>
       <c r="P84" s="4"/>
     </row>
-    <row r="85" spans="1:16" x14ac:dyDescent="0.45">
+    <row r="85" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A85" s="2" t="s">
-        <v>361</v>
+        <v>345</v>
       </c>
       <c r="B85" s="3" t="s">
-        <v>222</v>
+        <v>206</v>
       </c>
       <c r="C85" s="3" t="s">
-        <v>357</v>
+        <v>341</v>
       </c>
       <c r="D85" s="4" t="s">
-        <v>378</v>
+        <v>342</v>
       </c>
       <c r="E85" s="4" t="s">
-        <v>379</v>
+        <v>343</v>
       </c>
       <c r="F85" s="4" t="s">
-        <v>380</v>
+        <v>344</v>
       </c>
       <c r="G85" s="4" t="s">
-        <v>139</v>
+        <v>123</v>
       </c>
       <c r="H85" s="4"/>
       <c r="I85" s="4"/>
@@ -6200,34 +6277,34 @@
       <c r="L85" s="4"/>
       <c r="M85" s="4"/>
       <c r="N85" s="4" t="s">
-        <v>67</v>
+        <v>63</v>
       </c>
       <c r="O85" s="4" t="s">
-        <v>67</v>
+        <v>63</v>
       </c>
       <c r="P85" s="4"/>
     </row>
-    <row r="86" spans="1:16" x14ac:dyDescent="0.45">
+    <row r="86" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A86" s="2" t="s">
-        <v>365</v>
+        <v>349</v>
       </c>
       <c r="B86" s="3" t="s">
-        <v>222</v>
+        <v>206</v>
       </c>
       <c r="C86" s="3" t="s">
-        <v>810</v>
+        <v>341</v>
       </c>
       <c r="D86" s="4" t="s">
-        <v>218</v>
+        <v>346</v>
       </c>
       <c r="E86" s="4" t="s">
-        <v>342</v>
+        <v>347</v>
       </c>
       <c r="F86" s="4" t="s">
-        <v>343</v>
+        <v>348</v>
       </c>
       <c r="G86" s="4" t="s">
-        <v>139</v>
+        <v>123</v>
       </c>
       <c r="H86" s="4"/>
       <c r="I86" s="4"/>
@@ -6238,34 +6315,34 @@
       <c r="L86" s="4"/>
       <c r="M86" s="4"/>
       <c r="N86" s="4" t="s">
-        <v>67</v>
+        <v>63</v>
       </c>
       <c r="O86" s="4" t="s">
-        <v>67</v>
+        <v>63</v>
       </c>
       <c r="P86" s="4"/>
     </row>
-    <row r="87" spans="1:16" x14ac:dyDescent="0.45">
+    <row r="87" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A87" s="2" t="s">
-        <v>369</v>
+        <v>353</v>
       </c>
       <c r="B87" s="3" t="s">
-        <v>222</v>
+        <v>206</v>
       </c>
       <c r="C87" s="3" t="s">
-        <v>810</v>
+        <v>341</v>
       </c>
       <c r="D87" s="4" t="s">
-        <v>345</v>
+        <v>350</v>
       </c>
       <c r="E87" s="4" t="s">
-        <v>346</v>
+        <v>351</v>
       </c>
       <c r="F87" s="4" t="s">
-        <v>347</v>
+        <v>352</v>
       </c>
       <c r="G87" s="4" t="s">
-        <v>139</v>
+        <v>123</v>
       </c>
       <c r="H87" s="4"/>
       <c r="I87" s="4"/>
@@ -6276,34 +6353,34 @@
       <c r="L87" s="4"/>
       <c r="M87" s="4"/>
       <c r="N87" s="4" t="s">
-        <v>67</v>
+        <v>63</v>
       </c>
       <c r="O87" s="4" t="s">
-        <v>67</v>
+        <v>63</v>
       </c>
       <c r="P87" s="4"/>
     </row>
-    <row r="88" spans="1:16" x14ac:dyDescent="0.45">
+    <row r="88" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A88" s="2" t="s">
-        <v>373</v>
+        <v>357</v>
       </c>
       <c r="B88" s="3" t="s">
-        <v>222</v>
+        <v>206</v>
       </c>
       <c r="C88" s="3" t="s">
-        <v>810</v>
+        <v>341</v>
       </c>
       <c r="D88" s="4" t="s">
-        <v>349</v>
+        <v>354</v>
       </c>
       <c r="E88" s="4" t="s">
-        <v>350</v>
+        <v>355</v>
       </c>
       <c r="F88" s="4" t="s">
-        <v>351</v>
+        <v>356</v>
       </c>
       <c r="G88" s="4" t="s">
-        <v>139</v>
+        <v>123</v>
       </c>
       <c r="H88" s="4"/>
       <c r="I88" s="4"/>
@@ -6314,34 +6391,34 @@
       <c r="L88" s="4"/>
       <c r="M88" s="4"/>
       <c r="N88" s="4" t="s">
-        <v>67</v>
+        <v>63</v>
       </c>
       <c r="O88" s="4" t="s">
-        <v>67</v>
+        <v>63</v>
       </c>
       <c r="P88" s="4"/>
     </row>
-    <row r="89" spans="1:16" x14ac:dyDescent="0.45">
+    <row r="89" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A89" s="2" t="s">
-        <v>377</v>
+        <v>361</v>
       </c>
       <c r="B89" s="3" t="s">
-        <v>222</v>
+        <v>206</v>
       </c>
       <c r="C89" s="3" t="s">
-        <v>810</v>
+        <v>341</v>
       </c>
       <c r="D89" s="4" t="s">
-        <v>353</v>
+        <v>358</v>
       </c>
       <c r="E89" s="4" t="s">
-        <v>354</v>
+        <v>359</v>
       </c>
       <c r="F89" s="4" t="s">
-        <v>355</v>
+        <v>360</v>
       </c>
       <c r="G89" s="4" t="s">
-        <v>139</v>
+        <v>123</v>
       </c>
       <c r="H89" s="4"/>
       <c r="I89" s="4"/>
@@ -6352,38 +6429,36 @@
       <c r="L89" s="4"/>
       <c r="M89" s="4"/>
       <c r="N89" s="4" t="s">
-        <v>67</v>
+        <v>63</v>
       </c>
       <c r="O89" s="4" t="s">
-        <v>67</v>
+        <v>63</v>
       </c>
       <c r="P89" s="4"/>
     </row>
-    <row r="90" spans="1:16" x14ac:dyDescent="0.45">
+    <row r="90" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A90" s="2" t="s">
-        <v>381</v>
+        <v>365</v>
       </c>
       <c r="B90" s="3" t="s">
-        <v>382</v>
+        <v>206</v>
       </c>
       <c r="C90" s="3" t="s">
-        <v>383</v>
+        <v>341</v>
       </c>
       <c r="D90" s="4" t="s">
-        <v>384</v>
+        <v>362</v>
       </c>
       <c r="E90" s="4" t="s">
-        <v>385</v>
+        <v>363</v>
       </c>
       <c r="F90" s="4" t="s">
-        <v>386</v>
+        <v>364</v>
       </c>
       <c r="G90" s="4" t="s">
-        <v>66</v>
-      </c>
-      <c r="H90" s="4" t="s">
-        <v>46</v>
-      </c>
+        <v>123</v>
+      </c>
+      <c r="H90" s="4"/>
       <c r="I90" s="4"/>
       <c r="J90" s="4" t="s">
         <v>23</v>
@@ -6392,32 +6467,34 @@
       <c r="L90" s="4"/>
       <c r="M90" s="4"/>
       <c r="N90" s="4" t="s">
-        <v>67</v>
-      </c>
-      <c r="O90" s="4"/>
+        <v>63</v>
+      </c>
+      <c r="O90" s="4" t="s">
+        <v>63</v>
+      </c>
       <c r="P90" s="4"/>
     </row>
-    <row r="91" spans="1:16" x14ac:dyDescent="0.45">
+    <row r="91" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A91" s="2" t="s">
-        <v>387</v>
+        <v>371</v>
       </c>
       <c r="B91" s="3" t="s">
-        <v>382</v>
+        <v>206</v>
       </c>
       <c r="C91" s="3" t="s">
-        <v>383</v>
+        <v>794</v>
       </c>
       <c r="D91" s="4" t="s">
-        <v>388</v>
+        <v>202</v>
       </c>
       <c r="E91" s="4" t="s">
-        <v>389</v>
+        <v>326</v>
       </c>
       <c r="F91" s="4" t="s">
-        <v>390</v>
+        <v>327</v>
       </c>
       <c r="G91" s="4" t="s">
-        <v>139</v>
+        <v>123</v>
       </c>
       <c r="H91" s="4"/>
       <c r="I91" s="4"/>
@@ -6428,32 +6505,34 @@
       <c r="L91" s="4"/>
       <c r="M91" s="4"/>
       <c r="N91" s="4" t="s">
-        <v>67</v>
-      </c>
-      <c r="O91" s="4"/>
+        <v>63</v>
+      </c>
+      <c r="O91" s="4" t="s">
+        <v>63</v>
+      </c>
       <c r="P91" s="4"/>
     </row>
-    <row r="92" spans="1:16" x14ac:dyDescent="0.45">
+    <row r="92" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A92" s="2" t="s">
-        <v>391</v>
+        <v>375</v>
       </c>
       <c r="B92" s="3" t="s">
-        <v>382</v>
+        <v>206</v>
       </c>
       <c r="C92" s="3" t="s">
-        <v>383</v>
+        <v>794</v>
       </c>
       <c r="D92" s="4" t="s">
-        <v>392</v>
+        <v>329</v>
       </c>
       <c r="E92" s="4" t="s">
-        <v>393</v>
+        <v>330</v>
       </c>
       <c r="F92" s="4" t="s">
-        <v>394</v>
+        <v>331</v>
       </c>
       <c r="G92" s="4" t="s">
-        <v>139</v>
+        <v>123</v>
       </c>
       <c r="H92" s="4"/>
       <c r="I92" s="4"/>
@@ -6464,32 +6543,34 @@
       <c r="L92" s="4"/>
       <c r="M92" s="4"/>
       <c r="N92" s="4" t="s">
-        <v>67</v>
-      </c>
-      <c r="O92" s="4"/>
+        <v>63</v>
+      </c>
+      <c r="O92" s="4" t="s">
+        <v>63</v>
+      </c>
       <c r="P92" s="4"/>
     </row>
-    <row r="93" spans="1:16" x14ac:dyDescent="0.45">
+    <row r="93" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A93" s="2" t="s">
-        <v>395</v>
+        <v>379</v>
       </c>
       <c r="B93" s="3" t="s">
-        <v>382</v>
+        <v>206</v>
       </c>
       <c r="C93" s="3" t="s">
-        <v>383</v>
+        <v>794</v>
       </c>
       <c r="D93" s="4" t="s">
-        <v>396</v>
+        <v>333</v>
       </c>
       <c r="E93" s="4" t="s">
-        <v>397</v>
+        <v>334</v>
       </c>
       <c r="F93" s="4" t="s">
-        <v>398</v>
+        <v>335</v>
       </c>
       <c r="G93" s="4" t="s">
-        <v>139</v>
+        <v>123</v>
       </c>
       <c r="H93" s="4"/>
       <c r="I93" s="4"/>
@@ -6500,36 +6581,36 @@
       <c r="L93" s="4"/>
       <c r="M93" s="4"/>
       <c r="N93" s="4" t="s">
-        <v>67</v>
-      </c>
-      <c r="O93" s="4"/>
+        <v>63</v>
+      </c>
+      <c r="O93" s="4" t="s">
+        <v>63</v>
+      </c>
       <c r="P93" s="4"/>
     </row>
-    <row r="94" spans="1:16" x14ac:dyDescent="0.45">
+    <row r="94" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A94" s="2" t="s">
-        <v>399</v>
+        <v>383</v>
       </c>
       <c r="B94" s="3" t="s">
-        <v>382</v>
+        <v>206</v>
       </c>
       <c r="C94" s="3" t="s">
-        <v>383</v>
+        <v>794</v>
       </c>
       <c r="D94" s="4" t="s">
-        <v>400</v>
+        <v>337</v>
       </c>
       <c r="E94" s="4" t="s">
-        <v>401</v>
+        <v>338</v>
       </c>
       <c r="F94" s="4" t="s">
-        <v>402</v>
+        <v>339</v>
       </c>
       <c r="G94" s="4" t="s">
-        <v>66</v>
-      </c>
-      <c r="H94" s="4" t="s">
-        <v>46</v>
-      </c>
+        <v>123</v>
+      </c>
+      <c r="H94" s="4"/>
       <c r="I94" s="4"/>
       <c r="J94" s="4" t="s">
         <v>23</v>
@@ -6538,34 +6619,38 @@
       <c r="L94" s="4"/>
       <c r="M94" s="4"/>
       <c r="N94" s="4" t="s">
-        <v>67</v>
-      </c>
-      <c r="O94" s="4"/>
+        <v>63</v>
+      </c>
+      <c r="O94" s="4" t="s">
+        <v>63</v>
+      </c>
       <c r="P94" s="4"/>
     </row>
-    <row r="95" spans="1:16" x14ac:dyDescent="0.45">
+    <row r="95" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A95" s="2" t="s">
-        <v>403</v>
+        <v>387</v>
       </c>
       <c r="B95" s="3" t="s">
-        <v>382</v>
+        <v>366</v>
       </c>
       <c r="C95" s="3" t="s">
-        <v>383</v>
+        <v>367</v>
       </c>
       <c r="D95" s="4" t="s">
-        <v>404</v>
+        <v>368</v>
       </c>
       <c r="E95" s="4" t="s">
-        <v>405</v>
+        <v>369</v>
       </c>
       <c r="F95" s="4" t="s">
-        <v>406</v>
+        <v>370</v>
       </c>
       <c r="G95" s="4" t="s">
-        <v>139</v>
-      </c>
-      <c r="H95" s="4"/>
+        <v>62</v>
+      </c>
+      <c r="H95" s="4" t="s">
+        <v>46</v>
+      </c>
       <c r="I95" s="4"/>
       <c r="J95" s="4" t="s">
         <v>23</v>
@@ -6574,32 +6659,32 @@
       <c r="L95" s="4"/>
       <c r="M95" s="4"/>
       <c r="N95" s="4" t="s">
-        <v>67</v>
+        <v>63</v>
       </c>
       <c r="O95" s="4"/>
       <c r="P95" s="4"/>
     </row>
-    <row r="96" spans="1:16" x14ac:dyDescent="0.45">
+    <row r="96" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A96" s="2" t="s">
-        <v>407</v>
+        <v>391</v>
       </c>
       <c r="B96" s="3" t="s">
-        <v>382</v>
+        <v>366</v>
       </c>
       <c r="C96" s="3" t="s">
-        <v>383</v>
+        <v>367</v>
       </c>
       <c r="D96" s="4" t="s">
-        <v>408</v>
+        <v>372</v>
       </c>
       <c r="E96" s="4" t="s">
-        <v>409</v>
+        <v>373</v>
       </c>
       <c r="F96" s="4" t="s">
-        <v>410</v>
+        <v>374</v>
       </c>
       <c r="G96" s="4" t="s">
-        <v>139</v>
+        <v>123</v>
       </c>
       <c r="H96" s="4"/>
       <c r="I96" s="4"/>
@@ -6610,32 +6695,32 @@
       <c r="L96" s="4"/>
       <c r="M96" s="4"/>
       <c r="N96" s="4" t="s">
-        <v>67</v>
+        <v>63</v>
       </c>
       <c r="O96" s="4"/>
       <c r="P96" s="4"/>
     </row>
-    <row r="97" spans="1:16" x14ac:dyDescent="0.45">
+    <row r="97" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A97" s="2" t="s">
-        <v>411</v>
+        <v>395</v>
       </c>
       <c r="B97" s="3" t="s">
-        <v>382</v>
+        <v>366</v>
       </c>
       <c r="C97" s="3" t="s">
-        <v>383</v>
+        <v>367</v>
       </c>
       <c r="D97" s="4" t="s">
-        <v>412</v>
+        <v>376</v>
       </c>
       <c r="E97" s="4" t="s">
-        <v>413</v>
+        <v>377</v>
       </c>
       <c r="F97" s="4" t="s">
-        <v>414</v>
+        <v>378</v>
       </c>
       <c r="G97" s="4" t="s">
-        <v>139</v>
+        <v>123</v>
       </c>
       <c r="H97" s="4"/>
       <c r="I97" s="4"/>
@@ -6646,36 +6731,34 @@
       <c r="L97" s="4"/>
       <c r="M97" s="4"/>
       <c r="N97" s="4" t="s">
-        <v>67</v>
+        <v>63</v>
       </c>
       <c r="O97" s="4"/>
       <c r="P97" s="4"/>
     </row>
-    <row r="98" spans="1:16" x14ac:dyDescent="0.45">
+    <row r="98" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A98" s="2" t="s">
-        <v>415</v>
+        <v>399</v>
       </c>
       <c r="B98" s="3" t="s">
+        <v>366</v>
+      </c>
+      <c r="C98" s="3" t="s">
+        <v>367</v>
+      </c>
+      <c r="D98" s="4" t="s">
+        <v>380</v>
+      </c>
+      <c r="E98" s="4" t="s">
+        <v>381</v>
+      </c>
+      <c r="F98" s="4" t="s">
         <v>382</v>
       </c>
-      <c r="C98" s="3" t="s">
-        <v>383</v>
-      </c>
-      <c r="D98" s="4" t="s">
-        <v>416</v>
-      </c>
-      <c r="E98" s="4" t="s">
-        <v>417</v>
-      </c>
-      <c r="F98" s="4" t="s">
-        <v>418</v>
-      </c>
       <c r="G98" s="4" t="s">
-        <v>66</v>
-      </c>
-      <c r="H98" s="4" t="s">
-        <v>46</v>
-      </c>
+        <v>123</v>
+      </c>
+      <c r="H98" s="4"/>
       <c r="I98" s="4"/>
       <c r="J98" s="4" t="s">
         <v>23</v>
@@ -6684,34 +6767,36 @@
       <c r="L98" s="4"/>
       <c r="M98" s="4"/>
       <c r="N98" s="4" t="s">
-        <v>67</v>
+        <v>63</v>
       </c>
       <c r="O98" s="4"/>
       <c r="P98" s="4"/>
     </row>
-    <row r="99" spans="1:16" x14ac:dyDescent="0.45">
+    <row r="99" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A99" s="2" t="s">
-        <v>419</v>
+        <v>403</v>
       </c>
       <c r="B99" s="3" t="s">
-        <v>382</v>
+        <v>366</v>
       </c>
       <c r="C99" s="3" t="s">
-        <v>383</v>
+        <v>367</v>
       </c>
       <c r="D99" s="4" t="s">
-        <v>420</v>
+        <v>384</v>
       </c>
       <c r="E99" s="4" t="s">
-        <v>421</v>
+        <v>385</v>
       </c>
       <c r="F99" s="4" t="s">
-        <v>422</v>
+        <v>386</v>
       </c>
       <c r="G99" s="4" t="s">
-        <v>139</v>
-      </c>
-      <c r="H99" s="4"/>
+        <v>62</v>
+      </c>
+      <c r="H99" s="4" t="s">
+        <v>46</v>
+      </c>
       <c r="I99" s="4"/>
       <c r="J99" s="4" t="s">
         <v>23</v>
@@ -6720,36 +6805,34 @@
       <c r="L99" s="4"/>
       <c r="M99" s="4"/>
       <c r="N99" s="4" t="s">
-        <v>67</v>
+        <v>63</v>
       </c>
       <c r="O99" s="4"/>
       <c r="P99" s="4"/>
     </row>
-    <row r="100" spans="1:16" x14ac:dyDescent="0.45">
+    <row r="100" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A100" s="2" t="s">
-        <v>423</v>
+        <v>407</v>
       </c>
       <c r="B100" s="3" t="s">
-        <v>382</v>
+        <v>366</v>
       </c>
       <c r="C100" s="3" t="s">
-        <v>383</v>
+        <v>367</v>
       </c>
       <c r="D100" s="4" t="s">
-        <v>424</v>
+        <v>388</v>
       </c>
       <c r="E100" s="4" t="s">
-        <v>425</v>
+        <v>389</v>
       </c>
       <c r="F100" s="4" t="s">
-        <v>426</v>
+        <v>390</v>
       </c>
       <c r="G100" s="4" t="s">
-        <v>66</v>
-      </c>
-      <c r="H100" s="4" t="s">
-        <v>46</v>
-      </c>
+        <v>123</v>
+      </c>
+      <c r="H100" s="4"/>
       <c r="I100" s="4"/>
       <c r="J100" s="4" t="s">
         <v>23</v>
@@ -6758,36 +6841,34 @@
       <c r="L100" s="4"/>
       <c r="M100" s="4"/>
       <c r="N100" s="4" t="s">
-        <v>67</v>
+        <v>63</v>
       </c>
       <c r="O100" s="4"/>
       <c r="P100" s="4"/>
     </row>
-    <row r="101" spans="1:16" x14ac:dyDescent="0.45">
+    <row r="101" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A101" s="2" t="s">
-        <v>427</v>
+        <v>411</v>
       </c>
       <c r="B101" s="3" t="s">
-        <v>382</v>
+        <v>366</v>
       </c>
       <c r="C101" s="3" t="s">
-        <v>223</v>
+        <v>367</v>
       </c>
       <c r="D101" s="4" t="s">
-        <v>224</v>
+        <v>392</v>
       </c>
       <c r="E101" s="4" t="s">
-        <v>428</v>
+        <v>393</v>
       </c>
       <c r="F101" s="4" t="s">
-        <v>429</v>
+        <v>394</v>
       </c>
       <c r="G101" s="4" t="s">
-        <v>66</v>
-      </c>
-      <c r="H101" s="4" t="s">
-        <v>46</v>
-      </c>
+        <v>123</v>
+      </c>
+      <c r="H101" s="4"/>
       <c r="I101" s="4"/>
       <c r="J101" s="4" t="s">
         <v>23</v>
@@ -6796,34 +6877,32 @@
       <c r="L101" s="4"/>
       <c r="M101" s="4"/>
       <c r="N101" s="4" t="s">
-        <v>67</v>
-      </c>
-      <c r="O101" s="4" t="s">
-        <v>67</v>
-      </c>
+        <v>63</v>
+      </c>
+      <c r="O101" s="4"/>
       <c r="P101" s="4"/>
     </row>
-    <row r="102" spans="1:16" x14ac:dyDescent="0.45">
+    <row r="102" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A102" s="2" t="s">
-        <v>430</v>
+        <v>414</v>
       </c>
       <c r="B102" s="3" t="s">
-        <v>382</v>
+        <v>366</v>
       </c>
       <c r="C102" s="3" t="s">
-        <v>223</v>
+        <v>367</v>
       </c>
       <c r="D102" s="4" t="s">
-        <v>228</v>
+        <v>396</v>
       </c>
       <c r="E102" s="4" t="s">
-        <v>431</v>
+        <v>397</v>
       </c>
       <c r="F102" s="4" t="s">
-        <v>432</v>
+        <v>398</v>
       </c>
       <c r="G102" s="4" t="s">
-        <v>139</v>
+        <v>123</v>
       </c>
       <c r="H102" s="4"/>
       <c r="I102" s="4"/>
@@ -6834,34 +6913,32 @@
       <c r="L102" s="4"/>
       <c r="M102" s="4"/>
       <c r="N102" s="4" t="s">
-        <v>67</v>
-      </c>
-      <c r="O102" s="4" t="s">
-        <v>67</v>
-      </c>
+        <v>63</v>
+      </c>
+      <c r="O102" s="4"/>
       <c r="P102" s="4"/>
     </row>
-    <row r="103" spans="1:16" x14ac:dyDescent="0.45">
+    <row r="103" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A103" s="2" t="s">
-        <v>433</v>
+        <v>417</v>
       </c>
       <c r="B103" s="3" t="s">
-        <v>382</v>
+        <v>366</v>
       </c>
       <c r="C103" s="3" t="s">
-        <v>223</v>
+        <v>367</v>
       </c>
       <c r="D103" s="4" t="s">
-        <v>232</v>
+        <v>400</v>
       </c>
       <c r="E103" s="4" t="s">
-        <v>434</v>
+        <v>401</v>
       </c>
       <c r="F103" s="4" t="s">
-        <v>435</v>
+        <v>402</v>
       </c>
       <c r="G103" s="4" t="s">
-        <v>66</v>
+        <v>62</v>
       </c>
       <c r="H103" s="4" t="s">
         <v>46</v>
@@ -6874,34 +6951,32 @@
       <c r="L103" s="4"/>
       <c r="M103" s="4"/>
       <c r="N103" s="4" t="s">
-        <v>67</v>
-      </c>
-      <c r="O103" s="4" t="s">
-        <v>67</v>
-      </c>
+        <v>63</v>
+      </c>
+      <c r="O103" s="4"/>
       <c r="P103" s="4"/>
     </row>
-    <row r="104" spans="1:16" x14ac:dyDescent="0.45">
+    <row r="104" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A104" s="2" t="s">
-        <v>436</v>
+        <v>420</v>
       </c>
       <c r="B104" s="3" t="s">
-        <v>382</v>
+        <v>366</v>
       </c>
       <c r="C104" s="3" t="s">
-        <v>236</v>
+        <v>367</v>
       </c>
       <c r="D104" s="4" t="s">
-        <v>237</v>
+        <v>404</v>
       </c>
       <c r="E104" s="4" t="s">
-        <v>437</v>
+        <v>405</v>
       </c>
       <c r="F104" s="4" t="s">
-        <v>239</v>
+        <v>406</v>
       </c>
       <c r="G104" s="4" t="s">
-        <v>139</v>
+        <v>123</v>
       </c>
       <c r="H104" s="4"/>
       <c r="I104" s="4"/>
@@ -6912,36 +6987,36 @@
       <c r="L104" s="4"/>
       <c r="M104" s="4"/>
       <c r="N104" s="4" t="s">
-        <v>67</v>
-      </c>
-      <c r="O104" s="4" t="s">
-        <v>67</v>
-      </c>
+        <v>63</v>
+      </c>
+      <c r="O104" s="4"/>
       <c r="P104" s="4"/>
     </row>
-    <row r="105" spans="1:16" x14ac:dyDescent="0.45">
+    <row r="105" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A105" s="2" t="s">
-        <v>438</v>
+        <v>422</v>
       </c>
       <c r="B105" s="3" t="s">
-        <v>382</v>
+        <v>366</v>
       </c>
       <c r="C105" s="3" t="s">
-        <v>236</v>
+        <v>367</v>
       </c>
       <c r="D105" s="4" t="s">
-        <v>241</v>
+        <v>408</v>
       </c>
       <c r="E105" s="4" t="s">
-        <v>439</v>
+        <v>409</v>
       </c>
       <c r="F105" s="4" t="s">
-        <v>243</v>
+        <v>410</v>
       </c>
       <c r="G105" s="4" t="s">
-        <v>139</v>
-      </c>
-      <c r="H105" s="4"/>
+        <v>62</v>
+      </c>
+      <c r="H105" s="4" t="s">
+        <v>46</v>
+      </c>
       <c r="I105" s="4"/>
       <c r="J105" s="4" t="s">
         <v>23</v>
@@ -6950,36 +7025,36 @@
       <c r="L105" s="4"/>
       <c r="M105" s="4"/>
       <c r="N105" s="4" t="s">
-        <v>67</v>
-      </c>
-      <c r="O105" s="4" t="s">
-        <v>67</v>
-      </c>
+        <v>63</v>
+      </c>
+      <c r="O105" s="4"/>
       <c r="P105" s="4"/>
     </row>
-    <row r="106" spans="1:16" x14ac:dyDescent="0.45">
+    <row r="106" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A106" s="2" t="s">
-        <v>440</v>
+        <v>424</v>
       </c>
       <c r="B106" s="3" t="s">
-        <v>382</v>
+        <v>366</v>
       </c>
       <c r="C106" s="3" t="s">
-        <v>236</v>
+        <v>207</v>
       </c>
       <c r="D106" s="4" t="s">
-        <v>245</v>
+        <v>208</v>
       </c>
       <c r="E106" s="4" t="s">
-        <v>441</v>
+        <v>412</v>
       </c>
       <c r="F106" s="4" t="s">
-        <v>247</v>
+        <v>413</v>
       </c>
       <c r="G106" s="4" t="s">
-        <v>139</v>
-      </c>
-      <c r="H106" s="4"/>
+        <v>62</v>
+      </c>
+      <c r="H106" s="4" t="s">
+        <v>46</v>
+      </c>
       <c r="I106" s="4"/>
       <c r="J106" s="4" t="s">
         <v>23</v>
@@ -6988,34 +7063,34 @@
       <c r="L106" s="4"/>
       <c r="M106" s="4"/>
       <c r="N106" s="4" t="s">
-        <v>67</v>
+        <v>63</v>
       </c>
       <c r="O106" s="4" t="s">
-        <v>67</v>
+        <v>63</v>
       </c>
       <c r="P106" s="4"/>
     </row>
-    <row r="107" spans="1:16" x14ac:dyDescent="0.45">
+    <row r="107" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A107" s="2" t="s">
-        <v>442</v>
+        <v>426</v>
       </c>
       <c r="B107" s="3" t="s">
-        <v>382</v>
+        <v>366</v>
       </c>
       <c r="C107" s="3" t="s">
-        <v>236</v>
+        <v>207</v>
       </c>
       <c r="D107" s="4" t="s">
-        <v>249</v>
+        <v>212</v>
       </c>
       <c r="E107" s="4" t="s">
-        <v>443</v>
+        <v>415</v>
       </c>
       <c r="F107" s="4" t="s">
-        <v>251</v>
+        <v>416</v>
       </c>
       <c r="G107" s="4" t="s">
-        <v>139</v>
+        <v>123</v>
       </c>
       <c r="H107" s="4"/>
       <c r="I107" s="4"/>
@@ -7026,36 +7101,38 @@
       <c r="L107" s="4"/>
       <c r="M107" s="4"/>
       <c r="N107" s="4" t="s">
-        <v>67</v>
+        <v>63</v>
       </c>
       <c r="O107" s="4" t="s">
-        <v>67</v>
+        <v>63</v>
       </c>
       <c r="P107" s="4"/>
     </row>
-    <row r="108" spans="1:16" x14ac:dyDescent="0.45">
+    <row r="108" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A108" s="2" t="s">
-        <v>444</v>
+        <v>428</v>
       </c>
       <c r="B108" s="3" t="s">
-        <v>382</v>
+        <v>366</v>
       </c>
       <c r="C108" s="3" t="s">
-        <v>236</v>
+        <v>207</v>
       </c>
       <c r="D108" s="4" t="s">
-        <v>261</v>
+        <v>216</v>
       </c>
       <c r="E108" s="4" t="s">
-        <v>449</v>
+        <v>418</v>
       </c>
       <c r="F108" s="4" t="s">
-        <v>263</v>
+        <v>419</v>
       </c>
       <c r="G108" s="4" t="s">
-        <v>139</v>
-      </c>
-      <c r="H108" s="4"/>
+        <v>62</v>
+      </c>
+      <c r="H108" s="4" t="s">
+        <v>46</v>
+      </c>
       <c r="I108" s="4"/>
       <c r="J108" s="4" t="s">
         <v>23</v>
@@ -7064,34 +7141,34 @@
       <c r="L108" s="4"/>
       <c r="M108" s="4"/>
       <c r="N108" s="4" t="s">
-        <v>67</v>
+        <v>63</v>
       </c>
       <c r="O108" s="4" t="s">
-        <v>67</v>
+        <v>63</v>
       </c>
       <c r="P108" s="4"/>
     </row>
-    <row r="109" spans="1:16" x14ac:dyDescent="0.45">
+    <row r="109" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A109" s="2" t="s">
-        <v>446</v>
+        <v>430</v>
       </c>
       <c r="B109" s="3" t="s">
-        <v>382</v>
+        <v>366</v>
       </c>
       <c r="C109" s="3" t="s">
-        <v>236</v>
+        <v>220</v>
       </c>
       <c r="D109" s="4" t="s">
-        <v>265</v>
+        <v>221</v>
       </c>
       <c r="E109" s="4" t="s">
-        <v>451</v>
+        <v>421</v>
       </c>
       <c r="F109" s="4" t="s">
-        <v>267</v>
+        <v>223</v>
       </c>
       <c r="G109" s="4" t="s">
-        <v>139</v>
+        <v>123</v>
       </c>
       <c r="H109" s="4"/>
       <c r="I109" s="4"/>
@@ -7102,34 +7179,34 @@
       <c r="L109" s="4"/>
       <c r="M109" s="4"/>
       <c r="N109" s="4" t="s">
-        <v>67</v>
+        <v>63</v>
       </c>
       <c r="O109" s="4" t="s">
-        <v>67</v>
+        <v>63</v>
       </c>
       <c r="P109" s="4"/>
     </row>
-    <row r="110" spans="1:16" x14ac:dyDescent="0.45">
+    <row r="110" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A110" s="2" t="s">
-        <v>448</v>
+        <v>432</v>
       </c>
       <c r="B110" s="3" t="s">
-        <v>382</v>
+        <v>366</v>
       </c>
       <c r="C110" s="3" t="s">
-        <v>236</v>
+        <v>220</v>
       </c>
       <c r="D110" s="4" t="s">
-        <v>253</v>
+        <v>225</v>
       </c>
       <c r="E110" s="4" t="s">
-        <v>445</v>
+        <v>423</v>
       </c>
       <c r="F110" s="4" t="s">
-        <v>255</v>
+        <v>227</v>
       </c>
       <c r="G110" s="4" t="s">
-        <v>139</v>
+        <v>123</v>
       </c>
       <c r="H110" s="4"/>
       <c r="I110" s="4"/>
@@ -7140,34 +7217,34 @@
       <c r="L110" s="4"/>
       <c r="M110" s="4"/>
       <c r="N110" s="4" t="s">
-        <v>67</v>
+        <v>63</v>
       </c>
       <c r="O110" s="4" t="s">
-        <v>67</v>
+        <v>63</v>
       </c>
       <c r="P110" s="4"/>
     </row>
-    <row r="111" spans="1:16" x14ac:dyDescent="0.45">
+    <row r="111" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A111" s="2" t="s">
-        <v>450</v>
+        <v>434</v>
       </c>
       <c r="B111" s="3" t="s">
-        <v>382</v>
+        <v>366</v>
       </c>
       <c r="C111" s="3" t="s">
-        <v>236</v>
+        <v>220</v>
       </c>
       <c r="D111" s="4" t="s">
-        <v>257</v>
+        <v>229</v>
       </c>
       <c r="E111" s="4" t="s">
-        <v>447</v>
+        <v>425</v>
       </c>
       <c r="F111" s="4" t="s">
-        <v>259</v>
+        <v>231</v>
       </c>
       <c r="G111" s="4" t="s">
-        <v>139</v>
+        <v>123</v>
       </c>
       <c r="H111" s="4"/>
       <c r="I111" s="4"/>
@@ -7178,34 +7255,34 @@
       <c r="L111" s="4"/>
       <c r="M111" s="4"/>
       <c r="N111" s="4" t="s">
-        <v>67</v>
+        <v>63</v>
       </c>
       <c r="O111" s="4" t="s">
-        <v>67</v>
+        <v>63</v>
       </c>
       <c r="P111" s="4"/>
     </row>
-    <row r="112" spans="1:16" x14ac:dyDescent="0.45">
+    <row r="112" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A112" s="2" t="s">
-        <v>452</v>
+        <v>436</v>
       </c>
       <c r="B112" s="3" t="s">
-        <v>382</v>
+        <v>366</v>
       </c>
       <c r="C112" s="3" t="s">
-        <v>284</v>
+        <v>220</v>
       </c>
       <c r="D112" s="4" t="s">
-        <v>285</v>
+        <v>233</v>
       </c>
       <c r="E112" s="4" t="s">
-        <v>463</v>
+        <v>427</v>
       </c>
       <c r="F112" s="4" t="s">
-        <v>464</v>
+        <v>235</v>
       </c>
       <c r="G112" s="4" t="s">
-        <v>139</v>
+        <v>123</v>
       </c>
       <c r="H112" s="4"/>
       <c r="I112" s="4"/>
@@ -7216,34 +7293,34 @@
       <c r="L112" s="4"/>
       <c r="M112" s="4"/>
       <c r="N112" s="4" t="s">
-        <v>67</v>
+        <v>63</v>
       </c>
       <c r="O112" s="4" t="s">
-        <v>67</v>
+        <v>63</v>
       </c>
       <c r="P112" s="4"/>
     </row>
-    <row r="113" spans="1:16" x14ac:dyDescent="0.45">
+    <row r="113" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A113" s="2" t="s">
-        <v>454</v>
+        <v>438</v>
       </c>
       <c r="B113" s="3" t="s">
-        <v>382</v>
+        <v>366</v>
       </c>
       <c r="C113" s="3" t="s">
-        <v>284</v>
+        <v>220</v>
       </c>
       <c r="D113" s="4" t="s">
-        <v>289</v>
+        <v>245</v>
       </c>
       <c r="E113" s="4" t="s">
-        <v>466</v>
+        <v>433</v>
       </c>
       <c r="F113" s="4" t="s">
-        <v>467</v>
+        <v>247</v>
       </c>
       <c r="G113" s="4" t="s">
-        <v>139</v>
+        <v>123</v>
       </c>
       <c r="H113" s="4"/>
       <c r="I113" s="4"/>
@@ -7254,34 +7331,34 @@
       <c r="L113" s="4"/>
       <c r="M113" s="4"/>
       <c r="N113" s="4" t="s">
-        <v>67</v>
+        <v>63</v>
       </c>
       <c r="O113" s="4" t="s">
-        <v>67</v>
+        <v>63</v>
       </c>
       <c r="P113" s="4"/>
     </row>
-    <row r="114" spans="1:16" x14ac:dyDescent="0.45">
+    <row r="114" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A114" s="2" t="s">
-        <v>456</v>
+        <v>440</v>
       </c>
       <c r="B114" s="3" t="s">
-        <v>382</v>
+        <v>366</v>
       </c>
       <c r="C114" s="3" t="s">
-        <v>284</v>
+        <v>220</v>
       </c>
       <c r="D114" s="4" t="s">
-        <v>293</v>
+        <v>249</v>
       </c>
       <c r="E114" s="4" t="s">
-        <v>469</v>
+        <v>435</v>
       </c>
       <c r="F114" s="4" t="s">
-        <v>470</v>
+        <v>251</v>
       </c>
       <c r="G114" s="4" t="s">
-        <v>139</v>
+        <v>123</v>
       </c>
       <c r="H114" s="4"/>
       <c r="I114" s="4"/>
@@ -7292,34 +7369,34 @@
       <c r="L114" s="4"/>
       <c r="M114" s="4"/>
       <c r="N114" s="4" t="s">
-        <v>67</v>
+        <v>63</v>
       </c>
       <c r="O114" s="4" t="s">
-        <v>67</v>
+        <v>63</v>
       </c>
       <c r="P114" s="4"/>
     </row>
-    <row r="115" spans="1:16" x14ac:dyDescent="0.45">
+    <row r="115" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A115" s="2" t="s">
-        <v>458</v>
+        <v>442</v>
       </c>
       <c r="B115" s="3" t="s">
-        <v>382</v>
+        <v>366</v>
       </c>
       <c r="C115" s="3" t="s">
-        <v>284</v>
+        <v>220</v>
       </c>
       <c r="D115" s="4" t="s">
-        <v>297</v>
+        <v>237</v>
       </c>
       <c r="E115" s="4" t="s">
-        <v>472</v>
+        <v>429</v>
       </c>
       <c r="F115" s="4" t="s">
-        <v>473</v>
+        <v>239</v>
       </c>
       <c r="G115" s="4" t="s">
-        <v>139</v>
+        <v>123</v>
       </c>
       <c r="H115" s="4"/>
       <c r="I115" s="4"/>
@@ -7330,34 +7407,34 @@
       <c r="L115" s="4"/>
       <c r="M115" s="4"/>
       <c r="N115" s="4" t="s">
-        <v>67</v>
+        <v>63</v>
       </c>
       <c r="O115" s="4" t="s">
-        <v>67</v>
+        <v>63</v>
       </c>
       <c r="P115" s="4"/>
     </row>
-    <row r="116" spans="1:16" x14ac:dyDescent="0.45">
+    <row r="116" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A116" s="2" t="s">
-        <v>462</v>
+        <v>446</v>
       </c>
       <c r="B116" s="3" t="s">
-        <v>382</v>
+        <v>366</v>
       </c>
       <c r="C116" s="3" t="s">
-        <v>284</v>
+        <v>220</v>
       </c>
       <c r="D116" s="4" t="s">
-        <v>301</v>
+        <v>241</v>
       </c>
       <c r="E116" s="4" t="s">
-        <v>475</v>
+        <v>431</v>
       </c>
       <c r="F116" s="4" t="s">
-        <v>476</v>
+        <v>243</v>
       </c>
       <c r="G116" s="4" t="s">
-        <v>139</v>
+        <v>123</v>
       </c>
       <c r="H116" s="4"/>
       <c r="I116" s="4"/>
@@ -7368,34 +7445,34 @@
       <c r="L116" s="4"/>
       <c r="M116" s="4"/>
       <c r="N116" s="4" t="s">
-        <v>67</v>
+        <v>63</v>
       </c>
       <c r="O116" s="4" t="s">
-        <v>67</v>
+        <v>63</v>
       </c>
       <c r="P116" s="4"/>
     </row>
-    <row r="117" spans="1:16" x14ac:dyDescent="0.45">
+    <row r="117" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A117" s="2" t="s">
-        <v>465</v>
+        <v>449</v>
       </c>
       <c r="B117" s="3" t="s">
-        <v>382</v>
+        <v>366</v>
       </c>
       <c r="C117" s="3" t="s">
-        <v>284</v>
+        <v>268</v>
       </c>
       <c r="D117" s="4" t="s">
-        <v>305</v>
+        <v>269</v>
       </c>
       <c r="E117" s="4" t="s">
-        <v>478</v>
+        <v>447</v>
       </c>
       <c r="F117" s="4" t="s">
-        <v>479</v>
+        <v>448</v>
       </c>
       <c r="G117" s="4" t="s">
-        <v>139</v>
+        <v>123</v>
       </c>
       <c r="H117" s="4"/>
       <c r="I117" s="4"/>
@@ -7406,34 +7483,34 @@
       <c r="L117" s="4"/>
       <c r="M117" s="4"/>
       <c r="N117" s="4" t="s">
-        <v>67</v>
+        <v>63</v>
       </c>
       <c r="O117" s="4" t="s">
-        <v>67</v>
+        <v>63</v>
       </c>
       <c r="P117" s="4"/>
     </row>
-    <row r="118" spans="1:16" x14ac:dyDescent="0.45">
+    <row r="118" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A118" s="2" t="s">
-        <v>468</v>
+        <v>452</v>
       </c>
       <c r="B118" s="3" t="s">
-        <v>382</v>
+        <v>366</v>
       </c>
       <c r="C118" s="3" t="s">
-        <v>809</v>
+        <v>268</v>
       </c>
       <c r="D118" s="4" t="s">
-        <v>181</v>
+        <v>273</v>
       </c>
       <c r="E118" s="4" t="s">
-        <v>453</v>
+        <v>450</v>
       </c>
       <c r="F118" s="4" t="s">
-        <v>270</v>
+        <v>451</v>
       </c>
       <c r="G118" s="4" t="s">
-        <v>139</v>
+        <v>123</v>
       </c>
       <c r="H118" s="4"/>
       <c r="I118" s="4"/>
@@ -7444,34 +7521,34 @@
       <c r="L118" s="4"/>
       <c r="M118" s="4"/>
       <c r="N118" s="4" t="s">
-        <v>67</v>
+        <v>63</v>
       </c>
       <c r="O118" s="4" t="s">
-        <v>67</v>
+        <v>63</v>
       </c>
       <c r="P118" s="4"/>
     </row>
-    <row r="119" spans="1:16" x14ac:dyDescent="0.45">
+    <row r="119" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A119" s="2" t="s">
-        <v>471</v>
+        <v>455</v>
       </c>
       <c r="B119" s="3" t="s">
-        <v>382</v>
+        <v>366</v>
       </c>
       <c r="C119" s="3" t="s">
-        <v>809</v>
+        <v>268</v>
       </c>
       <c r="D119" s="4" t="s">
-        <v>272</v>
+        <v>277</v>
       </c>
       <c r="E119" s="4" t="s">
-        <v>455</v>
+        <v>453</v>
       </c>
       <c r="F119" s="4" t="s">
-        <v>274</v>
+        <v>454</v>
       </c>
       <c r="G119" s="4" t="s">
-        <v>139</v>
+        <v>123</v>
       </c>
       <c r="H119" s="4"/>
       <c r="I119" s="4"/>
@@ -7482,34 +7559,34 @@
       <c r="L119" s="4"/>
       <c r="M119" s="4"/>
       <c r="N119" s="4" t="s">
-        <v>67</v>
+        <v>63</v>
       </c>
       <c r="O119" s="4" t="s">
-        <v>67</v>
+        <v>63</v>
       </c>
       <c r="P119" s="4"/>
     </row>
-    <row r="120" spans="1:16" x14ac:dyDescent="0.45">
+    <row r="120" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A120" s="2" t="s">
-        <v>474</v>
+        <v>458</v>
       </c>
       <c r="B120" s="3" t="s">
-        <v>382</v>
+        <v>366</v>
       </c>
       <c r="C120" s="3" t="s">
-        <v>809</v>
+        <v>268</v>
       </c>
       <c r="D120" s="4" t="s">
-        <v>459</v>
+        <v>281</v>
       </c>
       <c r="E120" s="4" t="s">
-        <v>460</v>
+        <v>456</v>
       </c>
       <c r="F120" s="4" t="s">
-        <v>461</v>
+        <v>457</v>
       </c>
       <c r="G120" s="4" t="s">
-        <v>139</v>
+        <v>123</v>
       </c>
       <c r="H120" s="4"/>
       <c r="I120" s="4"/>
@@ -7520,34 +7597,34 @@
       <c r="L120" s="4"/>
       <c r="M120" s="4"/>
       <c r="N120" s="4" t="s">
-        <v>67</v>
+        <v>63</v>
       </c>
       <c r="O120" s="4" t="s">
-        <v>67</v>
+        <v>63</v>
       </c>
       <c r="P120" s="4"/>
     </row>
-    <row r="121" spans="1:16" x14ac:dyDescent="0.45">
+    <row r="121" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A121" s="2" t="s">
-        <v>477</v>
+        <v>461</v>
       </c>
       <c r="B121" s="3" t="s">
-        <v>382</v>
+        <v>366</v>
       </c>
       <c r="C121" s="3" t="s">
-        <v>809</v>
+        <v>268</v>
       </c>
       <c r="D121" s="4" t="s">
-        <v>276</v>
+        <v>285</v>
       </c>
       <c r="E121" s="4" t="s">
-        <v>457</v>
+        <v>459</v>
       </c>
       <c r="F121" s="4" t="s">
-        <v>278</v>
+        <v>460</v>
       </c>
       <c r="G121" s="4" t="s">
-        <v>139</v>
+        <v>123</v>
       </c>
       <c r="H121" s="4"/>
       <c r="I121" s="4"/>
@@ -7558,34 +7635,34 @@
       <c r="L121" s="4"/>
       <c r="M121" s="4"/>
       <c r="N121" s="4" t="s">
-        <v>67</v>
+        <v>63</v>
       </c>
       <c r="O121" s="4" t="s">
-        <v>67</v>
+        <v>63</v>
       </c>
       <c r="P121" s="4"/>
     </row>
-    <row r="122" spans="1:16" x14ac:dyDescent="0.45">
+    <row r="122" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A122" s="2" t="s">
-        <v>480</v>
+        <v>464</v>
       </c>
       <c r="B122" s="3" t="s">
-        <v>382</v>
+        <v>366</v>
       </c>
       <c r="C122" s="3" t="s">
-        <v>309</v>
+        <v>268</v>
       </c>
       <c r="D122" s="4" t="s">
-        <v>310</v>
+        <v>289</v>
       </c>
       <c r="E122" s="4" t="s">
-        <v>481</v>
+        <v>462</v>
       </c>
       <c r="F122" s="4" t="s">
-        <v>312</v>
+        <v>463</v>
       </c>
       <c r="G122" s="4" t="s">
-        <v>139</v>
+        <v>123</v>
       </c>
       <c r="H122" s="4"/>
       <c r="I122" s="4"/>
@@ -7596,34 +7673,34 @@
       <c r="L122" s="4"/>
       <c r="M122" s="4"/>
       <c r="N122" s="4" t="s">
-        <v>67</v>
+        <v>63</v>
       </c>
       <c r="O122" s="4" t="s">
-        <v>67</v>
+        <v>63</v>
       </c>
       <c r="P122" s="4"/>
     </row>
-    <row r="123" spans="1:16" x14ac:dyDescent="0.45">
+    <row r="123" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A123" s="2" t="s">
-        <v>482</v>
+        <v>466</v>
       </c>
       <c r="B123" s="3" t="s">
-        <v>382</v>
+        <v>366</v>
       </c>
       <c r="C123" s="3" t="s">
-        <v>309</v>
+        <v>793</v>
       </c>
       <c r="D123" s="4" t="s">
-        <v>314</v>
+        <v>165</v>
       </c>
       <c r="E123" s="4" t="s">
-        <v>483</v>
+        <v>437</v>
       </c>
       <c r="F123" s="4" t="s">
-        <v>316</v>
+        <v>254</v>
       </c>
       <c r="G123" s="4" t="s">
-        <v>139</v>
+        <v>123</v>
       </c>
       <c r="H123" s="4"/>
       <c r="I123" s="4"/>
@@ -7634,34 +7711,34 @@
       <c r="L123" s="4"/>
       <c r="M123" s="4"/>
       <c r="N123" s="4" t="s">
-        <v>67</v>
+        <v>63</v>
       </c>
       <c r="O123" s="4" t="s">
-        <v>67</v>
+        <v>63</v>
       </c>
       <c r="P123" s="4"/>
     </row>
-    <row r="124" spans="1:16" x14ac:dyDescent="0.45">
+    <row r="124" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A124" s="2" t="s">
-        <v>484</v>
+        <v>468</v>
       </c>
       <c r="B124" s="3" t="s">
-        <v>382</v>
+        <v>366</v>
       </c>
       <c r="C124" s="3" t="s">
-        <v>309</v>
+        <v>793</v>
       </c>
       <c r="D124" s="4" t="s">
-        <v>318</v>
+        <v>256</v>
       </c>
       <c r="E124" s="4" t="s">
-        <v>485</v>
+        <v>439</v>
       </c>
       <c r="F124" s="4" t="s">
-        <v>320</v>
+        <v>258</v>
       </c>
       <c r="G124" s="4" t="s">
-        <v>139</v>
+        <v>123</v>
       </c>
       <c r="H124" s="4"/>
       <c r="I124" s="4"/>
@@ -7672,34 +7749,34 @@
       <c r="L124" s="4"/>
       <c r="M124" s="4"/>
       <c r="N124" s="4" t="s">
-        <v>67</v>
+        <v>63</v>
       </c>
       <c r="O124" s="4" t="s">
-        <v>67</v>
+        <v>63</v>
       </c>
       <c r="P124" s="4"/>
     </row>
-    <row r="125" spans="1:16" x14ac:dyDescent="0.45">
+    <row r="125" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A125" s="2" t="s">
-        <v>486</v>
+        <v>470</v>
       </c>
       <c r="B125" s="3" t="s">
-        <v>382</v>
+        <v>366</v>
       </c>
       <c r="C125" s="3" t="s">
-        <v>309</v>
+        <v>793</v>
       </c>
       <c r="D125" s="4" t="s">
-        <v>322</v>
+        <v>443</v>
       </c>
       <c r="E125" s="4" t="s">
-        <v>487</v>
+        <v>444</v>
       </c>
       <c r="F125" s="4" t="s">
-        <v>324</v>
+        <v>445</v>
       </c>
       <c r="G125" s="4" t="s">
-        <v>139</v>
+        <v>123</v>
       </c>
       <c r="H125" s="4"/>
       <c r="I125" s="4"/>
@@ -7710,34 +7787,34 @@
       <c r="L125" s="4"/>
       <c r="M125" s="4"/>
       <c r="N125" s="4" t="s">
-        <v>67</v>
+        <v>63</v>
       </c>
       <c r="O125" s="4" t="s">
-        <v>67</v>
+        <v>63</v>
       </c>
       <c r="P125" s="4"/>
     </row>
-    <row r="126" spans="1:16" x14ac:dyDescent="0.45">
+    <row r="126" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A126" s="2" t="s">
-        <v>488</v>
+        <v>472</v>
       </c>
       <c r="B126" s="3" t="s">
-        <v>382</v>
+        <v>366</v>
       </c>
       <c r="C126" s="3" t="s">
-        <v>309</v>
+        <v>793</v>
       </c>
       <c r="D126" s="4" t="s">
-        <v>334</v>
+        <v>260</v>
       </c>
       <c r="E126" s="4" t="s">
-        <v>493</v>
+        <v>441</v>
       </c>
       <c r="F126" s="4" t="s">
-        <v>336</v>
+        <v>262</v>
       </c>
       <c r="G126" s="4" t="s">
-        <v>139</v>
+        <v>123</v>
       </c>
       <c r="H126" s="4"/>
       <c r="I126" s="4"/>
@@ -7748,34 +7825,34 @@
       <c r="L126" s="4"/>
       <c r="M126" s="4"/>
       <c r="N126" s="4" t="s">
-        <v>67</v>
+        <v>63</v>
       </c>
       <c r="O126" s="4" t="s">
-        <v>67</v>
+        <v>63</v>
       </c>
       <c r="P126" s="4"/>
     </row>
-    <row r="127" spans="1:16" x14ac:dyDescent="0.45">
+    <row r="127" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A127" s="2" t="s">
-        <v>490</v>
+        <v>474</v>
       </c>
       <c r="B127" s="3" t="s">
-        <v>382</v>
+        <v>366</v>
       </c>
       <c r="C127" s="3" t="s">
-        <v>309</v>
+        <v>293</v>
       </c>
       <c r="D127" s="4" t="s">
-        <v>338</v>
+        <v>294</v>
       </c>
       <c r="E127" s="4" t="s">
-        <v>495</v>
+        <v>465</v>
       </c>
       <c r="F127" s="4" t="s">
-        <v>340</v>
+        <v>296</v>
       </c>
       <c r="G127" s="4" t="s">
-        <v>139</v>
+        <v>123</v>
       </c>
       <c r="H127" s="4"/>
       <c r="I127" s="4"/>
@@ -7786,34 +7863,34 @@
       <c r="L127" s="4"/>
       <c r="M127" s="4"/>
       <c r="N127" s="4" t="s">
-        <v>67</v>
+        <v>63</v>
       </c>
       <c r="O127" s="4" t="s">
-        <v>67</v>
+        <v>63</v>
       </c>
       <c r="P127" s="4"/>
     </row>
-    <row r="128" spans="1:16" x14ac:dyDescent="0.45">
+    <row r="128" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A128" s="2" t="s">
-        <v>492</v>
+        <v>476</v>
       </c>
       <c r="B128" s="3" t="s">
-        <v>382</v>
+        <v>366</v>
       </c>
       <c r="C128" s="3" t="s">
-        <v>309</v>
+        <v>293</v>
       </c>
       <c r="D128" s="4" t="s">
-        <v>326</v>
+        <v>298</v>
       </c>
       <c r="E128" s="4" t="s">
-        <v>489</v>
+        <v>467</v>
       </c>
       <c r="F128" s="4" t="s">
-        <v>328</v>
+        <v>300</v>
       </c>
       <c r="G128" s="4" t="s">
-        <v>139</v>
+        <v>123</v>
       </c>
       <c r="H128" s="4"/>
       <c r="I128" s="4"/>
@@ -7824,34 +7901,34 @@
       <c r="L128" s="4"/>
       <c r="M128" s="4"/>
       <c r="N128" s="4" t="s">
-        <v>67</v>
+        <v>63</v>
       </c>
       <c r="O128" s="4" t="s">
-        <v>67</v>
+        <v>63</v>
       </c>
       <c r="P128" s="4"/>
     </row>
-    <row r="129" spans="1:16" x14ac:dyDescent="0.45">
+    <row r="129" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A129" s="2" t="s">
-        <v>494</v>
+        <v>478</v>
       </c>
       <c r="B129" s="3" t="s">
-        <v>382</v>
+        <v>366</v>
       </c>
       <c r="C129" s="3" t="s">
-        <v>309</v>
+        <v>293</v>
       </c>
       <c r="D129" s="4" t="s">
-        <v>330</v>
+        <v>302</v>
       </c>
       <c r="E129" s="4" t="s">
-        <v>491</v>
+        <v>469</v>
       </c>
       <c r="F129" s="4" t="s">
-        <v>332</v>
+        <v>304</v>
       </c>
       <c r="G129" s="4" t="s">
-        <v>139</v>
+        <v>123</v>
       </c>
       <c r="H129" s="4"/>
       <c r="I129" s="4"/>
@@ -7862,34 +7939,34 @@
       <c r="L129" s="4"/>
       <c r="M129" s="4"/>
       <c r="N129" s="4" t="s">
-        <v>67</v>
+        <v>63</v>
       </c>
       <c r="O129" s="4" t="s">
-        <v>67</v>
+        <v>63</v>
       </c>
       <c r="P129" s="4"/>
     </row>
-    <row r="130" spans="1:16" x14ac:dyDescent="0.45">
+    <row r="130" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A130" s="2" t="s">
-        <v>496</v>
+        <v>480</v>
       </c>
       <c r="B130" s="3" t="s">
-        <v>382</v>
+        <v>366</v>
       </c>
       <c r="C130" s="3" t="s">
-        <v>357</v>
+        <v>293</v>
       </c>
       <c r="D130" s="4" t="s">
-        <v>358</v>
+        <v>306</v>
       </c>
       <c r="E130" s="4" t="s">
-        <v>505</v>
+        <v>471</v>
       </c>
       <c r="F130" s="4" t="s">
-        <v>506</v>
+        <v>308</v>
       </c>
       <c r="G130" s="4" t="s">
-        <v>139</v>
+        <v>123</v>
       </c>
       <c r="H130" s="4"/>
       <c r="I130" s="4"/>
@@ -7900,34 +7977,34 @@
       <c r="L130" s="4"/>
       <c r="M130" s="4"/>
       <c r="N130" s="4" t="s">
-        <v>67</v>
+        <v>63</v>
       </c>
       <c r="O130" s="4" t="s">
-        <v>67</v>
+        <v>63</v>
       </c>
       <c r="P130" s="4"/>
     </row>
-    <row r="131" spans="1:16" x14ac:dyDescent="0.45">
+    <row r="131" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A131" s="2" t="s">
-        <v>498</v>
+        <v>482</v>
       </c>
       <c r="B131" s="3" t="s">
-        <v>382</v>
+        <v>366</v>
       </c>
       <c r="C131" s="3" t="s">
-        <v>357</v>
+        <v>293</v>
       </c>
       <c r="D131" s="4" t="s">
-        <v>362</v>
+        <v>318</v>
       </c>
       <c r="E131" s="4" t="s">
-        <v>508</v>
+        <v>477</v>
       </c>
       <c r="F131" s="4" t="s">
-        <v>509</v>
+        <v>320</v>
       </c>
       <c r="G131" s="4" t="s">
-        <v>139</v>
+        <v>123</v>
       </c>
       <c r="H131" s="4"/>
       <c r="I131" s="4"/>
@@ -7938,34 +8015,34 @@
       <c r="L131" s="4"/>
       <c r="M131" s="4"/>
       <c r="N131" s="4" t="s">
-        <v>67</v>
+        <v>63</v>
       </c>
       <c r="O131" s="4" t="s">
-        <v>67</v>
+        <v>63</v>
       </c>
       <c r="P131" s="4"/>
     </row>
-    <row r="132" spans="1:16" x14ac:dyDescent="0.45">
+    <row r="132" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A132" s="2" t="s">
-        <v>500</v>
+        <v>484</v>
       </c>
       <c r="B132" s="3" t="s">
-        <v>382</v>
+        <v>366</v>
       </c>
       <c r="C132" s="3" t="s">
-        <v>357</v>
+        <v>293</v>
       </c>
       <c r="D132" s="4" t="s">
-        <v>366</v>
+        <v>322</v>
       </c>
       <c r="E132" s="4" t="s">
-        <v>511</v>
+        <v>479</v>
       </c>
       <c r="F132" s="4" t="s">
-        <v>512</v>
+        <v>324</v>
       </c>
       <c r="G132" s="4" t="s">
-        <v>139</v>
+        <v>123</v>
       </c>
       <c r="H132" s="4"/>
       <c r="I132" s="4"/>
@@ -7976,34 +8053,34 @@
       <c r="L132" s="4"/>
       <c r="M132" s="4"/>
       <c r="N132" s="4" t="s">
-        <v>67</v>
+        <v>63</v>
       </c>
       <c r="O132" s="4" t="s">
-        <v>67</v>
+        <v>63</v>
       </c>
       <c r="P132" s="4"/>
     </row>
-    <row r="133" spans="1:16" x14ac:dyDescent="0.45">
+    <row r="133" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A133" s="2" t="s">
-        <v>502</v>
+        <v>486</v>
       </c>
       <c r="B133" s="3" t="s">
-        <v>382</v>
+        <v>366</v>
       </c>
       <c r="C133" s="3" t="s">
-        <v>357</v>
+        <v>293</v>
       </c>
       <c r="D133" s="4" t="s">
-        <v>370</v>
+        <v>310</v>
       </c>
       <c r="E133" s="4" t="s">
-        <v>514</v>
+        <v>473</v>
       </c>
       <c r="F133" s="4" t="s">
-        <v>515</v>
+        <v>312</v>
       </c>
       <c r="G133" s="4" t="s">
-        <v>139</v>
+        <v>123</v>
       </c>
       <c r="H133" s="4"/>
       <c r="I133" s="4"/>
@@ -8014,34 +8091,34 @@
       <c r="L133" s="4"/>
       <c r="M133" s="4"/>
       <c r="N133" s="4" t="s">
-        <v>67</v>
+        <v>63</v>
       </c>
       <c r="O133" s="4" t="s">
-        <v>67</v>
+        <v>63</v>
       </c>
       <c r="P133" s="4"/>
     </row>
-    <row r="134" spans="1:16" x14ac:dyDescent="0.45">
+    <row r="134" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A134" s="2" t="s">
-        <v>504</v>
+        <v>488</v>
       </c>
       <c r="B134" s="3" t="s">
-        <v>382</v>
+        <v>366</v>
       </c>
       <c r="C134" s="3" t="s">
-        <v>357</v>
+        <v>293</v>
       </c>
       <c r="D134" s="4" t="s">
-        <v>374</v>
+        <v>314</v>
       </c>
       <c r="E134" s="4" t="s">
-        <v>517</v>
+        <v>475</v>
       </c>
       <c r="F134" s="4" t="s">
-        <v>518</v>
+        <v>316</v>
       </c>
       <c r="G134" s="4" t="s">
-        <v>139</v>
+        <v>123</v>
       </c>
       <c r="H134" s="4"/>
       <c r="I134" s="4"/>
@@ -8052,34 +8129,34 @@
       <c r="L134" s="4"/>
       <c r="M134" s="4"/>
       <c r="N134" s="4" t="s">
-        <v>67</v>
+        <v>63</v>
       </c>
       <c r="O134" s="4" t="s">
-        <v>67</v>
+        <v>63</v>
       </c>
       <c r="P134" s="4"/>
     </row>
-    <row r="135" spans="1:16" x14ac:dyDescent="0.45">
+    <row r="135" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A135" s="2" t="s">
-        <v>507</v>
+        <v>491</v>
       </c>
       <c r="B135" s="3" t="s">
-        <v>382</v>
+        <v>366</v>
       </c>
       <c r="C135" s="3" t="s">
-        <v>357</v>
+        <v>341</v>
       </c>
       <c r="D135" s="4" t="s">
-        <v>378</v>
+        <v>342</v>
       </c>
       <c r="E135" s="4" t="s">
-        <v>520</v>
+        <v>489</v>
       </c>
       <c r="F135" s="4" t="s">
-        <v>521</v>
+        <v>490</v>
       </c>
       <c r="G135" s="4" t="s">
-        <v>139</v>
+        <v>123</v>
       </c>
       <c r="H135" s="4"/>
       <c r="I135" s="4"/>
@@ -8090,34 +8167,34 @@
       <c r="L135" s="4"/>
       <c r="M135" s="4"/>
       <c r="N135" s="4" t="s">
-        <v>67</v>
+        <v>63</v>
       </c>
       <c r="O135" s="4" t="s">
-        <v>67</v>
+        <v>63</v>
       </c>
       <c r="P135" s="4"/>
     </row>
-    <row r="136" spans="1:16" x14ac:dyDescent="0.45">
+    <row r="136" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A136" s="2" t="s">
-        <v>510</v>
+        <v>494</v>
       </c>
       <c r="B136" s="3" t="s">
-        <v>382</v>
+        <v>366</v>
       </c>
       <c r="C136" s="3" t="s">
-        <v>810</v>
+        <v>341</v>
       </c>
       <c r="D136" s="4" t="s">
-        <v>218</v>
+        <v>346</v>
       </c>
       <c r="E136" s="4" t="s">
-        <v>497</v>
+        <v>492</v>
       </c>
       <c r="F136" s="4" t="s">
-        <v>343</v>
+        <v>493</v>
       </c>
       <c r="G136" s="4" t="s">
-        <v>139</v>
+        <v>123</v>
       </c>
       <c r="H136" s="4"/>
       <c r="I136" s="4"/>
@@ -8128,34 +8205,34 @@
       <c r="L136" s="4"/>
       <c r="M136" s="4"/>
       <c r="N136" s="4" t="s">
-        <v>67</v>
+        <v>63</v>
       </c>
       <c r="O136" s="4" t="s">
-        <v>67</v>
+        <v>63</v>
       </c>
       <c r="P136" s="4"/>
     </row>
-    <row r="137" spans="1:16" x14ac:dyDescent="0.45">
+    <row r="137" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A137" s="2" t="s">
-        <v>513</v>
+        <v>497</v>
       </c>
       <c r="B137" s="3" t="s">
-        <v>382</v>
+        <v>366</v>
       </c>
       <c r="C137" s="3" t="s">
-        <v>810</v>
+        <v>341</v>
       </c>
       <c r="D137" s="4" t="s">
-        <v>345</v>
+        <v>350</v>
       </c>
       <c r="E137" s="4" t="s">
-        <v>499</v>
+        <v>495</v>
       </c>
       <c r="F137" s="4" t="s">
-        <v>347</v>
+        <v>496</v>
       </c>
       <c r="G137" s="4" t="s">
-        <v>139</v>
+        <v>123</v>
       </c>
       <c r="H137" s="4"/>
       <c r="I137" s="4"/>
@@ -8166,34 +8243,34 @@
       <c r="L137" s="4"/>
       <c r="M137" s="4"/>
       <c r="N137" s="4" t="s">
-        <v>67</v>
+        <v>63</v>
       </c>
       <c r="O137" s="4" t="s">
-        <v>67</v>
+        <v>63</v>
       </c>
       <c r="P137" s="4"/>
     </row>
-    <row r="138" spans="1:16" x14ac:dyDescent="0.45">
+    <row r="138" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A138" s="2" t="s">
-        <v>516</v>
+        <v>500</v>
       </c>
       <c r="B138" s="3" t="s">
-        <v>382</v>
+        <v>366</v>
       </c>
       <c r="C138" s="3" t="s">
-        <v>810</v>
+        <v>341</v>
       </c>
       <c r="D138" s="4" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="E138" s="4" t="s">
-        <v>503</v>
+        <v>498</v>
       </c>
       <c r="F138" s="4" t="s">
-        <v>355</v>
+        <v>499</v>
       </c>
       <c r="G138" s="4" t="s">
-        <v>139</v>
+        <v>123</v>
       </c>
       <c r="H138" s="4"/>
       <c r="I138" s="4"/>
@@ -8204,34 +8281,34 @@
       <c r="L138" s="4"/>
       <c r="M138" s="4"/>
       <c r="N138" s="4" t="s">
-        <v>67</v>
+        <v>63</v>
       </c>
       <c r="O138" s="4" t="s">
-        <v>67</v>
+        <v>63</v>
       </c>
       <c r="P138" s="4"/>
     </row>
-    <row r="139" spans="1:16" x14ac:dyDescent="0.45">
+    <row r="139" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A139" s="2" t="s">
-        <v>519</v>
+        <v>503</v>
       </c>
       <c r="B139" s="3" t="s">
-        <v>382</v>
+        <v>366</v>
       </c>
       <c r="C139" s="3" t="s">
-        <v>810</v>
+        <v>341</v>
       </c>
       <c r="D139" s="4" t="s">
-        <v>349</v>
+        <v>358</v>
       </c>
       <c r="E139" s="4" t="s">
         <v>501</v>
       </c>
       <c r="F139" s="4" t="s">
-        <v>351</v>
+        <v>502</v>
       </c>
       <c r="G139" s="4" t="s">
-        <v>139</v>
+        <v>123</v>
       </c>
       <c r="H139" s="4"/>
       <c r="I139" s="4"/>
@@ -8242,38 +8319,36 @@
       <c r="L139" s="4"/>
       <c r="M139" s="4"/>
       <c r="N139" s="4" t="s">
-        <v>67</v>
+        <v>63</v>
       </c>
       <c r="O139" s="4" t="s">
-        <v>67</v>
+        <v>63</v>
       </c>
       <c r="P139" s="4"/>
     </row>
-    <row r="140" spans="1:16" x14ac:dyDescent="0.45">
+    <row r="140" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A140" s="2" t="s">
-        <v>522</v>
+        <v>506</v>
       </c>
       <c r="B140" s="3" t="s">
-        <v>523</v>
+        <v>366</v>
       </c>
       <c r="C140" s="3" t="s">
-        <v>524</v>
+        <v>341</v>
       </c>
       <c r="D140" s="4" t="s">
-        <v>525</v>
+        <v>362</v>
       </c>
       <c r="E140" s="4" t="s">
-        <v>526</v>
+        <v>504</v>
       </c>
       <c r="F140" s="4" t="s">
-        <v>527</v>
+        <v>505</v>
       </c>
       <c r="G140" s="4" t="s">
-        <v>66</v>
-      </c>
-      <c r="H140" s="4" t="s">
-        <v>46</v>
-      </c>
+        <v>123</v>
+      </c>
+      <c r="H140" s="4"/>
       <c r="I140" s="4"/>
       <c r="J140" s="4" t="s">
         <v>23</v>
@@ -8282,38 +8357,36 @@
       <c r="L140" s="4"/>
       <c r="M140" s="4"/>
       <c r="N140" s="4" t="s">
-        <v>67</v>
+        <v>63</v>
       </c>
       <c r="O140" s="4" t="s">
-        <v>67</v>
+        <v>63</v>
       </c>
       <c r="P140" s="4"/>
     </row>
-    <row r="141" spans="1:16" x14ac:dyDescent="0.45">
+    <row r="141" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A141" s="2" t="s">
-        <v>528</v>
+        <v>512</v>
       </c>
       <c r="B141" s="3" t="s">
-        <v>523</v>
+        <v>366</v>
       </c>
       <c r="C141" s="3" t="s">
-        <v>524</v>
+        <v>794</v>
       </c>
       <c r="D141" s="4" t="s">
-        <v>529</v>
+        <v>202</v>
       </c>
       <c r="E141" s="4" t="s">
-        <v>530</v>
+        <v>481</v>
       </c>
       <c r="F141" s="4" t="s">
-        <v>531</v>
+        <v>327</v>
       </c>
       <c r="G141" s="4" t="s">
-        <v>66</v>
-      </c>
-      <c r="H141" s="4" t="s">
-        <v>46</v>
-      </c>
+        <v>123</v>
+      </c>
+      <c r="H141" s="4"/>
       <c r="I141" s="4"/>
       <c r="J141" s="4" t="s">
         <v>23</v>
@@ -8322,34 +8395,34 @@
       <c r="L141" s="4"/>
       <c r="M141" s="4"/>
       <c r="N141" s="4" t="s">
-        <v>67</v>
+        <v>63</v>
       </c>
       <c r="O141" s="4" t="s">
-        <v>67</v>
+        <v>63</v>
       </c>
       <c r="P141" s="4"/>
     </row>
-    <row r="142" spans="1:16" x14ac:dyDescent="0.45">
+    <row r="142" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A142" s="2" t="s">
-        <v>532</v>
+        <v>516</v>
       </c>
       <c r="B142" s="3" t="s">
-        <v>523</v>
+        <v>366</v>
       </c>
       <c r="C142" s="3" t="s">
-        <v>524</v>
+        <v>794</v>
       </c>
       <c r="D142" s="4" t="s">
-        <v>557</v>
+        <v>329</v>
       </c>
       <c r="E142" s="4" t="s">
-        <v>558</v>
+        <v>483</v>
       </c>
       <c r="F142" s="4" t="s">
-        <v>559</v>
+        <v>331</v>
       </c>
       <c r="G142" s="4" t="s">
-        <v>139</v>
+        <v>123</v>
       </c>
       <c r="H142" s="4"/>
       <c r="I142" s="4"/>
@@ -8360,34 +8433,34 @@
       <c r="L142" s="4"/>
       <c r="M142" s="4"/>
       <c r="N142" s="4" t="s">
-        <v>67</v>
+        <v>63</v>
       </c>
       <c r="O142" s="4" t="s">
-        <v>67</v>
+        <v>63</v>
       </c>
       <c r="P142" s="4"/>
     </row>
-    <row r="143" spans="1:16" x14ac:dyDescent="0.45">
+    <row r="143" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A143" s="2" t="s">
-        <v>536</v>
+        <v>520</v>
       </c>
       <c r="B143" s="3" t="s">
-        <v>523</v>
+        <v>366</v>
       </c>
       <c r="C143" s="3" t="s">
-        <v>524</v>
+        <v>794</v>
       </c>
       <c r="D143" s="4" t="s">
-        <v>561</v>
+        <v>337</v>
       </c>
       <c r="E143" s="4" t="s">
-        <v>562</v>
+        <v>487</v>
       </c>
       <c r="F143" s="4" t="s">
-        <v>559</v>
+        <v>339</v>
       </c>
       <c r="G143" s="4" t="s">
-        <v>139</v>
+        <v>123</v>
       </c>
       <c r="H143" s="4"/>
       <c r="I143" s="4"/>
@@ -8398,34 +8471,34 @@
       <c r="L143" s="4"/>
       <c r="M143" s="4"/>
       <c r="N143" s="4" t="s">
-        <v>67</v>
+        <v>63</v>
       </c>
       <c r="O143" s="4" t="s">
-        <v>67</v>
+        <v>63</v>
       </c>
       <c r="P143" s="4"/>
     </row>
-    <row r="144" spans="1:16" x14ac:dyDescent="0.45">
+    <row r="144" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A144" s="2" t="s">
-        <v>540</v>
+        <v>524</v>
       </c>
       <c r="B144" s="3" t="s">
-        <v>523</v>
+        <v>366</v>
       </c>
       <c r="C144" s="3" t="s">
-        <v>524</v>
+        <v>794</v>
       </c>
       <c r="D144" s="4" t="s">
-        <v>533</v>
+        <v>333</v>
       </c>
       <c r="E144" s="4" t="s">
-        <v>534</v>
+        <v>485</v>
       </c>
       <c r="F144" s="4" t="s">
-        <v>535</v>
+        <v>335</v>
       </c>
       <c r="G144" s="4" t="s">
-        <v>139</v>
+        <v>123</v>
       </c>
       <c r="H144" s="4"/>
       <c r="I144" s="4"/>
@@ -8436,36 +8509,38 @@
       <c r="L144" s="4"/>
       <c r="M144" s="4"/>
       <c r="N144" s="4" t="s">
-        <v>67</v>
+        <v>63</v>
       </c>
       <c r="O144" s="4" t="s">
-        <v>67</v>
+        <v>63</v>
       </c>
       <c r="P144" s="4"/>
     </row>
-    <row r="145" spans="1:16" x14ac:dyDescent="0.45">
+    <row r="145" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A145" s="2" t="s">
-        <v>544</v>
+        <v>528</v>
       </c>
       <c r="B145" s="3" t="s">
-        <v>523</v>
+        <v>507</v>
       </c>
       <c r="C145" s="3" t="s">
-        <v>524</v>
+        <v>508</v>
       </c>
       <c r="D145" s="4" t="s">
-        <v>537</v>
+        <v>509</v>
       </c>
       <c r="E145" s="4" t="s">
-        <v>538</v>
+        <v>510</v>
       </c>
       <c r="F145" s="4" t="s">
-        <v>539</v>
+        <v>511</v>
       </c>
       <c r="G145" s="4" t="s">
-        <v>139</v>
-      </c>
-      <c r="H145" s="4"/>
+        <v>62</v>
+      </c>
+      <c r="H145" s="4" t="s">
+        <v>46</v>
+      </c>
       <c r="I145" s="4"/>
       <c r="J145" s="4" t="s">
         <v>23</v>
@@ -8474,36 +8549,38 @@
       <c r="L145" s="4"/>
       <c r="M145" s="4"/>
       <c r="N145" s="4" t="s">
-        <v>67</v>
+        <v>63</v>
       </c>
       <c r="O145" s="4" t="s">
-        <v>67</v>
+        <v>63</v>
       </c>
       <c r="P145" s="4"/>
     </row>
-    <row r="146" spans="1:16" x14ac:dyDescent="0.45">
+    <row r="146" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A146" s="2" t="s">
-        <v>548</v>
+        <v>532</v>
       </c>
       <c r="B146" s="3" t="s">
-        <v>523</v>
+        <v>507</v>
       </c>
       <c r="C146" s="3" t="s">
-        <v>524</v>
+        <v>508</v>
       </c>
       <c r="D146" s="4" t="s">
-        <v>541</v>
+        <v>513</v>
       </c>
       <c r="E146" s="4" t="s">
-        <v>542</v>
+        <v>514</v>
       </c>
       <c r="F146" s="4" t="s">
-        <v>543</v>
+        <v>515</v>
       </c>
       <c r="G146" s="4" t="s">
-        <v>139</v>
-      </c>
-      <c r="H146" s="4"/>
+        <v>62</v>
+      </c>
+      <c r="H146" s="4" t="s">
+        <v>46</v>
+      </c>
       <c r="I146" s="4"/>
       <c r="J146" s="4" t="s">
         <v>23</v>
@@ -8512,34 +8589,34 @@
       <c r="L146" s="4"/>
       <c r="M146" s="4"/>
       <c r="N146" s="4" t="s">
-        <v>67</v>
+        <v>63</v>
       </c>
       <c r="O146" s="4" t="s">
-        <v>67</v>
+        <v>63</v>
       </c>
       <c r="P146" s="4"/>
     </row>
-    <row r="147" spans="1:16" x14ac:dyDescent="0.45">
+    <row r="147" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A147" s="2" t="s">
-        <v>552</v>
+        <v>536</v>
       </c>
       <c r="B147" s="3" t="s">
-        <v>523</v>
+        <v>507</v>
       </c>
       <c r="C147" s="3" t="s">
-        <v>524</v>
+        <v>508</v>
       </c>
       <c r="D147" s="4" t="s">
-        <v>545</v>
+        <v>541</v>
       </c>
       <c r="E147" s="4" t="s">
-        <v>546</v>
+        <v>542</v>
       </c>
       <c r="F147" s="4" t="s">
-        <v>547</v>
+        <v>543</v>
       </c>
       <c r="G147" s="4" t="s">
-        <v>139</v>
+        <v>123</v>
       </c>
       <c r="H147" s="4"/>
       <c r="I147" s="4"/>
@@ -8550,34 +8627,34 @@
       <c r="L147" s="4"/>
       <c r="M147" s="4"/>
       <c r="N147" s="4" t="s">
-        <v>67</v>
+        <v>63</v>
       </c>
       <c r="O147" s="4" t="s">
-        <v>67</v>
+        <v>63</v>
       </c>
       <c r="P147" s="4"/>
     </row>
-    <row r="148" spans="1:16" x14ac:dyDescent="0.45">
+    <row r="148" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A148" s="2" t="s">
-        <v>556</v>
+        <v>540</v>
       </c>
       <c r="B148" s="3" t="s">
-        <v>523</v>
+        <v>507</v>
       </c>
       <c r="C148" s="3" t="s">
-        <v>524</v>
+        <v>508</v>
       </c>
       <c r="D148" s="4" t="s">
-        <v>549</v>
+        <v>545</v>
       </c>
       <c r="E148" s="4" t="s">
-        <v>550</v>
+        <v>546</v>
       </c>
       <c r="F148" s="4" t="s">
-        <v>551</v>
+        <v>543</v>
       </c>
       <c r="G148" s="4" t="s">
-        <v>139</v>
+        <v>123</v>
       </c>
       <c r="H148" s="4"/>
       <c r="I148" s="4"/>
@@ -8588,34 +8665,34 @@
       <c r="L148" s="4"/>
       <c r="M148" s="4"/>
       <c r="N148" s="4" t="s">
-        <v>67</v>
+        <v>63</v>
       </c>
       <c r="O148" s="4" t="s">
-        <v>67</v>
+        <v>63</v>
       </c>
       <c r="P148" s="4"/>
     </row>
-    <row r="149" spans="1:16" x14ac:dyDescent="0.45">
+    <row r="149" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A149" s="2" t="s">
-        <v>560</v>
+        <v>544</v>
       </c>
       <c r="B149" s="3" t="s">
-        <v>523</v>
+        <v>507</v>
       </c>
       <c r="C149" s="3" t="s">
-        <v>524</v>
+        <v>508</v>
       </c>
       <c r="D149" s="4" t="s">
-        <v>553</v>
+        <v>517</v>
       </c>
       <c r="E149" s="4" t="s">
-        <v>554</v>
+        <v>518</v>
       </c>
       <c r="F149" s="4" t="s">
-        <v>555</v>
+        <v>519</v>
       </c>
       <c r="G149" s="4" t="s">
-        <v>139</v>
+        <v>123</v>
       </c>
       <c r="H149" s="4"/>
       <c r="I149" s="4"/>
@@ -8626,34 +8703,34 @@
       <c r="L149" s="4"/>
       <c r="M149" s="4"/>
       <c r="N149" s="4" t="s">
-        <v>67</v>
+        <v>63</v>
       </c>
       <c r="O149" s="4" t="s">
-        <v>67</v>
+        <v>63</v>
       </c>
       <c r="P149" s="4"/>
     </row>
-    <row r="150" spans="1:16" x14ac:dyDescent="0.45">
+    <row r="150" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A150" s="2" t="s">
-        <v>563</v>
+        <v>547</v>
       </c>
       <c r="B150" s="3" t="s">
+        <v>507</v>
+      </c>
+      <c r="C150" s="3" t="s">
+        <v>508</v>
+      </c>
+      <c r="D150" s="4" t="s">
+        <v>521</v>
+      </c>
+      <c r="E150" s="4" t="s">
+        <v>522</v>
+      </c>
+      <c r="F150" s="4" t="s">
         <v>523</v>
       </c>
-      <c r="C150" s="3" t="s">
-        <v>524</v>
-      </c>
-      <c r="D150" s="4" t="s">
-        <v>564</v>
-      </c>
-      <c r="E150" s="4" t="s">
-        <v>565</v>
-      </c>
-      <c r="F150" s="4" t="s">
-        <v>566</v>
-      </c>
       <c r="G150" s="4" t="s">
-        <v>139</v>
+        <v>123</v>
       </c>
       <c r="H150" s="4"/>
       <c r="I150" s="4"/>
@@ -8664,34 +8741,34 @@
       <c r="L150" s="4"/>
       <c r="M150" s="4"/>
       <c r="N150" s="4" t="s">
-        <v>67</v>
+        <v>63</v>
       </c>
       <c r="O150" s="4" t="s">
-        <v>67</v>
+        <v>63</v>
       </c>
       <c r="P150" s="4"/>
     </row>
-    <row r="151" spans="1:16" x14ac:dyDescent="0.45">
+    <row r="151" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A151" s="2" t="s">
-        <v>567</v>
+        <v>551</v>
       </c>
       <c r="B151" s="3" t="s">
-        <v>523</v>
+        <v>507</v>
       </c>
       <c r="C151" s="3" t="s">
-        <v>524</v>
+        <v>508</v>
       </c>
       <c r="D151" s="4" t="s">
-        <v>568</v>
+        <v>525</v>
       </c>
       <c r="E151" s="4" t="s">
-        <v>569</v>
+        <v>526</v>
       </c>
       <c r="F151" s="4" t="s">
-        <v>570</v>
+        <v>527</v>
       </c>
       <c r="G151" s="4" t="s">
-        <v>139</v>
+        <v>123</v>
       </c>
       <c r="H151" s="4"/>
       <c r="I151" s="4"/>
@@ -8702,34 +8779,34 @@
       <c r="L151" s="4"/>
       <c r="M151" s="4"/>
       <c r="N151" s="4" t="s">
-        <v>67</v>
+        <v>63</v>
       </c>
       <c r="O151" s="4" t="s">
-        <v>67</v>
+        <v>63</v>
       </c>
       <c r="P151" s="4"/>
     </row>
-    <row r="152" spans="1:16" x14ac:dyDescent="0.45">
+    <row r="152" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A152" s="2" t="s">
-        <v>571</v>
+        <v>555</v>
       </c>
       <c r="B152" s="3" t="s">
-        <v>523</v>
+        <v>507</v>
       </c>
       <c r="C152" s="3" t="s">
-        <v>524</v>
+        <v>508</v>
       </c>
       <c r="D152" s="4" t="s">
-        <v>181</v>
+        <v>529</v>
       </c>
       <c r="E152" s="4" t="s">
-        <v>572</v>
+        <v>530</v>
       </c>
       <c r="F152" s="4" t="s">
-        <v>573</v>
+        <v>531</v>
       </c>
       <c r="G152" s="4" t="s">
-        <v>139</v>
+        <v>123</v>
       </c>
       <c r="H152" s="4"/>
       <c r="I152" s="4"/>
@@ -8740,34 +8817,34 @@
       <c r="L152" s="4"/>
       <c r="M152" s="4"/>
       <c r="N152" s="4" t="s">
-        <v>67</v>
+        <v>63</v>
       </c>
       <c r="O152" s="4" t="s">
-        <v>67</v>
+        <v>63</v>
       </c>
       <c r="P152" s="4"/>
     </row>
-    <row r="153" spans="1:16" x14ac:dyDescent="0.45">
+    <row r="153" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A153" s="2" t="s">
-        <v>574</v>
+        <v>558</v>
       </c>
       <c r="B153" s="3" t="s">
-        <v>523</v>
+        <v>507</v>
       </c>
       <c r="C153" s="3" t="s">
-        <v>524</v>
+        <v>508</v>
       </c>
       <c r="D153" s="4" t="s">
-        <v>272</v>
+        <v>533</v>
       </c>
       <c r="E153" s="4" t="s">
-        <v>575</v>
+        <v>534</v>
       </c>
       <c r="F153" s="4" t="s">
-        <v>576</v>
+        <v>535</v>
       </c>
       <c r="G153" s="4" t="s">
-        <v>139</v>
+        <v>123</v>
       </c>
       <c r="H153" s="4"/>
       <c r="I153" s="4"/>
@@ -8778,34 +8855,34 @@
       <c r="L153" s="4"/>
       <c r="M153" s="4"/>
       <c r="N153" s="4" t="s">
-        <v>67</v>
+        <v>63</v>
       </c>
       <c r="O153" s="4" t="s">
-        <v>67</v>
+        <v>63</v>
       </c>
       <c r="P153" s="4"/>
     </row>
-    <row r="154" spans="1:16" x14ac:dyDescent="0.45">
+    <row r="154" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A154" s="2" t="s">
-        <v>577</v>
+        <v>561</v>
       </c>
       <c r="B154" s="3" t="s">
-        <v>523</v>
+        <v>507</v>
       </c>
       <c r="C154" s="3" t="s">
-        <v>524</v>
+        <v>508</v>
       </c>
       <c r="D154" s="4" t="s">
-        <v>459</v>
+        <v>537</v>
       </c>
       <c r="E154" s="4" t="s">
-        <v>578</v>
+        <v>538</v>
       </c>
       <c r="F154" s="4" t="s">
-        <v>579</v>
+        <v>539</v>
       </c>
       <c r="G154" s="4" t="s">
-        <v>139</v>
+        <v>123</v>
       </c>
       <c r="H154" s="4"/>
       <c r="I154" s="4"/>
@@ -8816,34 +8893,34 @@
       <c r="L154" s="4"/>
       <c r="M154" s="4"/>
       <c r="N154" s="4" t="s">
-        <v>67</v>
+        <v>63</v>
       </c>
       <c r="O154" s="4" t="s">
-        <v>67</v>
+        <v>63</v>
       </c>
       <c r="P154" s="4"/>
     </row>
-    <row r="155" spans="1:16" x14ac:dyDescent="0.45">
+    <row r="155" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A155" s="2" t="s">
-        <v>580</v>
+        <v>564</v>
       </c>
       <c r="B155" s="3" t="s">
-        <v>523</v>
+        <v>507</v>
       </c>
       <c r="C155" s="3" t="s">
-        <v>524</v>
+        <v>508</v>
       </c>
       <c r="D155" s="4" t="s">
-        <v>276</v>
+        <v>548</v>
       </c>
       <c r="E155" s="4" t="s">
-        <v>581</v>
+        <v>549</v>
       </c>
       <c r="F155" s="4" t="s">
-        <v>582</v>
+        <v>550</v>
       </c>
       <c r="G155" s="4" t="s">
-        <v>139</v>
+        <v>123</v>
       </c>
       <c r="H155" s="4"/>
       <c r="I155" s="4"/>
@@ -8854,34 +8931,34 @@
       <c r="L155" s="4"/>
       <c r="M155" s="4"/>
       <c r="N155" s="4" t="s">
-        <v>67</v>
+        <v>63</v>
       </c>
       <c r="O155" s="4" t="s">
-        <v>67</v>
+        <v>63</v>
       </c>
       <c r="P155" s="4"/>
     </row>
-    <row r="156" spans="1:16" x14ac:dyDescent="0.45">
+    <row r="156" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A156" s="2" t="s">
-        <v>583</v>
+        <v>567</v>
       </c>
       <c r="B156" s="3" t="s">
-        <v>523</v>
+        <v>507</v>
       </c>
       <c r="C156" s="3" t="s">
-        <v>524</v>
+        <v>508</v>
       </c>
       <c r="D156" s="4" t="s">
-        <v>584</v>
+        <v>552</v>
       </c>
       <c r="E156" s="4" t="s">
-        <v>585</v>
+        <v>553</v>
       </c>
       <c r="F156" s="4" t="s">
-        <v>586</v>
+        <v>554</v>
       </c>
       <c r="G156" s="4" t="s">
-        <v>139</v>
+        <v>123</v>
       </c>
       <c r="H156" s="4"/>
       <c r="I156" s="4"/>
@@ -8892,34 +8969,34 @@
       <c r="L156" s="4"/>
       <c r="M156" s="4"/>
       <c r="N156" s="4" t="s">
-        <v>67</v>
+        <v>63</v>
       </c>
       <c r="O156" s="4" t="s">
-        <v>67</v>
+        <v>63</v>
       </c>
       <c r="P156" s="4"/>
     </row>
-    <row r="157" spans="1:16" x14ac:dyDescent="0.45">
+    <row r="157" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A157" s="2" t="s">
-        <v>587</v>
+        <v>571</v>
       </c>
       <c r="B157" s="3" t="s">
-        <v>523</v>
+        <v>507</v>
       </c>
       <c r="C157" s="3" t="s">
-        <v>524</v>
+        <v>508</v>
       </c>
       <c r="D157" s="4" t="s">
-        <v>592</v>
+        <v>165</v>
       </c>
       <c r="E157" s="4" t="s">
-        <v>593</v>
+        <v>556</v>
       </c>
       <c r="F157" s="4" t="s">
-        <v>594</v>
+        <v>557</v>
       </c>
       <c r="G157" s="4" t="s">
-        <v>139</v>
+        <v>123</v>
       </c>
       <c r="H157" s="4"/>
       <c r="I157" s="4"/>
@@ -8930,34 +9007,34 @@
       <c r="L157" s="4"/>
       <c r="M157" s="4"/>
       <c r="N157" s="4" t="s">
-        <v>67</v>
+        <v>63</v>
       </c>
       <c r="O157" s="4" t="s">
-        <v>67</v>
+        <v>63</v>
       </c>
       <c r="P157" s="4"/>
     </row>
-    <row r="158" spans="1:16" x14ac:dyDescent="0.45">
+    <row r="158" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A158" s="2" t="s">
-        <v>591</v>
+        <v>575</v>
       </c>
       <c r="B158" s="3" t="s">
-        <v>523</v>
+        <v>507</v>
       </c>
       <c r="C158" s="3" t="s">
-        <v>524</v>
+        <v>508</v>
       </c>
       <c r="D158" s="4" t="s">
-        <v>588</v>
+        <v>256</v>
       </c>
       <c r="E158" s="4" t="s">
-        <v>589</v>
+        <v>559</v>
       </c>
       <c r="F158" s="4" t="s">
-        <v>590</v>
+        <v>560</v>
       </c>
       <c r="G158" s="4" t="s">
-        <v>139</v>
+        <v>123</v>
       </c>
       <c r="H158" s="4"/>
       <c r="I158" s="4"/>
@@ -8968,34 +9045,34 @@
       <c r="L158" s="4"/>
       <c r="M158" s="4"/>
       <c r="N158" s="4" t="s">
-        <v>67</v>
+        <v>63</v>
       </c>
       <c r="O158" s="4" t="s">
-        <v>67</v>
+        <v>63</v>
       </c>
       <c r="P158" s="4"/>
     </row>
-    <row r="159" spans="1:16" x14ac:dyDescent="0.45">
+    <row r="159" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A159" s="2" t="s">
-        <v>595</v>
+        <v>579</v>
       </c>
       <c r="B159" s="3" t="s">
-        <v>523</v>
+        <v>507</v>
       </c>
       <c r="C159" s="3" t="s">
-        <v>524</v>
+        <v>508</v>
       </c>
       <c r="D159" s="4" t="s">
-        <v>596</v>
+        <v>443</v>
       </c>
       <c r="E159" s="4" t="s">
-        <v>597</v>
+        <v>562</v>
       </c>
       <c r="F159" s="4" t="s">
-        <v>598</v>
+        <v>563</v>
       </c>
       <c r="G159" s="4" t="s">
-        <v>139</v>
+        <v>123</v>
       </c>
       <c r="H159" s="4"/>
       <c r="I159" s="4"/>
@@ -9006,38 +9083,36 @@
       <c r="L159" s="4"/>
       <c r="M159" s="4"/>
       <c r="N159" s="4" t="s">
-        <v>67</v>
+        <v>63</v>
       </c>
       <c r="O159" s="4" t="s">
-        <v>67</v>
+        <v>63</v>
       </c>
       <c r="P159" s="4"/>
     </row>
-    <row r="160" spans="1:16" x14ac:dyDescent="0.45">
+    <row r="160" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A160" s="2" t="s">
-        <v>599</v>
+        <v>583</v>
       </c>
       <c r="B160" s="3" t="s">
-        <v>523</v>
+        <v>507</v>
       </c>
       <c r="C160" s="3" t="s">
-        <v>600</v>
+        <v>508</v>
       </c>
       <c r="D160" s="4" t="s">
-        <v>601</v>
+        <v>260</v>
       </c>
       <c r="E160" s="4" t="s">
-        <v>602</v>
+        <v>565</v>
       </c>
       <c r="F160" s="4" t="s">
-        <v>527</v>
+        <v>566</v>
       </c>
       <c r="G160" s="4" t="s">
-        <v>66</v>
-      </c>
-      <c r="H160" s="4" t="s">
-        <v>46</v>
-      </c>
+        <v>123</v>
+      </c>
+      <c r="H160" s="4"/>
       <c r="I160" s="4"/>
       <c r="J160" s="4" t="s">
         <v>23</v>
@@ -9046,38 +9121,36 @@
       <c r="L160" s="4"/>
       <c r="M160" s="4"/>
       <c r="N160" s="4" t="s">
-        <v>67</v>
+        <v>63</v>
       </c>
       <c r="O160" s="4" t="s">
-        <v>67</v>
+        <v>63</v>
       </c>
       <c r="P160" s="4"/>
     </row>
-    <row r="161" spans="1:16" x14ac:dyDescent="0.45">
+    <row r="161" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A161" s="2" t="s">
-        <v>603</v>
+        <v>587</v>
       </c>
       <c r="B161" s="3" t="s">
-        <v>523</v>
+        <v>507</v>
       </c>
       <c r="C161" s="3" t="s">
-        <v>600</v>
+        <v>508</v>
       </c>
       <c r="D161" s="4" t="s">
-        <v>604</v>
+        <v>568</v>
       </c>
       <c r="E161" s="4" t="s">
-        <v>605</v>
+        <v>569</v>
       </c>
       <c r="F161" s="4" t="s">
-        <v>606</v>
+        <v>570</v>
       </c>
       <c r="G161" s="4" t="s">
-        <v>66</v>
-      </c>
-      <c r="H161" s="4" t="s">
-        <v>46</v>
-      </c>
+        <v>123</v>
+      </c>
+      <c r="H161" s="4"/>
       <c r="I161" s="4"/>
       <c r="J161" s="4" t="s">
         <v>23</v>
@@ -9086,34 +9159,34 @@
       <c r="L161" s="4"/>
       <c r="M161" s="4"/>
       <c r="N161" s="4" t="s">
-        <v>67</v>
+        <v>63</v>
       </c>
       <c r="O161" s="4" t="s">
-        <v>67</v>
+        <v>63</v>
       </c>
       <c r="P161" s="4"/>
     </row>
-    <row r="162" spans="1:16" x14ac:dyDescent="0.45">
+    <row r="162" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A162" s="2" t="s">
-        <v>607</v>
+        <v>591</v>
       </c>
       <c r="B162" s="3" t="s">
-        <v>523</v>
+        <v>507</v>
       </c>
       <c r="C162" s="3" t="s">
-        <v>600</v>
+        <v>508</v>
       </c>
       <c r="D162" s="4" t="s">
-        <v>632</v>
+        <v>576</v>
       </c>
       <c r="E162" s="4" t="s">
-        <v>633</v>
+        <v>577</v>
       </c>
       <c r="F162" s="4" t="s">
-        <v>634</v>
+        <v>578</v>
       </c>
       <c r="G162" s="4" t="s">
-        <v>139</v>
+        <v>123</v>
       </c>
       <c r="H162" s="4"/>
       <c r="I162" s="4"/>
@@ -9124,34 +9197,34 @@
       <c r="L162" s="4"/>
       <c r="M162" s="4"/>
       <c r="N162" s="4" t="s">
-        <v>67</v>
+        <v>63</v>
       </c>
       <c r="O162" s="4" t="s">
-        <v>67</v>
+        <v>63</v>
       </c>
       <c r="P162" s="4"/>
     </row>
-    <row r="163" spans="1:16" x14ac:dyDescent="0.45">
+    <row r="163" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A163" s="2" t="s">
-        <v>611</v>
+        <v>595</v>
       </c>
       <c r="B163" s="3" t="s">
-        <v>523</v>
+        <v>507</v>
       </c>
       <c r="C163" s="3" t="s">
-        <v>600</v>
+        <v>508</v>
       </c>
       <c r="D163" s="4" t="s">
-        <v>636</v>
+        <v>572</v>
       </c>
       <c r="E163" s="4" t="s">
-        <v>637</v>
+        <v>573</v>
       </c>
       <c r="F163" s="4" t="s">
-        <v>634</v>
+        <v>574</v>
       </c>
       <c r="G163" s="4" t="s">
-        <v>139</v>
+        <v>123</v>
       </c>
       <c r="H163" s="4"/>
       <c r="I163" s="4"/>
@@ -9162,34 +9235,34 @@
       <c r="L163" s="4"/>
       <c r="M163" s="4"/>
       <c r="N163" s="4" t="s">
-        <v>67</v>
+        <v>63</v>
       </c>
       <c r="O163" s="4" t="s">
-        <v>67</v>
+        <v>63</v>
       </c>
       <c r="P163" s="4"/>
     </row>
-    <row r="164" spans="1:16" x14ac:dyDescent="0.45">
+    <row r="164" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A164" s="2" t="s">
-        <v>615</v>
+        <v>599</v>
       </c>
       <c r="B164" s="3" t="s">
-        <v>523</v>
+        <v>507</v>
       </c>
       <c r="C164" s="3" t="s">
-        <v>600</v>
+        <v>508</v>
       </c>
       <c r="D164" s="4" t="s">
-        <v>608</v>
+        <v>580</v>
       </c>
       <c r="E164" s="4" t="s">
-        <v>609</v>
+        <v>581</v>
       </c>
       <c r="F164" s="4" t="s">
-        <v>610</v>
+        <v>582</v>
       </c>
       <c r="G164" s="4" t="s">
-        <v>139</v>
+        <v>123</v>
       </c>
       <c r="H164" s="4"/>
       <c r="I164" s="4"/>
@@ -9200,36 +9273,38 @@
       <c r="L164" s="4"/>
       <c r="M164" s="4"/>
       <c r="N164" s="4" t="s">
-        <v>67</v>
+        <v>63</v>
       </c>
       <c r="O164" s="4" t="s">
-        <v>67</v>
+        <v>63</v>
       </c>
       <c r="P164" s="4"/>
     </row>
-    <row r="165" spans="1:16" x14ac:dyDescent="0.45">
+    <row r="165" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A165" s="2" t="s">
-        <v>619</v>
+        <v>603</v>
       </c>
       <c r="B165" s="3" t="s">
-        <v>523</v>
+        <v>507</v>
       </c>
       <c r="C165" s="3" t="s">
-        <v>600</v>
+        <v>584</v>
       </c>
       <c r="D165" s="4" t="s">
-        <v>612</v>
+        <v>585</v>
       </c>
       <c r="E165" s="4" t="s">
-        <v>613</v>
+        <v>586</v>
       </c>
       <c r="F165" s="4" t="s">
-        <v>614</v>
+        <v>511</v>
       </c>
       <c r="G165" s="4" t="s">
-        <v>139</v>
-      </c>
-      <c r="H165" s="4"/>
+        <v>62</v>
+      </c>
+      <c r="H165" s="4" t="s">
+        <v>46</v>
+      </c>
       <c r="I165" s="4"/>
       <c r="J165" s="4" t="s">
         <v>23</v>
@@ -9238,36 +9313,38 @@
       <c r="L165" s="4"/>
       <c r="M165" s="4"/>
       <c r="N165" s="4" t="s">
-        <v>67</v>
+        <v>63</v>
       </c>
       <c r="O165" s="4" t="s">
-        <v>67</v>
+        <v>63</v>
       </c>
       <c r="P165" s="4"/>
     </row>
-    <row r="166" spans="1:16" x14ac:dyDescent="0.45">
+    <row r="166" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A166" s="2" t="s">
-        <v>623</v>
+        <v>607</v>
       </c>
       <c r="B166" s="3" t="s">
-        <v>523</v>
+        <v>507</v>
       </c>
       <c r="C166" s="3" t="s">
-        <v>600</v>
+        <v>584</v>
       </c>
       <c r="D166" s="4" t="s">
-        <v>616</v>
+        <v>588</v>
       </c>
       <c r="E166" s="4" t="s">
-        <v>617</v>
+        <v>589</v>
       </c>
       <c r="F166" s="4" t="s">
-        <v>618</v>
+        <v>590</v>
       </c>
       <c r="G166" s="4" t="s">
-        <v>139</v>
-      </c>
-      <c r="H166" s="4"/>
+        <v>62</v>
+      </c>
+      <c r="H166" s="4" t="s">
+        <v>46</v>
+      </c>
       <c r="I166" s="4"/>
       <c r="J166" s="4" t="s">
         <v>23</v>
@@ -9276,34 +9353,34 @@
       <c r="L166" s="4"/>
       <c r="M166" s="4"/>
       <c r="N166" s="4" t="s">
-        <v>67</v>
+        <v>63</v>
       </c>
       <c r="O166" s="4" t="s">
-        <v>67</v>
+        <v>63</v>
       </c>
       <c r="P166" s="4"/>
     </row>
-    <row r="167" spans="1:16" x14ac:dyDescent="0.45">
+    <row r="167" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A167" s="2" t="s">
-        <v>627</v>
+        <v>611</v>
       </c>
       <c r="B167" s="3" t="s">
-        <v>523</v>
+        <v>507</v>
       </c>
       <c r="C167" s="3" t="s">
-        <v>600</v>
+        <v>584</v>
       </c>
       <c r="D167" s="4" t="s">
-        <v>620</v>
+        <v>616</v>
       </c>
       <c r="E167" s="4" t="s">
-        <v>621</v>
+        <v>617</v>
       </c>
       <c r="F167" s="4" t="s">
-        <v>622</v>
+        <v>618</v>
       </c>
       <c r="G167" s="4" t="s">
-        <v>139</v>
+        <v>123</v>
       </c>
       <c r="H167" s="4"/>
       <c r="I167" s="4"/>
@@ -9314,34 +9391,34 @@
       <c r="L167" s="4"/>
       <c r="M167" s="4"/>
       <c r="N167" s="4" t="s">
-        <v>67</v>
+        <v>63</v>
       </c>
       <c r="O167" s="4" t="s">
-        <v>67</v>
+        <v>63</v>
       </c>
       <c r="P167" s="4"/>
     </row>
-    <row r="168" spans="1:16" x14ac:dyDescent="0.45">
+    <row r="168" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A168" s="2" t="s">
-        <v>631</v>
+        <v>615</v>
       </c>
       <c r="B168" s="3" t="s">
-        <v>523</v>
+        <v>507</v>
       </c>
       <c r="C168" s="3" t="s">
-        <v>600</v>
+        <v>584</v>
       </c>
       <c r="D168" s="4" t="s">
-        <v>624</v>
+        <v>620</v>
       </c>
       <c r="E168" s="4" t="s">
-        <v>625</v>
+        <v>621</v>
       </c>
       <c r="F168" s="4" t="s">
-        <v>626</v>
+        <v>618</v>
       </c>
       <c r="G168" s="4" t="s">
-        <v>139</v>
+        <v>123</v>
       </c>
       <c r="H168" s="4"/>
       <c r="I168" s="4"/>
@@ -9352,34 +9429,34 @@
       <c r="L168" s="4"/>
       <c r="M168" s="4"/>
       <c r="N168" s="4" t="s">
-        <v>67</v>
+        <v>63</v>
       </c>
       <c r="O168" s="4" t="s">
-        <v>67</v>
+        <v>63</v>
       </c>
       <c r="P168" s="4"/>
     </row>
-    <row r="169" spans="1:16" x14ac:dyDescent="0.45">
+    <row r="169" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A169" s="2" t="s">
-        <v>635</v>
+        <v>619</v>
       </c>
       <c r="B169" s="3" t="s">
-        <v>523</v>
+        <v>507</v>
       </c>
       <c r="C169" s="3" t="s">
-        <v>600</v>
+        <v>584</v>
       </c>
       <c r="D169" s="4" t="s">
-        <v>628</v>
+        <v>592</v>
       </c>
       <c r="E169" s="4" t="s">
-        <v>629</v>
+        <v>593</v>
       </c>
       <c r="F169" s="4" t="s">
-        <v>630</v>
+        <v>594</v>
       </c>
       <c r="G169" s="4" t="s">
-        <v>139</v>
+        <v>123</v>
       </c>
       <c r="H169" s="4"/>
       <c r="I169" s="4"/>
@@ -9390,34 +9467,34 @@
       <c r="L169" s="4"/>
       <c r="M169" s="4"/>
       <c r="N169" s="4" t="s">
-        <v>67</v>
+        <v>63</v>
       </c>
       <c r="O169" s="4" t="s">
-        <v>67</v>
+        <v>63</v>
       </c>
       <c r="P169" s="4"/>
     </row>
-    <row r="170" spans="1:16" x14ac:dyDescent="0.45">
+    <row r="170" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A170" s="2" t="s">
-        <v>638</v>
+        <v>622</v>
       </c>
       <c r="B170" s="3" t="s">
-        <v>523</v>
+        <v>507</v>
       </c>
       <c r="C170" s="3" t="s">
-        <v>600</v>
+        <v>584</v>
       </c>
       <c r="D170" s="4" t="s">
-        <v>639</v>
+        <v>596</v>
       </c>
       <c r="E170" s="4" t="s">
-        <v>640</v>
+        <v>597</v>
       </c>
       <c r="F170" s="4" t="s">
-        <v>641</v>
+        <v>598</v>
       </c>
       <c r="G170" s="4" t="s">
-        <v>139</v>
+        <v>123</v>
       </c>
       <c r="H170" s="4"/>
       <c r="I170" s="4"/>
@@ -9428,34 +9505,34 @@
       <c r="L170" s="4"/>
       <c r="M170" s="4"/>
       <c r="N170" s="4" t="s">
-        <v>67</v>
+        <v>63</v>
       </c>
       <c r="O170" s="4" t="s">
-        <v>67</v>
+        <v>63</v>
       </c>
       <c r="P170" s="4"/>
     </row>
-    <row r="171" spans="1:16" x14ac:dyDescent="0.45">
+    <row r="171" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A171" s="2" t="s">
-        <v>642</v>
+        <v>626</v>
       </c>
       <c r="B171" s="3" t="s">
-        <v>523</v>
+        <v>507</v>
       </c>
       <c r="C171" s="3" t="s">
+        <v>584</v>
+      </c>
+      <c r="D171" s="4" t="s">
         <v>600</v>
       </c>
-      <c r="D171" s="4" t="s">
-        <v>643</v>
-      </c>
       <c r="E171" s="4" t="s">
-        <v>644</v>
+        <v>601</v>
       </c>
       <c r="F171" s="4" t="s">
-        <v>645</v>
+        <v>602</v>
       </c>
       <c r="G171" s="4" t="s">
-        <v>139</v>
+        <v>123</v>
       </c>
       <c r="H171" s="4"/>
       <c r="I171" s="4"/>
@@ -9466,34 +9543,34 @@
       <c r="L171" s="4"/>
       <c r="M171" s="4"/>
       <c r="N171" s="4" t="s">
-        <v>67</v>
+        <v>63</v>
       </c>
       <c r="O171" s="4" t="s">
-        <v>67</v>
+        <v>63</v>
       </c>
       <c r="P171" s="4"/>
     </row>
-    <row r="172" spans="1:16" x14ac:dyDescent="0.45">
+    <row r="172" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A172" s="2" t="s">
-        <v>646</v>
+        <v>630</v>
       </c>
       <c r="B172" s="3" t="s">
-        <v>523</v>
+        <v>507</v>
       </c>
       <c r="C172" s="3" t="s">
-        <v>600</v>
+        <v>584</v>
       </c>
       <c r="D172" s="4" t="s">
-        <v>218</v>
+        <v>604</v>
       </c>
       <c r="E172" s="4" t="s">
-        <v>647</v>
+        <v>605</v>
       </c>
       <c r="F172" s="4" t="s">
-        <v>648</v>
+        <v>606</v>
       </c>
       <c r="G172" s="4" t="s">
-        <v>139</v>
+        <v>123</v>
       </c>
       <c r="H172" s="4"/>
       <c r="I172" s="4"/>
@@ -9504,34 +9581,34 @@
       <c r="L172" s="4"/>
       <c r="M172" s="4"/>
       <c r="N172" s="4" t="s">
-        <v>67</v>
+        <v>63</v>
       </c>
       <c r="O172" s="4" t="s">
-        <v>67</v>
+        <v>63</v>
       </c>
       <c r="P172" s="4"/>
     </row>
-    <row r="173" spans="1:16" x14ac:dyDescent="0.45">
+    <row r="173" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A173" s="2" t="s">
-        <v>649</v>
+        <v>633</v>
       </c>
       <c r="B173" s="3" t="s">
-        <v>523</v>
+        <v>507</v>
       </c>
       <c r="C173" s="3" t="s">
-        <v>600</v>
+        <v>584</v>
       </c>
       <c r="D173" s="4" t="s">
-        <v>345</v>
+        <v>608</v>
       </c>
       <c r="E173" s="4" t="s">
-        <v>650</v>
+        <v>609</v>
       </c>
       <c r="F173" s="4" t="s">
-        <v>651</v>
+        <v>610</v>
       </c>
       <c r="G173" s="4" t="s">
-        <v>139</v>
+        <v>123</v>
       </c>
       <c r="H173" s="4"/>
       <c r="I173" s="4"/>
@@ -9542,34 +9619,34 @@
       <c r="L173" s="4"/>
       <c r="M173" s="4"/>
       <c r="N173" s="4" t="s">
-        <v>67</v>
+        <v>63</v>
       </c>
       <c r="O173" s="4" t="s">
-        <v>67</v>
+        <v>63</v>
       </c>
       <c r="P173" s="4"/>
     </row>
-    <row r="174" spans="1:16" x14ac:dyDescent="0.45">
+    <row r="174" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A174" s="2" t="s">
-        <v>652</v>
+        <v>636</v>
       </c>
       <c r="B174" s="3" t="s">
-        <v>523</v>
+        <v>507</v>
       </c>
       <c r="C174" s="3" t="s">
-        <v>600</v>
+        <v>584</v>
       </c>
       <c r="D174" s="4" t="s">
-        <v>653</v>
+        <v>612</v>
       </c>
       <c r="E174" s="4" t="s">
-        <v>654</v>
+        <v>613</v>
       </c>
       <c r="F174" s="4" t="s">
-        <v>655</v>
+        <v>614</v>
       </c>
       <c r="G174" s="4" t="s">
-        <v>139</v>
+        <v>123</v>
       </c>
       <c r="H174" s="4"/>
       <c r="I174" s="4"/>
@@ -9580,34 +9657,34 @@
       <c r="L174" s="4"/>
       <c r="M174" s="4"/>
       <c r="N174" s="4" t="s">
-        <v>67</v>
+        <v>63</v>
       </c>
       <c r="O174" s="4" t="s">
-        <v>67</v>
+        <v>63</v>
       </c>
       <c r="P174" s="4"/>
     </row>
-    <row r="175" spans="1:16" x14ac:dyDescent="0.45">
+    <row r="175" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A175" s="2" t="s">
-        <v>656</v>
+        <v>640</v>
       </c>
       <c r="B175" s="3" t="s">
-        <v>523</v>
+        <v>507</v>
       </c>
       <c r="C175" s="3" t="s">
-        <v>600</v>
+        <v>584</v>
       </c>
       <c r="D175" s="4" t="s">
-        <v>349</v>
+        <v>623</v>
       </c>
       <c r="E175" s="4" t="s">
-        <v>657</v>
+        <v>624</v>
       </c>
       <c r="F175" s="4" t="s">
-        <v>658</v>
+        <v>625</v>
       </c>
       <c r="G175" s="4" t="s">
-        <v>139</v>
+        <v>123</v>
       </c>
       <c r="H175" s="4"/>
       <c r="I175" s="4"/>
@@ -9618,34 +9695,34 @@
       <c r="L175" s="4"/>
       <c r="M175" s="4"/>
       <c r="N175" s="4" t="s">
-        <v>67</v>
+        <v>63</v>
       </c>
       <c r="O175" s="4" t="s">
-        <v>67</v>
+        <v>63</v>
       </c>
       <c r="P175" s="4"/>
     </row>
-    <row r="176" spans="1:16" x14ac:dyDescent="0.45">
+    <row r="176" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A176" s="2" t="s">
-        <v>659</v>
+        <v>643</v>
       </c>
       <c r="B176" s="3" t="s">
-        <v>523</v>
+        <v>507</v>
       </c>
       <c r="C176" s="3" t="s">
-        <v>600</v>
+        <v>584</v>
       </c>
       <c r="D176" s="4" t="s">
-        <v>660</v>
+        <v>627</v>
       </c>
       <c r="E176" s="4" t="s">
-        <v>661</v>
+        <v>628</v>
       </c>
       <c r="F176" s="4" t="s">
-        <v>662</v>
+        <v>629</v>
       </c>
       <c r="G176" s="4" t="s">
-        <v>139</v>
+        <v>123</v>
       </c>
       <c r="H176" s="4"/>
       <c r="I176" s="4"/>
@@ -9656,34 +9733,34 @@
       <c r="L176" s="4"/>
       <c r="M176" s="4"/>
       <c r="N176" s="4" t="s">
-        <v>67</v>
+        <v>63</v>
       </c>
       <c r="O176" s="4" t="s">
-        <v>67</v>
+        <v>63</v>
       </c>
       <c r="P176" s="4"/>
     </row>
-    <row r="177" spans="1:16" x14ac:dyDescent="0.45">
+    <row r="177" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A177" s="2" t="s">
-        <v>663</v>
+        <v>647</v>
       </c>
       <c r="B177" s="3" t="s">
-        <v>523</v>
+        <v>507</v>
       </c>
       <c r="C177" s="3" t="s">
-        <v>600</v>
+        <v>584</v>
       </c>
       <c r="D177" s="4" t="s">
-        <v>668</v>
+        <v>202</v>
       </c>
       <c r="E177" s="4" t="s">
-        <v>669</v>
+        <v>631</v>
       </c>
       <c r="F177" s="4" t="s">
-        <v>670</v>
+        <v>632</v>
       </c>
       <c r="G177" s="4" t="s">
-        <v>139</v>
+        <v>123</v>
       </c>
       <c r="H177" s="4"/>
       <c r="I177" s="4"/>
@@ -9694,34 +9771,34 @@
       <c r="L177" s="4"/>
       <c r="M177" s="4"/>
       <c r="N177" s="4" t="s">
-        <v>67</v>
+        <v>63</v>
       </c>
       <c r="O177" s="4" t="s">
-        <v>67</v>
+        <v>63</v>
       </c>
       <c r="P177" s="4"/>
     </row>
-    <row r="178" spans="1:16" x14ac:dyDescent="0.45">
+    <row r="178" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A178" s="2" t="s">
-        <v>667</v>
+        <v>651</v>
       </c>
       <c r="B178" s="3" t="s">
-        <v>523</v>
+        <v>507</v>
       </c>
       <c r="C178" s="3" t="s">
-        <v>600</v>
+        <v>584</v>
       </c>
       <c r="D178" s="4" t="s">
-        <v>664</v>
+        <v>329</v>
       </c>
       <c r="E178" s="4" t="s">
-        <v>665</v>
+        <v>634</v>
       </c>
       <c r="F178" s="4" t="s">
-        <v>666</v>
+        <v>635</v>
       </c>
       <c r="G178" s="4" t="s">
-        <v>139</v>
+        <v>123</v>
       </c>
       <c r="H178" s="4"/>
       <c r="I178" s="4"/>
@@ -9732,34 +9809,34 @@
       <c r="L178" s="4"/>
       <c r="M178" s="4"/>
       <c r="N178" s="4" t="s">
-        <v>67</v>
+        <v>63</v>
       </c>
       <c r="O178" s="4" t="s">
-        <v>67</v>
+        <v>63</v>
       </c>
       <c r="P178" s="4"/>
     </row>
-    <row r="179" spans="1:16" x14ac:dyDescent="0.45">
+    <row r="179" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A179" s="2" t="s">
-        <v>671</v>
+        <v>655</v>
       </c>
       <c r="B179" s="3" t="s">
-        <v>523</v>
+        <v>507</v>
       </c>
       <c r="C179" s="3" t="s">
-        <v>600</v>
+        <v>584</v>
       </c>
       <c r="D179" s="4" t="s">
-        <v>672</v>
+        <v>637</v>
       </c>
       <c r="E179" s="4" t="s">
-        <v>673</v>
+        <v>638</v>
       </c>
       <c r="F179" s="4" t="s">
-        <v>674</v>
+        <v>639</v>
       </c>
       <c r="G179" s="4" t="s">
-        <v>139</v>
+        <v>123</v>
       </c>
       <c r="H179" s="4"/>
       <c r="I179" s="4"/>
@@ -9770,38 +9847,36 @@
       <c r="L179" s="4"/>
       <c r="M179" s="4"/>
       <c r="N179" s="4" t="s">
-        <v>67</v>
+        <v>63</v>
       </c>
       <c r="O179" s="4" t="s">
-        <v>67</v>
+        <v>63</v>
       </c>
       <c r="P179" s="4"/>
     </row>
-    <row r="180" spans="1:16" x14ac:dyDescent="0.45">
+    <row r="180" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A180" s="2" t="s">
-        <v>675</v>
+        <v>659</v>
       </c>
       <c r="B180" s="3" t="s">
-        <v>523</v>
+        <v>507</v>
       </c>
       <c r="C180" s="3" t="s">
-        <v>676</v>
+        <v>584</v>
       </c>
       <c r="D180" s="4" t="s">
-        <v>677</v>
+        <v>333</v>
       </c>
       <c r="E180" s="4" t="s">
-        <v>678</v>
+        <v>641</v>
       </c>
       <c r="F180" s="4" t="s">
-        <v>679</v>
+        <v>642</v>
       </c>
       <c r="G180" s="4" t="s">
-        <v>66</v>
-      </c>
-      <c r="H180" s="4" t="s">
-        <v>46</v>
-      </c>
+        <v>123</v>
+      </c>
+      <c r="H180" s="4"/>
       <c r="I180" s="4"/>
       <c r="J180" s="4" t="s">
         <v>23</v>
@@ -9810,38 +9885,36 @@
       <c r="L180" s="4"/>
       <c r="M180" s="4"/>
       <c r="N180" s="4" t="s">
-        <v>67</v>
+        <v>63</v>
       </c>
       <c r="O180" s="4" t="s">
-        <v>67</v>
+        <v>63</v>
       </c>
       <c r="P180" s="4"/>
     </row>
-    <row r="181" spans="1:16" x14ac:dyDescent="0.45">
+    <row r="181" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A181" s="2" t="s">
-        <v>680</v>
+        <v>664</v>
       </c>
       <c r="B181" s="3" t="s">
-        <v>523</v>
+        <v>507</v>
       </c>
       <c r="C181" s="3" t="s">
-        <v>676</v>
+        <v>584</v>
       </c>
       <c r="D181" s="4" t="s">
-        <v>681</v>
+        <v>644</v>
       </c>
       <c r="E181" s="4" t="s">
-        <v>682</v>
+        <v>645</v>
       </c>
       <c r="F181" s="4" t="s">
-        <v>683</v>
+        <v>646</v>
       </c>
       <c r="G181" s="4" t="s">
-        <v>66</v>
-      </c>
-      <c r="H181" s="4" t="s">
-        <v>46</v>
-      </c>
+        <v>123</v>
+      </c>
+      <c r="H181" s="4"/>
       <c r="I181" s="4"/>
       <c r="J181" s="4" t="s">
         <v>23</v>
@@ -9850,34 +9923,34 @@
       <c r="L181" s="4"/>
       <c r="M181" s="4"/>
       <c r="N181" s="4" t="s">
-        <v>67</v>
+        <v>63</v>
       </c>
       <c r="O181" s="4" t="s">
-        <v>67</v>
+        <v>63</v>
       </c>
       <c r="P181" s="4"/>
     </row>
-    <row r="182" spans="1:16" x14ac:dyDescent="0.45">
+    <row r="182" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A182" s="2" t="s">
-        <v>684</v>
+        <v>668</v>
       </c>
       <c r="B182" s="3" t="s">
-        <v>523</v>
+        <v>507</v>
       </c>
       <c r="C182" s="3" t="s">
-        <v>676</v>
+        <v>584</v>
       </c>
       <c r="D182" s="4" t="s">
-        <v>709</v>
+        <v>652</v>
       </c>
       <c r="E182" s="4" t="s">
-        <v>710</v>
+        <v>653</v>
       </c>
       <c r="F182" s="4" t="s">
-        <v>711</v>
+        <v>654</v>
       </c>
       <c r="G182" s="4" t="s">
-        <v>139</v>
+        <v>123</v>
       </c>
       <c r="H182" s="4"/>
       <c r="I182" s="4"/>
@@ -9888,34 +9961,34 @@
       <c r="L182" s="4"/>
       <c r="M182" s="4"/>
       <c r="N182" s="4" t="s">
-        <v>67</v>
+        <v>63</v>
       </c>
       <c r="O182" s="4" t="s">
-        <v>67</v>
+        <v>63</v>
       </c>
       <c r="P182" s="4"/>
     </row>
-    <row r="183" spans="1:16" x14ac:dyDescent="0.45">
+    <row r="183" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A183" s="2" t="s">
-        <v>688</v>
+        <v>672</v>
       </c>
       <c r="B183" s="3" t="s">
-        <v>523</v>
+        <v>507</v>
       </c>
       <c r="C183" s="3" t="s">
-        <v>676</v>
+        <v>584</v>
       </c>
       <c r="D183" s="4" t="s">
-        <v>713</v>
+        <v>648</v>
       </c>
       <c r="E183" s="4" t="s">
-        <v>714</v>
+        <v>649</v>
       </c>
       <c r="F183" s="4" t="s">
-        <v>711</v>
+        <v>650</v>
       </c>
       <c r="G183" s="4" t="s">
-        <v>139</v>
+        <v>123</v>
       </c>
       <c r="H183" s="4"/>
       <c r="I183" s="4"/>
@@ -9926,34 +9999,34 @@
       <c r="L183" s="4"/>
       <c r="M183" s="4"/>
       <c r="N183" s="4" t="s">
-        <v>67</v>
+        <v>63</v>
       </c>
       <c r="O183" s="4" t="s">
-        <v>67</v>
+        <v>63</v>
       </c>
       <c r="P183" s="4"/>
     </row>
-    <row r="184" spans="1:16" x14ac:dyDescent="0.45">
+    <row r="184" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A184" s="2" t="s">
-        <v>692</v>
+        <v>676</v>
       </c>
       <c r="B184" s="3" t="s">
-        <v>523</v>
+        <v>507</v>
       </c>
       <c r="C184" s="3" t="s">
-        <v>676</v>
+        <v>584</v>
       </c>
       <c r="D184" s="4" t="s">
-        <v>685</v>
+        <v>656</v>
       </c>
       <c r="E184" s="4" t="s">
-        <v>686</v>
+        <v>657</v>
       </c>
       <c r="F184" s="4" t="s">
-        <v>687</v>
+        <v>658</v>
       </c>
       <c r="G184" s="4" t="s">
-        <v>139</v>
+        <v>123</v>
       </c>
       <c r="H184" s="4"/>
       <c r="I184" s="4"/>
@@ -9964,36 +10037,38 @@
       <c r="L184" s="4"/>
       <c r="M184" s="4"/>
       <c r="N184" s="4" t="s">
-        <v>67</v>
+        <v>63</v>
       </c>
       <c r="O184" s="4" t="s">
-        <v>67</v>
+        <v>63</v>
       </c>
       <c r="P184" s="4"/>
     </row>
-    <row r="185" spans="1:16" x14ac:dyDescent="0.45">
+    <row r="185" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A185" s="2" t="s">
-        <v>696</v>
+        <v>680</v>
       </c>
       <c r="B185" s="3" t="s">
-        <v>523</v>
+        <v>507</v>
       </c>
       <c r="C185" s="3" t="s">
-        <v>676</v>
+        <v>660</v>
       </c>
       <c r="D185" s="4" t="s">
-        <v>689</v>
+        <v>661</v>
       </c>
       <c r="E185" s="4" t="s">
-        <v>690</v>
+        <v>662</v>
       </c>
       <c r="F185" s="4" t="s">
-        <v>691</v>
+        <v>663</v>
       </c>
       <c r="G185" s="4" t="s">
-        <v>139</v>
-      </c>
-      <c r="H185" s="4"/>
+        <v>62</v>
+      </c>
+      <c r="H185" s="4" t="s">
+        <v>46</v>
+      </c>
       <c r="I185" s="4"/>
       <c r="J185" s="4" t="s">
         <v>23</v>
@@ -10002,36 +10077,38 @@
       <c r="L185" s="4"/>
       <c r="M185" s="4"/>
       <c r="N185" s="4" t="s">
-        <v>67</v>
+        <v>63</v>
       </c>
       <c r="O185" s="4" t="s">
-        <v>67</v>
+        <v>63</v>
       </c>
       <c r="P185" s="4"/>
     </row>
-    <row r="186" spans="1:16" x14ac:dyDescent="0.45">
+    <row r="186" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A186" s="2" t="s">
-        <v>700</v>
+        <v>684</v>
       </c>
       <c r="B186" s="3" t="s">
-        <v>523</v>
+        <v>507</v>
       </c>
       <c r="C186" s="3" t="s">
-        <v>676</v>
+        <v>660</v>
       </c>
       <c r="D186" s="4" t="s">
-        <v>693</v>
+        <v>665</v>
       </c>
       <c r="E186" s="4" t="s">
-        <v>694</v>
+        <v>666</v>
       </c>
       <c r="F186" s="4" t="s">
-        <v>695</v>
+        <v>667</v>
       </c>
       <c r="G186" s="4" t="s">
-        <v>139</v>
-      </c>
-      <c r="H186" s="4"/>
+        <v>62</v>
+      </c>
+      <c r="H186" s="4" t="s">
+        <v>46</v>
+      </c>
       <c r="I186" s="4"/>
       <c r="J186" s="4" t="s">
         <v>23</v>
@@ -10040,34 +10117,34 @@
       <c r="L186" s="4"/>
       <c r="M186" s="4"/>
       <c r="N186" s="4" t="s">
-        <v>67</v>
+        <v>63</v>
       </c>
       <c r="O186" s="4" t="s">
-        <v>67</v>
+        <v>63</v>
       </c>
       <c r="P186" s="4"/>
     </row>
-    <row r="187" spans="1:16" x14ac:dyDescent="0.45">
+    <row r="187" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A187" s="2" t="s">
-        <v>704</v>
+        <v>688</v>
       </c>
       <c r="B187" s="3" t="s">
-        <v>523</v>
+        <v>507</v>
       </c>
       <c r="C187" s="3" t="s">
-        <v>676</v>
+        <v>660</v>
       </c>
       <c r="D187" s="4" t="s">
-        <v>697</v>
+        <v>693</v>
       </c>
       <c r="E187" s="4" t="s">
-        <v>698</v>
+        <v>694</v>
       </c>
       <c r="F187" s="4" t="s">
-        <v>699</v>
+        <v>695</v>
       </c>
       <c r="G187" s="4" t="s">
-        <v>139</v>
+        <v>123</v>
       </c>
       <c r="H187" s="4"/>
       <c r="I187" s="4"/>
@@ -10078,34 +10155,34 @@
       <c r="L187" s="4"/>
       <c r="M187" s="4"/>
       <c r="N187" s="4" t="s">
-        <v>67</v>
+        <v>63</v>
       </c>
       <c r="O187" s="4" t="s">
-        <v>67</v>
+        <v>63</v>
       </c>
       <c r="P187" s="4"/>
     </row>
-    <row r="188" spans="1:16" x14ac:dyDescent="0.45">
+    <row r="188" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A188" s="2" t="s">
-        <v>708</v>
+        <v>692</v>
       </c>
       <c r="B188" s="3" t="s">
-        <v>523</v>
+        <v>507</v>
       </c>
       <c r="C188" s="3" t="s">
-        <v>676</v>
+        <v>660</v>
       </c>
       <c r="D188" s="4" t="s">
-        <v>701</v>
+        <v>697</v>
       </c>
       <c r="E188" s="4" t="s">
-        <v>702</v>
+        <v>698</v>
       </c>
       <c r="F188" s="4" t="s">
-        <v>703</v>
+        <v>695</v>
       </c>
       <c r="G188" s="4" t="s">
-        <v>139</v>
+        <v>123</v>
       </c>
       <c r="H188" s="4"/>
       <c r="I188" s="4"/>
@@ -10116,34 +10193,34 @@
       <c r="L188" s="4"/>
       <c r="M188" s="4"/>
       <c r="N188" s="4" t="s">
-        <v>67</v>
+        <v>63</v>
       </c>
       <c r="O188" s="4" t="s">
-        <v>67</v>
+        <v>63</v>
       </c>
       <c r="P188" s="4"/>
     </row>
-    <row r="189" spans="1:16" x14ac:dyDescent="0.45">
+    <row r="189" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A189" s="2" t="s">
-        <v>712</v>
+        <v>696</v>
       </c>
       <c r="B189" s="3" t="s">
-        <v>523</v>
+        <v>507</v>
       </c>
       <c r="C189" s="3" t="s">
-        <v>676</v>
+        <v>660</v>
       </c>
       <c r="D189" s="4" t="s">
-        <v>705</v>
+        <v>669</v>
       </c>
       <c r="E189" s="4" t="s">
-        <v>706</v>
+        <v>670</v>
       </c>
       <c r="F189" s="4" t="s">
-        <v>707</v>
+        <v>671</v>
       </c>
       <c r="G189" s="4" t="s">
-        <v>139</v>
+        <v>123</v>
       </c>
       <c r="H189" s="4"/>
       <c r="I189" s="4"/>
@@ -10154,34 +10231,34 @@
       <c r="L189" s="4"/>
       <c r="M189" s="4"/>
       <c r="N189" s="4" t="s">
-        <v>67</v>
+        <v>63</v>
       </c>
       <c r="O189" s="4" t="s">
-        <v>67</v>
+        <v>63</v>
       </c>
       <c r="P189" s="4"/>
     </row>
-    <row r="190" spans="1:16" x14ac:dyDescent="0.45">
+    <row r="190" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A190" s="2" t="s">
-        <v>715</v>
+        <v>699</v>
       </c>
       <c r="B190" s="3" t="s">
-        <v>523</v>
+        <v>507</v>
       </c>
       <c r="C190" s="3" t="s">
-        <v>676</v>
+        <v>660</v>
       </c>
       <c r="D190" s="4" t="s">
-        <v>716</v>
+        <v>673</v>
       </c>
       <c r="E190" s="4" t="s">
-        <v>717</v>
+        <v>674</v>
       </c>
       <c r="F190" s="4" t="s">
-        <v>718</v>
+        <v>675</v>
       </c>
       <c r="G190" s="4" t="s">
-        <v>139</v>
+        <v>123</v>
       </c>
       <c r="H190" s="4"/>
       <c r="I190" s="4"/>
@@ -10192,34 +10269,34 @@
       <c r="L190" s="4"/>
       <c r="M190" s="4"/>
       <c r="N190" s="4" t="s">
-        <v>67</v>
+        <v>63</v>
       </c>
       <c r="O190" s="4" t="s">
-        <v>67</v>
+        <v>63</v>
       </c>
       <c r="P190" s="4"/>
     </row>
-    <row r="191" spans="1:16" x14ac:dyDescent="0.45">
+    <row r="191" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A191" s="2" t="s">
-        <v>719</v>
+        <v>703</v>
       </c>
       <c r="B191" s="3" t="s">
-        <v>523</v>
+        <v>507</v>
       </c>
       <c r="C191" s="3" t="s">
-        <v>676</v>
+        <v>660</v>
       </c>
       <c r="D191" s="4" t="s">
-        <v>720</v>
+        <v>677</v>
       </c>
       <c r="E191" s="4" t="s">
-        <v>721</v>
+        <v>678</v>
       </c>
       <c r="F191" s="4" t="s">
-        <v>722</v>
+        <v>679</v>
       </c>
       <c r="G191" s="4" t="s">
-        <v>139</v>
+        <v>123</v>
       </c>
       <c r="H191" s="4"/>
       <c r="I191" s="4"/>
@@ -10230,34 +10307,34 @@
       <c r="L191" s="4"/>
       <c r="M191" s="4"/>
       <c r="N191" s="4" t="s">
-        <v>67</v>
+        <v>63</v>
       </c>
       <c r="O191" s="4" t="s">
-        <v>67</v>
+        <v>63</v>
       </c>
       <c r="P191" s="4"/>
     </row>
-    <row r="192" spans="1:16" x14ac:dyDescent="0.45">
+    <row r="192" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A192" s="2" t="s">
-        <v>723</v>
+        <v>707</v>
       </c>
       <c r="B192" s="3" t="s">
-        <v>523</v>
+        <v>507</v>
       </c>
       <c r="C192" s="3" t="s">
-        <v>676</v>
+        <v>660</v>
       </c>
       <c r="D192" s="4" t="s">
-        <v>181</v>
+        <v>681</v>
       </c>
       <c r="E192" s="4" t="s">
-        <v>724</v>
+        <v>682</v>
       </c>
       <c r="F192" s="4" t="s">
-        <v>725</v>
+        <v>683</v>
       </c>
       <c r="G192" s="4" t="s">
-        <v>139</v>
+        <v>123</v>
       </c>
       <c r="H192" s="4"/>
       <c r="I192" s="4"/>
@@ -10268,34 +10345,34 @@
       <c r="L192" s="4"/>
       <c r="M192" s="4"/>
       <c r="N192" s="4" t="s">
-        <v>67</v>
+        <v>63</v>
       </c>
       <c r="O192" s="4" t="s">
-        <v>67</v>
+        <v>63</v>
       </c>
       <c r="P192" s="4"/>
     </row>
-    <row r="193" spans="1:16" x14ac:dyDescent="0.45">
+    <row r="193" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A193" s="2" t="s">
-        <v>726</v>
+        <v>710</v>
       </c>
       <c r="B193" s="3" t="s">
-        <v>523</v>
+        <v>507</v>
       </c>
       <c r="C193" s="3" t="s">
-        <v>676</v>
+        <v>660</v>
       </c>
       <c r="D193" s="4" t="s">
-        <v>727</v>
+        <v>685</v>
       </c>
       <c r="E193" s="4" t="s">
-        <v>728</v>
+        <v>686</v>
       </c>
       <c r="F193" s="4" t="s">
-        <v>729</v>
+        <v>687</v>
       </c>
       <c r="G193" s="4" t="s">
-        <v>139</v>
+        <v>123</v>
       </c>
       <c r="H193" s="4"/>
       <c r="I193" s="4"/>
@@ -10306,34 +10383,34 @@
       <c r="L193" s="4"/>
       <c r="M193" s="4"/>
       <c r="N193" s="4" t="s">
-        <v>67</v>
+        <v>63</v>
       </c>
       <c r="O193" s="4" t="s">
-        <v>67</v>
+        <v>63</v>
       </c>
       <c r="P193" s="4"/>
     </row>
-    <row r="194" spans="1:16" x14ac:dyDescent="0.45">
+    <row r="194" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A194" s="2" t="s">
-        <v>730</v>
+        <v>714</v>
       </c>
       <c r="B194" s="3" t="s">
-        <v>523</v>
+        <v>507</v>
       </c>
       <c r="C194" s="3" t="s">
-        <v>676</v>
+        <v>660</v>
       </c>
       <c r="D194" s="4" t="s">
-        <v>735</v>
+        <v>689</v>
       </c>
       <c r="E194" s="4" t="s">
-        <v>736</v>
+        <v>690</v>
       </c>
       <c r="F194" s="4" t="s">
-        <v>737</v>
+        <v>691</v>
       </c>
       <c r="G194" s="4" t="s">
-        <v>139</v>
+        <v>123</v>
       </c>
       <c r="H194" s="4"/>
       <c r="I194" s="4"/>
@@ -10344,34 +10421,34 @@
       <c r="L194" s="4"/>
       <c r="M194" s="4"/>
       <c r="N194" s="4" t="s">
-        <v>67</v>
+        <v>63</v>
       </c>
       <c r="O194" s="4" t="s">
-        <v>67</v>
+        <v>63</v>
       </c>
       <c r="P194" s="4"/>
     </row>
-    <row r="195" spans="1:16" x14ac:dyDescent="0.45">
+    <row r="195" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A195" s="2" t="s">
-        <v>734</v>
+        <v>718</v>
       </c>
       <c r="B195" s="3" t="s">
-        <v>523</v>
+        <v>507</v>
       </c>
       <c r="C195" s="3" t="s">
-        <v>676</v>
+        <v>660</v>
       </c>
       <c r="D195" s="4" t="s">
-        <v>731</v>
+        <v>700</v>
       </c>
       <c r="E195" s="4" t="s">
-        <v>732</v>
+        <v>701</v>
       </c>
       <c r="F195" s="4" t="s">
-        <v>733</v>
+        <v>702</v>
       </c>
       <c r="G195" s="4" t="s">
-        <v>139</v>
+        <v>123</v>
       </c>
       <c r="H195" s="4"/>
       <c r="I195" s="4"/>
@@ -10382,34 +10459,34 @@
       <c r="L195" s="4"/>
       <c r="M195" s="4"/>
       <c r="N195" s="4" t="s">
-        <v>67</v>
+        <v>63</v>
       </c>
       <c r="O195" s="4" t="s">
-        <v>67</v>
+        <v>63</v>
       </c>
       <c r="P195" s="4"/>
     </row>
-    <row r="196" spans="1:16" x14ac:dyDescent="0.45">
+    <row r="196" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A196" s="2" t="s">
-        <v>738</v>
+        <v>722</v>
       </c>
       <c r="B196" s="3" t="s">
-        <v>523</v>
+        <v>507</v>
       </c>
       <c r="C196" s="3" t="s">
-        <v>676</v>
+        <v>660</v>
       </c>
       <c r="D196" s="4" t="s">
-        <v>739</v>
+        <v>704</v>
       </c>
       <c r="E196" s="4" t="s">
-        <v>740</v>
+        <v>705</v>
       </c>
       <c r="F196" s="4" t="s">
-        <v>741</v>
+        <v>706</v>
       </c>
       <c r="G196" s="4" t="s">
-        <v>139</v>
+        <v>123</v>
       </c>
       <c r="H196" s="4"/>
       <c r="I196" s="4"/>
@@ -10420,38 +10497,36 @@
       <c r="L196" s="4"/>
       <c r="M196" s="4"/>
       <c r="N196" s="4" t="s">
-        <v>67</v>
+        <v>63</v>
       </c>
       <c r="O196" s="4" t="s">
-        <v>67</v>
+        <v>63</v>
       </c>
       <c r="P196" s="4"/>
     </row>
-    <row r="197" spans="1:16" x14ac:dyDescent="0.45">
+    <row r="197" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A197" s="2" t="s">
-        <v>742</v>
+        <v>726</v>
       </c>
       <c r="B197" s="3" t="s">
-        <v>523</v>
+        <v>507</v>
       </c>
       <c r="C197" s="3" t="s">
-        <v>743</v>
+        <v>660</v>
       </c>
       <c r="D197" s="4" t="s">
-        <v>744</v>
+        <v>165</v>
       </c>
       <c r="E197" s="4" t="s">
-        <v>745</v>
+        <v>708</v>
       </c>
       <c r="F197" s="4" t="s">
-        <v>746</v>
+        <v>709</v>
       </c>
       <c r="G197" s="4" t="s">
-        <v>66</v>
-      </c>
-      <c r="H197" s="4" t="s">
-        <v>46</v>
-      </c>
+        <v>123</v>
+      </c>
+      <c r="H197" s="4"/>
       <c r="I197" s="4"/>
       <c r="J197" s="4" t="s">
         <v>23</v>
@@ -10460,38 +10535,36 @@
       <c r="L197" s="4"/>
       <c r="M197" s="4"/>
       <c r="N197" s="4" t="s">
-        <v>67</v>
+        <v>63</v>
       </c>
       <c r="O197" s="4" t="s">
-        <v>67</v>
+        <v>63</v>
       </c>
       <c r="P197" s="4"/>
     </row>
-    <row r="198" spans="1:16" x14ac:dyDescent="0.45">
+    <row r="198" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A198" s="2" t="s">
-        <v>747</v>
+        <v>731</v>
       </c>
       <c r="B198" s="3" t="s">
-        <v>523</v>
+        <v>507</v>
       </c>
       <c r="C198" s="3" t="s">
-        <v>743</v>
+        <v>660</v>
       </c>
       <c r="D198" s="4" t="s">
-        <v>748</v>
+        <v>711</v>
       </c>
       <c r="E198" s="4" t="s">
-        <v>749</v>
+        <v>712</v>
       </c>
       <c r="F198" s="4" t="s">
-        <v>750</v>
+        <v>713</v>
       </c>
       <c r="G198" s="4" t="s">
-        <v>66</v>
-      </c>
-      <c r="H198" s="4" t="s">
-        <v>46</v>
-      </c>
+        <v>123</v>
+      </c>
+      <c r="H198" s="4"/>
       <c r="I198" s="4"/>
       <c r="J198" s="4" t="s">
         <v>23</v>
@@ -10500,34 +10573,34 @@
       <c r="L198" s="4"/>
       <c r="M198" s="4"/>
       <c r="N198" s="4" t="s">
-        <v>67</v>
+        <v>63</v>
       </c>
       <c r="O198" s="4" t="s">
-        <v>67</v>
+        <v>63</v>
       </c>
       <c r="P198" s="4"/>
     </row>
-    <row r="199" spans="1:16" x14ac:dyDescent="0.45">
+    <row r="199" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A199" s="2" t="s">
-        <v>751</v>
+        <v>735</v>
       </c>
       <c r="B199" s="3" t="s">
-        <v>523</v>
+        <v>507</v>
       </c>
       <c r="C199" s="3" t="s">
-        <v>743</v>
+        <v>660</v>
       </c>
       <c r="D199" s="4" t="s">
-        <v>776</v>
+        <v>719</v>
       </c>
       <c r="E199" s="4" t="s">
-        <v>777</v>
+        <v>720</v>
       </c>
       <c r="F199" s="4" t="s">
-        <v>778</v>
+        <v>721</v>
       </c>
       <c r="G199" s="4" t="s">
-        <v>139</v>
+        <v>123</v>
       </c>
       <c r="H199" s="4"/>
       <c r="I199" s="4"/>
@@ -10538,34 +10611,34 @@
       <c r="L199" s="4"/>
       <c r="M199" s="4"/>
       <c r="N199" s="4" t="s">
-        <v>67</v>
+        <v>63</v>
       </c>
       <c r="O199" s="4" t="s">
-        <v>67</v>
+        <v>63</v>
       </c>
       <c r="P199" s="4"/>
     </row>
-    <row r="200" spans="1:16" x14ac:dyDescent="0.45">
+    <row r="200" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A200" s="2" t="s">
-        <v>755</v>
+        <v>739</v>
       </c>
       <c r="B200" s="3" t="s">
-        <v>523</v>
+        <v>507</v>
       </c>
       <c r="C200" s="3" t="s">
-        <v>743</v>
+        <v>660</v>
       </c>
       <c r="D200" s="4" t="s">
-        <v>780</v>
+        <v>715</v>
       </c>
       <c r="E200" s="4" t="s">
-        <v>781</v>
+        <v>716</v>
       </c>
       <c r="F200" s="4" t="s">
-        <v>778</v>
+        <v>717</v>
       </c>
       <c r="G200" s="4" t="s">
-        <v>139</v>
+        <v>123</v>
       </c>
       <c r="H200" s="4"/>
       <c r="I200" s="4"/>
@@ -10576,34 +10649,34 @@
       <c r="L200" s="4"/>
       <c r="M200" s="4"/>
       <c r="N200" s="4" t="s">
-        <v>67</v>
+        <v>63</v>
       </c>
       <c r="O200" s="4" t="s">
-        <v>67</v>
+        <v>63</v>
       </c>
       <c r="P200" s="4"/>
     </row>
-    <row r="201" spans="1:16" x14ac:dyDescent="0.45">
+    <row r="201" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A201" s="2" t="s">
-        <v>759</v>
+        <v>743</v>
       </c>
       <c r="B201" s="3" t="s">
-        <v>523</v>
+        <v>507</v>
       </c>
       <c r="C201" s="3" t="s">
-        <v>743</v>
+        <v>660</v>
       </c>
       <c r="D201" s="4" t="s">
-        <v>752</v>
+        <v>723</v>
       </c>
       <c r="E201" s="4" t="s">
-        <v>753</v>
+        <v>724</v>
       </c>
       <c r="F201" s="4" t="s">
-        <v>754</v>
+        <v>725</v>
       </c>
       <c r="G201" s="4" t="s">
-        <v>139</v>
+        <v>123</v>
       </c>
       <c r="H201" s="4"/>
       <c r="I201" s="4"/>
@@ -10614,36 +10687,38 @@
       <c r="L201" s="4"/>
       <c r="M201" s="4"/>
       <c r="N201" s="4" t="s">
-        <v>67</v>
+        <v>63</v>
       </c>
       <c r="O201" s="4" t="s">
-        <v>67</v>
+        <v>63</v>
       </c>
       <c r="P201" s="4"/>
     </row>
-    <row r="202" spans="1:16" x14ac:dyDescent="0.45">
+    <row r="202" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A202" s="2" t="s">
-        <v>763</v>
+        <v>747</v>
       </c>
       <c r="B202" s="3" t="s">
-        <v>523</v>
+        <v>507</v>
       </c>
       <c r="C202" s="3" t="s">
-        <v>743</v>
+        <v>727</v>
       </c>
       <c r="D202" s="4" t="s">
-        <v>756</v>
+        <v>728</v>
       </c>
       <c r="E202" s="4" t="s">
-        <v>757</v>
+        <v>729</v>
       </c>
       <c r="F202" s="4" t="s">
-        <v>758</v>
+        <v>730</v>
       </c>
       <c r="G202" s="4" t="s">
-        <v>139</v>
-      </c>
-      <c r="H202" s="4"/>
+        <v>62</v>
+      </c>
+      <c r="H202" s="4" t="s">
+        <v>46</v>
+      </c>
       <c r="I202" s="4"/>
       <c r="J202" s="4" t="s">
         <v>23</v>
@@ -10652,36 +10727,38 @@
       <c r="L202" s="4"/>
       <c r="M202" s="4"/>
       <c r="N202" s="4" t="s">
-        <v>67</v>
+        <v>63</v>
       </c>
       <c r="O202" s="4" t="s">
-        <v>67</v>
+        <v>63</v>
       </c>
       <c r="P202" s="4"/>
     </row>
-    <row r="203" spans="1:16" x14ac:dyDescent="0.45">
+    <row r="203" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A203" s="2" t="s">
-        <v>767</v>
+        <v>751</v>
       </c>
       <c r="B203" s="3" t="s">
-        <v>523</v>
+        <v>507</v>
       </c>
       <c r="C203" s="3" t="s">
-        <v>743</v>
+        <v>727</v>
       </c>
       <c r="D203" s="4" t="s">
-        <v>760</v>
+        <v>732</v>
       </c>
       <c r="E203" s="4" t="s">
-        <v>761</v>
+        <v>733</v>
       </c>
       <c r="F203" s="4" t="s">
-        <v>762</v>
+        <v>734</v>
       </c>
       <c r="G203" s="4" t="s">
-        <v>139</v>
-      </c>
-      <c r="H203" s="4"/>
+        <v>62</v>
+      </c>
+      <c r="H203" s="4" t="s">
+        <v>46</v>
+      </c>
       <c r="I203" s="4"/>
       <c r="J203" s="4" t="s">
         <v>23</v>
@@ -10690,34 +10767,34 @@
       <c r="L203" s="4"/>
       <c r="M203" s="4"/>
       <c r="N203" s="4" t="s">
-        <v>67</v>
+        <v>63</v>
       </c>
       <c r="O203" s="4" t="s">
-        <v>67</v>
+        <v>63</v>
       </c>
       <c r="P203" s="4"/>
     </row>
-    <row r="204" spans="1:16" x14ac:dyDescent="0.45">
+    <row r="204" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A204" s="2" t="s">
-        <v>771</v>
+        <v>755</v>
       </c>
       <c r="B204" s="3" t="s">
-        <v>523</v>
+        <v>507</v>
       </c>
       <c r="C204" s="3" t="s">
-        <v>743</v>
+        <v>727</v>
       </c>
       <c r="D204" s="4" t="s">
-        <v>764</v>
+        <v>760</v>
       </c>
       <c r="E204" s="4" t="s">
-        <v>765</v>
+        <v>761</v>
       </c>
       <c r="F204" s="4" t="s">
-        <v>766</v>
+        <v>762</v>
       </c>
       <c r="G204" s="4" t="s">
-        <v>139</v>
+        <v>123</v>
       </c>
       <c r="H204" s="4"/>
       <c r="I204" s="4"/>
@@ -10728,34 +10805,34 @@
       <c r="L204" s="4"/>
       <c r="M204" s="4"/>
       <c r="N204" s="4" t="s">
-        <v>67</v>
+        <v>63</v>
       </c>
       <c r="O204" s="4" t="s">
-        <v>67</v>
+        <v>63</v>
       </c>
       <c r="P204" s="4"/>
     </row>
-    <row r="205" spans="1:16" x14ac:dyDescent="0.45">
+    <row r="205" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A205" s="2" t="s">
-        <v>775</v>
+        <v>759</v>
       </c>
       <c r="B205" s="3" t="s">
-        <v>523</v>
+        <v>507</v>
       </c>
       <c r="C205" s="3" t="s">
-        <v>743</v>
+        <v>727</v>
       </c>
       <c r="D205" s="4" t="s">
-        <v>768</v>
+        <v>764</v>
       </c>
       <c r="E205" s="4" t="s">
-        <v>769</v>
+        <v>765</v>
       </c>
       <c r="F205" s="4" t="s">
-        <v>770</v>
+        <v>762</v>
       </c>
       <c r="G205" s="4" t="s">
-        <v>139</v>
+        <v>123</v>
       </c>
       <c r="H205" s="4"/>
       <c r="I205" s="4"/>
@@ -10766,34 +10843,34 @@
       <c r="L205" s="4"/>
       <c r="M205" s="4"/>
       <c r="N205" s="4" t="s">
-        <v>67</v>
+        <v>63</v>
       </c>
       <c r="O205" s="4" t="s">
-        <v>67</v>
+        <v>63</v>
       </c>
       <c r="P205" s="4"/>
     </row>
-    <row r="206" spans="1:16" x14ac:dyDescent="0.45">
+    <row r="206" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A206" s="2" t="s">
-        <v>779</v>
+        <v>763</v>
       </c>
       <c r="B206" s="3" t="s">
-        <v>523</v>
+        <v>507</v>
       </c>
       <c r="C206" s="3" t="s">
-        <v>743</v>
+        <v>727</v>
       </c>
       <c r="D206" s="4" t="s">
-        <v>772</v>
+        <v>736</v>
       </c>
       <c r="E206" s="4" t="s">
-        <v>773</v>
+        <v>737</v>
       </c>
       <c r="F206" s="4" t="s">
-        <v>774</v>
+        <v>738</v>
       </c>
       <c r="G206" s="4" t="s">
-        <v>139</v>
+        <v>123</v>
       </c>
       <c r="H206" s="4"/>
       <c r="I206" s="4"/>
@@ -10804,34 +10881,34 @@
       <c r="L206" s="4"/>
       <c r="M206" s="4"/>
       <c r="N206" s="4" t="s">
-        <v>67</v>
+        <v>63</v>
       </c>
       <c r="O206" s="4" t="s">
-        <v>67</v>
+        <v>63</v>
       </c>
       <c r="P206" s="4"/>
     </row>
-    <row r="207" spans="1:16" x14ac:dyDescent="0.45">
+    <row r="207" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A207" s="2" t="s">
-        <v>782</v>
+        <v>766</v>
       </c>
       <c r="B207" s="3" t="s">
-        <v>523</v>
+        <v>507</v>
       </c>
       <c r="C207" s="3" t="s">
-        <v>743</v>
+        <v>727</v>
       </c>
       <c r="D207" s="4" t="s">
-        <v>783</v>
+        <v>740</v>
       </c>
       <c r="E207" s="4" t="s">
-        <v>784</v>
+        <v>741</v>
       </c>
       <c r="F207" s="4" t="s">
-        <v>785</v>
+        <v>742</v>
       </c>
       <c r="G207" s="4" t="s">
-        <v>139</v>
+        <v>123</v>
       </c>
       <c r="H207" s="4"/>
       <c r="I207" s="4"/>
@@ -10842,34 +10919,34 @@
       <c r="L207" s="4"/>
       <c r="M207" s="4"/>
       <c r="N207" s="4" t="s">
-        <v>67</v>
+        <v>63</v>
       </c>
       <c r="O207" s="4" t="s">
-        <v>67</v>
+        <v>63</v>
       </c>
       <c r="P207" s="4"/>
     </row>
-    <row r="208" spans="1:16" x14ac:dyDescent="0.45">
+    <row r="208" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A208" s="2" t="s">
-        <v>786</v>
+        <v>770</v>
       </c>
       <c r="B208" s="3" t="s">
-        <v>523</v>
+        <v>507</v>
       </c>
       <c r="C208" s="3" t="s">
-        <v>743</v>
+        <v>727</v>
       </c>
       <c r="D208" s="4" t="s">
-        <v>787</v>
+        <v>744</v>
       </c>
       <c r="E208" s="4" t="s">
-        <v>788</v>
+        <v>745</v>
       </c>
       <c r="F208" s="4" t="s">
-        <v>789</v>
+        <v>746</v>
       </c>
       <c r="G208" s="4" t="s">
-        <v>139</v>
+        <v>123</v>
       </c>
       <c r="H208" s="4"/>
       <c r="I208" s="4"/>
@@ -10880,34 +10957,34 @@
       <c r="L208" s="4"/>
       <c r="M208" s="4"/>
       <c r="N208" s="4" t="s">
-        <v>67</v>
+        <v>63</v>
       </c>
       <c r="O208" s="4" t="s">
-        <v>67</v>
+        <v>63</v>
       </c>
       <c r="P208" s="4"/>
     </row>
-    <row r="209" spans="1:16" x14ac:dyDescent="0.45">
+    <row r="209" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A209" s="2" t="s">
-        <v>790</v>
+        <v>774</v>
       </c>
       <c r="B209" s="3" t="s">
-        <v>523</v>
+        <v>507</v>
       </c>
       <c r="C209" s="3" t="s">
-        <v>743</v>
+        <v>727</v>
       </c>
       <c r="D209" s="4" t="s">
-        <v>218</v>
+        <v>748</v>
       </c>
       <c r="E209" s="4" t="s">
-        <v>791</v>
+        <v>749</v>
       </c>
       <c r="F209" s="4" t="s">
-        <v>792</v>
+        <v>750</v>
       </c>
       <c r="G209" s="4" t="s">
-        <v>139</v>
+        <v>123</v>
       </c>
       <c r="H209" s="4"/>
       <c r="I209" s="4"/>
@@ -10918,34 +10995,34 @@
       <c r="L209" s="4"/>
       <c r="M209" s="4"/>
       <c r="N209" s="4" t="s">
-        <v>67</v>
+        <v>63</v>
       </c>
       <c r="O209" s="4" t="s">
-        <v>67</v>
+        <v>63</v>
       </c>
       <c r="P209" s="4"/>
     </row>
-    <row r="210" spans="1:16" x14ac:dyDescent="0.45">
+    <row r="210" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A210" s="2" t="s">
-        <v>793</v>
+        <v>777</v>
       </c>
       <c r="B210" s="3" t="s">
-        <v>523</v>
+        <v>507</v>
       </c>
       <c r="C210" s="3" t="s">
-        <v>743</v>
+        <v>727</v>
       </c>
       <c r="D210" s="4" t="s">
-        <v>794</v>
+        <v>752</v>
       </c>
       <c r="E210" s="4" t="s">
-        <v>795</v>
+        <v>753</v>
       </c>
       <c r="F210" s="4" t="s">
-        <v>796</v>
+        <v>754</v>
       </c>
       <c r="G210" s="4" t="s">
-        <v>139</v>
+        <v>123</v>
       </c>
       <c r="H210" s="4"/>
       <c r="I210" s="4"/>
@@ -10956,34 +11033,34 @@
       <c r="L210" s="4"/>
       <c r="M210" s="4"/>
       <c r="N210" s="4" t="s">
-        <v>67</v>
+        <v>63</v>
       </c>
       <c r="O210" s="4" t="s">
-        <v>67</v>
+        <v>63</v>
       </c>
       <c r="P210" s="4"/>
     </row>
-    <row r="211" spans="1:16" x14ac:dyDescent="0.45">
+    <row r="211" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A211" s="2" t="s">
-        <v>797</v>
+        <v>781</v>
       </c>
       <c r="B211" s="3" t="s">
-        <v>523</v>
+        <v>507</v>
       </c>
       <c r="C211" s="3" t="s">
-        <v>743</v>
+        <v>727</v>
       </c>
       <c r="D211" s="4" t="s">
-        <v>802</v>
+        <v>756</v>
       </c>
       <c r="E211" s="4" t="s">
-        <v>803</v>
+        <v>757</v>
       </c>
       <c r="F211" s="4" t="s">
-        <v>804</v>
+        <v>758</v>
       </c>
       <c r="G211" s="4" t="s">
-        <v>139</v>
+        <v>123</v>
       </c>
       <c r="H211" s="4"/>
       <c r="I211" s="4"/>
@@ -10994,34 +11071,34 @@
       <c r="L211" s="4"/>
       <c r="M211" s="4"/>
       <c r="N211" s="4" t="s">
-        <v>67</v>
+        <v>63</v>
       </c>
       <c r="O211" s="4" t="s">
-        <v>67</v>
+        <v>63</v>
       </c>
       <c r="P211" s="4"/>
     </row>
-    <row r="212" spans="1:16" x14ac:dyDescent="0.45">
+    <row r="212" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A212" s="2" t="s">
-        <v>801</v>
+        <v>785</v>
       </c>
       <c r="B212" s="3" t="s">
-        <v>523</v>
+        <v>507</v>
       </c>
       <c r="C212" s="3" t="s">
-        <v>743</v>
+        <v>727</v>
       </c>
       <c r="D212" s="4" t="s">
-        <v>798</v>
+        <v>767</v>
       </c>
       <c r="E212" s="4" t="s">
-        <v>799</v>
+        <v>768</v>
       </c>
       <c r="F212" s="4" t="s">
-        <v>800</v>
+        <v>769</v>
       </c>
       <c r="G212" s="4" t="s">
-        <v>139</v>
+        <v>123</v>
       </c>
       <c r="H212" s="4"/>
       <c r="I212" s="4"/>
@@ -11032,34 +11109,34 @@
       <c r="L212" s="4"/>
       <c r="M212" s="4"/>
       <c r="N212" s="4" t="s">
-        <v>67</v>
+        <v>63</v>
       </c>
       <c r="O212" s="4" t="s">
-        <v>67</v>
+        <v>63</v>
       </c>
       <c r="P212" s="4"/>
     </row>
-    <row r="213" spans="1:16" x14ac:dyDescent="0.45">
+    <row r="213" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A213" s="2" t="s">
-        <v>805</v>
+        <v>789</v>
       </c>
       <c r="B213" s="3" t="s">
-        <v>523</v>
+        <v>507</v>
       </c>
       <c r="C213" s="3" t="s">
-        <v>743</v>
+        <v>727</v>
       </c>
       <c r="D213" s="4" t="s">
-        <v>806</v>
+        <v>771</v>
       </c>
       <c r="E213" s="4" t="s">
-        <v>807</v>
+        <v>772</v>
       </c>
       <c r="F213" s="4" t="s">
-        <v>808</v>
+        <v>773</v>
       </c>
       <c r="G213" s="4" t="s">
-        <v>139</v>
+        <v>123</v>
       </c>
       <c r="H213" s="4"/>
       <c r="I213" s="4"/>
@@ -11070,12 +11147,202 @@
       <c r="L213" s="4"/>
       <c r="M213" s="4"/>
       <c r="N213" s="4" t="s">
-        <v>67</v>
+        <v>63</v>
       </c>
       <c r="O213" s="4" t="s">
-        <v>67</v>
+        <v>63</v>
       </c>
       <c r="P213" s="4"/>
+    </row>
+    <row r="214" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A214" s="2" t="s">
+        <v>817</v>
+      </c>
+      <c r="B214" s="3" t="s">
+        <v>507</v>
+      </c>
+      <c r="C214" s="3" t="s">
+        <v>727</v>
+      </c>
+      <c r="D214" s="4" t="s">
+        <v>202</v>
+      </c>
+      <c r="E214" s="4" t="s">
+        <v>775</v>
+      </c>
+      <c r="F214" s="4" t="s">
+        <v>776</v>
+      </c>
+      <c r="G214" s="4" t="s">
+        <v>123</v>
+      </c>
+      <c r="H214" s="4"/>
+      <c r="I214" s="4"/>
+      <c r="J214" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="K214" s="4"/>
+      <c r="L214" s="4"/>
+      <c r="M214" s="4"/>
+      <c r="N214" s="4" t="s">
+        <v>63</v>
+      </c>
+      <c r="O214" s="4" t="s">
+        <v>63</v>
+      </c>
+      <c r="P214" s="4"/>
+    </row>
+    <row r="215" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A215" s="2" t="s">
+        <v>818</v>
+      </c>
+      <c r="B215" s="3" t="s">
+        <v>507</v>
+      </c>
+      <c r="C215" s="3" t="s">
+        <v>727</v>
+      </c>
+      <c r="D215" s="4" t="s">
+        <v>778</v>
+      </c>
+      <c r="E215" s="4" t="s">
+        <v>779</v>
+      </c>
+      <c r="F215" s="4" t="s">
+        <v>780</v>
+      </c>
+      <c r="G215" s="4" t="s">
+        <v>123</v>
+      </c>
+      <c r="H215" s="4"/>
+      <c r="I215" s="4"/>
+      <c r="J215" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="K215" s="4"/>
+      <c r="L215" s="4"/>
+      <c r="M215" s="4"/>
+      <c r="N215" s="4" t="s">
+        <v>63</v>
+      </c>
+      <c r="O215" s="4" t="s">
+        <v>63</v>
+      </c>
+      <c r="P215" s="4"/>
+    </row>
+    <row r="216" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A216" s="2" t="s">
+        <v>819</v>
+      </c>
+      <c r="B216" s="3" t="s">
+        <v>507</v>
+      </c>
+      <c r="C216" s="3" t="s">
+        <v>727</v>
+      </c>
+      <c r="D216" s="4" t="s">
+        <v>786</v>
+      </c>
+      <c r="E216" s="4" t="s">
+        <v>787</v>
+      </c>
+      <c r="F216" s="4" t="s">
+        <v>788</v>
+      </c>
+      <c r="G216" s="4" t="s">
+        <v>123</v>
+      </c>
+      <c r="H216" s="4"/>
+      <c r="I216" s="4"/>
+      <c r="J216" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="K216" s="4"/>
+      <c r="L216" s="4"/>
+      <c r="M216" s="4"/>
+      <c r="N216" s="4" t="s">
+        <v>63</v>
+      </c>
+      <c r="O216" s="4" t="s">
+        <v>63</v>
+      </c>
+      <c r="P216" s="4"/>
+    </row>
+    <row r="217" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A217" s="2" t="s">
+        <v>820</v>
+      </c>
+      <c r="B217" s="3" t="s">
+        <v>507</v>
+      </c>
+      <c r="C217" s="3" t="s">
+        <v>727</v>
+      </c>
+      <c r="D217" s="4" t="s">
+        <v>782</v>
+      </c>
+      <c r="E217" s="4" t="s">
+        <v>783</v>
+      </c>
+      <c r="F217" s="4" t="s">
+        <v>784</v>
+      </c>
+      <c r="G217" s="4" t="s">
+        <v>123</v>
+      </c>
+      <c r="H217" s="4"/>
+      <c r="I217" s="4"/>
+      <c r="J217" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="K217" s="4"/>
+      <c r="L217" s="4"/>
+      <c r="M217" s="4"/>
+      <c r="N217" s="4" t="s">
+        <v>63</v>
+      </c>
+      <c r="O217" s="4" t="s">
+        <v>63</v>
+      </c>
+      <c r="P217" s="4"/>
+    </row>
+    <row r="218" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="A218" s="2" t="s">
+        <v>821</v>
+      </c>
+      <c r="B218" s="3" t="s">
+        <v>507</v>
+      </c>
+      <c r="C218" s="3" t="s">
+        <v>727</v>
+      </c>
+      <c r="D218" s="4" t="s">
+        <v>790</v>
+      </c>
+      <c r="E218" s="4" t="s">
+        <v>791</v>
+      </c>
+      <c r="F218" s="4" t="s">
+        <v>792</v>
+      </c>
+      <c r="G218" s="4" t="s">
+        <v>123</v>
+      </c>
+      <c r="H218" s="4"/>
+      <c r="I218" s="4"/>
+      <c r="J218" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="K218" s="4"/>
+      <c r="L218" s="4"/>
+      <c r="M218" s="4"/>
+      <c r="N218" s="4" t="s">
+        <v>63</v>
+      </c>
+      <c r="O218" s="4" t="s">
+        <v>63</v>
+      </c>
+      <c r="P218" s="4"/>
     </row>
   </sheetData>
   <phoneticPr fontId="4" type="noConversion"/>

--- a/dataland-framework-toolbox/inputs/eutaxonomy-financials-2026-73/eutaxonomy-financials-2026-73.xlsx
+++ b/dataland-framework-toolbox/inputs/eutaxonomy-financials-2026-73/eutaxonomy-financials-2026-73.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\d92477\IdeaProjects\Dataland\dataland-framework-toolbox\inputs\eutaxonomy-financials-2026-73\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A461C037-8824-48B8-9BAB-53AB5FCB7BC3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0D114AE9-54E2-4988-BAA4-7286623F029C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Framework Data Model" sheetId="1" r:id="rId1"/>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2202" uniqueCount="832">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2222" uniqueCount="852">
   <si>
     <t>Field Identifier</t>
   </si>
@@ -2474,9 +2474,6 @@
     <t>CI_CAPEX_BASED_GAR_ASSETS_NON_ASSESSED_NO_ELIGIBLE_CP</t>
   </si>
   <si>
-    <t>CapEx-based total amount of assets Of which exposures financing counterparties reporting in accordance with Article 7(9) of Regulation (EU) 2026/73</t>
-  </si>
-  <si>
     <t>CapEx-based Total Amount Of Non-Assessed Exposures - Of which Not Assessed Considered Non-Material by the Credit Institution</t>
   </si>
   <si>
@@ -2525,10 +2522,73 @@
     <t>Turnover-based total amount of assets of which Financing Non-Material Activities of Counterparties</t>
   </si>
   <si>
-    <t>Turnover-based total amount of assets Of which exposures financing counterparties reporting in accordance with Article 7(9) of Regulation (EU) 2026/73</t>
-  </si>
-  <si>
     <t>Turnover-based total amount of assets of which Not Assessed Considered Non-Material by the Credit Institution</t>
+  </si>
+  <si>
+    <t>Field Calculation</t>
+  </si>
+  <si>
+    <t>Identity: [extendedEnumYesNoIsNfrdMandatory]</t>
+  </si>
+  <si>
+    <t>Identity: [extendedCurrencyCreditInstitutionAssetsForCalculationOfGreenAssetRatioTotalGrossCarryingAmount]</t>
+  </si>
+  <si>
+    <t>DivisionByPercent: [extendedCurrencyAssetManagementWeightedAverageValueOfAllInvestmentsTurnoverBasedMonetaryAmount,extendedDecimalAssetManagementWeightedAverageValueOfAllInvestmentsTurnoverBasedInPercent]; DivisionByPercent: [extendedCurrencyAssetManagementWeightedAverageValueOfAllInvestmentsCapexBasedMonetaryAmount,extendedDecimalAssetManagementWeightedAverageValueOfAllInvestmentsCapexBasedInPercent]</t>
+  </si>
+  <si>
+    <t>Identity: [extendedDecimalAssetManagementWeightedAverageValueOfAllInvestmentsTurnoverBasedInPercent]</t>
+  </si>
+  <si>
+    <t>Identity: [extendedDecimalAssetManagementBreakdownOfTheNumeratorOfTheKpiPerEnvironmentalObjectiveTurnoverBasedShareOfTurnoverBasedKpiSubstantiallyContributingToClimateChangeMitigationInPercentOfWhichTransitional]</t>
+  </si>
+  <si>
+    <t>Sum: [extendedDecimalAssetManagementBreakdownOfTheNumeratorOfTheKpiPerEnvironmentalObjectiveTurnoverBasedShareOfTurnoverBasedKpiSubstantiallyContributingToClimateChangeMitigationInPercentOfWhichEnabling,extendedDecimalAssetManagementBreakdownOfTheNumeratorOfTheKpiPerEnvironmentalObjectiveTurnoverBasedShareOfTurnoverBasedKpiSubstantiallyContributingToClimateChangeAdaptationInPercentOfWhichEnabling,extendedDecimalAssetManagementBreakdownOfTheNumeratorOfTheKpiPerEnvironmentalObjectiveTurnoverBasedShareOfTurnoverBasedKpiSubstantiallyContributingToSustainableUseAndProtectionOfWaterAndMarineResourcesInPercentOfWhichEnabling,extendedDecimalAssetManagementBreakdownOfTheNumeratorOfTheKpiPerEnvironmentalObjectiveTurnoverBasedShareOfTurnoverBasedKpiSubstantiallyContributingToTransitionToACircularEconomyInPercentOfWhichEnabling,extendedDecimalAssetManagementBreakdownOfTheNumeratorOfTheKpiPerEnvironmentalObjectiveTurnoverBasedShareOfTurnoverBasedKpiSubstantiallyContributingToPollutionPreventionAndControlInPercentOfWhichEnabling,extendedDecimalAssetManagementBreakdownOfTheNumeratorOfTheKpiPerEnvironmentalObjectiveTurnoverBasedShareOfTurnoverBasedKpiSubstantiallyContributingToProtectionAndRestorationOfBiodiversityAndEcosystemsInPercentOfWhichEnabling]</t>
+  </si>
+  <si>
+    <t>Identity: [extendedDecimalAssetManagementWeightedAverageValueOfAllInvestmentsCapexBasedInPercent]</t>
+  </si>
+  <si>
+    <t>Identity: [extendedDecimalAssetManagementBreakdownOfTheNumeratorOfTheKpiPerEnvironmentalObjectiveCapexBasedShareOfCapexBasedKpiSubstantiallyContributingToClimateChangeMitigationInPercentOfWhichTransitional]</t>
+  </si>
+  <si>
+    <t>Sum: [extendedDecimalAssetManagementBreakdownOfTheNumeratorOfTheKpiPerEnvironmentalObjectiveCapexBasedShareOfCapexBasedKpiSubstantiallyContributingToClimateChangeMitigationInPercentOfWhichEnabling,extendedDecimalAssetManagementBreakdownOfTheNumeratorOfTheKpiPerEnvironmentalObjectiveCapexBasedShareOfCapexBasedKpiSubstantiallyContributingToClimateChangeAdaptationInPercentOfWhichEnabling,extendedDecimalAssetManagementBreakdownOfTheNumeratorOfTheKpiPerEnvironmentalObjectiveCapexBasedShareOfCapexBasedKpiSubstantiallyContributingToSustainableUseAndProtectionOfWaterAndMarineResourcesInPercentOfWhichEnabling,extendedDecimalAssetManagementBreakdownOfTheNumeratorOfTheKpiPerEnvironmentalObjectiveCapexBasedShareOfCapexBasedKpiSubstantiallyContributingToTransitionToACircularEconomyInPercentOfWhichEnabling,extendedDecimalAssetManagementBreakdownOfTheNumeratorOfTheKpiPerEnvironmentalObjectiveCapexBasedShareOfCapexBasedKpiSubstantiallyContributingToPollutionPreventionAndControlInPercentOfWhichEnabling,extendedDecimalAssetManagementBreakdownOfTheNumeratorOfTheKpiPerEnvironmentalObjectiveCapexBasedShareOfCapexBasedKpiSubstantiallyContributingToProtectionAndRestorationOfBiodiversityAndEcosystemsInPercentOfWhichEnabling]</t>
+  </si>
+  <si>
+    <t>Sum: [extendedCurrencyInsuranceReinsuranceTotalOfAbsolutePremiumsOfTaxonomyAlignedActivities,extendedCurrencyInsuranceReinsuranceTotalOfAbsolutePremiumsOfTaxonomyEligibleButTaxonomyNonAlignedActivities]</t>
+  </si>
+  <si>
+    <t>Sum: [extendedDecimalInsuranceReinsuranceProportionOfAbsolutePremiumsOfTaxonomyAlignedActivities,extendedDecimalInsuranceReinsuranceProportionOfAbsolutePremiumsOfTaxonomyEligibleButTaxonomyNonAlignedActivities]</t>
+  </si>
+  <si>
+    <t>Sum: [extendedCurrencyInsuranceReinsuranceTotalOfAbsolutePremiumsOfTaxonomyAlignedActivities,extendedCurrencyInsuranceReinsuranceTotalOfAbsolutePremiumsOfTaxonomyEligibleButTaxonomyNonAlignedActivities,extendedCurrencyInsuranceReinsuranceTotalOfAbsolutePremiumsOfTaxonomyNonEligibleActivities]</t>
+  </si>
+  <si>
+    <t>DivisionByPercent: [extendedCurrencyInsuranceReinsuranceWeightedAverageValueOfAllInvestmentsTurnoverBasedMonetaryAmount,extendedDecimalInsuranceReinsuranceWeightedAverageValueOfAllInvestmentsTurnoverBasedInPercent]; DivisionByPercent: [extendedCurrencyInsuranceReinsuranceWeightedAverageValueOfAllInvestmentsCapexBasedMonetaryAmount,extendedDecimalInsuranceReinsuranceWeightedAverageValueOfAllInvestmentsCapexBasedInPercent]</t>
+  </si>
+  <si>
+    <t>Identity: [extendedDecimalInsuranceReinsuranceWeightedAverageValueOfAllInvestmentsTurnoverBasedInPercent]</t>
+  </si>
+  <si>
+    <t>Identity: [extendedDecimalInsuranceReinsuranceBreakdownOfTheNumeratorOfTheKpiPerEnvironmentalObjectiveTurnoverBasedShareOfTurnoverBasedKpiSubstantiallyContributingToClimateChangeMitigationInPercentOfWhichTransitional]</t>
+  </si>
+  <si>
+    <t>Sum: [extendedDecimalInsuranceReinsuranceBreakdownOfTheNumeratorOfTheKpiPerEnvironmentalObjectiveTurnoverBasedShareOfTurnoverBasedKpiSubstantiallyContributingToClimateChangeMitigationInPercentOfWhichEnabling,extendedDecimalInsuranceReinsuranceBreakdownOfTheNumeratorOfTheKpiPerEnvironmentalObjectiveTurnoverBasedShareOfTurnoverBasedKpiSubstantiallyContributingToClimateChangeAdaptationInPercentOfWhichEnabling,extendedDecimalInsuranceReinsuranceBreakdownOfTheNumeratorOfTheKpiPerEnvironmentalObjectiveTurnoverBasedShareOfTurnoverBasedKpiSubstantiallyContributingToSustainableUseAndProtectionOfWaterAndMarineResourcesInPercentOfWhichEnabling,extendedDecimalInsuranceReinsuranceBreakdownOfTheNumeratorOfTheKpiPerEnvironmentalObjectiveTurnoverBasedShareOfTurnoverBasedKpiSubstantiallyContributingToTransitionToACircularEconomyInPercentOfWhichEnabling,extendedDecimalInsuranceReinsuranceBreakdownOfTheNumeratorOfTheKpiPerEnvironmentalObjectiveTurnoverBasedShareOfTurnoverBasedKpiSubstantiallyContributingToPollutionPreventionAndControlInPercentOfWhichEnabling,extendedDecimalInsuranceReinsuranceBreakdownOfTheNumeratorOfTheKpiPerEnvironmentalObjectiveTurnoverBasedShareOfTurnoverBasedKpiSubstantiallyContributingToProtectionAndRestorationOfBiodiversityAndEcosystemsInPercentOfWhichEnabling]</t>
+  </si>
+  <si>
+    <t>Identity: [extendedDecimalInsuranceReinsuranceWeightedAverageValueOfAllInvestmentsCapexBasedInPercent]</t>
+  </si>
+  <si>
+    <t>Identity: [extendedDecimalInsuranceReinsuranceBreakdownOfTheNumeratorOfTheKpiPerEnvironmentalObjectiveCapexBasedShareOfCapexBasedKpiSubstantiallyContributingToClimateChangeMitigationInPercentOfWhichTransitional]</t>
+  </si>
+  <si>
+    <t>Sum: [extendedDecimalInsuranceReinsuranceBreakdownOfTheNumeratorOfTheKpiPerEnvironmentalObjectiveCapexBasedShareOfCapexBasedKpiSubstantiallyContributingToClimateChangeMitigationInPercentOfWhichEnabling,extendedDecimalInsuranceReinsuranceBreakdownOfTheNumeratorOfTheKpiPerEnvironmentalObjectiveCapexBasedShareOfCapexBasedKpiSubstantiallyContributingToClimateChangeAdaptationInPercentOfWhichEnabling,extendedDecimalInsuranceReinsuranceBreakdownOfTheNumeratorOfTheKpiPerEnvironmentalObjectiveCapexBasedShareOfCapexBasedKpiSubstantiallyContributingToSustainableUseAndProtectionOfWaterAndMarineResourcesInPercentOfWhichEnabling,extendedDecimalInsuranceReinsuranceBreakdownOfTheNumeratorOfTheKpiPerEnvironmentalObjectiveCapexBasedShareOfCapexBasedKpiSubstantiallyContributingToTransitionToACircularEconomyInPercentOfWhichEnabling,extendedDecimalInsuranceReinsuranceBreakdownOfTheNumeratorOfTheKpiPerEnvironmentalObjectiveCapexBasedShareOfCapexBasedKpiSubstantiallyContributingToPollutionPreventionAndControlInPercentOfWhichEnabling,extendedDecimalInsuranceReinsuranceBreakdownOfTheNumeratorOfTheKpiPerEnvironmentalObjectiveCapexBasedShareOfCapexBasedKpiSubstantiallyContributingToProtectionAndRestorationOfBiodiversityAndEcosystemsInPercentOfWhichEnabling]</t>
+  </si>
+  <si>
+    <t>Turnover-based total amount of assets of which exposures financing counterparties reporting in accordance with Article 7(9) of Regulation (EU) 2026/73</t>
+  </si>
+  <si>
+    <t>CapEx-based total amount of assets of which exposures financing counterparties reporting in accordance with Article 7(9) of Regulation (EU) 2026/73</t>
   </si>
 </sst>
 </file>
@@ -2669,10 +2729,6 @@
     </ext>
   </extLst>
 </styleSheet>
-</file>
-
-<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
-<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -2998,26 +3054,26 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:Q218"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="15" customWidth="1"/>
-    <col min="2" max="2" width="18.42578125" customWidth="1"/>
-    <col min="3" max="3" width="70.140625" customWidth="1"/>
-    <col min="4" max="5" width="117.85546875" customWidth="1"/>
+    <col min="2" max="2" width="18.453125" customWidth="1"/>
+    <col min="3" max="3" width="70.1796875" customWidth="1"/>
+    <col min="4" max="5" width="117.81640625" customWidth="1"/>
     <col min="6" max="6" width="92" customWidth="1"/>
-    <col min="7" max="7" width="36.42578125" customWidth="1"/>
-    <col min="8" max="8" width="19.85546875" customWidth="1"/>
-    <col min="9" max="9" width="6.42578125" customWidth="1"/>
-    <col min="10" max="10" width="18.7109375" customWidth="1"/>
-    <col min="11" max="11" width="13.28515625" customWidth="1"/>
-    <col min="12" max="12" width="19.5703125" customWidth="1"/>
-    <col min="13" max="13" width="16.140625" customWidth="1"/>
-    <col min="14" max="14" width="26.42578125" customWidth="1"/>
-    <col min="15" max="16" width="30.28515625" customWidth="1"/>
+    <col min="7" max="7" width="36.453125" customWidth="1"/>
+    <col min="8" max="8" width="19.81640625" customWidth="1"/>
+    <col min="9" max="9" width="6.453125" customWidth="1"/>
+    <col min="10" max="10" width="18.7265625" customWidth="1"/>
+    <col min="11" max="11" width="13.26953125" customWidth="1"/>
+    <col min="12" max="12" width="19.54296875" customWidth="1"/>
+    <col min="13" max="13" width="16.1796875" customWidth="1"/>
+    <col min="14" max="14" width="26.453125" customWidth="1"/>
+    <col min="15" max="16" width="30.26953125" customWidth="1"/>
     <col min="17" max="17" width="13" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:17" ht="14.65" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:17" ht="14.65" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -3066,13 +3122,11 @@
       <c r="P1" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="Q1" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Field Calculation</t>
-        </is>
-      </c>
-    </row>
-    <row r="2" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="Q1" s="1" t="s">
+        <v>830</v>
+      </c>
+    </row>
+    <row r="2" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A2" s="2" t="s">
         <v>16</v>
       </c>
@@ -3109,7 +3163,7 @@
       <c r="P2" s="4"/>
       <c r="Q2" s="4"/>
     </row>
-    <row r="3" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A3" s="2" t="s">
         <v>24</v>
       </c>
@@ -3146,7 +3200,7 @@
       <c r="P3" s="4"/>
       <c r="Q3" s="4"/>
     </row>
-    <row r="4" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A4" s="2" t="s">
         <v>30</v>
       </c>
@@ -3181,7 +3235,7 @@
       <c r="P4" s="4"/>
       <c r="Q4" s="4"/>
     </row>
-    <row r="5" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A5" s="2" t="s">
         <v>35</v>
       </c>
@@ -3220,7 +3274,7 @@
       </c>
       <c r="Q5" s="4"/>
     </row>
-    <row r="6" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A6" s="2" t="s">
         <v>41</v>
       </c>
@@ -3257,7 +3311,7 @@
       <c r="P6" s="4"/>
       <c r="Q6" s="4"/>
     </row>
-    <row r="7" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A7" s="2" t="s">
         <v>47</v>
       </c>
@@ -3290,13 +3344,11 @@
       <c r="N7" s="4"/>
       <c r="O7" s="4"/>
       <c r="P7" s="4"/>
-      <c r="Q7" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Identity: [extendedEnumYesNoIsNfrdMandatory]</t>
-        </is>
-      </c>
-    </row>
-    <row r="8" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="Q7" s="4" t="s">
+        <v>831</v>
+      </c>
+    </row>
+    <row r="8" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A8" s="2" t="s">
         <v>51</v>
       </c>
@@ -3331,7 +3383,7 @@
       <c r="P8" s="4"/>
       <c r="Q8" s="4"/>
     </row>
-    <row r="9" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A9" s="2" t="s">
         <v>56</v>
       </c>
@@ -3366,7 +3418,7 @@
       <c r="P9" s="4"/>
       <c r="Q9" s="4"/>
     </row>
-    <row r="10" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A10" s="2" t="s">
         <v>60</v>
       </c>
@@ -3380,10 +3432,10 @@
         <v>796</v>
       </c>
       <c r="E10" s="4" t="s">
-        <v>822</v>
+        <v>821</v>
       </c>
       <c r="F10" s="4" t="s">
-        <v>827</v>
+        <v>826</v>
       </c>
       <c r="G10" s="4" t="s">
         <v>62</v>
@@ -3405,13 +3457,11 @@
         <v>63</v>
       </c>
       <c r="P10" s="4"/>
-      <c r="Q10" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Identity: [extendedCurrencyCreditInstitutionAssetsForCalculationOfGreenAssetRatioTotalGrossCarryingAmount]</t>
-        </is>
-      </c>
-    </row>
-    <row r="11" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="Q10" s="4" t="s">
+        <v>832</v>
+      </c>
+    </row>
+    <row r="11" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A11" s="2" t="s">
         <v>64</v>
       </c>
@@ -3425,10 +3475,10 @@
         <v>797</v>
       </c>
       <c r="E11" s="4" t="s">
-        <v>823</v>
+        <v>822</v>
       </c>
       <c r="F11" s="4" t="s">
-        <v>828</v>
+        <v>827</v>
       </c>
       <c r="G11" s="4" t="s">
         <v>62</v>
@@ -3452,7 +3502,7 @@
       <c r="P11" s="4"/>
       <c r="Q11" s="4"/>
     </row>
-    <row r="12" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A12" s="2" t="s">
         <v>65</v>
       </c>
@@ -3466,10 +3516,10 @@
         <v>798</v>
       </c>
       <c r="E12" s="4" t="s">
-        <v>824</v>
+        <v>823</v>
       </c>
       <c r="F12" s="4" t="s">
-        <v>829</v>
+        <v>828</v>
       </c>
       <c r="G12" s="4" t="s">
         <v>62</v>
@@ -3493,7 +3543,7 @@
       <c r="P12" s="4"/>
       <c r="Q12" s="4"/>
     </row>
-    <row r="13" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A13" s="2" t="s">
         <v>66</v>
       </c>
@@ -3507,10 +3557,10 @@
         <v>799</v>
       </c>
       <c r="E13" s="4" t="s">
-        <v>825</v>
+        <v>824</v>
       </c>
       <c r="F13" s="4" t="s">
-        <v>830</v>
+        <v>850</v>
       </c>
       <c r="G13" s="4" t="s">
         <v>62</v>
@@ -3534,7 +3584,7 @@
       <c r="P13" s="4"/>
       <c r="Q13" s="4"/>
     </row>
-    <row r="14" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A14" s="2" t="s">
         <v>67</v>
       </c>
@@ -3548,10 +3598,10 @@
         <v>800</v>
       </c>
       <c r="E14" s="4" t="s">
-        <v>826</v>
+        <v>825</v>
       </c>
       <c r="F14" s="4" t="s">
-        <v>831</v>
+        <v>829</v>
       </c>
       <c r="G14" s="4" t="s">
         <v>62</v>
@@ -3575,7 +3625,7 @@
       <c r="P14" s="4"/>
       <c r="Q14" s="4"/>
     </row>
-    <row r="15" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A15" s="2" t="s">
         <v>68</v>
       </c>
@@ -3616,7 +3666,7 @@
       <c r="P15" s="4"/>
       <c r="Q15" s="4"/>
     </row>
-    <row r="16" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A16" s="2" t="s">
         <v>73</v>
       </c>
@@ -3657,7 +3707,7 @@
       <c r="P16" s="4"/>
       <c r="Q16" s="4"/>
     </row>
-    <row r="17" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A17" s="2" t="s">
         <v>77</v>
       </c>
@@ -3698,7 +3748,7 @@
       <c r="P17" s="4"/>
       <c r="Q17" s="4"/>
     </row>
-    <row r="18" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A18" s="2" t="s">
         <v>81</v>
       </c>
@@ -3715,7 +3765,7 @@
         <v>812</v>
       </c>
       <c r="F18" s="4" t="s">
-        <v>813</v>
+        <v>851</v>
       </c>
       <c r="G18" s="4" t="s">
         <v>62</v>
@@ -3739,7 +3789,7 @@
       <c r="P18" s="4"/>
       <c r="Q18" s="4"/>
     </row>
-    <row r="19" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A19" s="2" t="s">
         <v>85</v>
       </c>
@@ -3750,13 +3800,13 @@
         <v>801</v>
       </c>
       <c r="D19" s="4" t="s">
+        <v>813</v>
+      </c>
+      <c r="E19" s="4" t="s">
         <v>814</v>
       </c>
-      <c r="E19" s="4" t="s">
+      <c r="F19" s="4" t="s">
         <v>815</v>
-      </c>
-      <c r="F19" s="4" t="s">
-        <v>816</v>
       </c>
       <c r="G19" s="4" t="s">
         <v>62</v>
@@ -3780,7 +3830,7 @@
       <c r="P19" s="4"/>
       <c r="Q19" s="4"/>
     </row>
-    <row r="20" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A20" s="2" t="s">
         <v>89</v>
       </c>
@@ -3821,7 +3871,7 @@
       <c r="P20" s="4"/>
       <c r="Q20" s="4"/>
     </row>
-    <row r="21" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A21" s="2" t="s">
         <v>93</v>
       </c>
@@ -3862,7 +3912,7 @@
       <c r="P21" s="4"/>
       <c r="Q21" s="4"/>
     </row>
-    <row r="22" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A22" s="2" t="s">
         <v>98</v>
       </c>
@@ -3903,7 +3953,7 @@
       <c r="P22" s="4"/>
       <c r="Q22" s="4"/>
     </row>
-    <row r="23" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A23" s="2" t="s">
         <v>102</v>
       </c>
@@ -3944,7 +3994,7 @@
       <c r="P23" s="4"/>
       <c r="Q23" s="4"/>
     </row>
-    <row r="24" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A24" s="2" t="s">
         <v>106</v>
       </c>
@@ -3985,7 +4035,7 @@
       <c r="P24" s="4"/>
       <c r="Q24" s="4"/>
     </row>
-    <row r="25" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A25" s="2" t="s">
         <v>110</v>
       </c>
@@ -4026,7 +4076,7 @@
       <c r="P25" s="4"/>
       <c r="Q25" s="4"/>
     </row>
-    <row r="26" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A26" s="2" t="s">
         <v>114</v>
       </c>
@@ -4067,7 +4117,7 @@
       <c r="P26" s="4"/>
       <c r="Q26" s="4"/>
     </row>
-    <row r="27" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A27" s="2" t="s">
         <v>118</v>
       </c>
@@ -4108,7 +4158,7 @@
       <c r="P27" s="4"/>
       <c r="Q27" s="4"/>
     </row>
-    <row r="28" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A28" s="2" t="s">
         <v>124</v>
       </c>
@@ -4149,7 +4199,7 @@
       <c r="P28" s="4"/>
       <c r="Q28" s="4"/>
     </row>
-    <row r="29" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A29" s="2" t="s">
         <v>128</v>
       </c>
@@ -4190,7 +4240,7 @@
       <c r="P29" s="4"/>
       <c r="Q29" s="4"/>
     </row>
-    <row r="30" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A30" s="2" t="s">
         <v>132</v>
       </c>
@@ -4231,7 +4281,7 @@
       <c r="P30" s="4"/>
       <c r="Q30" s="4"/>
     </row>
-    <row r="31" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A31" s="2" t="s">
         <v>136</v>
       </c>
@@ -4272,7 +4322,7 @@
       <c r="P31" s="4"/>
       <c r="Q31" s="4"/>
     </row>
-    <row r="32" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A32" s="2" t="s">
         <v>140</v>
       </c>
@@ -4311,7 +4361,7 @@
       <c r="P32" s="4"/>
       <c r="Q32" s="4"/>
     </row>
-    <row r="33" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A33" s="2" t="s">
         <v>144</v>
       </c>
@@ -4350,7 +4400,7 @@
       <c r="P33" s="4"/>
       <c r="Q33" s="4"/>
     </row>
-    <row r="34" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A34" s="2" t="s">
         <v>148</v>
       </c>
@@ -4389,7 +4439,7 @@
       <c r="P34" s="4"/>
       <c r="Q34" s="4"/>
     </row>
-    <row r="35" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A35" s="2" t="s">
         <v>152</v>
       </c>
@@ -4428,7 +4478,7 @@
       <c r="P35" s="4"/>
       <c r="Q35" s="4"/>
     </row>
-    <row r="36" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A36" s="2" t="s">
         <v>156</v>
       </c>
@@ -4467,7 +4517,7 @@
       <c r="P36" s="4"/>
       <c r="Q36" s="4"/>
     </row>
-    <row r="37" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A37" s="2" t="s">
         <v>160</v>
       </c>
@@ -4506,7 +4556,7 @@
       <c r="P37" s="4"/>
       <c r="Q37" s="4"/>
     </row>
-    <row r="38" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A38" s="2" t="s">
         <v>164</v>
       </c>
@@ -4545,7 +4595,7 @@
       <c r="P38" s="4"/>
       <c r="Q38" s="4"/>
     </row>
-    <row r="39" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A39" s="2" t="s">
         <v>168</v>
       </c>
@@ -4584,7 +4634,7 @@
       <c r="P39" s="4"/>
       <c r="Q39" s="4"/>
     </row>
-    <row r="40" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A40" s="2" t="s">
         <v>172</v>
       </c>
@@ -4623,7 +4673,7 @@
       <c r="P40" s="4"/>
       <c r="Q40" s="4"/>
     </row>
-    <row r="41" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A41" s="2" t="s">
         <v>175</v>
       </c>
@@ -4662,7 +4712,7 @@
       <c r="P41" s="4"/>
       <c r="Q41" s="4"/>
     </row>
-    <row r="42" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A42" s="2" t="s">
         <v>178</v>
       </c>
@@ -4701,7 +4751,7 @@
       <c r="P42" s="4"/>
       <c r="Q42" s="4"/>
     </row>
-    <row r="43" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A43" s="2" t="s">
         <v>181</v>
       </c>
@@ -4740,7 +4790,7 @@
       <c r="P43" s="4"/>
       <c r="Q43" s="4"/>
     </row>
-    <row r="44" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A44" s="2" t="s">
         <v>184</v>
       </c>
@@ -4779,7 +4829,7 @@
       <c r="P44" s="4"/>
       <c r="Q44" s="4"/>
     </row>
-    <row r="45" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A45" s="2" t="s">
         <v>187</v>
       </c>
@@ -4818,7 +4868,7 @@
       <c r="P45" s="4"/>
       <c r="Q45" s="4"/>
     </row>
-    <row r="46" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A46" s="2" t="s">
         <v>190</v>
       </c>
@@ -4857,7 +4907,7 @@
       <c r="P46" s="4"/>
       <c r="Q46" s="4"/>
     </row>
-    <row r="47" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A47" s="2" t="s">
         <v>193</v>
       </c>
@@ -4896,7 +4946,7 @@
       <c r="P47" s="4"/>
       <c r="Q47" s="4"/>
     </row>
-    <row r="48" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A48" s="2" t="s">
         <v>195</v>
       </c>
@@ -4935,7 +4985,7 @@
       <c r="P48" s="4"/>
       <c r="Q48" s="4"/>
     </row>
-    <row r="49" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A49" s="2" t="s">
         <v>198</v>
       </c>
@@ -4974,7 +5024,7 @@
       <c r="P49" s="4"/>
       <c r="Q49" s="4"/>
     </row>
-    <row r="50" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A50" s="2" t="s">
         <v>201</v>
       </c>
@@ -5013,7 +5063,7 @@
       <c r="P50" s="4"/>
       <c r="Q50" s="4"/>
     </row>
-    <row r="51" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A51" s="2" t="s">
         <v>205</v>
       </c>
@@ -5052,7 +5102,7 @@
       <c r="P51" s="4"/>
       <c r="Q51" s="4"/>
     </row>
-    <row r="52" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A52" s="2" t="s">
         <v>211</v>
       </c>
@@ -5091,7 +5141,7 @@
       <c r="P52" s="4"/>
       <c r="Q52" s="4"/>
     </row>
-    <row r="53" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A53" s="2" t="s">
         <v>215</v>
       </c>
@@ -5130,7 +5180,7 @@
       <c r="P53" s="4"/>
       <c r="Q53" s="4"/>
     </row>
-    <row r="54" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A54" s="2" t="s">
         <v>219</v>
       </c>
@@ -5169,7 +5219,7 @@
       <c r="P54" s="4"/>
       <c r="Q54" s="4"/>
     </row>
-    <row r="55" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A55" s="2" t="s">
         <v>224</v>
       </c>
@@ -5208,7 +5258,7 @@
       <c r="P55" s="4"/>
       <c r="Q55" s="4"/>
     </row>
-    <row r="56" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A56" s="2" t="s">
         <v>228</v>
       </c>
@@ -5249,7 +5299,7 @@
       <c r="P56" s="4"/>
       <c r="Q56" s="4"/>
     </row>
-    <row r="57" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A57" s="2" t="s">
         <v>232</v>
       </c>
@@ -5288,7 +5338,7 @@
       <c r="P57" s="4"/>
       <c r="Q57" s="4"/>
     </row>
-    <row r="58" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A58" s="2" t="s">
         <v>236</v>
       </c>
@@ -5327,13 +5377,11 @@
         <v>63</v>
       </c>
       <c r="P58" s="4"/>
-      <c r="Q58" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">DivisionByPercent: [extendedCurrencyAssetManagementWeightedAverageValueOfAllInvestmentsTurnoverBasedMonetaryAmount,extendedDecimalAssetManagementWeightedAverageValueOfAllInvestmentsTurnoverBasedInPercent]; DivisionByPercent: [extendedCurrencyAssetManagementWeightedAverageValueOfAllInvestmentsCapexBasedMonetaryAmount,extendedDecimalAssetManagementWeightedAverageValueOfAllInvestmentsCapexBasedInPercent]</t>
-        </is>
-      </c>
-    </row>
-    <row r="59" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="Q58" s="4" t="s">
+        <v>833</v>
+      </c>
+    </row>
+    <row r="59" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A59" s="2" t="s">
         <v>240</v>
       </c>
@@ -5372,7 +5420,7 @@
       <c r="P59" s="4"/>
       <c r="Q59" s="4"/>
     </row>
-    <row r="60" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A60" s="2" t="s">
         <v>244</v>
       </c>
@@ -5411,7 +5459,7 @@
       <c r="P60" s="4"/>
       <c r="Q60" s="4"/>
     </row>
-    <row r="61" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A61" s="2" t="s">
         <v>248</v>
       </c>
@@ -5450,7 +5498,7 @@
       <c r="P61" s="4"/>
       <c r="Q61" s="4"/>
     </row>
-    <row r="62" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A62" s="2" t="s">
         <v>252</v>
       </c>
@@ -5487,13 +5535,11 @@
         <v>63</v>
       </c>
       <c r="P62" s="4"/>
-      <c r="Q62" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Identity: [extendedDecimalAssetManagementWeightedAverageValueOfAllInvestmentsTurnoverBasedInPercent]</t>
-        </is>
-      </c>
-    </row>
-    <row r="63" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="Q62" s="4" t="s">
+        <v>834</v>
+      </c>
+    </row>
+    <row r="63" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A63" s="2" t="s">
         <v>255</v>
       </c>
@@ -5530,13 +5576,11 @@
         <v>63</v>
       </c>
       <c r="P63" s="4"/>
-      <c r="Q63" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Identity: [extendedDecimalAssetManagementBreakdownOfTheNumeratorOfTheKpiPerEnvironmentalObjectiveTurnoverBasedShareOfTurnoverBasedKpiSubstantiallyContributingToClimateChangeMitigationInPercentOfWhichTransitional]</t>
-        </is>
-      </c>
-    </row>
-    <row r="64" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="Q63" s="4" t="s">
+        <v>835</v>
+      </c>
+    </row>
+    <row r="64" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A64" s="2" t="s">
         <v>259</v>
       </c>
@@ -5573,13 +5617,11 @@
         <v>63</v>
       </c>
       <c r="P64" s="4"/>
-      <c r="Q64" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Sum: [extendedDecimalAssetManagementBreakdownOfTheNumeratorOfTheKpiPerEnvironmentalObjectiveTurnoverBasedShareOfTurnoverBasedKpiSubstantiallyContributingToClimateChangeMitigationInPercentOfWhichEnabling,extendedDecimalAssetManagementBreakdownOfTheNumeratorOfTheKpiPerEnvironmentalObjectiveTurnoverBasedShareOfTurnoverBasedKpiSubstantiallyContributingToClimateChangeAdaptationInPercentOfWhichEnabling,extendedDecimalAssetManagementBreakdownOfTheNumeratorOfTheKpiPerEnvironmentalObjectiveTurnoverBasedShareOfTurnoverBasedKpiSubstantiallyContributingToSustainableUseAndProtectionOfWaterAndMarineResourcesInPercentOfWhichEnabling,extendedDecimalAssetManagementBreakdownOfTheNumeratorOfTheKpiPerEnvironmentalObjectiveTurnoverBasedShareOfTurnoverBasedKpiSubstantiallyContributingToTransitionToACircularEconomyInPercentOfWhichEnabling,extendedDecimalAssetManagementBreakdownOfTheNumeratorOfTheKpiPerEnvironmentalObjectiveTurnoverBasedShareOfTurnoverBasedKpiSubstantiallyContributingToPollutionPreventionAndControlInPercentOfWhichEnabling,extendedDecimalAssetManagementBreakdownOfTheNumeratorOfTheKpiPerEnvironmentalObjectiveTurnoverBasedShareOfTurnoverBasedKpiSubstantiallyContributingToProtectionAndRestorationOfBiodiversityAndEcosystemsInPercentOfWhichEnabling]</t>
-        </is>
-      </c>
-    </row>
-    <row r="65" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="Q64" s="4" t="s">
+        <v>836</v>
+      </c>
+    </row>
+    <row r="65" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A65" s="2" t="s">
         <v>263</v>
       </c>
@@ -5618,7 +5660,7 @@
       <c r="P65" s="4"/>
       <c r="Q65" s="4"/>
     </row>
-    <row r="66" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A66" s="2" t="s">
         <v>267</v>
       </c>
@@ -5657,7 +5699,7 @@
       <c r="P66" s="4"/>
       <c r="Q66" s="4"/>
     </row>
-    <row r="67" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A67" s="2" t="s">
         <v>272</v>
       </c>
@@ -5696,7 +5738,7 @@
       <c r="P67" s="4"/>
       <c r="Q67" s="4"/>
     </row>
-    <row r="68" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A68" s="2" t="s">
         <v>276</v>
       </c>
@@ -5735,7 +5777,7 @@
       <c r="P68" s="4"/>
       <c r="Q68" s="4"/>
     </row>
-    <row r="69" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A69" s="2" t="s">
         <v>280</v>
       </c>
@@ -5774,7 +5816,7 @@
       <c r="P69" s="4"/>
       <c r="Q69" s="4"/>
     </row>
-    <row r="70" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A70" s="2" t="s">
         <v>284</v>
       </c>
@@ -5813,7 +5855,7 @@
       <c r="P70" s="4"/>
       <c r="Q70" s="4"/>
     </row>
-    <row r="71" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A71" s="2" t="s">
         <v>288</v>
       </c>
@@ -5852,7 +5894,7 @@
       <c r="P71" s="4"/>
       <c r="Q71" s="4"/>
     </row>
-    <row r="72" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A72" s="2" t="s">
         <v>292</v>
       </c>
@@ -5891,7 +5933,7 @@
       <c r="P72" s="4"/>
       <c r="Q72" s="4"/>
     </row>
-    <row r="73" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A73" s="2" t="s">
         <v>297</v>
       </c>
@@ -5930,7 +5972,7 @@
       <c r="P73" s="4"/>
       <c r="Q73" s="4"/>
     </row>
-    <row r="74" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A74" s="2" t="s">
         <v>301</v>
       </c>
@@ -5969,7 +6011,7 @@
       <c r="P74" s="4"/>
       <c r="Q74" s="4"/>
     </row>
-    <row r="75" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="75" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A75" s="2" t="s">
         <v>305</v>
       </c>
@@ -6008,7 +6050,7 @@
       <c r="P75" s="4"/>
       <c r="Q75" s="4"/>
     </row>
-    <row r="76" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="76" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A76" s="2" t="s">
         <v>309</v>
       </c>
@@ -6047,7 +6089,7 @@
       <c r="P76" s="4"/>
       <c r="Q76" s="4"/>
     </row>
-    <row r="77" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="77" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A77" s="2" t="s">
         <v>313</v>
       </c>
@@ -6086,7 +6128,7 @@
       <c r="P77" s="4"/>
       <c r="Q77" s="4"/>
     </row>
-    <row r="78" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="78" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A78" s="2" t="s">
         <v>317</v>
       </c>
@@ -6125,7 +6167,7 @@
       <c r="P78" s="4"/>
       <c r="Q78" s="4"/>
     </row>
-    <row r="79" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="79" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A79" s="2" t="s">
         <v>321</v>
       </c>
@@ -6164,7 +6206,7 @@
       <c r="P79" s="4"/>
       <c r="Q79" s="4"/>
     </row>
-    <row r="80" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="80" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A80" s="2" t="s">
         <v>325</v>
       </c>
@@ -6201,13 +6243,11 @@
         <v>63</v>
       </c>
       <c r="P80" s="4"/>
-      <c r="Q80" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Identity: [extendedDecimalAssetManagementWeightedAverageValueOfAllInvestmentsCapexBasedInPercent]</t>
-        </is>
-      </c>
-    </row>
-    <row r="81" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="Q80" s="4" t="s">
+        <v>837</v>
+      </c>
+    </row>
+    <row r="81" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A81" s="2" t="s">
         <v>328</v>
       </c>
@@ -6244,13 +6284,11 @@
         <v>63</v>
       </c>
       <c r="P81" s="4"/>
-      <c r="Q81" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Identity: [extendedDecimalAssetManagementBreakdownOfTheNumeratorOfTheKpiPerEnvironmentalObjectiveCapexBasedShareOfCapexBasedKpiSubstantiallyContributingToClimateChangeMitigationInPercentOfWhichTransitional]</t>
-        </is>
-      </c>
-    </row>
-    <row r="82" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="Q81" s="4" t="s">
+        <v>838</v>
+      </c>
+    </row>
+    <row r="82" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A82" s="2" t="s">
         <v>332</v>
       </c>
@@ -6287,13 +6325,11 @@
         <v>63</v>
       </c>
       <c r="P82" s="4"/>
-      <c r="Q82" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Sum: [extendedDecimalAssetManagementBreakdownOfTheNumeratorOfTheKpiPerEnvironmentalObjectiveCapexBasedShareOfCapexBasedKpiSubstantiallyContributingToClimateChangeMitigationInPercentOfWhichEnabling,extendedDecimalAssetManagementBreakdownOfTheNumeratorOfTheKpiPerEnvironmentalObjectiveCapexBasedShareOfCapexBasedKpiSubstantiallyContributingToClimateChangeAdaptationInPercentOfWhichEnabling,extendedDecimalAssetManagementBreakdownOfTheNumeratorOfTheKpiPerEnvironmentalObjectiveCapexBasedShareOfCapexBasedKpiSubstantiallyContributingToSustainableUseAndProtectionOfWaterAndMarineResourcesInPercentOfWhichEnabling,extendedDecimalAssetManagementBreakdownOfTheNumeratorOfTheKpiPerEnvironmentalObjectiveCapexBasedShareOfCapexBasedKpiSubstantiallyContributingToTransitionToACircularEconomyInPercentOfWhichEnabling,extendedDecimalAssetManagementBreakdownOfTheNumeratorOfTheKpiPerEnvironmentalObjectiveCapexBasedShareOfCapexBasedKpiSubstantiallyContributingToPollutionPreventionAndControlInPercentOfWhichEnabling,extendedDecimalAssetManagementBreakdownOfTheNumeratorOfTheKpiPerEnvironmentalObjectiveCapexBasedShareOfCapexBasedKpiSubstantiallyContributingToProtectionAndRestorationOfBiodiversityAndEcosystemsInPercentOfWhichEnabling]</t>
-        </is>
-      </c>
-    </row>
-    <row r="83" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="Q82" s="4" t="s">
+        <v>839</v>
+      </c>
+    </row>
+    <row r="83" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A83" s="2" t="s">
         <v>336</v>
       </c>
@@ -6332,7 +6368,7 @@
       <c r="P83" s="4"/>
       <c r="Q83" s="4"/>
     </row>
-    <row r="84" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="84" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A84" s="2" t="s">
         <v>340</v>
       </c>
@@ -6371,7 +6407,7 @@
       <c r="P84" s="4"/>
       <c r="Q84" s="4"/>
     </row>
-    <row r="85" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="85" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A85" s="2" t="s">
         <v>345</v>
       </c>
@@ -6410,7 +6446,7 @@
       <c r="P85" s="4"/>
       <c r="Q85" s="4"/>
     </row>
-    <row r="86" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="86" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A86" s="2" t="s">
         <v>349</v>
       </c>
@@ -6449,7 +6485,7 @@
       <c r="P86" s="4"/>
       <c r="Q86" s="4"/>
     </row>
-    <row r="87" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="87" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A87" s="2" t="s">
         <v>353</v>
       </c>
@@ -6488,7 +6524,7 @@
       <c r="P87" s="4"/>
       <c r="Q87" s="4"/>
     </row>
-    <row r="88" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="88" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A88" s="2" t="s">
         <v>357</v>
       </c>
@@ -6527,7 +6563,7 @@
       <c r="P88" s="4"/>
       <c r="Q88" s="4"/>
     </row>
-    <row r="89" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="89" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A89" s="2" t="s">
         <v>361</v>
       </c>
@@ -6566,7 +6602,7 @@
       <c r="P89" s="4"/>
       <c r="Q89" s="4"/>
     </row>
-    <row r="90" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="90" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A90" s="2" t="s">
         <v>365</v>
       </c>
@@ -6605,7 +6641,7 @@
       <c r="P90" s="4"/>
       <c r="Q90" s="4"/>
     </row>
-    <row r="91" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="91" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A91" s="2" t="s">
         <v>371</v>
       </c>
@@ -6644,7 +6680,7 @@
       <c r="P91" s="4"/>
       <c r="Q91" s="4"/>
     </row>
-    <row r="92" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="92" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A92" s="2" t="s">
         <v>375</v>
       </c>
@@ -6683,7 +6719,7 @@
       <c r="P92" s="4"/>
       <c r="Q92" s="4"/>
     </row>
-    <row r="93" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="93" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A93" s="2" t="s">
         <v>379</v>
       </c>
@@ -6722,7 +6758,7 @@
       <c r="P93" s="4"/>
       <c r="Q93" s="4"/>
     </row>
-    <row r="94" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="94" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A94" s="2" t="s">
         <v>383</v>
       </c>
@@ -6761,7 +6797,7 @@
       <c r="P94" s="4"/>
       <c r="Q94" s="4"/>
     </row>
-    <row r="95" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="95" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A95" s="2" t="s">
         <v>387</v>
       </c>
@@ -6800,7 +6836,7 @@
       <c r="P95" s="4"/>
       <c r="Q95" s="4"/>
     </row>
-    <row r="96" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="96" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A96" s="2" t="s">
         <v>391</v>
       </c>
@@ -6837,7 +6873,7 @@
       <c r="P96" s="4"/>
       <c r="Q96" s="4"/>
     </row>
-    <row r="97" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="97" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A97" s="2" t="s">
         <v>395</v>
       </c>
@@ -6874,7 +6910,7 @@
       <c r="P97" s="4"/>
       <c r="Q97" s="4"/>
     </row>
-    <row r="98" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="98" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A98" s="2" t="s">
         <v>399</v>
       </c>
@@ -6911,7 +6947,7 @@
       <c r="P98" s="4"/>
       <c r="Q98" s="4"/>
     </row>
-    <row r="99" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="99" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A99" s="2" t="s">
         <v>403</v>
       </c>
@@ -6948,13 +6984,11 @@
       </c>
       <c r="O99" s="4"/>
       <c r="P99" s="4"/>
-      <c r="Q99" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Sum: [extendedCurrencyInsuranceReinsuranceTotalOfAbsolutePremiumsOfTaxonomyAlignedActivities,extendedCurrencyInsuranceReinsuranceTotalOfAbsolutePremiumsOfTaxonomyEligibleButTaxonomyNonAlignedActivities]</t>
-        </is>
-      </c>
-    </row>
-    <row r="100" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="Q99" s="4" t="s">
+        <v>840</v>
+      </c>
+    </row>
+    <row r="100" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A100" s="2" t="s">
         <v>407</v>
       </c>
@@ -6989,13 +7023,11 @@
       </c>
       <c r="O100" s="4"/>
       <c r="P100" s="4"/>
-      <c r="Q100" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Sum: [extendedDecimalInsuranceReinsuranceProportionOfAbsolutePremiumsOfTaxonomyAlignedActivities,extendedDecimalInsuranceReinsuranceProportionOfAbsolutePremiumsOfTaxonomyEligibleButTaxonomyNonAlignedActivities]</t>
-        </is>
-      </c>
-    </row>
-    <row r="101" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="Q100" s="4" t="s">
+        <v>841</v>
+      </c>
+    </row>
+    <row r="101" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A101" s="2" t="s">
         <v>411</v>
       </c>
@@ -7032,7 +7064,7 @@
       <c r="P101" s="4"/>
       <c r="Q101" s="4"/>
     </row>
-    <row r="102" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="102" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A102" s="2" t="s">
         <v>414</v>
       </c>
@@ -7069,7 +7101,7 @@
       <c r="P102" s="4"/>
       <c r="Q102" s="4"/>
     </row>
-    <row r="103" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="103" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A103" s="2" t="s">
         <v>417</v>
       </c>
@@ -7108,7 +7140,7 @@
       <c r="P103" s="4"/>
       <c r="Q103" s="4"/>
     </row>
-    <row r="104" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="104" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A104" s="2" t="s">
         <v>420</v>
       </c>
@@ -7145,7 +7177,7 @@
       <c r="P104" s="4"/>
       <c r="Q104" s="4"/>
     </row>
-    <row r="105" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="105" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A105" s="2" t="s">
         <v>422</v>
       </c>
@@ -7182,13 +7214,11 @@
       </c>
       <c r="O105" s="4"/>
       <c r="P105" s="4"/>
-      <c r="Q105" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Sum: [extendedCurrencyInsuranceReinsuranceTotalOfAbsolutePremiumsOfTaxonomyAlignedActivities,extendedCurrencyInsuranceReinsuranceTotalOfAbsolutePremiumsOfTaxonomyEligibleButTaxonomyNonAlignedActivities,extendedCurrencyInsuranceReinsuranceTotalOfAbsolutePremiumsOfTaxonomyNonEligibleActivities]</t>
-        </is>
-      </c>
-    </row>
-    <row r="106" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="Q105" s="4" t="s">
+        <v>842</v>
+      </c>
+    </row>
+    <row r="106" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A106" s="2" t="s">
         <v>424</v>
       </c>
@@ -7229,7 +7259,7 @@
       <c r="P106" s="4"/>
       <c r="Q106" s="4"/>
     </row>
-    <row r="107" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="107" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A107" s="2" t="s">
         <v>426</v>
       </c>
@@ -7268,7 +7298,7 @@
       <c r="P107" s="4"/>
       <c r="Q107" s="4"/>
     </row>
-    <row r="108" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="108" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A108" s="2" t="s">
         <v>428</v>
       </c>
@@ -7307,13 +7337,11 @@
         <v>63</v>
       </c>
       <c r="P108" s="4"/>
-      <c r="Q108" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">DivisionByPercent: [extendedCurrencyInsuranceReinsuranceWeightedAverageValueOfAllInvestmentsTurnoverBasedMonetaryAmount,extendedDecimalInsuranceReinsuranceWeightedAverageValueOfAllInvestmentsTurnoverBasedInPercent]; DivisionByPercent: [extendedCurrencyInsuranceReinsuranceWeightedAverageValueOfAllInvestmentsCapexBasedMonetaryAmount,extendedDecimalInsuranceReinsuranceWeightedAverageValueOfAllInvestmentsCapexBasedInPercent]</t>
-        </is>
-      </c>
-    </row>
-    <row r="109" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="Q108" s="4" t="s">
+        <v>843</v>
+      </c>
+    </row>
+    <row r="109" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A109" s="2" t="s">
         <v>430</v>
       </c>
@@ -7352,7 +7380,7 @@
       <c r="P109" s="4"/>
       <c r="Q109" s="4"/>
     </row>
-    <row r="110" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="110" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A110" s="2" t="s">
         <v>432</v>
       </c>
@@ -7391,7 +7419,7 @@
       <c r="P110" s="4"/>
       <c r="Q110" s="4"/>
     </row>
-    <row r="111" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="111" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A111" s="2" t="s">
         <v>434</v>
       </c>
@@ -7430,7 +7458,7 @@
       <c r="P111" s="4"/>
       <c r="Q111" s="4"/>
     </row>
-    <row r="112" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="112" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A112" s="2" t="s">
         <v>436</v>
       </c>
@@ -7467,13 +7495,11 @@
         <v>63</v>
       </c>
       <c r="P112" s="4"/>
-      <c r="Q112" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Identity: [extendedDecimalInsuranceReinsuranceWeightedAverageValueOfAllInvestmentsTurnoverBasedInPercent]</t>
-        </is>
-      </c>
-    </row>
-    <row r="113" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="Q112" s="4" t="s">
+        <v>844</v>
+      </c>
+    </row>
+    <row r="113" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A113" s="2" t="s">
         <v>438</v>
       </c>
@@ -7510,13 +7536,11 @@
         <v>63</v>
       </c>
       <c r="P113" s="4"/>
-      <c r="Q113" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Identity: [extendedDecimalInsuranceReinsuranceBreakdownOfTheNumeratorOfTheKpiPerEnvironmentalObjectiveTurnoverBasedShareOfTurnoverBasedKpiSubstantiallyContributingToClimateChangeMitigationInPercentOfWhichTransitional]</t>
-        </is>
-      </c>
-    </row>
-    <row r="114" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="Q113" s="4" t="s">
+        <v>845</v>
+      </c>
+    </row>
+    <row r="114" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A114" s="2" t="s">
         <v>440</v>
       </c>
@@ -7553,13 +7577,11 @@
         <v>63</v>
       </c>
       <c r="P114" s="4"/>
-      <c r="Q114" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Sum: [extendedDecimalInsuranceReinsuranceBreakdownOfTheNumeratorOfTheKpiPerEnvironmentalObjectiveTurnoverBasedShareOfTurnoverBasedKpiSubstantiallyContributingToClimateChangeMitigationInPercentOfWhichEnabling,extendedDecimalInsuranceReinsuranceBreakdownOfTheNumeratorOfTheKpiPerEnvironmentalObjectiveTurnoverBasedShareOfTurnoverBasedKpiSubstantiallyContributingToClimateChangeAdaptationInPercentOfWhichEnabling,extendedDecimalInsuranceReinsuranceBreakdownOfTheNumeratorOfTheKpiPerEnvironmentalObjectiveTurnoverBasedShareOfTurnoverBasedKpiSubstantiallyContributingToSustainableUseAndProtectionOfWaterAndMarineResourcesInPercentOfWhichEnabling,extendedDecimalInsuranceReinsuranceBreakdownOfTheNumeratorOfTheKpiPerEnvironmentalObjectiveTurnoverBasedShareOfTurnoverBasedKpiSubstantiallyContributingToTransitionToACircularEconomyInPercentOfWhichEnabling,extendedDecimalInsuranceReinsuranceBreakdownOfTheNumeratorOfTheKpiPerEnvironmentalObjectiveTurnoverBasedShareOfTurnoverBasedKpiSubstantiallyContributingToPollutionPreventionAndControlInPercentOfWhichEnabling,extendedDecimalInsuranceReinsuranceBreakdownOfTheNumeratorOfTheKpiPerEnvironmentalObjectiveTurnoverBasedShareOfTurnoverBasedKpiSubstantiallyContributingToProtectionAndRestorationOfBiodiversityAndEcosystemsInPercentOfWhichEnabling]</t>
-        </is>
-      </c>
-    </row>
-    <row r="115" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="Q114" s="4" t="s">
+        <v>846</v>
+      </c>
+    </row>
+    <row r="115" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A115" s="2" t="s">
         <v>442</v>
       </c>
@@ -7598,7 +7620,7 @@
       <c r="P115" s="4"/>
       <c r="Q115" s="4"/>
     </row>
-    <row r="116" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="116" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A116" s="2" t="s">
         <v>446</v>
       </c>
@@ -7637,7 +7659,7 @@
       <c r="P116" s="4"/>
       <c r="Q116" s="4"/>
     </row>
-    <row r="117" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="117" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A117" s="2" t="s">
         <v>449</v>
       </c>
@@ -7676,7 +7698,7 @@
       <c r="P117" s="4"/>
       <c r="Q117" s="4"/>
     </row>
-    <row r="118" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="118" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A118" s="2" t="s">
         <v>452</v>
       </c>
@@ -7715,7 +7737,7 @@
       <c r="P118" s="4"/>
       <c r="Q118" s="4"/>
     </row>
-    <row r="119" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="119" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A119" s="2" t="s">
         <v>455</v>
       </c>
@@ -7754,7 +7776,7 @@
       <c r="P119" s="4"/>
       <c r="Q119" s="4"/>
     </row>
-    <row r="120" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="120" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A120" s="2" t="s">
         <v>458</v>
       </c>
@@ -7793,7 +7815,7 @@
       <c r="P120" s="4"/>
       <c r="Q120" s="4"/>
     </row>
-    <row r="121" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="121" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A121" s="2" t="s">
         <v>461</v>
       </c>
@@ -7832,7 +7854,7 @@
       <c r="P121" s="4"/>
       <c r="Q121" s="4"/>
     </row>
-    <row r="122" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="122" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A122" s="2" t="s">
         <v>464</v>
       </c>
@@ -7871,7 +7893,7 @@
       <c r="P122" s="4"/>
       <c r="Q122" s="4"/>
     </row>
-    <row r="123" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="123" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A123" s="2" t="s">
         <v>466</v>
       </c>
@@ -7910,7 +7932,7 @@
       <c r="P123" s="4"/>
       <c r="Q123" s="4"/>
     </row>
-    <row r="124" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="124" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A124" s="2" t="s">
         <v>468</v>
       </c>
@@ -7949,7 +7971,7 @@
       <c r="P124" s="4"/>
       <c r="Q124" s="4"/>
     </row>
-    <row r="125" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="125" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A125" s="2" t="s">
         <v>470</v>
       </c>
@@ -7988,7 +8010,7 @@
       <c r="P125" s="4"/>
       <c r="Q125" s="4"/>
     </row>
-    <row r="126" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="126" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A126" s="2" t="s">
         <v>472</v>
       </c>
@@ -8027,7 +8049,7 @@
       <c r="P126" s="4"/>
       <c r="Q126" s="4"/>
     </row>
-    <row r="127" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="127" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A127" s="2" t="s">
         <v>474</v>
       </c>
@@ -8066,7 +8088,7 @@
       <c r="P127" s="4"/>
       <c r="Q127" s="4"/>
     </row>
-    <row r="128" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="128" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A128" s="2" t="s">
         <v>476</v>
       </c>
@@ -8105,7 +8127,7 @@
       <c r="P128" s="4"/>
       <c r="Q128" s="4"/>
     </row>
-    <row r="129" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="129" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A129" s="2" t="s">
         <v>478</v>
       </c>
@@ -8144,7 +8166,7 @@
       <c r="P129" s="4"/>
       <c r="Q129" s="4"/>
     </row>
-    <row r="130" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="130" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A130" s="2" t="s">
         <v>480</v>
       </c>
@@ -8181,13 +8203,11 @@
         <v>63</v>
       </c>
       <c r="P130" s="4"/>
-      <c r="Q130" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Identity: [extendedDecimalInsuranceReinsuranceWeightedAverageValueOfAllInvestmentsCapexBasedInPercent]</t>
-        </is>
-      </c>
-    </row>
-    <row r="131" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="Q130" s="4" t="s">
+        <v>847</v>
+      </c>
+    </row>
+    <row r="131" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A131" s="2" t="s">
         <v>482</v>
       </c>
@@ -8224,13 +8244,11 @@
         <v>63</v>
       </c>
       <c r="P131" s="4"/>
-      <c r="Q131" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Identity: [extendedDecimalInsuranceReinsuranceBreakdownOfTheNumeratorOfTheKpiPerEnvironmentalObjectiveCapexBasedShareOfCapexBasedKpiSubstantiallyContributingToClimateChangeMitigationInPercentOfWhichTransitional]</t>
-        </is>
-      </c>
-    </row>
-    <row r="132" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="Q131" s="4" t="s">
+        <v>848</v>
+      </c>
+    </row>
+    <row r="132" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A132" s="2" t="s">
         <v>484</v>
       </c>
@@ -8267,13 +8285,11 @@
         <v>63</v>
       </c>
       <c r="P132" s="4"/>
-      <c r="Q132" s="4" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Sum: [extendedDecimalInsuranceReinsuranceBreakdownOfTheNumeratorOfTheKpiPerEnvironmentalObjectiveCapexBasedShareOfCapexBasedKpiSubstantiallyContributingToClimateChangeMitigationInPercentOfWhichEnabling,extendedDecimalInsuranceReinsuranceBreakdownOfTheNumeratorOfTheKpiPerEnvironmentalObjectiveCapexBasedShareOfCapexBasedKpiSubstantiallyContributingToClimateChangeAdaptationInPercentOfWhichEnabling,extendedDecimalInsuranceReinsuranceBreakdownOfTheNumeratorOfTheKpiPerEnvironmentalObjectiveCapexBasedShareOfCapexBasedKpiSubstantiallyContributingToSustainableUseAndProtectionOfWaterAndMarineResourcesInPercentOfWhichEnabling,extendedDecimalInsuranceReinsuranceBreakdownOfTheNumeratorOfTheKpiPerEnvironmentalObjectiveCapexBasedShareOfCapexBasedKpiSubstantiallyContributingToTransitionToACircularEconomyInPercentOfWhichEnabling,extendedDecimalInsuranceReinsuranceBreakdownOfTheNumeratorOfTheKpiPerEnvironmentalObjectiveCapexBasedShareOfCapexBasedKpiSubstantiallyContributingToPollutionPreventionAndControlInPercentOfWhichEnabling,extendedDecimalInsuranceReinsuranceBreakdownOfTheNumeratorOfTheKpiPerEnvironmentalObjectiveCapexBasedShareOfCapexBasedKpiSubstantiallyContributingToProtectionAndRestorationOfBiodiversityAndEcosystemsInPercentOfWhichEnabling]</t>
-        </is>
-      </c>
-    </row>
-    <row r="133" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="Q132" s="4" t="s">
+        <v>849</v>
+      </c>
+    </row>
+    <row r="133" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A133" s="2" t="s">
         <v>486</v>
       </c>
@@ -8312,7 +8328,7 @@
       <c r="P133" s="4"/>
       <c r="Q133" s="4"/>
     </row>
-    <row r="134" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="134" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A134" s="2" t="s">
         <v>488</v>
       </c>
@@ -8351,7 +8367,7 @@
       <c r="P134" s="4"/>
       <c r="Q134" s="4"/>
     </row>
-    <row r="135" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="135" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A135" s="2" t="s">
         <v>491</v>
       </c>
@@ -8390,7 +8406,7 @@
       <c r="P135" s="4"/>
       <c r="Q135" s="4"/>
     </row>
-    <row r="136" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="136" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A136" s="2" t="s">
         <v>494</v>
       </c>
@@ -8429,7 +8445,7 @@
       <c r="P136" s="4"/>
       <c r="Q136" s="4"/>
     </row>
-    <row r="137" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="137" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A137" s="2" t="s">
         <v>497</v>
       </c>
@@ -8468,7 +8484,7 @@
       <c r="P137" s="4"/>
       <c r="Q137" s="4"/>
     </row>
-    <row r="138" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="138" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A138" s="2" t="s">
         <v>500</v>
       </c>
@@ -8507,7 +8523,7 @@
       <c r="P138" s="4"/>
       <c r="Q138" s="4"/>
     </row>
-    <row r="139" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="139" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A139" s="2" t="s">
         <v>503</v>
       </c>
@@ -8546,7 +8562,7 @@
       <c r="P139" s="4"/>
       <c r="Q139" s="4"/>
     </row>
-    <row r="140" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="140" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A140" s="2" t="s">
         <v>506</v>
       </c>
@@ -8585,7 +8601,7 @@
       <c r="P140" s="4"/>
       <c r="Q140" s="4"/>
     </row>
-    <row r="141" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="141" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A141" s="2" t="s">
         <v>512</v>
       </c>
@@ -8624,7 +8640,7 @@
       <c r="P141" s="4"/>
       <c r="Q141" s="4"/>
     </row>
-    <row r="142" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="142" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A142" s="2" t="s">
         <v>516</v>
       </c>
@@ -8663,7 +8679,7 @@
       <c r="P142" s="4"/>
       <c r="Q142" s="4"/>
     </row>
-    <row r="143" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="143" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A143" s="2" t="s">
         <v>520</v>
       </c>
@@ -8702,7 +8718,7 @@
       <c r="P143" s="4"/>
       <c r="Q143" s="4"/>
     </row>
-    <row r="144" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="144" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A144" s="2" t="s">
         <v>524</v>
       </c>
@@ -8741,7 +8757,7 @@
       <c r="P144" s="4"/>
       <c r="Q144" s="4"/>
     </row>
-    <row r="145" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="145" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A145" s="2" t="s">
         <v>528</v>
       </c>
@@ -8782,7 +8798,7 @@
       <c r="P145" s="4"/>
       <c r="Q145" s="4"/>
     </row>
-    <row r="146" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="146" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A146" s="2" t="s">
         <v>532</v>
       </c>
@@ -8823,7 +8839,7 @@
       <c r="P146" s="4"/>
       <c r="Q146" s="4"/>
     </row>
-    <row r="147" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="147" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A147" s="2" t="s">
         <v>536</v>
       </c>
@@ -8862,7 +8878,7 @@
       <c r="P147" s="4"/>
       <c r="Q147" s="4"/>
     </row>
-    <row r="148" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="148" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A148" s="2" t="s">
         <v>540</v>
       </c>
@@ -8901,7 +8917,7 @@
       <c r="P148" s="4"/>
       <c r="Q148" s="4"/>
     </row>
-    <row r="149" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="149" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A149" s="2" t="s">
         <v>544</v>
       </c>
@@ -8940,7 +8956,7 @@
       <c r="P149" s="4"/>
       <c r="Q149" s="4"/>
     </row>
-    <row r="150" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="150" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A150" s="2" t="s">
         <v>547</v>
       </c>
@@ -8979,7 +8995,7 @@
       <c r="P150" s="4"/>
       <c r="Q150" s="4"/>
     </row>
-    <row r="151" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="151" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A151" s="2" t="s">
         <v>551</v>
       </c>
@@ -9018,7 +9034,7 @@
       <c r="P151" s="4"/>
       <c r="Q151" s="4"/>
     </row>
-    <row r="152" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="152" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A152" s="2" t="s">
         <v>555</v>
       </c>
@@ -9057,7 +9073,7 @@
       <c r="P152" s="4"/>
       <c r="Q152" s="4"/>
     </row>
-    <row r="153" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="153" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A153" s="2" t="s">
         <v>558</v>
       </c>
@@ -9096,7 +9112,7 @@
       <c r="P153" s="4"/>
       <c r="Q153" s="4"/>
     </row>
-    <row r="154" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="154" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A154" s="2" t="s">
         <v>561</v>
       </c>
@@ -9135,7 +9151,7 @@
       <c r="P154" s="4"/>
       <c r="Q154" s="4"/>
     </row>
-    <row r="155" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="155" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A155" s="2" t="s">
         <v>564</v>
       </c>
@@ -9174,7 +9190,7 @@
       <c r="P155" s="4"/>
       <c r="Q155" s="4"/>
     </row>
-    <row r="156" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="156" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A156" s="2" t="s">
         <v>567</v>
       </c>
@@ -9213,7 +9229,7 @@
       <c r="P156" s="4"/>
       <c r="Q156" s="4"/>
     </row>
-    <row r="157" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="157" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A157" s="2" t="s">
         <v>571</v>
       </c>
@@ -9252,7 +9268,7 @@
       <c r="P157" s="4"/>
       <c r="Q157" s="4"/>
     </row>
-    <row r="158" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="158" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A158" s="2" t="s">
         <v>575</v>
       </c>
@@ -9291,7 +9307,7 @@
       <c r="P158" s="4"/>
       <c r="Q158" s="4"/>
     </row>
-    <row r="159" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="159" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A159" s="2" t="s">
         <v>579</v>
       </c>
@@ -9330,7 +9346,7 @@
       <c r="P159" s="4"/>
       <c r="Q159" s="4"/>
     </row>
-    <row r="160" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="160" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A160" s="2" t="s">
         <v>583</v>
       </c>
@@ -9369,7 +9385,7 @@
       <c r="P160" s="4"/>
       <c r="Q160" s="4"/>
     </row>
-    <row r="161" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="161" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A161" s="2" t="s">
         <v>587</v>
       </c>
@@ -9408,7 +9424,7 @@
       <c r="P161" s="4"/>
       <c r="Q161" s="4"/>
     </row>
-    <row r="162" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="162" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A162" s="2" t="s">
         <v>591</v>
       </c>
@@ -9447,7 +9463,7 @@
       <c r="P162" s="4"/>
       <c r="Q162" s="4"/>
     </row>
-    <row r="163" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="163" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A163" s="2" t="s">
         <v>595</v>
       </c>
@@ -9486,7 +9502,7 @@
       <c r="P163" s="4"/>
       <c r="Q163" s="4"/>
     </row>
-    <row r="164" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="164" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A164" s="2" t="s">
         <v>599</v>
       </c>
@@ -9525,7 +9541,7 @@
       <c r="P164" s="4"/>
       <c r="Q164" s="4"/>
     </row>
-    <row r="165" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="165" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A165" s="2" t="s">
         <v>603</v>
       </c>
@@ -9566,7 +9582,7 @@
       <c r="P165" s="4"/>
       <c r="Q165" s="4"/>
     </row>
-    <row r="166" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="166" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A166" s="2" t="s">
         <v>607</v>
       </c>
@@ -9607,7 +9623,7 @@
       <c r="P166" s="4"/>
       <c r="Q166" s="4"/>
     </row>
-    <row r="167" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="167" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A167" s="2" t="s">
         <v>611</v>
       </c>
@@ -9646,7 +9662,7 @@
       <c r="P167" s="4"/>
       <c r="Q167" s="4"/>
     </row>
-    <row r="168" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="168" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A168" s="2" t="s">
         <v>615</v>
       </c>
@@ -9685,7 +9701,7 @@
       <c r="P168" s="4"/>
       <c r="Q168" s="4"/>
     </row>
-    <row r="169" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="169" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A169" s="2" t="s">
         <v>619</v>
       </c>
@@ -9724,7 +9740,7 @@
       <c r="P169" s="4"/>
       <c r="Q169" s="4"/>
     </row>
-    <row r="170" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="170" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A170" s="2" t="s">
         <v>622</v>
       </c>
@@ -9763,7 +9779,7 @@
       <c r="P170" s="4"/>
       <c r="Q170" s="4"/>
     </row>
-    <row r="171" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="171" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A171" s="2" t="s">
         <v>626</v>
       </c>
@@ -9802,7 +9818,7 @@
       <c r="P171" s="4"/>
       <c r="Q171" s="4"/>
     </row>
-    <row r="172" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="172" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A172" s="2" t="s">
         <v>630</v>
       </c>
@@ -9841,7 +9857,7 @@
       <c r="P172" s="4"/>
       <c r="Q172" s="4"/>
     </row>
-    <row r="173" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="173" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A173" s="2" t="s">
         <v>633</v>
       </c>
@@ -9880,7 +9896,7 @@
       <c r="P173" s="4"/>
       <c r="Q173" s="4"/>
     </row>
-    <row r="174" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="174" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A174" s="2" t="s">
         <v>636</v>
       </c>
@@ -9919,7 +9935,7 @@
       <c r="P174" s="4"/>
       <c r="Q174" s="4"/>
     </row>
-    <row r="175" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="175" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A175" s="2" t="s">
         <v>640</v>
       </c>
@@ -9958,7 +9974,7 @@
       <c r="P175" s="4"/>
       <c r="Q175" s="4"/>
     </row>
-    <row r="176" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="176" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A176" s="2" t="s">
         <v>643</v>
       </c>
@@ -9997,7 +10013,7 @@
       <c r="P176" s="4"/>
       <c r="Q176" s="4"/>
     </row>
-    <row r="177" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="177" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A177" s="2" t="s">
         <v>647</v>
       </c>
@@ -10036,7 +10052,7 @@
       <c r="P177" s="4"/>
       <c r="Q177" s="4"/>
     </row>
-    <row r="178" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="178" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A178" s="2" t="s">
         <v>651</v>
       </c>
@@ -10075,7 +10091,7 @@
       <c r="P178" s="4"/>
       <c r="Q178" s="4"/>
     </row>
-    <row r="179" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="179" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A179" s="2" t="s">
         <v>655</v>
       </c>
@@ -10114,7 +10130,7 @@
       <c r="P179" s="4"/>
       <c r="Q179" s="4"/>
     </row>
-    <row r="180" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="180" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A180" s="2" t="s">
         <v>659</v>
       </c>
@@ -10153,7 +10169,7 @@
       <c r="P180" s="4"/>
       <c r="Q180" s="4"/>
     </row>
-    <row r="181" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="181" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A181" s="2" t="s">
         <v>664</v>
       </c>
@@ -10192,7 +10208,7 @@
       <c r="P181" s="4"/>
       <c r="Q181" s="4"/>
     </row>
-    <row r="182" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="182" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A182" s="2" t="s">
         <v>668</v>
       </c>
@@ -10231,7 +10247,7 @@
       <c r="P182" s="4"/>
       <c r="Q182" s="4"/>
     </row>
-    <row r="183" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="183" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A183" s="2" t="s">
         <v>672</v>
       </c>
@@ -10270,7 +10286,7 @@
       <c r="P183" s="4"/>
       <c r="Q183" s="4"/>
     </row>
-    <row r="184" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="184" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A184" s="2" t="s">
         <v>676</v>
       </c>
@@ -10309,7 +10325,7 @@
       <c r="P184" s="4"/>
       <c r="Q184" s="4"/>
     </row>
-    <row r="185" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="185" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A185" s="2" t="s">
         <v>680</v>
       </c>
@@ -10350,7 +10366,7 @@
       <c r="P185" s="4"/>
       <c r="Q185" s="4"/>
     </row>
-    <row r="186" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="186" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A186" s="2" t="s">
         <v>684</v>
       </c>
@@ -10391,7 +10407,7 @@
       <c r="P186" s="4"/>
       <c r="Q186" s="4"/>
     </row>
-    <row r="187" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="187" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A187" s="2" t="s">
         <v>688</v>
       </c>
@@ -10430,7 +10446,7 @@
       <c r="P187" s="4"/>
       <c r="Q187" s="4"/>
     </row>
-    <row r="188" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="188" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A188" s="2" t="s">
         <v>692</v>
       </c>
@@ -10469,7 +10485,7 @@
       <c r="P188" s="4"/>
       <c r="Q188" s="4"/>
     </row>
-    <row r="189" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="189" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A189" s="2" t="s">
         <v>696</v>
       </c>
@@ -10508,7 +10524,7 @@
       <c r="P189" s="4"/>
       <c r="Q189" s="4"/>
     </row>
-    <row r="190" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="190" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A190" s="2" t="s">
         <v>699</v>
       </c>
@@ -10547,7 +10563,7 @@
       <c r="P190" s="4"/>
       <c r="Q190" s="4"/>
     </row>
-    <row r="191" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="191" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A191" s="2" t="s">
         <v>703</v>
       </c>
@@ -10586,7 +10602,7 @@
       <c r="P191" s="4"/>
       <c r="Q191" s="4"/>
     </row>
-    <row r="192" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="192" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A192" s="2" t="s">
         <v>707</v>
       </c>
@@ -10625,7 +10641,7 @@
       <c r="P192" s="4"/>
       <c r="Q192" s="4"/>
     </row>
-    <row r="193" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="193" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A193" s="2" t="s">
         <v>710</v>
       </c>
@@ -10664,7 +10680,7 @@
       <c r="P193" s="4"/>
       <c r="Q193" s="4"/>
     </row>
-    <row r="194" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="194" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A194" s="2" t="s">
         <v>714</v>
       </c>
@@ -10703,7 +10719,7 @@
       <c r="P194" s="4"/>
       <c r="Q194" s="4"/>
     </row>
-    <row r="195" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="195" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A195" s="2" t="s">
         <v>718</v>
       </c>
@@ -10742,7 +10758,7 @@
       <c r="P195" s="4"/>
       <c r="Q195" s="4"/>
     </row>
-    <row r="196" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="196" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A196" s="2" t="s">
         <v>722</v>
       </c>
@@ -10781,7 +10797,7 @@
       <c r="P196" s="4"/>
       <c r="Q196" s="4"/>
     </row>
-    <row r="197" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="197" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A197" s="2" t="s">
         <v>726</v>
       </c>
@@ -10820,7 +10836,7 @@
       <c r="P197" s="4"/>
       <c r="Q197" s="4"/>
     </row>
-    <row r="198" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="198" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A198" s="2" t="s">
         <v>731</v>
       </c>
@@ -10859,7 +10875,7 @@
       <c r="P198" s="4"/>
       <c r="Q198" s="4"/>
     </row>
-    <row r="199" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="199" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A199" s="2" t="s">
         <v>735</v>
       </c>
@@ -10898,7 +10914,7 @@
       <c r="P199" s="4"/>
       <c r="Q199" s="4"/>
     </row>
-    <row r="200" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="200" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A200" s="2" t="s">
         <v>739</v>
       </c>
@@ -10937,7 +10953,7 @@
       <c r="P200" s="4"/>
       <c r="Q200" s="4"/>
     </row>
-    <row r="201" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="201" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A201" s="2" t="s">
         <v>743</v>
       </c>
@@ -10976,7 +10992,7 @@
       <c r="P201" s="4"/>
       <c r="Q201" s="4"/>
     </row>
-    <row r="202" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="202" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A202" s="2" t="s">
         <v>747</v>
       </c>
@@ -11017,7 +11033,7 @@
       <c r="P202" s="4"/>
       <c r="Q202" s="4"/>
     </row>
-    <row r="203" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="203" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A203" s="2" t="s">
         <v>751</v>
       </c>
@@ -11058,7 +11074,7 @@
       <c r="P203" s="4"/>
       <c r="Q203" s="4"/>
     </row>
-    <row r="204" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="204" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A204" s="2" t="s">
         <v>755</v>
       </c>
@@ -11097,7 +11113,7 @@
       <c r="P204" s="4"/>
       <c r="Q204" s="4"/>
     </row>
-    <row r="205" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="205" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A205" s="2" t="s">
         <v>759</v>
       </c>
@@ -11136,7 +11152,7 @@
       <c r="P205" s="4"/>
       <c r="Q205" s="4"/>
     </row>
-    <row r="206" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="206" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A206" s="2" t="s">
         <v>763</v>
       </c>
@@ -11175,7 +11191,7 @@
       <c r="P206" s="4"/>
       <c r="Q206" s="4"/>
     </row>
-    <row r="207" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="207" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A207" s="2" t="s">
         <v>766</v>
       </c>
@@ -11214,7 +11230,7 @@
       <c r="P207" s="4"/>
       <c r="Q207" s="4"/>
     </row>
-    <row r="208" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="208" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A208" s="2" t="s">
         <v>770</v>
       </c>
@@ -11253,7 +11269,7 @@
       <c r="P208" s="4"/>
       <c r="Q208" s="4"/>
     </row>
-    <row r="209" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="209" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A209" s="2" t="s">
         <v>774</v>
       </c>
@@ -11292,7 +11308,7 @@
       <c r="P209" s="4"/>
       <c r="Q209" s="4"/>
     </row>
-    <row r="210" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="210" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A210" s="2" t="s">
         <v>777</v>
       </c>
@@ -11331,7 +11347,7 @@
       <c r="P210" s="4"/>
       <c r="Q210" s="4"/>
     </row>
-    <row r="211" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="211" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A211" s="2" t="s">
         <v>781</v>
       </c>
@@ -11370,7 +11386,7 @@
       <c r="P211" s="4"/>
       <c r="Q211" s="4"/>
     </row>
-    <row r="212" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="212" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A212" s="2" t="s">
         <v>785</v>
       </c>
@@ -11409,7 +11425,7 @@
       <c r="P212" s="4"/>
       <c r="Q212" s="4"/>
     </row>
-    <row r="213" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="213" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A213" s="2" t="s">
         <v>789</v>
       </c>
@@ -11448,9 +11464,9 @@
       <c r="P213" s="4"/>
       <c r="Q213" s="4"/>
     </row>
-    <row r="214" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="214" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A214" s="2" t="s">
-        <v>817</v>
+        <v>816</v>
       </c>
       <c r="B214" s="3" t="s">
         <v>507</v>
@@ -11487,9 +11503,9 @@
       <c r="P214" s="4"/>
       <c r="Q214" s="4"/>
     </row>
-    <row r="215" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="215" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A215" s="2" t="s">
-        <v>818</v>
+        <v>817</v>
       </c>
       <c r="B215" s="3" t="s">
         <v>507</v>
@@ -11526,9 +11542,9 @@
       <c r="P215" s="4"/>
       <c r="Q215" s="4"/>
     </row>
-    <row r="216" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="216" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A216" s="2" t="s">
-        <v>819</v>
+        <v>818</v>
       </c>
       <c r="B216" s="3" t="s">
         <v>507</v>
@@ -11565,9 +11581,9 @@
       <c r="P216" s="4"/>
       <c r="Q216" s="4"/>
     </row>
-    <row r="217" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="217" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A217" s="2" t="s">
-        <v>820</v>
+        <v>819</v>
       </c>
       <c r="B217" s="3" t="s">
         <v>507</v>
@@ -11604,9 +11620,9 @@
       <c r="P217" s="4"/>
       <c r="Q217" s="4"/>
     </row>
-    <row r="218" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="218" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A218" s="2" t="s">
-        <v>821</v>
+        <v>820</v>
       </c>
       <c r="B218" s="3" t="s">
         <v>507</v>

--- a/dataland-framework-toolbox/inputs/eutaxonomy-financials-2026-73/eutaxonomy-financials-2026-73.xlsx
+++ b/dataland-framework-toolbox/inputs/eutaxonomy-financials-2026-73/eutaxonomy-financials-2026-73.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\d92477\IdeaProjects\Dataland\dataland-framework-toolbox\inputs\eutaxonomy-financials-2026-73\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="\\wsl.localhost\Ubuntu-24.04\srv\data\dataland\dataland-framework-toolbox\inputs\eutaxonomy-financials-2026-73\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0D114AE9-54E2-4988-BAA4-7286623F029C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A473F6A4-F53E-4C72-981E-EB67BB22B6D4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="16080" windowWidth="29040" windowHeight="17520" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Framework Data Model" sheetId="1" r:id="rId1"/>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2222" uniqueCount="852">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2221" uniqueCount="851">
   <si>
     <t>Field Identifier</t>
   </si>
@@ -2526,9 +2526,6 @@
   </si>
   <si>
     <t>Field Calculation</t>
-  </si>
-  <si>
-    <t>Identity: [extendedEnumYesNoIsNfrdMandatory]</t>
   </si>
   <si>
     <t>Identity: [extendedCurrencyCreditInstitutionAssetsForCalculationOfGreenAssetRatioTotalGrossCarryingAmount]</t>
@@ -3054,26 +3051,27 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:Q218"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="15" customWidth="1"/>
-    <col min="2" max="2" width="18.453125" customWidth="1"/>
-    <col min="3" max="3" width="70.1796875" customWidth="1"/>
-    <col min="4" max="5" width="117.81640625" customWidth="1"/>
+    <col min="2" max="2" width="18.42578125" customWidth="1"/>
+    <col min="3" max="3" width="70.140625" customWidth="1"/>
+    <col min="4" max="5" width="117.85546875" customWidth="1"/>
     <col min="6" max="6" width="92" customWidth="1"/>
-    <col min="7" max="7" width="36.453125" customWidth="1"/>
-    <col min="8" max="8" width="19.81640625" customWidth="1"/>
-    <col min="9" max="9" width="6.453125" customWidth="1"/>
-    <col min="10" max="10" width="18.7265625" customWidth="1"/>
-    <col min="11" max="11" width="13.26953125" customWidth="1"/>
-    <col min="12" max="12" width="19.54296875" customWidth="1"/>
-    <col min="13" max="13" width="16.1796875" customWidth="1"/>
-    <col min="14" max="14" width="26.453125" customWidth="1"/>
-    <col min="15" max="16" width="30.26953125" customWidth="1"/>
+    <col min="7" max="7" width="36.42578125" customWidth="1"/>
+    <col min="8" max="8" width="19.85546875" customWidth="1"/>
+    <col min="9" max="9" width="6.42578125" customWidth="1"/>
+    <col min="10" max="10" width="18.7109375" customWidth="1"/>
+    <col min="11" max="11" width="13.28515625" customWidth="1"/>
+    <col min="12" max="12" width="19.5703125" customWidth="1"/>
+    <col min="13" max="13" width="16.140625" customWidth="1"/>
+    <col min="14" max="14" width="26.42578125" customWidth="1"/>
+    <col min="15" max="15" width="30.28515625" customWidth="1"/>
+    <col min="16" max="16" width="42.140625" bestFit="1" customWidth="1"/>
     <col min="17" max="17" width="13" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:17" ht="14.65" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:17" ht="14.65" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -3126,7 +3124,7 @@
         <v>830</v>
       </c>
     </row>
-    <row r="2" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
         <v>16</v>
       </c>
@@ -3163,7 +3161,7 @@
       <c r="P2" s="4"/>
       <c r="Q2" s="4"/>
     </row>
-    <row r="3" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A3" s="2" t="s">
         <v>24</v>
       </c>
@@ -3200,7 +3198,7 @@
       <c r="P3" s="4"/>
       <c r="Q3" s="4"/>
     </row>
-    <row r="4" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A4" s="2" t="s">
         <v>30</v>
       </c>
@@ -3235,7 +3233,7 @@
       <c r="P4" s="4"/>
       <c r="Q4" s="4"/>
     </row>
-    <row r="5" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A5" s="2" t="s">
         <v>35</v>
       </c>
@@ -3274,7 +3272,7 @@
       </c>
       <c r="Q5" s="4"/>
     </row>
-    <row r="6" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A6" s="2" t="s">
         <v>41</v>
       </c>
@@ -3311,7 +3309,7 @@
       <c r="P6" s="4"/>
       <c r="Q6" s="4"/>
     </row>
-    <row r="7" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A7" s="2" t="s">
         <v>47</v>
       </c>
@@ -3344,11 +3342,9 @@
       <c r="N7" s="4"/>
       <c r="O7" s="4"/>
       <c r="P7" s="4"/>
-      <c r="Q7" s="4" t="s">
-        <v>831</v>
-      </c>
-    </row>
-    <row r="8" spans="1:17" x14ac:dyDescent="0.35">
+      <c r="Q7" s="4"/>
+    </row>
+    <row r="8" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A8" s="2" t="s">
         <v>51</v>
       </c>
@@ -3383,7 +3379,7 @@
       <c r="P8" s="4"/>
       <c r="Q8" s="4"/>
     </row>
-    <row r="9" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A9" s="2" t="s">
         <v>56</v>
       </c>
@@ -3418,7 +3414,7 @@
       <c r="P9" s="4"/>
       <c r="Q9" s="4"/>
     </row>
-    <row r="10" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A10" s="2" t="s">
         <v>60</v>
       </c>
@@ -3458,10 +3454,10 @@
       </c>
       <c r="P10" s="4"/>
       <c r="Q10" s="4" t="s">
-        <v>832</v>
-      </c>
-    </row>
-    <row r="11" spans="1:17" x14ac:dyDescent="0.35">
+        <v>831</v>
+      </c>
+    </row>
+    <row r="11" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A11" s="2" t="s">
         <v>64</v>
       </c>
@@ -3502,7 +3498,7 @@
       <c r="P11" s="4"/>
       <c r="Q11" s="4"/>
     </row>
-    <row r="12" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A12" s="2" t="s">
         <v>65</v>
       </c>
@@ -3543,7 +3539,7 @@
       <c r="P12" s="4"/>
       <c r="Q12" s="4"/>
     </row>
-    <row r="13" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A13" s="2" t="s">
         <v>66</v>
       </c>
@@ -3560,7 +3556,7 @@
         <v>824</v>
       </c>
       <c r="F13" s="4" t="s">
-        <v>850</v>
+        <v>849</v>
       </c>
       <c r="G13" s="4" t="s">
         <v>62</v>
@@ -3584,7 +3580,7 @@
       <c r="P13" s="4"/>
       <c r="Q13" s="4"/>
     </row>
-    <row r="14" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A14" s="2" t="s">
         <v>67</v>
       </c>
@@ -3625,7 +3621,7 @@
       <c r="P14" s="4"/>
       <c r="Q14" s="4"/>
     </row>
-    <row r="15" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A15" s="2" t="s">
         <v>68</v>
       </c>
@@ -3666,7 +3662,7 @@
       <c r="P15" s="4"/>
       <c r="Q15" s="4"/>
     </row>
-    <row r="16" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A16" s="2" t="s">
         <v>73</v>
       </c>
@@ -3707,7 +3703,7 @@
       <c r="P16" s="4"/>
       <c r="Q16" s="4"/>
     </row>
-    <row r="17" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A17" s="2" t="s">
         <v>77</v>
       </c>
@@ -3748,7 +3744,7 @@
       <c r="P17" s="4"/>
       <c r="Q17" s="4"/>
     </row>
-    <row r="18" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A18" s="2" t="s">
         <v>81</v>
       </c>
@@ -3765,7 +3761,7 @@
         <v>812</v>
       </c>
       <c r="F18" s="4" t="s">
-        <v>851</v>
+        <v>850</v>
       </c>
       <c r="G18" s="4" t="s">
         <v>62</v>
@@ -3789,7 +3785,7 @@
       <c r="P18" s="4"/>
       <c r="Q18" s="4"/>
     </row>
-    <row r="19" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A19" s="2" t="s">
         <v>85</v>
       </c>
@@ -3830,7 +3826,7 @@
       <c r="P19" s="4"/>
       <c r="Q19" s="4"/>
     </row>
-    <row r="20" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="20" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A20" s="2" t="s">
         <v>89</v>
       </c>
@@ -3871,7 +3867,7 @@
       <c r="P20" s="4"/>
       <c r="Q20" s="4"/>
     </row>
-    <row r="21" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="21" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A21" s="2" t="s">
         <v>93</v>
       </c>
@@ -3912,7 +3908,7 @@
       <c r="P21" s="4"/>
       <c r="Q21" s="4"/>
     </row>
-    <row r="22" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="22" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A22" s="2" t="s">
         <v>98</v>
       </c>
@@ -3953,7 +3949,7 @@
       <c r="P22" s="4"/>
       <c r="Q22" s="4"/>
     </row>
-    <row r="23" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="23" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A23" s="2" t="s">
         <v>102</v>
       </c>
@@ -3994,7 +3990,7 @@
       <c r="P23" s="4"/>
       <c r="Q23" s="4"/>
     </row>
-    <row r="24" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="24" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A24" s="2" t="s">
         <v>106</v>
       </c>
@@ -4035,7 +4031,7 @@
       <c r="P24" s="4"/>
       <c r="Q24" s="4"/>
     </row>
-    <row r="25" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="25" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A25" s="2" t="s">
         <v>110</v>
       </c>
@@ -4076,7 +4072,7 @@
       <c r="P25" s="4"/>
       <c r="Q25" s="4"/>
     </row>
-    <row r="26" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="26" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A26" s="2" t="s">
         <v>114</v>
       </c>
@@ -4117,7 +4113,7 @@
       <c r="P26" s="4"/>
       <c r="Q26" s="4"/>
     </row>
-    <row r="27" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="27" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A27" s="2" t="s">
         <v>118</v>
       </c>
@@ -4158,7 +4154,7 @@
       <c r="P27" s="4"/>
       <c r="Q27" s="4"/>
     </row>
-    <row r="28" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="28" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A28" s="2" t="s">
         <v>124</v>
       </c>
@@ -4199,7 +4195,7 @@
       <c r="P28" s="4"/>
       <c r="Q28" s="4"/>
     </row>
-    <row r="29" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="29" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A29" s="2" t="s">
         <v>128</v>
       </c>
@@ -4240,7 +4236,7 @@
       <c r="P29" s="4"/>
       <c r="Q29" s="4"/>
     </row>
-    <row r="30" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="30" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A30" s="2" t="s">
         <v>132</v>
       </c>
@@ -4281,7 +4277,7 @@
       <c r="P30" s="4"/>
       <c r="Q30" s="4"/>
     </row>
-    <row r="31" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="31" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A31" s="2" t="s">
         <v>136</v>
       </c>
@@ -4322,7 +4318,7 @@
       <c r="P31" s="4"/>
       <c r="Q31" s="4"/>
     </row>
-    <row r="32" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="32" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A32" s="2" t="s">
         <v>140</v>
       </c>
@@ -4361,7 +4357,7 @@
       <c r="P32" s="4"/>
       <c r="Q32" s="4"/>
     </row>
-    <row r="33" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="33" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A33" s="2" t="s">
         <v>144</v>
       </c>
@@ -4400,7 +4396,7 @@
       <c r="P33" s="4"/>
       <c r="Q33" s="4"/>
     </row>
-    <row r="34" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="34" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A34" s="2" t="s">
         <v>148</v>
       </c>
@@ -4439,7 +4435,7 @@
       <c r="P34" s="4"/>
       <c r="Q34" s="4"/>
     </row>
-    <row r="35" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="35" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A35" s="2" t="s">
         <v>152</v>
       </c>
@@ -4478,7 +4474,7 @@
       <c r="P35" s="4"/>
       <c r="Q35" s="4"/>
     </row>
-    <row r="36" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="36" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A36" s="2" t="s">
         <v>156</v>
       </c>
@@ -4517,7 +4513,7 @@
       <c r="P36" s="4"/>
       <c r="Q36" s="4"/>
     </row>
-    <row r="37" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="37" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A37" s="2" t="s">
         <v>160</v>
       </c>
@@ -4556,7 +4552,7 @@
       <c r="P37" s="4"/>
       <c r="Q37" s="4"/>
     </row>
-    <row r="38" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="38" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A38" s="2" t="s">
         <v>164</v>
       </c>
@@ -4595,7 +4591,7 @@
       <c r="P38" s="4"/>
       <c r="Q38" s="4"/>
     </row>
-    <row r="39" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="39" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A39" s="2" t="s">
         <v>168</v>
       </c>
@@ -4634,7 +4630,7 @@
       <c r="P39" s="4"/>
       <c r="Q39" s="4"/>
     </row>
-    <row r="40" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="40" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A40" s="2" t="s">
         <v>172</v>
       </c>
@@ -4673,7 +4669,7 @@
       <c r="P40" s="4"/>
       <c r="Q40" s="4"/>
     </row>
-    <row r="41" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="41" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A41" s="2" t="s">
         <v>175</v>
       </c>
@@ -4712,7 +4708,7 @@
       <c r="P41" s="4"/>
       <c r="Q41" s="4"/>
     </row>
-    <row r="42" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="42" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A42" s="2" t="s">
         <v>178</v>
       </c>
@@ -4751,7 +4747,7 @@
       <c r="P42" s="4"/>
       <c r="Q42" s="4"/>
     </row>
-    <row r="43" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="43" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A43" s="2" t="s">
         <v>181</v>
       </c>
@@ -4790,7 +4786,7 @@
       <c r="P43" s="4"/>
       <c r="Q43" s="4"/>
     </row>
-    <row r="44" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="44" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A44" s="2" t="s">
         <v>184</v>
       </c>
@@ -4829,7 +4825,7 @@
       <c r="P44" s="4"/>
       <c r="Q44" s="4"/>
     </row>
-    <row r="45" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="45" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A45" s="2" t="s">
         <v>187</v>
       </c>
@@ -4868,7 +4864,7 @@
       <c r="P45" s="4"/>
       <c r="Q45" s="4"/>
     </row>
-    <row r="46" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="46" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A46" s="2" t="s">
         <v>190</v>
       </c>
@@ -4907,7 +4903,7 @@
       <c r="P46" s="4"/>
       <c r="Q46" s="4"/>
     </row>
-    <row r="47" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="47" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A47" s="2" t="s">
         <v>193</v>
       </c>
@@ -4946,7 +4942,7 @@
       <c r="P47" s="4"/>
       <c r="Q47" s="4"/>
     </row>
-    <row r="48" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="48" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A48" s="2" t="s">
         <v>195</v>
       </c>
@@ -4985,7 +4981,7 @@
       <c r="P48" s="4"/>
       <c r="Q48" s="4"/>
     </row>
-    <row r="49" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="49" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A49" s="2" t="s">
         <v>198</v>
       </c>
@@ -5024,7 +5020,7 @@
       <c r="P49" s="4"/>
       <c r="Q49" s="4"/>
     </row>
-    <row r="50" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="50" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A50" s="2" t="s">
         <v>201</v>
       </c>
@@ -5063,7 +5059,7 @@
       <c r="P50" s="4"/>
       <c r="Q50" s="4"/>
     </row>
-    <row r="51" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="51" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A51" s="2" t="s">
         <v>205</v>
       </c>
@@ -5102,7 +5098,7 @@
       <c r="P51" s="4"/>
       <c r="Q51" s="4"/>
     </row>
-    <row r="52" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="52" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A52" s="2" t="s">
         <v>211</v>
       </c>
@@ -5141,7 +5137,7 @@
       <c r="P52" s="4"/>
       <c r="Q52" s="4"/>
     </row>
-    <row r="53" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="53" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A53" s="2" t="s">
         <v>215</v>
       </c>
@@ -5180,7 +5176,7 @@
       <c r="P53" s="4"/>
       <c r="Q53" s="4"/>
     </row>
-    <row r="54" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="54" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A54" s="2" t="s">
         <v>219</v>
       </c>
@@ -5219,7 +5215,7 @@
       <c r="P54" s="4"/>
       <c r="Q54" s="4"/>
     </row>
-    <row r="55" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="55" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A55" s="2" t="s">
         <v>224</v>
       </c>
@@ -5258,7 +5254,7 @@
       <c r="P55" s="4"/>
       <c r="Q55" s="4"/>
     </row>
-    <row r="56" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="56" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A56" s="2" t="s">
         <v>228</v>
       </c>
@@ -5299,7 +5295,7 @@
       <c r="P56" s="4"/>
       <c r="Q56" s="4"/>
     </row>
-    <row r="57" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="57" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A57" s="2" t="s">
         <v>232</v>
       </c>
@@ -5338,7 +5334,7 @@
       <c r="P57" s="4"/>
       <c r="Q57" s="4"/>
     </row>
-    <row r="58" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="58" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A58" s="2" t="s">
         <v>236</v>
       </c>
@@ -5378,10 +5374,10 @@
       </c>
       <c r="P58" s="4"/>
       <c r="Q58" s="4" t="s">
-        <v>833</v>
-      </c>
-    </row>
-    <row r="59" spans="1:17" x14ac:dyDescent="0.35">
+        <v>832</v>
+      </c>
+    </row>
+    <row r="59" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A59" s="2" t="s">
         <v>240</v>
       </c>
@@ -5420,7 +5416,7 @@
       <c r="P59" s="4"/>
       <c r="Q59" s="4"/>
     </row>
-    <row r="60" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="60" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A60" s="2" t="s">
         <v>244</v>
       </c>
@@ -5459,7 +5455,7 @@
       <c r="P60" s="4"/>
       <c r="Q60" s="4"/>
     </row>
-    <row r="61" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="61" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A61" s="2" t="s">
         <v>248</v>
       </c>
@@ -5498,7 +5494,7 @@
       <c r="P61" s="4"/>
       <c r="Q61" s="4"/>
     </row>
-    <row r="62" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="62" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A62" s="2" t="s">
         <v>252</v>
       </c>
@@ -5536,10 +5532,10 @@
       </c>
       <c r="P62" s="4"/>
       <c r="Q62" s="4" t="s">
-        <v>834</v>
-      </c>
-    </row>
-    <row r="63" spans="1:17" x14ac:dyDescent="0.35">
+        <v>833</v>
+      </c>
+    </row>
+    <row r="63" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A63" s="2" t="s">
         <v>255</v>
       </c>
@@ -5577,10 +5573,10 @@
       </c>
       <c r="P63" s="4"/>
       <c r="Q63" s="4" t="s">
-        <v>835</v>
-      </c>
-    </row>
-    <row r="64" spans="1:17" x14ac:dyDescent="0.35">
+        <v>834</v>
+      </c>
+    </row>
+    <row r="64" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A64" s="2" t="s">
         <v>259</v>
       </c>
@@ -5618,10 +5614,10 @@
       </c>
       <c r="P64" s="4"/>
       <c r="Q64" s="4" t="s">
-        <v>836</v>
-      </c>
-    </row>
-    <row r="65" spans="1:17" x14ac:dyDescent="0.35">
+        <v>835</v>
+      </c>
+    </row>
+    <row r="65" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A65" s="2" t="s">
         <v>263</v>
       </c>
@@ -5660,7 +5656,7 @@
       <c r="P65" s="4"/>
       <c r="Q65" s="4"/>
     </row>
-    <row r="66" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="66" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A66" s="2" t="s">
         <v>267</v>
       </c>
@@ -5699,7 +5695,7 @@
       <c r="P66" s="4"/>
       <c r="Q66" s="4"/>
     </row>
-    <row r="67" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="67" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A67" s="2" t="s">
         <v>272</v>
       </c>
@@ -5738,7 +5734,7 @@
       <c r="P67" s="4"/>
       <c r="Q67" s="4"/>
     </row>
-    <row r="68" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="68" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A68" s="2" t="s">
         <v>276</v>
       </c>
@@ -5777,7 +5773,7 @@
       <c r="P68" s="4"/>
       <c r="Q68" s="4"/>
     </row>
-    <row r="69" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="69" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A69" s="2" t="s">
         <v>280</v>
       </c>
@@ -5816,7 +5812,7 @@
       <c r="P69" s="4"/>
       <c r="Q69" s="4"/>
     </row>
-    <row r="70" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="70" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A70" s="2" t="s">
         <v>284</v>
       </c>
@@ -5855,7 +5851,7 @@
       <c r="P70" s="4"/>
       <c r="Q70" s="4"/>
     </row>
-    <row r="71" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="71" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A71" s="2" t="s">
         <v>288</v>
       </c>
@@ -5894,7 +5890,7 @@
       <c r="P71" s="4"/>
       <c r="Q71" s="4"/>
     </row>
-    <row r="72" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="72" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A72" s="2" t="s">
         <v>292</v>
       </c>
@@ -5933,7 +5929,7 @@
       <c r="P72" s="4"/>
       <c r="Q72" s="4"/>
     </row>
-    <row r="73" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="73" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A73" s="2" t="s">
         <v>297</v>
       </c>
@@ -5972,7 +5968,7 @@
       <c r="P73" s="4"/>
       <c r="Q73" s="4"/>
     </row>
-    <row r="74" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="74" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A74" s="2" t="s">
         <v>301</v>
       </c>
@@ -6011,7 +6007,7 @@
       <c r="P74" s="4"/>
       <c r="Q74" s="4"/>
     </row>
-    <row r="75" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="75" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A75" s="2" t="s">
         <v>305</v>
       </c>
@@ -6050,7 +6046,7 @@
       <c r="P75" s="4"/>
       <c r="Q75" s="4"/>
     </row>
-    <row r="76" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="76" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A76" s="2" t="s">
         <v>309</v>
       </c>
@@ -6089,7 +6085,7 @@
       <c r="P76" s="4"/>
       <c r="Q76" s="4"/>
     </row>
-    <row r="77" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="77" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A77" s="2" t="s">
         <v>313</v>
       </c>
@@ -6128,7 +6124,7 @@
       <c r="P77" s="4"/>
       <c r="Q77" s="4"/>
     </row>
-    <row r="78" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="78" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A78" s="2" t="s">
         <v>317</v>
       </c>
@@ -6167,7 +6163,7 @@
       <c r="P78" s="4"/>
       <c r="Q78" s="4"/>
     </row>
-    <row r="79" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="79" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A79" s="2" t="s">
         <v>321</v>
       </c>
@@ -6206,7 +6202,7 @@
       <c r="P79" s="4"/>
       <c r="Q79" s="4"/>
     </row>
-    <row r="80" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="80" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A80" s="2" t="s">
         <v>325</v>
       </c>
@@ -6244,10 +6240,10 @@
       </c>
       <c r="P80" s="4"/>
       <c r="Q80" s="4" t="s">
-        <v>837</v>
-      </c>
-    </row>
-    <row r="81" spans="1:17" x14ac:dyDescent="0.35">
+        <v>836</v>
+      </c>
+    </row>
+    <row r="81" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A81" s="2" t="s">
         <v>328</v>
       </c>
@@ -6285,10 +6281,10 @@
       </c>
       <c r="P81" s="4"/>
       <c r="Q81" s="4" t="s">
-        <v>838</v>
-      </c>
-    </row>
-    <row r="82" spans="1:17" x14ac:dyDescent="0.35">
+        <v>837</v>
+      </c>
+    </row>
+    <row r="82" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A82" s="2" t="s">
         <v>332</v>
       </c>
@@ -6326,10 +6322,10 @@
       </c>
       <c r="P82" s="4"/>
       <c r="Q82" s="4" t="s">
-        <v>839</v>
-      </c>
-    </row>
-    <row r="83" spans="1:17" x14ac:dyDescent="0.35">
+        <v>838</v>
+      </c>
+    </row>
+    <row r="83" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A83" s="2" t="s">
         <v>336</v>
       </c>
@@ -6368,7 +6364,7 @@
       <c r="P83" s="4"/>
       <c r="Q83" s="4"/>
     </row>
-    <row r="84" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="84" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A84" s="2" t="s">
         <v>340</v>
       </c>
@@ -6407,7 +6403,7 @@
       <c r="P84" s="4"/>
       <c r="Q84" s="4"/>
     </row>
-    <row r="85" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="85" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A85" s="2" t="s">
         <v>345</v>
       </c>
@@ -6446,7 +6442,7 @@
       <c r="P85" s="4"/>
       <c r="Q85" s="4"/>
     </row>
-    <row r="86" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="86" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A86" s="2" t="s">
         <v>349</v>
       </c>
@@ -6485,7 +6481,7 @@
       <c r="P86" s="4"/>
       <c r="Q86" s="4"/>
     </row>
-    <row r="87" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="87" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A87" s="2" t="s">
         <v>353</v>
       </c>
@@ -6524,7 +6520,7 @@
       <c r="P87" s="4"/>
       <c r="Q87" s="4"/>
     </row>
-    <row r="88" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="88" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A88" s="2" t="s">
         <v>357</v>
       </c>
@@ -6563,7 +6559,7 @@
       <c r="P88" s="4"/>
       <c r="Q88" s="4"/>
     </row>
-    <row r="89" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="89" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A89" s="2" t="s">
         <v>361</v>
       </c>
@@ -6602,7 +6598,7 @@
       <c r="P89" s="4"/>
       <c r="Q89" s="4"/>
     </row>
-    <row r="90" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="90" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A90" s="2" t="s">
         <v>365</v>
       </c>
@@ -6641,7 +6637,7 @@
       <c r="P90" s="4"/>
       <c r="Q90" s="4"/>
     </row>
-    <row r="91" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="91" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A91" s="2" t="s">
         <v>371</v>
       </c>
@@ -6680,7 +6676,7 @@
       <c r="P91" s="4"/>
       <c r="Q91" s="4"/>
     </row>
-    <row r="92" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="92" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A92" s="2" t="s">
         <v>375</v>
       </c>
@@ -6719,7 +6715,7 @@
       <c r="P92" s="4"/>
       <c r="Q92" s="4"/>
     </row>
-    <row r="93" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="93" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A93" s="2" t="s">
         <v>379</v>
       </c>
@@ -6758,7 +6754,7 @@
       <c r="P93" s="4"/>
       <c r="Q93" s="4"/>
     </row>
-    <row r="94" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="94" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A94" s="2" t="s">
         <v>383</v>
       </c>
@@ -6797,7 +6793,7 @@
       <c r="P94" s="4"/>
       <c r="Q94" s="4"/>
     </row>
-    <row r="95" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="95" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A95" s="2" t="s">
         <v>387</v>
       </c>
@@ -6836,7 +6832,7 @@
       <c r="P95" s="4"/>
       <c r="Q95" s="4"/>
     </row>
-    <row r="96" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="96" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A96" s="2" t="s">
         <v>391</v>
       </c>
@@ -6873,7 +6869,7 @@
       <c r="P96" s="4"/>
       <c r="Q96" s="4"/>
     </row>
-    <row r="97" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="97" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A97" s="2" t="s">
         <v>395</v>
       </c>
@@ -6910,7 +6906,7 @@
       <c r="P97" s="4"/>
       <c r="Q97" s="4"/>
     </row>
-    <row r="98" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="98" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A98" s="2" t="s">
         <v>399</v>
       </c>
@@ -6947,7 +6943,7 @@
       <c r="P98" s="4"/>
       <c r="Q98" s="4"/>
     </row>
-    <row r="99" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="99" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A99" s="2" t="s">
         <v>403</v>
       </c>
@@ -6985,10 +6981,10 @@
       <c r="O99" s="4"/>
       <c r="P99" s="4"/>
       <c r="Q99" s="4" t="s">
-        <v>840</v>
-      </c>
-    </row>
-    <row r="100" spans="1:17" x14ac:dyDescent="0.35">
+        <v>839</v>
+      </c>
+    </row>
+    <row r="100" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A100" s="2" t="s">
         <v>407</v>
       </c>
@@ -7024,10 +7020,10 @@
       <c r="O100" s="4"/>
       <c r="P100" s="4"/>
       <c r="Q100" s="4" t="s">
-        <v>841</v>
-      </c>
-    </row>
-    <row r="101" spans="1:17" x14ac:dyDescent="0.35">
+        <v>840</v>
+      </c>
+    </row>
+    <row r="101" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A101" s="2" t="s">
         <v>411</v>
       </c>
@@ -7064,7 +7060,7 @@
       <c r="P101" s="4"/>
       <c r="Q101" s="4"/>
     </row>
-    <row r="102" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="102" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A102" s="2" t="s">
         <v>414</v>
       </c>
@@ -7101,7 +7097,7 @@
       <c r="P102" s="4"/>
       <c r="Q102" s="4"/>
     </row>
-    <row r="103" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="103" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A103" s="2" t="s">
         <v>417</v>
       </c>
@@ -7140,7 +7136,7 @@
       <c r="P103" s="4"/>
       <c r="Q103" s="4"/>
     </row>
-    <row r="104" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="104" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A104" s="2" t="s">
         <v>420</v>
       </c>
@@ -7177,7 +7173,7 @@
       <c r="P104" s="4"/>
       <c r="Q104" s="4"/>
     </row>
-    <row r="105" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="105" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A105" s="2" t="s">
         <v>422</v>
       </c>
@@ -7215,10 +7211,10 @@
       <c r="O105" s="4"/>
       <c r="P105" s="4"/>
       <c r="Q105" s="4" t="s">
-        <v>842</v>
-      </c>
-    </row>
-    <row r="106" spans="1:17" x14ac:dyDescent="0.35">
+        <v>841</v>
+      </c>
+    </row>
+    <row r="106" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A106" s="2" t="s">
         <v>424</v>
       </c>
@@ -7259,7 +7255,7 @@
       <c r="P106" s="4"/>
       <c r="Q106" s="4"/>
     </row>
-    <row r="107" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="107" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A107" s="2" t="s">
         <v>426</v>
       </c>
@@ -7298,7 +7294,7 @@
       <c r="P107" s="4"/>
       <c r="Q107" s="4"/>
     </row>
-    <row r="108" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="108" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A108" s="2" t="s">
         <v>428</v>
       </c>
@@ -7338,10 +7334,10 @@
       </c>
       <c r="P108" s="4"/>
       <c r="Q108" s="4" t="s">
-        <v>843</v>
-      </c>
-    </row>
-    <row r="109" spans="1:17" x14ac:dyDescent="0.35">
+        <v>842</v>
+      </c>
+    </row>
+    <row r="109" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A109" s="2" t="s">
         <v>430</v>
       </c>
@@ -7380,7 +7376,7 @@
       <c r="P109" s="4"/>
       <c r="Q109" s="4"/>
     </row>
-    <row r="110" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="110" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A110" s="2" t="s">
         <v>432</v>
       </c>
@@ -7419,7 +7415,7 @@
       <c r="P110" s="4"/>
       <c r="Q110" s="4"/>
     </row>
-    <row r="111" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="111" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A111" s="2" t="s">
         <v>434</v>
       </c>
@@ -7458,7 +7454,7 @@
       <c r="P111" s="4"/>
       <c r="Q111" s="4"/>
     </row>
-    <row r="112" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="112" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A112" s="2" t="s">
         <v>436</v>
       </c>
@@ -7496,10 +7492,10 @@
       </c>
       <c r="P112" s="4"/>
       <c r="Q112" s="4" t="s">
-        <v>844</v>
-      </c>
-    </row>
-    <row r="113" spans="1:17" x14ac:dyDescent="0.35">
+        <v>843</v>
+      </c>
+    </row>
+    <row r="113" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A113" s="2" t="s">
         <v>438</v>
       </c>
@@ -7537,10 +7533,10 @@
       </c>
       <c r="P113" s="4"/>
       <c r="Q113" s="4" t="s">
-        <v>845</v>
-      </c>
-    </row>
-    <row r="114" spans="1:17" x14ac:dyDescent="0.35">
+        <v>844</v>
+      </c>
+    </row>
+    <row r="114" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A114" s="2" t="s">
         <v>440</v>
       </c>
@@ -7578,10 +7574,10 @@
       </c>
       <c r="P114" s="4"/>
       <c r="Q114" s="4" t="s">
-        <v>846</v>
-      </c>
-    </row>
-    <row r="115" spans="1:17" x14ac:dyDescent="0.35">
+        <v>845</v>
+      </c>
+    </row>
+    <row r="115" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A115" s="2" t="s">
         <v>442</v>
       </c>
@@ -7620,7 +7616,7 @@
       <c r="P115" s="4"/>
       <c r="Q115" s="4"/>
     </row>
-    <row r="116" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="116" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A116" s="2" t="s">
         <v>446</v>
       </c>
@@ -7659,7 +7655,7 @@
       <c r="P116" s="4"/>
       <c r="Q116" s="4"/>
     </row>
-    <row r="117" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="117" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A117" s="2" t="s">
         <v>449</v>
       </c>
@@ -7698,7 +7694,7 @@
       <c r="P117" s="4"/>
       <c r="Q117" s="4"/>
     </row>
-    <row r="118" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="118" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A118" s="2" t="s">
         <v>452</v>
       </c>
@@ -7737,7 +7733,7 @@
       <c r="P118" s="4"/>
       <c r="Q118" s="4"/>
     </row>
-    <row r="119" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="119" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A119" s="2" t="s">
         <v>455</v>
       </c>
@@ -7776,7 +7772,7 @@
       <c r="P119" s="4"/>
       <c r="Q119" s="4"/>
     </row>
-    <row r="120" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="120" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A120" s="2" t="s">
         <v>458</v>
       </c>
@@ -7815,7 +7811,7 @@
       <c r="P120" s="4"/>
       <c r="Q120" s="4"/>
     </row>
-    <row r="121" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="121" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A121" s="2" t="s">
         <v>461</v>
       </c>
@@ -7854,7 +7850,7 @@
       <c r="P121" s="4"/>
       <c r="Q121" s="4"/>
     </row>
-    <row r="122" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="122" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A122" s="2" t="s">
         <v>464</v>
       </c>
@@ -7893,7 +7889,7 @@
       <c r="P122" s="4"/>
       <c r="Q122" s="4"/>
     </row>
-    <row r="123" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="123" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A123" s="2" t="s">
         <v>466</v>
       </c>
@@ -7932,7 +7928,7 @@
       <c r="P123" s="4"/>
       <c r="Q123" s="4"/>
     </row>
-    <row r="124" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="124" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A124" s="2" t="s">
         <v>468</v>
       </c>
@@ -7971,7 +7967,7 @@
       <c r="P124" s="4"/>
       <c r="Q124" s="4"/>
     </row>
-    <row r="125" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="125" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A125" s="2" t="s">
         <v>470</v>
       </c>
@@ -8010,7 +8006,7 @@
       <c r="P125" s="4"/>
       <c r="Q125" s="4"/>
     </row>
-    <row r="126" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="126" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A126" s="2" t="s">
         <v>472</v>
       </c>
@@ -8049,7 +8045,7 @@
       <c r="P126" s="4"/>
       <c r="Q126" s="4"/>
     </row>
-    <row r="127" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="127" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A127" s="2" t="s">
         <v>474</v>
       </c>
@@ -8088,7 +8084,7 @@
       <c r="P127" s="4"/>
       <c r="Q127" s="4"/>
     </row>
-    <row r="128" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="128" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A128" s="2" t="s">
         <v>476</v>
       </c>
@@ -8127,7 +8123,7 @@
       <c r="P128" s="4"/>
       <c r="Q128" s="4"/>
     </row>
-    <row r="129" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="129" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A129" s="2" t="s">
         <v>478</v>
       </c>
@@ -8166,7 +8162,7 @@
       <c r="P129" s="4"/>
       <c r="Q129" s="4"/>
     </row>
-    <row r="130" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="130" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A130" s="2" t="s">
         <v>480</v>
       </c>
@@ -8204,10 +8200,10 @@
       </c>
       <c r="P130" s="4"/>
       <c r="Q130" s="4" t="s">
-        <v>847</v>
-      </c>
-    </row>
-    <row r="131" spans="1:17" x14ac:dyDescent="0.35">
+        <v>846</v>
+      </c>
+    </row>
+    <row r="131" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A131" s="2" t="s">
         <v>482</v>
       </c>
@@ -8245,10 +8241,10 @@
       </c>
       <c r="P131" s="4"/>
       <c r="Q131" s="4" t="s">
-        <v>848</v>
-      </c>
-    </row>
-    <row r="132" spans="1:17" x14ac:dyDescent="0.35">
+        <v>847</v>
+      </c>
+    </row>
+    <row r="132" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A132" s="2" t="s">
         <v>484</v>
       </c>
@@ -8286,10 +8282,10 @@
       </c>
       <c r="P132" s="4"/>
       <c r="Q132" s="4" t="s">
-        <v>849</v>
-      </c>
-    </row>
-    <row r="133" spans="1:17" x14ac:dyDescent="0.35">
+        <v>848</v>
+      </c>
+    </row>
+    <row r="133" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A133" s="2" t="s">
         <v>486</v>
       </c>
@@ -8328,7 +8324,7 @@
       <c r="P133" s="4"/>
       <c r="Q133" s="4"/>
     </row>
-    <row r="134" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="134" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A134" s="2" t="s">
         <v>488</v>
       </c>
@@ -8367,7 +8363,7 @@
       <c r="P134" s="4"/>
       <c r="Q134" s="4"/>
     </row>
-    <row r="135" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="135" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A135" s="2" t="s">
         <v>491</v>
       </c>
@@ -8406,7 +8402,7 @@
       <c r="P135" s="4"/>
       <c r="Q135" s="4"/>
     </row>
-    <row r="136" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="136" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A136" s="2" t="s">
         <v>494</v>
       </c>
@@ -8445,7 +8441,7 @@
       <c r="P136" s="4"/>
       <c r="Q136" s="4"/>
     </row>
-    <row r="137" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="137" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A137" s="2" t="s">
         <v>497</v>
       </c>
@@ -8484,7 +8480,7 @@
       <c r="P137" s="4"/>
       <c r="Q137" s="4"/>
     </row>
-    <row r="138" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="138" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A138" s="2" t="s">
         <v>500</v>
       </c>
@@ -8523,7 +8519,7 @@
       <c r="P138" s="4"/>
       <c r="Q138" s="4"/>
     </row>
-    <row r="139" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="139" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A139" s="2" t="s">
         <v>503</v>
       </c>
@@ -8562,7 +8558,7 @@
       <c r="P139" s="4"/>
       <c r="Q139" s="4"/>
     </row>
-    <row r="140" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="140" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A140" s="2" t="s">
         <v>506</v>
       </c>
@@ -8601,7 +8597,7 @@
       <c r="P140" s="4"/>
       <c r="Q140" s="4"/>
     </row>
-    <row r="141" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="141" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A141" s="2" t="s">
         <v>512</v>
       </c>
@@ -8640,7 +8636,7 @@
       <c r="P141" s="4"/>
       <c r="Q141" s="4"/>
     </row>
-    <row r="142" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="142" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A142" s="2" t="s">
         <v>516</v>
       </c>
@@ -8679,7 +8675,7 @@
       <c r="P142" s="4"/>
       <c r="Q142" s="4"/>
     </row>
-    <row r="143" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="143" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A143" s="2" t="s">
         <v>520</v>
       </c>
@@ -8718,7 +8714,7 @@
       <c r="P143" s="4"/>
       <c r="Q143" s="4"/>
     </row>
-    <row r="144" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="144" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A144" s="2" t="s">
         <v>524</v>
       </c>
@@ -8757,7 +8753,7 @@
       <c r="P144" s="4"/>
       <c r="Q144" s="4"/>
     </row>
-    <row r="145" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="145" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A145" s="2" t="s">
         <v>528</v>
       </c>
@@ -8798,7 +8794,7 @@
       <c r="P145" s="4"/>
       <c r="Q145" s="4"/>
     </row>
-    <row r="146" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="146" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A146" s="2" t="s">
         <v>532</v>
       </c>
@@ -8839,7 +8835,7 @@
       <c r="P146" s="4"/>
       <c r="Q146" s="4"/>
     </row>
-    <row r="147" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="147" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A147" s="2" t="s">
         <v>536</v>
       </c>
@@ -8878,7 +8874,7 @@
       <c r="P147" s="4"/>
       <c r="Q147" s="4"/>
     </row>
-    <row r="148" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="148" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A148" s="2" t="s">
         <v>540</v>
       </c>
@@ -8917,7 +8913,7 @@
       <c r="P148" s="4"/>
       <c r="Q148" s="4"/>
     </row>
-    <row r="149" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="149" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A149" s="2" t="s">
         <v>544</v>
       </c>
@@ -8956,7 +8952,7 @@
       <c r="P149" s="4"/>
       <c r="Q149" s="4"/>
     </row>
-    <row r="150" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="150" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A150" s="2" t="s">
         <v>547</v>
       </c>
@@ -8995,7 +8991,7 @@
       <c r="P150" s="4"/>
       <c r="Q150" s="4"/>
     </row>
-    <row r="151" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="151" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A151" s="2" t="s">
         <v>551</v>
       </c>
@@ -9034,7 +9030,7 @@
       <c r="P151" s="4"/>
       <c r="Q151" s="4"/>
     </row>
-    <row r="152" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="152" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A152" s="2" t="s">
         <v>555</v>
       </c>
@@ -9073,7 +9069,7 @@
       <c r="P152" s="4"/>
       <c r="Q152" s="4"/>
     </row>
-    <row r="153" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="153" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A153" s="2" t="s">
         <v>558</v>
       </c>
@@ -9112,7 +9108,7 @@
       <c r="P153" s="4"/>
       <c r="Q153" s="4"/>
     </row>
-    <row r="154" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="154" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A154" s="2" t="s">
         <v>561</v>
       </c>
@@ -9151,7 +9147,7 @@
       <c r="P154" s="4"/>
       <c r="Q154" s="4"/>
     </row>
-    <row r="155" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="155" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A155" s="2" t="s">
         <v>564</v>
       </c>
@@ -9190,7 +9186,7 @@
       <c r="P155" s="4"/>
       <c r="Q155" s="4"/>
     </row>
-    <row r="156" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="156" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A156" s="2" t="s">
         <v>567</v>
       </c>
@@ -9229,7 +9225,7 @@
       <c r="P156" s="4"/>
       <c r="Q156" s="4"/>
     </row>
-    <row r="157" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="157" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A157" s="2" t="s">
         <v>571</v>
       </c>
@@ -9268,7 +9264,7 @@
       <c r="P157" s="4"/>
       <c r="Q157" s="4"/>
     </row>
-    <row r="158" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="158" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A158" s="2" t="s">
         <v>575</v>
       </c>
@@ -9307,7 +9303,7 @@
       <c r="P158" s="4"/>
       <c r="Q158" s="4"/>
     </row>
-    <row r="159" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="159" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A159" s="2" t="s">
         <v>579</v>
       </c>
@@ -9346,7 +9342,7 @@
       <c r="P159" s="4"/>
       <c r="Q159" s="4"/>
     </row>
-    <row r="160" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="160" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A160" s="2" t="s">
         <v>583</v>
       </c>
@@ -9385,7 +9381,7 @@
       <c r="P160" s="4"/>
       <c r="Q160" s="4"/>
     </row>
-    <row r="161" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="161" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A161" s="2" t="s">
         <v>587</v>
       </c>
@@ -9424,7 +9420,7 @@
       <c r="P161" s="4"/>
       <c r="Q161" s="4"/>
     </row>
-    <row r="162" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="162" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A162" s="2" t="s">
         <v>591</v>
       </c>
@@ -9463,7 +9459,7 @@
       <c r="P162" s="4"/>
       <c r="Q162" s="4"/>
     </row>
-    <row r="163" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="163" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A163" s="2" t="s">
         <v>595</v>
       </c>
@@ -9502,7 +9498,7 @@
       <c r="P163" s="4"/>
       <c r="Q163" s="4"/>
     </row>
-    <row r="164" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="164" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A164" s="2" t="s">
         <v>599</v>
       </c>
@@ -9541,7 +9537,7 @@
       <c r="P164" s="4"/>
       <c r="Q164" s="4"/>
     </row>
-    <row r="165" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="165" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A165" s="2" t="s">
         <v>603</v>
       </c>
@@ -9582,7 +9578,7 @@
       <c r="P165" s="4"/>
       <c r="Q165" s="4"/>
     </row>
-    <row r="166" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="166" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A166" s="2" t="s">
         <v>607</v>
       </c>
@@ -9623,7 +9619,7 @@
       <c r="P166" s="4"/>
       <c r="Q166" s="4"/>
     </row>
-    <row r="167" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="167" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A167" s="2" t="s">
         <v>611</v>
       </c>
@@ -9662,7 +9658,7 @@
       <c r="P167" s="4"/>
       <c r="Q167" s="4"/>
     </row>
-    <row r="168" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="168" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A168" s="2" t="s">
         <v>615</v>
       </c>
@@ -9701,7 +9697,7 @@
       <c r="P168" s="4"/>
       <c r="Q168" s="4"/>
     </row>
-    <row r="169" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="169" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A169" s="2" t="s">
         <v>619</v>
       </c>
@@ -9740,7 +9736,7 @@
       <c r="P169" s="4"/>
       <c r="Q169" s="4"/>
     </row>
-    <row r="170" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="170" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A170" s="2" t="s">
         <v>622</v>
       </c>
@@ -9779,7 +9775,7 @@
       <c r="P170" s="4"/>
       <c r="Q170" s="4"/>
     </row>
-    <row r="171" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="171" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A171" s="2" t="s">
         <v>626</v>
       </c>
@@ -9818,7 +9814,7 @@
       <c r="P171" s="4"/>
       <c r="Q171" s="4"/>
     </row>
-    <row r="172" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="172" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A172" s="2" t="s">
         <v>630</v>
       </c>
@@ -9857,7 +9853,7 @@
       <c r="P172" s="4"/>
       <c r="Q172" s="4"/>
     </row>
-    <row r="173" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="173" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A173" s="2" t="s">
         <v>633</v>
       </c>
@@ -9896,7 +9892,7 @@
       <c r="P173" s="4"/>
       <c r="Q173" s="4"/>
     </row>
-    <row r="174" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="174" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A174" s="2" t="s">
         <v>636</v>
       </c>
@@ -9935,7 +9931,7 @@
       <c r="P174" s="4"/>
       <c r="Q174" s="4"/>
     </row>
-    <row r="175" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="175" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A175" s="2" t="s">
         <v>640</v>
       </c>
@@ -9974,7 +9970,7 @@
       <c r="P175" s="4"/>
       <c r="Q175" s="4"/>
     </row>
-    <row r="176" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="176" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A176" s="2" t="s">
         <v>643</v>
       </c>
@@ -10013,7 +10009,7 @@
       <c r="P176" s="4"/>
       <c r="Q176" s="4"/>
     </row>
-    <row r="177" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="177" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A177" s="2" t="s">
         <v>647</v>
       </c>
@@ -10052,7 +10048,7 @@
       <c r="P177" s="4"/>
       <c r="Q177" s="4"/>
     </row>
-    <row r="178" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="178" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A178" s="2" t="s">
         <v>651</v>
       </c>
@@ -10091,7 +10087,7 @@
       <c r="P178" s="4"/>
       <c r="Q178" s="4"/>
     </row>
-    <row r="179" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="179" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A179" s="2" t="s">
         <v>655</v>
       </c>
@@ -10130,7 +10126,7 @@
       <c r="P179" s="4"/>
       <c r="Q179" s="4"/>
     </row>
-    <row r="180" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="180" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A180" s="2" t="s">
         <v>659</v>
       </c>
@@ -10169,7 +10165,7 @@
       <c r="P180" s="4"/>
       <c r="Q180" s="4"/>
     </row>
-    <row r="181" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="181" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A181" s="2" t="s">
         <v>664</v>
       </c>
@@ -10208,7 +10204,7 @@
       <c r="P181" s="4"/>
       <c r="Q181" s="4"/>
     </row>
-    <row r="182" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="182" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A182" s="2" t="s">
         <v>668</v>
       </c>
@@ -10247,7 +10243,7 @@
       <c r="P182" s="4"/>
       <c r="Q182" s="4"/>
     </row>
-    <row r="183" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="183" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A183" s="2" t="s">
         <v>672</v>
       </c>
@@ -10286,7 +10282,7 @@
       <c r="P183" s="4"/>
       <c r="Q183" s="4"/>
     </row>
-    <row r="184" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="184" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A184" s="2" t="s">
         <v>676</v>
       </c>
@@ -10325,7 +10321,7 @@
       <c r="P184" s="4"/>
       <c r="Q184" s="4"/>
     </row>
-    <row r="185" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="185" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A185" s="2" t="s">
         <v>680</v>
       </c>
@@ -10366,7 +10362,7 @@
       <c r="P185" s="4"/>
       <c r="Q185" s="4"/>
     </row>
-    <row r="186" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="186" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A186" s="2" t="s">
         <v>684</v>
       </c>
@@ -10407,7 +10403,7 @@
       <c r="P186" s="4"/>
       <c r="Q186" s="4"/>
     </row>
-    <row r="187" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="187" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A187" s="2" t="s">
         <v>688</v>
       </c>
@@ -10446,7 +10442,7 @@
       <c r="P187" s="4"/>
       <c r="Q187" s="4"/>
     </row>
-    <row r="188" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="188" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A188" s="2" t="s">
         <v>692</v>
       </c>
@@ -10485,7 +10481,7 @@
       <c r="P188" s="4"/>
       <c r="Q188" s="4"/>
     </row>
-    <row r="189" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="189" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A189" s="2" t="s">
         <v>696</v>
       </c>
@@ -10524,7 +10520,7 @@
       <c r="P189" s="4"/>
       <c r="Q189" s="4"/>
     </row>
-    <row r="190" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="190" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A190" s="2" t="s">
         <v>699</v>
       </c>
@@ -10563,7 +10559,7 @@
       <c r="P190" s="4"/>
       <c r="Q190" s="4"/>
     </row>
-    <row r="191" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="191" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A191" s="2" t="s">
         <v>703</v>
       </c>
@@ -10602,7 +10598,7 @@
       <c r="P191" s="4"/>
       <c r="Q191" s="4"/>
     </row>
-    <row r="192" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="192" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A192" s="2" t="s">
         <v>707</v>
       </c>
@@ -10641,7 +10637,7 @@
       <c r="P192" s="4"/>
       <c r="Q192" s="4"/>
     </row>
-    <row r="193" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="193" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A193" s="2" t="s">
         <v>710</v>
       </c>
@@ -10680,7 +10676,7 @@
       <c r="P193" s="4"/>
       <c r="Q193" s="4"/>
     </row>
-    <row r="194" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="194" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A194" s="2" t="s">
         <v>714</v>
       </c>
@@ -10719,7 +10715,7 @@
       <c r="P194" s="4"/>
       <c r="Q194" s="4"/>
     </row>
-    <row r="195" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="195" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A195" s="2" t="s">
         <v>718</v>
       </c>
@@ -10758,7 +10754,7 @@
       <c r="P195" s="4"/>
       <c r="Q195" s="4"/>
     </row>
-    <row r="196" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="196" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A196" s="2" t="s">
         <v>722</v>
       </c>
@@ -10797,7 +10793,7 @@
       <c r="P196" s="4"/>
       <c r="Q196" s="4"/>
     </row>
-    <row r="197" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="197" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A197" s="2" t="s">
         <v>726</v>
       </c>
@@ -10836,7 +10832,7 @@
       <c r="P197" s="4"/>
       <c r="Q197" s="4"/>
     </row>
-    <row r="198" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="198" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A198" s="2" t="s">
         <v>731</v>
       </c>
@@ -10875,7 +10871,7 @@
       <c r="P198" s="4"/>
       <c r="Q198" s="4"/>
     </row>
-    <row r="199" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="199" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A199" s="2" t="s">
         <v>735</v>
       </c>
@@ -10914,7 +10910,7 @@
       <c r="P199" s="4"/>
       <c r="Q199" s="4"/>
     </row>
-    <row r="200" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="200" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A200" s="2" t="s">
         <v>739</v>
       </c>
@@ -10953,7 +10949,7 @@
       <c r="P200" s="4"/>
       <c r="Q200" s="4"/>
     </row>
-    <row r="201" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="201" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A201" s="2" t="s">
         <v>743</v>
       </c>
@@ -10992,7 +10988,7 @@
       <c r="P201" s="4"/>
       <c r="Q201" s="4"/>
     </row>
-    <row r="202" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="202" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A202" s="2" t="s">
         <v>747</v>
       </c>
@@ -11033,7 +11029,7 @@
       <c r="P202" s="4"/>
       <c r="Q202" s="4"/>
     </row>
-    <row r="203" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="203" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A203" s="2" t="s">
         <v>751</v>
       </c>
@@ -11074,7 +11070,7 @@
       <c r="P203" s="4"/>
       <c r="Q203" s="4"/>
     </row>
-    <row r="204" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="204" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A204" s="2" t="s">
         <v>755</v>
       </c>
@@ -11113,7 +11109,7 @@
       <c r="P204" s="4"/>
       <c r="Q204" s="4"/>
     </row>
-    <row r="205" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="205" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A205" s="2" t="s">
         <v>759</v>
       </c>
@@ -11152,7 +11148,7 @@
       <c r="P205" s="4"/>
       <c r="Q205" s="4"/>
     </row>
-    <row r="206" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="206" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A206" s="2" t="s">
         <v>763</v>
       </c>
@@ -11191,7 +11187,7 @@
       <c r="P206" s="4"/>
       <c r="Q206" s="4"/>
     </row>
-    <row r="207" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="207" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A207" s="2" t="s">
         <v>766</v>
       </c>
@@ -11230,7 +11226,7 @@
       <c r="P207" s="4"/>
       <c r="Q207" s="4"/>
     </row>
-    <row r="208" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="208" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A208" s="2" t="s">
         <v>770</v>
       </c>
@@ -11269,7 +11265,7 @@
       <c r="P208" s="4"/>
       <c r="Q208" s="4"/>
     </row>
-    <row r="209" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="209" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A209" s="2" t="s">
         <v>774</v>
       </c>
@@ -11308,7 +11304,7 @@
       <c r="P209" s="4"/>
       <c r="Q209" s="4"/>
     </row>
-    <row r="210" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="210" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A210" s="2" t="s">
         <v>777</v>
       </c>
@@ -11347,7 +11343,7 @@
       <c r="P210" s="4"/>
       <c r="Q210" s="4"/>
     </row>
-    <row r="211" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="211" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A211" s="2" t="s">
         <v>781</v>
       </c>
@@ -11386,7 +11382,7 @@
       <c r="P211" s="4"/>
       <c r="Q211" s="4"/>
     </row>
-    <row r="212" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="212" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A212" s="2" t="s">
         <v>785</v>
       </c>
@@ -11425,7 +11421,7 @@
       <c r="P212" s="4"/>
       <c r="Q212" s="4"/>
     </row>
-    <row r="213" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="213" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A213" s="2" t="s">
         <v>789</v>
       </c>
@@ -11464,7 +11460,7 @@
       <c r="P213" s="4"/>
       <c r="Q213" s="4"/>
     </row>
-    <row r="214" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="214" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A214" s="2" t="s">
         <v>816</v>
       </c>
@@ -11503,7 +11499,7 @@
       <c r="P214" s="4"/>
       <c r="Q214" s="4"/>
     </row>
-    <row r="215" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="215" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A215" s="2" t="s">
         <v>817</v>
       </c>
@@ -11542,7 +11538,7 @@
       <c r="P215" s="4"/>
       <c r="Q215" s="4"/>
     </row>
-    <row r="216" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="216" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A216" s="2" t="s">
         <v>818</v>
       </c>
@@ -11581,7 +11577,7 @@
       <c r="P216" s="4"/>
       <c r="Q216" s="4"/>
     </row>
-    <row r="217" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="217" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A217" s="2" t="s">
         <v>819</v>
       </c>
@@ -11620,7 +11616,7 @@
       <c r="P217" s="4"/>
       <c r="Q217" s="4"/>
     </row>
-    <row r="218" spans="1:17" x14ac:dyDescent="0.35">
+    <row r="218" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A218" s="2" t="s">
         <v>820</v>
       </c>
